--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -439,7 +439,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="51" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 06:39:20 IST</t>
+          <t>2026-09-04 12:50:03 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -553,56 +553,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>BIRLAPREC.NS</t>
+          <t>JINDWORLD.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Birla Precision Technologies Limited</t>
+          <t>Jindal Worldwide Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>42.77000045776367</v>
+        <v>49.66999816894531</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>51.66999816894531</v>
+        <v>57.75</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>42.75</v>
+        <v>49.02000045776367</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>51.66999816894531</v>
+        <v>57.29000091552734</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>43.11000061035156</v>
+        <v>48.15000152587891</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>51.66999816894531</v>
+        <v>57.29000091552734</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>984427</v>
+        <v>165843995</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>19.86</v>
+        <v>18.98</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Birla Precision Technologies Ltd. (BIRLAPREC) Share Price Rises 10.68% Today - Univest</t>
+          <t>Most Active Equities on September 3, 2026 at 4:00 PM - hdfcsky.com</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Birla Precision Technologies Ltd. (BIRLAPREC) Share Price Rises 10.68% Today - Univest</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
+          <t>Most Active Equities on September 4, 2026 at 12:00 PM - hdfcsky.com</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Jindal Worldwide seeks approval for ₹650 Cr rights issue at AGM - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Most Active Equities on September 4, 2026 at 12:00 PM - hdfcsky.com</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>Jindal Worldwide shares surge again, up about 30% in two sessions on EV showroom expansion plan - Business Upturn</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 06:39:20 IST</t>
+          <t>2026-09-04 12:50:03 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -610,68 +622,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>HIKAL.NS</t>
+          <t>NIACL.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Hikal Limited</t>
+          <t>The New India Assurance Company Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>201.1499938964844</v>
+        <v>196.4900054931641</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>240.7200012207031</v>
+        <v>229.2200012207031</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>201.1499938964844</v>
+        <v>196.4900054931641</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>240.3600006103516</v>
+        <v>227.0700073242188</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>200.6000061035156</v>
+        <v>195.3300018310547</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>239.9600067138672</v>
+        <v>227.0700073242188</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>20195810</v>
+        <v>41018366</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>19.82</v>
+        <v>16.25</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Don't Race Out To Buy Hikal Limited (NSE:HIKAL) Just Because It's Going Ex-Dividend - simplywall.st</t>
+          <t>NSE targets listing on Sep 25, reports CNBC-TV18; IFCI, NIACL shares rise up to 11% - TradingView</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Hikal files FY26 sustainability report with ESG metrics - scanx.trade</t>
+          <t>NSE targets listing on Sep 25, reports CNBC-TV18; IFCI, NIACL shares rise up to 11% - TradingView</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Hikal FY26 net loss of ₹49 crore on exceptional items - scanx.trade</t>
+          <t>NSE IPO Speculation Lifts IFCI, NIACL; Profit Booking Cuts Gains - hdfcsky.com</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Hikal Q1 Consolidated Net Loss Narrows to ₹7.4 Crore; Revenue At ₹403 Crore - Sahi</t>
+          <t>IFCI, NIACL stocks jump up to 14%; NSE IPO buzz lifts focus: Analysts share outlook - Business Today</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Hikal Share Price Gains After Sameer Hiremath Named CMD - Univest</t>
+          <t>NSE IPO soon? NIACL, IFCI shares jump up to 11% on buzz over issue launch - TradingView</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 06:39:20 IST</t>
+          <t>2026-09-04 12:50:03 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -679,60 +691,56 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>JINDWORLD.NS</t>
+          <t>RESPONIND.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Jindal Worldwide Limited</t>
+          <t>Responsive Industries Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>40.52000045776367</v>
+        <v>151.25</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>48.22000122070312</v>
+        <v>176.1399993896484</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>40.52000045776367</v>
+        <v>151.25</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>48.15000152587891</v>
+        <v>173.0299987792969</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>40.18999862670898</v>
+        <v>151.8699951171875</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>48.15000152587891</v>
+        <v>173.0299987792969</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>110819795</v>
+        <v>22911336</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>19.81</v>
+        <v>13.93</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Most Active Equities on September 3, 2026 at 4:00 PM - hdfcsky.com</t>
+          <t>Responsive Industries board to consider equity share buyback on Aug 14 - scanx.trade</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Most Active Equities on September 3, 2026 at 4:00 PM - hdfcsky.com</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>Jindal Worldwide seeks approval for ₹650 Cr rights issue at AGM - scanx.trade</t>
-        </is>
-      </c>
+          <t>Responsive Industries board to consider equity share buyback on Aug 14 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr"/>
       <c r="P4" s="2" t="inlineStr"/>
       <c r="Q4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 06:39:20 IST</t>
+          <t>2026-09-04 12:50:03 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -740,68 +748,56 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>RAYMOND.NS</t>
+          <t>LANCORHOL.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Raymond Limited</t>
+          <t>Lancor Holdings Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>672.2000122070312</v>
+        <v>35.13000106811523</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>765</v>
+        <v>40</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>672.2000122070312</v>
+        <v>34.20999908447266</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>757.9000244140625</v>
+        <v>39.5099983215332</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>667.25</v>
+        <v>34.75</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>757.9000244140625</v>
+        <v>39.5099983215332</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>16593917</v>
+        <v>1244384</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>13.59</v>
+        <v>13.7</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Why Raymond, Raymond Realty shares are surging today - Business Today</t>
+          <t>Lancor Holdings Ltd. Share Price News and Stock Analysis - Univest</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>The technical leader behind a 2012 uranium discovery takes over F3's exploration - Stock Titan</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>Raymond James raises Ciena stock price target on supply visibility By Investing.com - Investing.com India</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>Buzzing stock: Raymond zooms 14% on huge volume, up 137% from 52-week low - Business Standard</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>Defence re-rating buzz | Raymond share price hits 52-week high, logging over 14% intraday rise - Livemint</t>
-        </is>
-      </c>
+          <t>Lancor Holdings Ltd. Share Price News and Stock Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 06:39:20 IST</t>
+          <t>2026-09-04 12:50:03 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -809,46 +805,46 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>ALPINETEX.NS</t>
+          <t>MARSONS.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Alpine Texworld Limited</t>
+          <t>Marsons Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>51.11999893188477</v>
+        <v>125.8899993896484</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>59.34000015258789</v>
+        <v>140.7299957275391</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>51.11999893188477</v>
+        <v>125.3000030517578</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>57.16999816894531</v>
+        <v>139.4400024414062</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>51.09000015258789</v>
+        <v>125.5299987792969</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>57.16999816894531</v>
+        <v>139.4400024414062</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>1147753</v>
+        <v>10070759</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>11.9</v>
+        <v>11.08</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Alpine Texworld Share Price news and valuation - Univest</t>
+          <t>Marsons Limited Receives PGCIL Vendor Approval for Supply of Power Transformers - scanx.trade</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Alpine Texworld Share Price news and valuation - Univest</t>
+          <t>Marsons Limited Receives PGCIL Vendor Approval for Supply of Power Transformers - scanx.trade</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr"/>
@@ -858,7 +854,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 06:39:20 IST</t>
+          <t>2026-09-04 12:50:03 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -866,68 +862,56 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>BRIGADE.NS</t>
+          <t>BIRLAPREC.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Brigade Enterprises Limited</t>
+          <t>Birla Precision Technologies Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>646.4500122070312</v>
+        <v>53.25</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>733</v>
+        <v>59.79000091552734</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>642.7000122070312</v>
+        <v>52.72999954223633</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>712.2999877929688</v>
+        <v>57.15000152587891</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>640</v>
+        <v>51.66999816894531</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>712.2999877929688</v>
+        <v>57.15000152587891</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>5390980</v>
+        <v>2011222</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>11.3</v>
+        <v>10.61</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Anant Raj shares jump 8% today: What’s driving the rally? - BusinessLine</t>
+          <t>Birla Precision Technologies Ltd. (BIRLAPREC) Share Price Rises 10.68% Today - Univest</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Brigade Hotel Ventures seeks approval for ESOP and ₹64.22 crore RPT - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>Brigade Enterprises Share Price update on Realty sector move - Univest</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>Brigade Hotel Ventures seeks approval for ESOP and ₹64.22 crore RPT - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>Brigade Enterprises shares: Analyst on when to exit the real estate counter - Business Today</t>
-        </is>
-      </c>
+          <t>Birla Precision Technologies Ltd. (BIRLAPREC) Share Price Rises 10.68% Today - Univest</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr"/>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 06:39:20 IST</t>
+          <t>2026-09-04 12:50:03 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -935,68 +919,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>SHUKRAPHAR.NS</t>
+          <t>TBZ.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Shukra Pharmaceuticals Limited</t>
+          <t>Tribhovandas Bhimji Zaveri Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>47.36999893188477</v>
+        <v>456</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>54.90000152587891</v>
+        <v>480.8500061035156</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>47.09999847412109</v>
+        <v>456</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>51.93000030517578</v>
+        <v>480.8500061035156</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>46.79000091552734</v>
+        <v>437.1499938964844</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>51.93000030517578</v>
+        <v>480.8500061035156</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>8949935</v>
+        <v>3433517</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>10.99</v>
+        <v>10</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>SHUKRAPHAR Stock Price and Chart — NSE:SHUKRAPHAR - TradingView</t>
+          <t>Tribhovandas Bhimji Zaveri is now GRT's jewel - Finshots</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Shukra Pharmaceuticals Reschedules 33rd AGM and Revises Book Closure - TipRanks</t>
+          <t>Tribhovandas Bhimji Zaveri soars 58% in 4 days; zooms 107% from Aug low - Business Standard</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Diluted shares outstanding of Shukra Pharmaceuticals Ltd. – NSE:SHUKRAPHAR - TradingView</t>
+          <t>Tribhovandas Bhimji Zaveri soars 58% in 4 days; zooms 107% from Aug low - Business Standard</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Shukra Pharmaceuticals equity shares listed on NSE; trading begins August 14 - scanx.trade</t>
+          <t>56% Jump In 5 Sessions: Why Is Tribhovandas Bhimji Zaveri Stock Locked In 10% Upper Circuit Today? - NDTV Profit</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>SHUKRA PHARMA Stock/Share price , NSE/BSE Forecast News and Live Quotes - Equitymaster</t>
+          <t>TBZ shares zoom 20%, hit upper circuit after GRT Jewellers open offer - economictimes.com</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 06:39:20 IST</t>
+          <t>2026-09-04 12:50:03 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1004,60 +988,56 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>KIRIINDUS.NS</t>
+          <t>RAMBHAJO.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Kiri Industries Limited</t>
+          <t>Advit Jewels Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>527</v>
+        <v>249.8999938964844</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>591.2000122070312</v>
+        <v>267.5</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>527</v>
+        <v>247.0599975585938</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>578.9500122070312</v>
+        <v>264.6400146484375</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>523.6500244140625</v>
+        <v>244.2599945068359</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>578.9500122070312</v>
+        <v>264.6400146484375</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>7182969</v>
+        <v>1505092</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>10.56</v>
+        <v>8.34</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Kiri Industries Share Price today: valuation and sector view - Univest</t>
+          <t>Advit Jewels Q1 Results: Earnings call audio now available online - scanx.trade</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Kiri Industries Share Price today: valuation and sector view - Univest</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>Kiri Industries Share Price Today: Price Rise and Valuation - Univest</t>
-        </is>
-      </c>
+          <t>Advit Jewels Q1 Results: Earnings call audio now available online - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr"/>
       <c r="P9" s="2" t="inlineStr"/>
       <c r="Q9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 06:39:20 IST</t>
+          <t>2026-09-04 12:50:03 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1065,60 +1045,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>MAKERSL.NS</t>
+          <t>MOTISONS.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Makers Laboratories Limited</t>
+          <t>Motisons Jewellers Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>188</v>
+        <v>15.21000003814697</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>200.9700012207031</v>
+        <v>17.5</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>182.0599975585938</v>
+        <v>15.21000003814697</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>200.7700042724609</v>
+        <v>16.39999961853027</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>182.6999969482422</v>
+        <v>15.36999988555908</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>200.7700042724609</v>
+        <v>16.39999961853027</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>9968</v>
+        <v>103761387</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>9.890000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Makers Laboratories Ltd. (MAKERSL) Fundamental and Financial Data - Stocktwits</t>
+          <t>Motisons Jewellers Q1FY27 net profit rises 38% to ₹110.5 crore - scanx.trade</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Makers Laboratories Ltd. (MAKERSL) Fundamental and Financial Data - Stocktwits</t>
+          <t>Vodafone Idea, Motisons, LEAP India Among Top NSE Movers - hdfcsky.com</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Makers Laboratories Q1 Results: Consolidated Net Profit Surges 244% YoY to ₹150.43 lacs - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="2" t="inlineStr"/>
+          <t>Vodafone Idea, Motisons, LEAP India Among Top NSE Movers - hdfcsky.com</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>Motisons Jewellers standalone net profit rises 37.61% in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>Motisons Jewellers shares jump 5% on heavy volumes after Q1 results: Here's what the numbers showed - Business Upturn</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 06:39:20 IST</t>
+          <t>2026-09-04 12:50:03 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1126,68 +1114,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>OAL.NS</t>
+          <t>PURVA.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Oriental Aromatics Limited</t>
+          <t>Puravankara Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>463.8999938964844</v>
+        <v>215</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>503.7000122070312</v>
+        <v>236</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>460</v>
+        <v>215</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>502.2999877929688</v>
+        <v>224.7299957275391</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>457.9500122070312</v>
+        <v>211.0899963378906</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>502.2999877929688</v>
+        <v>224.7299957275391</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>162215</v>
+        <v>13276061</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>9.68</v>
+        <v>6.46</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Oriental Aromatics Share Price rises 8.72%; valuation view - Univest</t>
+          <t>TTI Enterprise appoints Purva Sharegistry as new RTA - scanx.trade</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Oriental Aromatics Share Price rises 8.72%; valuation view - Univest</t>
+          <t>Puravankara Ltd. Share Price Rise: Valuation and Sector - Univest</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Oriental Aromatics Share Price update: OAL gains 12.35% - Univest</t>
+          <t>Puravankara Ltd. Share Price Rise: Valuation and Sector - Univest</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Oriental Aromatics Share Price rises 9.72% on key metrics - Univest</t>
+          <t>What Drove Puravankara’s Q1 FY27 Profit Turnaround? Key Factors Explained - Trade Brains</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>Ruger American (.17hmr) - For Sale, Used - Excellent Condition - Guns.com</t>
+          <t>Puravankara Moves AGM Online, Directs Offline Shareholders to Digital Annual Report - TipRanks</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 06:39:20 IST</t>
+          <t>2026-09-04 12:50:03 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1195,60 +1183,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>ALEMBICLTD.NS</t>
+          <t>AFFLE.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Alembic Limited</t>
+          <t>Affle 3i Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>100.5199966430664</v>
+        <v>1529</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>117.7200012207031</v>
+        <v>1620.699951171875</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>100.5199966430664</v>
+        <v>1521</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>109.5100021362305</v>
+        <v>1611.300048828125</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>100.1399993896484</v>
+        <v>1519.199951171875</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>109.5100021362305</v>
+        <v>1611.300048828125</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>35036495</v>
+        <v>650727</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>9.359999999999999</v>
+        <v>6.06</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Alembic Ltd. Share Price Today Up 12.67% on Price Action - Univest</t>
+          <t>Affle 3i Share Price: Buy, Hold or Sell Guide - Univest</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Alembic Ltd. Share Price Today Up 12.67% on Price Action - Univest</t>
+          <t>Affle 3i Share Price: Is It a Good Buy After Q1 FY27 Results? - Univest</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ISSC Dips 0.92% to $20.51: Innovative Solutions and Support Holds Key Support Level - ATR Stop - vinanet.vn</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr"/>
-      <c r="Q12" s="2" t="inlineStr"/>
+          <t>Affle 3i Share Price: Is It a Good Buy After Q1 FY27 Results? - Univest</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>Affle 3i to participate in Elara Capital investor conference - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>Affle 3i holds investor meet with Stallion Asset Management - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 06:39:20 IST</t>
+          <t>2026-09-04 12:50:03 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1256,64 +1252,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>BFUTILITIE.NS</t>
+          <t>WELSPLSOL.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>BF Utilities Limited</t>
+          <t>Welspun Specialty Solutions Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>500.0499877929688</v>
+        <v>56.95000076293945</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>585.7999877929688</v>
+        <v>59.43999862670898</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>500.0499877929688</v>
+        <v>56.0099983215332</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>544</v>
+        <v>59.38000106811523</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>500.6499938964844</v>
+        <v>56.02000045776367</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>544</v>
+        <v>59.38000106811523</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>4460017</v>
+        <v>1434273</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>8.66</v>
+        <v>6</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>BF Utilities Ltd. Share Price Rises 11.72% on Valuation - Univest</t>
+          <t>WELSPLSOL Stock Price and Chart — NSE:WELSPLSOL - TradingView</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>BF Utilities Ltd. Share Price Rises 11.72% on Valuation - Univest</t>
+          <t>Welspun Specialty Solutions (WELSPLSOL) Mar 2026 Earnings: Modest Profitability Amid Revenue Stability - Capex Guidance - vinanet.vn</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>BF Utilities board notes BSE fine, promoter freeze for FY26 delay - scanx.trade</t>
+          <t>Shareholders Will Be Pleased With The Quality of Welspun Specialty Solutions' (NSE:WELSPLSOL) Earnings - simplywall.st</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>BF Utilities gets 3-month extension for 26th AGM from ROC Pune - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr"/>
+          <t>Welspun Specialty Solutions Limited (WELSPLSOL.NS) Mar 2026 Earnings: Marginal Profitability Maintained on Steady Revenue - Revenue Growth Outlook - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>WELSPLSOL Mar 2026 Earnings: Modest Profitability Amidst Stable Revenue Run-Rate - Revenue Estimate Trend - vinanet.vn</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 06:39:20 IST</t>
+          <t>2026-09-04 12:50:03 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1321,56 +1321,64 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>MANALIPETC.NS</t>
+          <t>WELENT.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Manali Petrochemicals Limited</t>
+          <t>Welspun Enterprises Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>83</v>
+        <v>761.7999877929688</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>90.88999938964844</v>
+        <v>825</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>82</v>
+        <v>757.4000244140625</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>89.73000335693359</v>
+        <v>810.5</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>82.76000213623047</v>
+        <v>764.75</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>89.73000335693359</v>
+        <v>810.5</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>39146179</v>
+        <v>1719692</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>8.42</v>
+        <v>5.98</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Manali Petrochemicals Share Price update: Rs 89.95, up 8.64% - Univest</t>
+          <t>Welspun Enterprises Share Price News: Fresh 52-Week Peak - Univest</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Manali Petrochemicals Share Price update: Rs 89.95, up 8.64% - Univest</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr"/>
-      <c r="P14" s="2" t="inlineStr"/>
+          <t>Welspun Enterprises Share Price: fresh 52-week high update - Univest</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>Welspun Enterprises Share Price: fresh 52-week high update - Univest</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>Welspun Enterprises Ltd. Share Price at Fresh 52-Week High - Univest</t>
+        </is>
+      </c>
       <c r="Q14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 06:39:20 IST</t>
+          <t>2026-09-04 12:50:03 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1378,68 +1386,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>BESTAGRO.NS</t>
+          <t>SKIPPER.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Best Agrolife Limited</t>
+          <t>Skipper Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>20</v>
+        <v>538.1500244140625</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>20.70000076293945</v>
+        <v>578.7999877929688</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>19.86000061035156</v>
+        <v>533.75</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>20.34000015258789</v>
+        <v>578.7999877929688</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>18.81999969482422</v>
+        <v>546.9000244140625</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>20.34000015258789</v>
+        <v>578.7999877929688</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>4461640</v>
+        <v>1388238</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>8.08</v>
+        <v>5.83</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Best Agrolife schedules No Deal Roadshow for Mumbai investors on August 10 - scanx.trade</t>
+          <t>Skipper Q1FY27 net profit rises 26.5% to ₹565M on infra surge - scanx.trade</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Best Agrolife Publishes Newspaper Notice on Special Window - TipRanks</t>
+          <t>Skipper Q1FY27 net profit rises 26.5% to ₹565M on infra surge - scanx.trade</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Best Agrolife Ltd. Share Price Declines: An 8.33% Drop Today - Univest</t>
+          <t>Skipper Shares Rise 3% on Rs 1,305 Cr T&amp;D Order Wins - Equitypandit</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Best Agrolife schedules board meeting to approve FY26 annual report - scanx.trade</t>
+          <t>News by CNBC TV18 on TradingView, 2026-08-27 — cnbctv:6bc1348a7094b:0 - TradingView</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>Best Agrolife Publishes Newspaper Notice on Special Window - TipRanks</t>
+          <t>50% Return in Six Months: This Stock Jumped 3% After Getting Rs 1,305 Crore New Project Order - NDTV Profit</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 06:39:20 IST</t>
+          <t>2026-09-04 12:50:03 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1447,56 +1455,56 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>GOCLCORP.NS</t>
+          <t>ANGELONE.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>GOCL Corporation Limited</t>
+          <t>Angel One Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>417</v>
+        <v>295.1000061035156</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>448</v>
+        <v>308.3500061035156</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>412.8999938964844</v>
+        <v>294.75</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>422.9500122070312</v>
+        <v>302.1499938964844</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>391.7000122070312</v>
+        <v>286</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>422.9500122070312</v>
+        <v>302.1499938964844</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>6030677</v>
+        <v>25159255</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>7.98</v>
+        <v>5.65</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1500% dividend stock alert! Check amount per share, record date, payment timeline and performance - TradingView</t>
+          <t>Angel One Stock And Indian Trading Platforms Facing A Volatile Market Test - simplywall.st</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1500% dividend stock alert! Check amount per share, record date, payment timeline and performance - TradingView</t>
+          <t>Angel One Stock And Indian Trading Platforms Facing A Volatile Market Test - simplywall.st</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>GOCL Corporation Share Price Today: 8.63% Gain Analysis - Univest</t>
+          <t>Should You Buy Angel One Shares On Monday To Be Eligible For 2nd Interim Dividend By Record Date? - Goodreturns</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>EFX Q2 2026 Earnings: EPS Beat Drives 3.85% Stock Uptick - Earnings Volatility Report - vinanet.vn</t>
+          <t>Angel One Allots 3.49 Lakh Shares Under Employee Incentive Plan - TipRanks</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr"/>
@@ -1504,7 +1512,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 06:39:20 IST</t>
+          <t>2026-09-04 12:50:03 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1521,28 +1529,28 @@
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>5370</v>
+        <v>5725</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>5790</v>
+        <v>6094</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>5291</v>
+        <v>5719.5</v>
       </c>
       <c r="H17" s="2" t="n">
+        <v>6049.5</v>
+      </c>
+      <c r="I17" s="2" t="n">
         <v>5726</v>
       </c>
-      <c r="I17" s="2" t="n">
-        <v>5318.5</v>
-      </c>
       <c r="J17" s="2" t="n">
-        <v>5726</v>
+        <v>6049.5</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>246795</v>
+        <v>226226</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>7.66</v>
+        <v>5.65</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
@@ -1565,7 +1573,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 06:39:20 IST</t>
+          <t>2026-09-04 12:50:03 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1573,56 +1581,56 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>CMPDI.NS</t>
+          <t>INDORAMA.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Central Mine Planning &amp; Design Institute Limited</t>
+          <t>Indo Rama Synthetics (India) Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>223</v>
+        <v>69.79000091552734</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>241.8999938964844</v>
+        <v>74.25</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>223</v>
+        <v>69.55000305175781</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>239.6600036621094</v>
+        <v>72.56999969482422</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>222.9700012207031</v>
+        <v>68.87000274658203</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>239.6600036621094</v>
+        <v>72.56999969482422</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>6449983</v>
+        <v>1298184</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>7.49</v>
+        <v>5.37</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>CMPDI Dividend Alert: Coal India Subsidiary To Announce Q4 Result, Final Dividend On THIS Date - Goodreturns</t>
+          <t>Indo Rama Synthetics (India) Ltd. (INDORAMA) Share Price Rises 10.14% Today - Univest</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Mahanadi Coalfields IPO: After Bharat Coking &amp; CMPDI, Coal India to offload 10% stake in third subsidiary - financialexpress.com</t>
+          <t>Indo Rama Synthetics (India) Ltd. (INDORAMA) Share Price Rises 10.14% Today - Univest</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>CMPDI IPO Lists at 7% Discount on NSE, BSE; Weak Demand Keeps Stock Under Pressure Despite Mild Recovery - Goodreturns</t>
+          <t>Indorama Ventures posts strong 1H26 recovery as EBITDA jumps 61% - Thai Enquirer</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Mahanadi Coalfields IPO: After Bharat Coking &amp; CMPDI, Coal India to offload 10% stake in third subsidiary - financialexpress.com</t>
+          <t>Indorama Ventures Public Company Limited 2026 Q2 - Results - Earnings Call Presentation - Seeking Alpha</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr"/>
@@ -1630,7 +1638,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 06:39:20 IST</t>
+          <t>2026-09-04 12:50:03 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1638,64 +1646,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>JYOTICNC.NS</t>
+          <t>PAISALO.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Jyoti CNC Automation Limited</t>
+          <t>Paisalo Digital Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>964.7000122070312</v>
+        <v>71.65000152587891</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>1039</v>
+        <v>74.05999755859375</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>964.2000122070312</v>
+        <v>70.05000305175781</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>1026.849975585938</v>
+        <v>74</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>955.6500244140625</v>
+        <v>70.27999877929688</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1026.849975585938</v>
+        <v>74</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>3413377</v>
+        <v>19527382</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>7.45</v>
+        <v>5.29</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Jyoti CNC Automation Limited Just Missed EPS By 10%: Here's What Analysts Think Will Happen Next - simplywall.st</t>
+          <t>Paisalo Digital Share Price rises 5.78%: valuation view - Univest</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Jyoti CNC Automation: Promoter Pledges 8.07% Stake - InvestyWise</t>
+          <t>Paisalo Digital Share Price rises 5.78%: valuation view - Univest</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Jyoti CNC Automation Ltd. Share Price: Price Action View - Univest</t>
+          <t>Paisalo Digital Operations and Finance Committee to review NCD issuance on September 5 - scanx.trade</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Jyoti CNC Automation: Promoter Pledges 8.07% Stake - InvestyWise</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr"/>
+          <t>Paisalo Digital Ltd. Stock News - Value Research</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>Paisalo Digital Ltd. Share Price Today - Paisalo Digital Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 06:39:20 IST</t>
+          <t>2026-09-04 12:50:03 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1703,68 +1715,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>DEEPINDS.NS</t>
+          <t>CARBORUNIV.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Deep Industries Limited</t>
+          <t>Carborundum Universal Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>712</v>
+        <v>1078.699951171875</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>749</v>
+        <v>1140.900024414062</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>704.0999755859375</v>
+        <v>1069.900024414062</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>744.8499755859375</v>
+        <v>1135</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>693.6500244140625</v>
+        <v>1078</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>744.8499755859375</v>
+        <v>1135</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>1577916</v>
+        <v>218121</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>7.38</v>
+        <v>5.29</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Deep Industries (DEEPINDS.NS) Gains Marginally as Stock Holds Above Key Support - ETF NAV Deviation - vinanet.vn</t>
+          <t>Carborundum Universal Ltd. Share Price Rise: Price Action - Univest</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>DEEPINDS Q2 2026 Earnings: Revenue Surges 54.6% YoY, EPS At ₹28.12 - Earnings Manipulation Risk - vinanet.vn</t>
+          <t>Carborundum Universal Share Price Rises 3.69%: Analysis - Univest</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Why Investors Shouldn't Be Surprised By Deep Industries Limited's (NSE:DEEPINDS) P/S - simplywall.st</t>
+          <t>Carborundum Universal Share Price: 4.87% Price Rise Analysis - Univest</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Deep Industries (DEEPINDS.NS) Faces Selling Pressure, Holds Near ₹508 Support Zone - Quality Factor - vinanet.vn</t>
+          <t>Carborundum Universal Share Price Rises 3.69%: Analysis - Univest</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Deep Industries Limited Receives NCLT Approval for Amalgamation with Wholly-Owned Subsidiary KECL - scanx.trade</t>
+          <t>Carborundum Universal Ltd. Share Price Price Action View - Univest</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 06:39:20 IST</t>
+          <t>2026-09-04 12:50:03 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1772,46 +1784,46 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>MUKKA.NS</t>
+          <t>PWL.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Mukka Proteins Limited</t>
+          <t>Physicswallah Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>26.98999977111816</v>
+        <v>123.370002746582</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>28.92000007629395</v>
+        <v>129.6999969482422</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>26.89999961853027</v>
+        <v>123.0299987792969</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>28.71999931335449</v>
+        <v>126.9000015258789</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>26.85000038146973</v>
+        <v>120.5999984741211</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>28.71999931335449</v>
+        <v>126.9000015258789</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>3369622</v>
+        <v>35587662</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>6.96</v>
+        <v>5.22</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Mukka Proteins approves ₹13.19 crore stake in Shipwaves Online - scanx.trade</t>
+          <t>PW Gyaan-E Finance | 33+ Courses, Guides &amp; 200+ Skill Courses - PW</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Mukka Proteins approves ₹13.19 crore stake in Shipwaves Online - scanx.trade</t>
+          <t>PW Gyaan-E Finance | 33+ Courses, Guides &amp; 200+ Skill Courses - PW</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr"/>
@@ -1835,7 +1847,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -1941,7 +1953,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 06:39:20 IST</t>
+          <t>2026-09-04 12:50:03 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -1949,46 +1961,46 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>SALASAR.NS</t>
+          <t>JAYNECOIND.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Salasar Techno Engineering Limited</t>
+          <t>Jayaswal Neco Industries Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>5.639999866485596</v>
+        <v>92</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>5.690000057220459</v>
+        <v>94.37000274658203</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>4.730000019073486</v>
+        <v>85.22000122070312</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>5.079999923706055</v>
+        <v>86.76000213623047</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>5.650000095367432</v>
+        <v>98.68000030517578</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>5.079999923706055</v>
+        <v>86.76000213623047</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>40156990</v>
+        <v>39076238</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-10.09</v>
+        <v>-12.08</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Salasar Techno Engineering Ltd. Stock News - valueresearchonline.com</t>
+          <t>With EPS Growth And More, Jayaswal Neco Industries (NSE:JAYNECOIND) Makes An Interesting Case - simplywall.st</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Salasar Techno Engineering Ltd. Stock News - valueresearchonline.com</t>
+          <t>With EPS Growth And More, Jayaswal Neco Industries (NSE:JAYNECOIND) Makes An Interesting Case - simplywall.st</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr"/>
@@ -1998,7 +2010,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 06:39:20 IST</t>
+          <t>2026-09-04 12:50:03 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -2006,68 +2018,56 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>INDBANK.NS</t>
+          <t>UGARSUGAR.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Indbank Merchant Banking Services Limited</t>
+          <t>The Ugar Sugar Works Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>30.79999923706055</v>
+        <v>58.40000152587891</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>31.10000038146973</v>
+        <v>58.5</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>28.10000038146973</v>
+        <v>53.43000030517578</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>28.70999908447266</v>
+        <v>53.84000015258789</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>31.10000038146973</v>
+        <v>58.56000137329102</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>28.70999908447266</v>
+        <v>53.84000015258789</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>719248</v>
+        <v>1106436</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-7.68</v>
+        <v>-8.06</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Indbank Merchant Banking sets Sep 17 as AGM record date - scanx.trade</t>
+          <t>Ugar Sugar Works director Hari Athawale retires, Prafulla Shirgaokar resigns from board - ChiniMandi</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Indbank Merchant Banking sets Sep 17 as AGM record date - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>Indbank Merchant Banking Services Share Price Rises 14.75% - Univest</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>Kestrel Group Ltd. (KG) Slips 0.82% to $7.45 as Shares Test Key Support Zone - Hull Moving Average - vinanet.vn</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>Indbank Merchant Banking: ਮੁਨਾਫੇ ਵਿੱਚ ਆਈ ਗਿਰਾਵਟ, ਕੰਪਨੀ ਨੇ ਡਿਵੀਡੈਂਡ ਦੇਣ ਤੋਂ ਕੀਤਾ ਇਨਕਾਰ - Whalesbook</t>
-        </is>
-      </c>
+          <t>Ugar Sugar Works director Hari Athawale retires, Prafulla Shirgaokar resigns from board - ChiniMandi</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr"/>
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 06:39:20 IST</t>
+          <t>2026-09-04 12:50:03 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -2075,68 +2075,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>RTNINDIA.NS</t>
+          <t>DYCL.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>RattanIndia Enterprises Limited</t>
+          <t>Dynamic Cables Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>29.65999984741211</v>
+        <v>541.9000244140625</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>29.89999961853027</v>
+        <v>546.7999877929688</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>27.20999908447266</v>
+        <v>500</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>27.43000030517578</v>
+        <v>505.25</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>29.59000015258789</v>
+        <v>544.2999877929688</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>27.43000030517578</v>
+        <v>505.25</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>7638164</v>
+        <v>994101</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-7.3</v>
+        <v>-7.17</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>RattanIndia Enterprises Reprices 54 Lakh Stock Options Under ESOP 2022 - scanx.trade</t>
+          <t>We Ran A Stock Scan For Earnings Growth And Dynamic Cables (NSE:DYCL) Passed With Ease - simplywall.st</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>RattanIndia Enterprises Sees Positive Momentum: RTNINDIA Rises 2.53%, Eyes Key Resistance - PCR Extreme - vinanet.vn</t>
+          <t>Dynamic Cables (DYCL.NS): Modest Uptick Mirrors Cautious Sector Optimism - Reversal Setup Alerts - vinanet.vn</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>CMPDI Stock Price and Chart — NSE:CMPDI - TradingView</t>
+          <t>Dynamic Cables Limited Confirms No Share Encumbrance by Promoters for FY26 - scanx.trade</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>RTNINDIA.NS Q2 2026 Earnings: Revenue Growth Continues Despite Narrowing Losses - Earnings Risk Report - vinanet.vn</t>
+          <t>Dynamic Cables Limited (DYCL.NS) Q2 2026 Earnings: Revenue Growth Drivers and Operational Resilience - ROA Comparison - vinanet.vn</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>RattanIndia Enterprises Reports Q3FY26 Loss of ₹1,620M Amid Investment Valuation Impact - scanx.trade</t>
+          <t>Dynamic Cables Limited Receives CRISIL Credit Rating Reaffirmation for Rs. 350 Crore Banking Facilities - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 06:39:20 IST</t>
+          <t>2026-09-04 12:50:03 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -2144,60 +2144,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>SURAJEST.NS</t>
+          <t>POLYCAB.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Suraj Estate Developers Limited</t>
+          <t>Polycab India Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>187.4400024414062</v>
+        <v>8500</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>187.4400024414062</v>
+        <v>8500</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>175.2100067138672</v>
+        <v>8287.5</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>177.8000030517578</v>
+        <v>8308.5</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>189.9400024414062</v>
+        <v>8807.5</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>177.8000030517578</v>
+        <v>8308.5</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>336506</v>
+        <v>1026763</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-6.39</v>
+        <v>-5.67</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Suraj Estate promoters hold 3.33 crore shares, no encumbrance in FY26 - scanx.trade</t>
+          <t>Polycab, KEI Industries shares crash up to 9% after UltraTech Cement enters wires &amp; cables business. What - economictimes.com</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Suraj Estate promoters hold 3.33 crore shares, no encumbrance in FY26 - scanx.trade</t>
+          <t>RR Kabel, KEI Industries, Polycab shares sink up to 8%; Nuvama lists preferred picks - Business Today</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Suraj Estate Developers Limited Begins FY27 on Strong Footing, Driven by Robust Sales Momentum - Business Standard</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
+          <t>Polycab, KEI Industries Shares up to 8% as Ultratech Enters Wires &amp; Cables Business with Ultravolt - India Infoline</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>Cable stocks crash up to 6% as UltraTech launches Ultravolt; Polycab, KEI, RR Kabel among top losers - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>Copper Shock Hits Cables Stocks: Polycab, Finolex, RR Kabel Slide Up To 6% After Price Hikes - NDTV Profit</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 06:39:20 IST</t>
+          <t>2026-09-04 12:50:03 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2205,68 +2213,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>GSS.NS</t>
+          <t>UTTAMSUGAR.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>GSS Infotech Limited</t>
+          <t>Uttam Sugar Mills Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>12.28999996185303</v>
+        <v>300.8999938964844</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>12.4399995803833</v>
+        <v>302</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>10.76000022888184</v>
+        <v>281.0499877929688</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>11.15999984741211</v>
+        <v>283.2000122070312</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>11.82999992370605</v>
+        <v>299</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>11.15999984741211</v>
+        <v>283.2000122070312</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>192431</v>
+        <v>231891</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-5.66</v>
+        <v>-5.28</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>GSS Infotech sets Sep 18 record date for AGM e-voting - scanx.trade</t>
+          <t>Uttam Sugar Mills Share Price Today: 8.75% rise - Univest</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>BCAL Diagnostics Issues Section 249D Notice to Genetic Signatures for Board Restructuring - Kalkine Media</t>
+          <t>Uttam Sugar Mills Share Price Today: 8.75% rise - Univest</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Genetic Signatures (ASX:GSS): Board Challenge Emerges Amid Shareholding Queries - Kalkine</t>
+          <t>Uttam Sugar Mills Share Price: Technical, Fundamental View - Univest</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>GSS Infotech Submits Q4FY26 Depositories Compliance Certificate to Exchanges - scanx.trade</t>
+          <t>Uttam Sugar Mills Ltd. Share Price Today Near 52-Week High - Univest</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>BCAL Diagnostics Issues Section 249D Notice to Genetic Signatures for Board Restructuring - Kalkine Media</t>
+          <t>Uttam Sugar Mills Q1 Net Profit Plummets 94.69% YoY to ₹85 lakh - Sahi</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 06:39:20 IST</t>
+          <t>2026-09-04 12:50:03 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2274,68 +2282,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>ANNU.NS</t>
+          <t>RNBDENIMS.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Annu Projects Limited</t>
+          <t>R&amp;B Denims Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>74.80000305175781</v>
+        <v>10.8100004196167</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>74.80000305175781</v>
+        <v>10.8100004196167</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>71.81999969482422</v>
+        <v>10.27000045776367</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>71.81999969482422</v>
+        <v>10.27000045776367</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>75.59999847412109</v>
+        <v>10.8100004196167</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>71.81999969482422</v>
+        <v>10.27000045776367</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>2067647</v>
+        <v>406522</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>-5</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Weak Start! Annu Projects shares list at 27% discount to IPO price - The Economic Times</t>
+          <t>RNBDENIMS Stock Price and Chart — NSE:RNBDENIMS - TradingView</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Share Price Today - Annu Projects Ltd. Stock Price Live NSE/BSE - hdfcsky.com</t>
+          <t>R&amp;B Denims (RNBDENIMS.NS) Slips 1.5%: Testing Key Support Near ₹9.89 - Defined Outcome ETF - vinanet.vn</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Weak market debut: Annu Projects shares list at over 27% discount to its IPO price - Moneycontrol.com</t>
+          <t>R&amp;B Denims Limited Allots Bonus Shares in 1:2 Ratio with Record Date April 03, 2026 - scanx.trade</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Annu Projects Limited Stock (ANNU) - Quote NSE India S.E. - marketscreener.com</t>
+          <t>R&amp;B Denims (RNBDENIMS.NS) Slips 1.5%: Testing Key Support Near ₹9.89 - Defined Outcome ETF - vinanet.vn</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>Share Price Today - Annu Projects Ltd. Stock Price Live NSE/BSE - hdfcsky.com</t>
+          <t>R&amp;B Denims Limited Sets Record Date April 3, 2026 for 1:2 Bonus Equity Shares - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 06:39:20 IST</t>
+          <t>2026-09-04 12:50:03 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2343,68 +2351,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>GAUDIUMIVF.NS</t>
+          <t>PAR.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Gaudium IVF and Women Health Limited</t>
+          <t>Par Drugs And Chemicals Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>123.4000015258789</v>
+        <v>168</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>124.8399963378906</v>
+        <v>168</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>117.2300033569336</v>
+        <v>156.7100067138672</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>117.2399978637695</v>
+        <v>156.7100067138672</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>123.4000015258789</v>
+        <v>164.9499969482422</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>117.2399978637695</v>
+        <v>156.7100067138672</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>217233</v>
+        <v>9717</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-4.99</v>
+        <v>-5</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Gaudium IVF and Women Health Limited’s Initial Public Offer of Equity Shares to open on February 20, 2026 - english.metrovaartha.com</t>
+          <t>Alliance Select Foods International Announces Equity Restructuring For Common Shares Par Value Reduction To 0.10 Pesos Per Share - TradingView</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>GAUDIUMIVF.NS Mar 2026 Earnings: Strong Revenue Base Amid Weak Comparative Benchmarks - Earnings Preview - vinanet.vn</t>
+          <t>Par Pacific (NYSE: PARR) officer lines up new stock sale - Stock Titan</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>GAUDIUMIVF.NS Mar 2026 Earnings: Revenue at ₹22.17 Crore, EPS of ₹1.06; Stock Declines 2% - Profit Recovery Report - vinanet.vn</t>
+          <t>Symbiotec Pharmalab makes tepid market debut, lists at par with IPO price - Business Standard</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>GAUDIUMIVF Mar 2026 Earnings: Solid EPS of ₹1.06 on Revenue of ₹22.17 Cr; Stock Down 2.66% - Earnings Weakness Phase - vinanet.vn</t>
+          <t>Strategy’s (MSTR) STRC remains below par as Strive’s SATA attracts investors - coindesk.com</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Gaudium IVF Gains 2%: Navigating Support and Resistance Levels at ₹108.72 - Trading Ideas - vinanet.vn</t>
+          <t>GFL Environmental Inc. Subordinate voting shares no par value - ADR Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 06:39:20 IST</t>
+          <t>2026-09-04 12:50:03 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2412,68 +2420,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>MODISONLTD.NS</t>
+          <t>HIKAL.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>MODISON LIMITED</t>
+          <t>Hikal Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>520.6500244140625</v>
+        <v>234</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>544.9000244140625</v>
+        <v>236.7400054931641</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>494.6499938964844</v>
+        <v>226.1999969482422</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>494.6499938964844</v>
+        <v>230.0200042724609</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>520.6500244140625</v>
+        <v>240.3600006103516</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>494.6499938964844</v>
+        <v>230.0200042724609</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>583790</v>
+        <v>3668424</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-4.99</v>
+        <v>-4.3</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Modison's (NSE:MODISONLTD) Promising Earnings May Rest On Soft Foundations - simplywall.st</t>
+          <t>Hikal Ltd. Share Price Rise: Price Action and Fundamentals - Univest</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Modison Limited (MODISONLTD.NS) Slips 4% as Shares Approach Key Support Level - Zero Gamma Level - vinanet.vn</t>
+          <t>Hikal Ltd. Share Price Rise: Price Action and Fundamentals - Univest</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Here's Why Modison (NSE:MODISONLTD) Has Caught The Eye Of Investors - simplywall.st</t>
+          <t>Don't Race Out To Buy Hikal Limited (NSE:HIKAL) Just Because It's Going Ex-Dividend - simplywall.st</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Modison Limited Schedules Board Meeting on May 22, 2026 to Consider Q4FY26 Audited Results and Dividend - scanx.trade</t>
+          <t>Hikal files FY26 sustainability report with ESG metrics - scanx.trade</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>Modison Limited (MODISONLTD.NS) Slips 4% as Shares Approach Key Support Level - Zero Gamma Level - vinanet.vn</t>
+          <t>Hikal Q1 Consolidated Net Loss Narrows to ₹7.4 Crore; Revenue At ₹403 Crore - Sahi</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 06:39:20 IST</t>
+          <t>2026-09-04 12:50:03 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2481,68 +2489,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>RNBDENIMS.NS</t>
+          <t>DWARKESH.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>R&amp;B Denims Limited</t>
+          <t>Dwarikesh Sugar Industries Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>11.93000030517578</v>
+        <v>49.40999984741211</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>11.93000030517578</v>
+        <v>49.40999984741211</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>10.8100004196167</v>
+        <v>47.13999938964844</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>10.8100004196167</v>
+        <v>47.25</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>11.36999988555908</v>
+        <v>49.31999969482422</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>10.8100004196167</v>
+        <v>47.25</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>3089346</v>
+        <v>1456612</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-4.93</v>
+        <v>-4.2</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>RNBDENIMS Stock Price and Chart — NSE:RNBDENIMS - TradingView</t>
+          <t>Dwarikesh Sugar Industries: Promoter Gautam Morarka Increases Stake to 15.22% - scanx.trade</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>R&amp;B Denims (RNBDENIMS.NS) Slips 1.5%: Testing Key Support Near ₹9.89 - Defined Outcome ETF - vinanet.vn</t>
+          <t>AI: The Tech ‘Go-Direct’ Ethos Meets Grassroots AI Revolt. AI-RTZ #1198 - AI: Reset to Zero</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>R&amp;B Denims Schedules EGM for March 13 to Approve Stock Split and Corporate Actions - scanx.trade</t>
+          <t>Dwarikesh Sugar Industries Share Price Rises 8.3% Today - Univest</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>R&amp;B Denims (RNBDENIMS.NS) Slips 1.5%: Testing Key Support Near ₹9.89 - Defined Outcome ETF - vinanet.vn</t>
+          <t>Dwarkesh Patels’s wildly popular but dangerously misleading account of the OpenAI Hugging Face incident - Marcus on AI | Substack</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>R&amp;B Denims Limited (RNBDENIMS.NS) Faces Selling Pressure, Holds Above Key Support - Institutional Sentiment - vinanet.vn</t>
+          <t>OpenAI-Hugging Face controversy deepens as experts debate Dwarkesh Patel's 'AI civilisation' claims - Moneycontrol.com</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 06:39:20 IST</t>
+          <t>2026-09-04 12:50:03 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2550,68 +2558,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>RAJTV.NS</t>
+          <t>SYNCOMF.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Raj Television Network Limited</t>
+          <t>Syncom Formulations (India) Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>8.489999771118164</v>
+        <v>20.93000030517578</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>9.25</v>
+        <v>21.8799991607666</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>8.489999771118164</v>
+        <v>20.04999923706055</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>8.489999771118164</v>
+        <v>20.54000091552734</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>8.930000305175781</v>
+        <v>21.36000061035156</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>8.489999771118164</v>
+        <v>20.54000091552734</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>96443</v>
+        <v>11553212</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-4.93</v>
+        <v>-3.84</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Raj Television Network schedules 32nd AGM for September 30 - scanx.trade</t>
+          <t>Here's Why Syncom Formulations (India) (NSE:SYNCOMF) Has Caught The Eye Of Investors - simplywall.st</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Raj Television Network schedules 32nd AGM for September 30 - scanx.trade</t>
+          <t>Syncom Formulations Sees Minor Pullback, Holds Above Key Support at ₹13.27 - Last Point Support - vinanet.vn</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Raj TV Network Q1 Results: Unaudited financials for June quarter filed - scanx.trade</t>
+          <t>Syncom Formulations (India) Limited Acquires Commercial Property from HDFC Bank Ltd for ₹57,26,00,000 - scanx.trade</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Raj TV Network Q1 Results: Net Loss Widens To ₹10.08 Million - scanx.trade</t>
+          <t>SYNCOMF.NS Q2 2025 Earnings: Robust Revenue Growth of 76% YoY Despite Marginal Stock Dip - Tax Rate Impact - vinanet.vn</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>Kiran Kumar Jain M sells 5.87 lakh Raj TV Network shares via open market - scanx.trade</t>
+          <t>SYNCOMF Stock Price and Chart — NSE:SYNCOMF - TradingView</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 06:39:20 IST</t>
+          <t>2026-09-04 12:50:03 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2619,56 +2627,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>GANGAFORGE.NS</t>
+          <t>DBOL.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Ganga Forging Limited</t>
+          <t>Dhampur Bio Organics Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1.820000052452087</v>
+        <v>128.9600067138672</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1.850000023841858</v>
+        <v>128.9600067138672</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>1.759999990463257</v>
+        <v>124</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1.759999990463257</v>
+        <v>124.6900024414062</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1.850000023841858</v>
+        <v>129.6399993896484</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.759999990463257</v>
+        <v>124.6900024414062</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>7489255</v>
+        <v>181551</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-4.86</v>
+        <v>-3.82</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Adamas (ADAM) Q2 2026 Results: EPS Exceeds Its Estimate on the Day; Trading Response: Shares Finish 0.80% Down at the Close - Product Revenue Analysis - vinanet.vn</t>
+          <t>Dhampur Bio Organics promoters confirm no share encumbrance in FY26 - scanx.trade</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Adamas (ADAM) Q2 2026 Results: EPS Exceeds Its Estimate on the Day; Trading Response: Shares Finish 0.80% Down at the Close - Product Revenue Analysis - vinanet.vn</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr"/>
-      <c r="P12" s="2" t="inlineStr"/>
-      <c r="Q12" s="2" t="inlineStr"/>
+          <t>Dhampur Bio Organics promoters confirm no share encumbrance in FY26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>Dhampur Bio Organics Share Price, Valuation, Sector View - Univest</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>Sonitron acquires 40,000 Dhampur Bio Organics shares in open market - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>PHAT Q2 2026 Earnings: Narrower Loss Beats Estimates, Shares Gain 4.36% - Earnings Yield Spread - vinanet.vn</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 06:39:20 IST</t>
+          <t>2026-09-04 12:50:03 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2676,68 +2696,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>HTEL.NS</t>
+          <t>ATHERENERG.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers Limited</t>
+          <t>Ather Energy Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>77</v>
+        <v>1644</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>77.90000152587891</v>
+        <v>1644.5</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>74.62999725341797</v>
+        <v>1573.5</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>74.73000335693359</v>
+        <v>1576.5</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>78.55000305175781</v>
+        <v>1638.900024414062</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>74.73000335693359</v>
+        <v>1576.5</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>2290257</v>
+        <v>3222709</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-4.86</v>
+        <v>-3.81</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Share Price Today - Hy-Tech Engineers Ltd. Stock Price Live NSE/BSE - hdfcsky.com</t>
+          <t>ATHER ENERGY LIMITED Share Price - Live NSE: ATHERENERG Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Share Price Today - Hy-Tech Engineers Ltd. Stock Price Live NSE/BSE - hdfcsky.com</t>
+          <t>ATHER ENERGY Share Price: Today's 2.45% Decline - Univest</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers Limited Financial Statements – NSE:HTEL - TradingView</t>
+          <t>When Can We Expect A Profit From Ather Energy Limited (NSE:ATHERENERG)? - simplywall.st</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers Ltd Share Price Today,, HTEL Share Price NSE, BSE - Business Today</t>
+          <t>Ather Energy shares climb to all-time high, rising 17% above Hero MotoCorp block price - TechStock²</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>HTEL: Static price chart | Hy-Tech Engineers Limited | INE0LEG01024 - marketscreener.com</t>
+          <t>Ather Energy Share Price Rise: Market Cap and Valuation - Univest</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 06:39:20 IST</t>
+          <t>2026-09-04 12:50:03 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2745,60 +2765,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>EMPOWER.NS</t>
+          <t>EMIL.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Empower India Limited</t>
+          <t>Electronics Mart India Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1.820000052452087</v>
+        <v>175.3999938964844</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1.820000052452087</v>
+        <v>176.6699981689453</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>1.820000052452087</v>
+        <v>168.9299926757812</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>1.820000052452087</v>
+        <v>169.7200012207031</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1.909999966621399</v>
+        <v>176.1600036621094</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.820000052452087</v>
+        <v>169.7200012207031</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>4402278</v>
+        <v>753170</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-4.71</v>
+        <v>-3.66</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>NET Power Closes Acquisition of 123 MW Power Generation Rights From EMPower; Shares Rise - marketscreener.com</t>
+          <t>Pentagon official overseeing military AI sold millions worth of stock in AI firm - The Guardian</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>NET Power Closes Acquisition of 123 MW Power Generation Rights From EMPower; Shares Rise - marketscreener.com</t>
+          <t>Top Pentagon AI Official Sold Millions in Perplexity Stock, Disclosures Show - Decrypt</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>A West Texas project plans 10 gas engines totaling 123 megawatts - Stock Titan</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr"/>
-      <c r="Q14" s="2" t="inlineStr"/>
+          <t>Electronics Mart India Share Price Within 2% of 52W High - Univest</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>Most Active Equities, August 10, 2026, 3:30 PM IST - hdfcsky.com</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>Earnings Update: Here's Why Analysts Just Lifted Their Electronics Mart India Limited (NSE:EMIL) Price Target To ₹186 - simplywall.st</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 06:39:20 IST</t>
+          <t>2026-09-04 12:50:03 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2806,68 +2834,60 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>ARIHANTSUP.NS</t>
+          <t>FIVESTAR.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Arihant Superstructures Limited</t>
+          <t>Five-Star Business Finance Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>249</v>
+        <v>538</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>249</v>
+        <v>538</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>231.3500061035156</v>
+        <v>512.5</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>236.1499938964844</v>
+        <v>515.25</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>247.75</v>
+        <v>534.5999755859375</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>236.1499938964844</v>
+        <v>515.25</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>30352</v>
+        <v>554474</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-4.68</v>
+        <v>-3.62</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Arihant Superstructures Ltd (ARIHANTSUP.NS) Q2 2026 Earnings: Robust Revenue Growth Amid Strong Affordable Housing Demand - Guidance Revision Trend - vinanet.vn</t>
+          <t>Five-Star Business Finance Limited Appoints Sreeram Ranganathan Iyer as A Non­ Executive Independent Director, Effective July 25, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Arihant Superstructures Q2 2026 Earnings: Revenue Growth of 10.45% Amid Modest Market Reaction - Analyst Earnings Estimate - vinanet.vn</t>
+          <t>Five-Star Business Finance Limited Appoints Sreeram Ranganathan Iyer as A Non­ Executive Independent Director, Effective July 25, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>The Compensation For Arihant Superstructures Limited's (NSE:ARIHANTSUP) CEO Looks Deserved And Here's Why - simplywall.st</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>ARIHANTSUP Q2 2026 Earnings: Revenue Growth of 10.45% and Strong EPS of ₹10.65 Highlight Steady Performance - Capex Guidance - vinanet.vn</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>Arihant Superstructures Shows Mild Upside as Price Hovers Near Support, Resistance in Focus - Call Resistance - vinanet.vn</t>
-        </is>
-      </c>
+          <t>Five Star Business Finance Submits Business Responsibility and Sustainability Report for FY 2025-26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 06:39:20 IST</t>
+          <t>2026-09-04 12:50:03 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2875,68 +2895,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>OMNI.NS</t>
+          <t>EBGNG.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Omnitech Engineering Limited</t>
+          <t>GNG Electronics Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>546.7000122070312</v>
+        <v>622</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>546.7000122070312</v>
+        <v>633.4000244140625</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>514.0999755859375</v>
+        <v>598</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>519.25</v>
+        <v>600</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>543.1500244140625</v>
+        <v>622.0999755859375</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>519.25</v>
+        <v>600</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>648674</v>
+        <v>572288</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-4.4</v>
+        <v>-3.55</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7,329,803 Equity Shares of Omnitech Engineering Limited are subject to a Lock-Up Agreement Ending on 2-SEP-2026. - marketscreener.com</t>
+          <t>Should You Be Adding GNG Electronics (NSE:EBGNG) To Your Watchlist Today? - simplywall.st</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,329,803 Equity Shares of Omnitech Engineering Limited are subject to a Lock-Up Agreement Ending on 2-SEP-2026. - marketscreener.com</t>
+          <t>GNG Electronics Schedules 20th AGM and Releases FY 2025-26 Annual Report - TipRanks</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Omni Bridgeway (ASX:OBL) Shares Reflect Valuation Strain Despite Profitable FY 2026 - webull.com</t>
+          <t>GNG Electronics Limited (NSE: EBGNG) Stock Price, News &amp; Analysis - Kalkine</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Omni-Lite Industries Stock Falls 2.18%: Aerospace Demand Risks and Growth Uncertainty Pressure TSXV:OML Sentiment - kalkine.ca</t>
+          <t>GNG Electronics reports 32% revenue surge in Q1FY27 on margin expansion - scanx.trade</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>Kotak Diversified Equity All Cap Omni FoF Regular-Growth (₹ 10.02) - NAV, Reviews &amp; asset allocation - The Economic Times</t>
+          <t>GNG Electronics Schedules 20th AGM and Releases FY 2025-26 Annual Report - TipRanks</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 06:39:20 IST</t>
+          <t>2026-09-04 12:50:03 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -2944,56 +2964,60 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>DEEPAKFERT.NS</t>
+          <t>MACPOWER.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Deepak Fertilizers and Petrochemicals Corporation Limited</t>
+          <t>Macpower CNC Machines Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1385</v>
+        <v>1955.800048828125</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>1411</v>
+        <v>1960</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>1351.099975585938</v>
+        <v>1868.300048828125</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>1355.900024414062</v>
+        <v>1878.599975585938</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1416.699951171875</v>
+        <v>1944.099975585938</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1355.900024414062</v>
+        <v>1878.599975585938</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>816334</v>
+        <v>23752</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-4.29</v>
+        <v>-3.37</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>News by CNBC TV18 on TradingView, 2026-08-23 — cnbctv:8653cb759094b:0 - TradingView</t>
+          <t>Macpower CNC Machines Ltd is Rated Hold - MarketsMojo</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>News by CNBC TV18 on TradingView, 2026-08-23 — cnbctv:8653cb759094b:0 - TradingView</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr"/>
+          <t>Macpower CNC Machines Ltd is Rated Hold - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>Rs 21,932 cr opportunity: 2 stocks powering India’s next manufacturing wave - financialexpress.com</t>
+        </is>
+      </c>
       <c r="P17" s="2" t="inlineStr"/>
       <c r="Q17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 06:39:20 IST</t>
+          <t>2026-09-04 12:50:03 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -3001,68 +3025,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>OMAXE.NS</t>
+          <t>GRAVITA.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Omaxe Limited</t>
+          <t>Gravita India Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>133.5800018310547</v>
+        <v>1684.800048828125</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>135.8000030517578</v>
+        <v>1696.599975585938</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>125.5100021362305</v>
+        <v>1626.900024414062</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>127.2900009155273</v>
+        <v>1630</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>132.6699981689453</v>
+        <v>1684.800048828125</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>127.2900009155273</v>
+        <v>1630</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>5734642</v>
+        <v>255828</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-4.06</v>
+        <v>-3.25</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>SAT dismisses Omaxe appeal against SEBI order over financial statement irregularities - Moneycontrol.com</t>
+          <t>Gravita India closes books for AGM from Sep 22 to Sep 28 - scanx.trade</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Omaxe files FY26 BRSR report highlighting zero safety incidents - scanx.trade</t>
+          <t>Gravita India closes books for AGM from Sep 22 to Sep 28 - scanx.trade</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Omaxe files FY26 BRSR report highlighting zero safety incidents - scanx.trade</t>
+          <t>Gravita India approves ₹100 Cr corporate guarantee for subsidiary RMIL - scanx.trade</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Omaxe Ltd. Share Price Rise: Price Action and Fundamentals - Univest</t>
+          <t>Gravita India to add 59,200 MTPA copper recycling capacity at Mundra with ₹64 crore capex - CNBC TV18</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>Omaxe clarifies on share price movement - Business Upturn</t>
+          <t>Gravita India schedules physical investor meet in Jaipur on Sep 2 - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 06:39:20 IST</t>
+          <t>2026-09-04 12:50:03 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -3070,60 +3094,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>ROSSARI.NS</t>
+          <t>WEL.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Rossari Biotech Limited</t>
+          <t>Wonder Electricals Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>479.5</v>
+        <v>79.25</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>482.3500061035156</v>
+        <v>79.25</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>451.3999938964844</v>
+        <v>75.41000366210938</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>457</v>
+        <v>76.83000183105469</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>476.2000122070312</v>
+        <v>79.37000274658203</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>457</v>
+        <v>76.83000183105469</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>342764</v>
+        <v>914005</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-4.03</v>
+        <v>-3.2</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Sudarshan Chemical Industries vs Rossari Biotech: Which Specialty Stock - Univest</t>
+          <t>Integrated Wellness Acquisition Corp (WEL) Peer Comparison – Compare with Others - Value Research</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Specialty Chemicals Stocks To Buy: Navin Fluorine, Rossari Among Nirmal Bang's Eight Picks With Up To 37% Upside — Full List Inside - NDTV Profit</t>
+          <t>Integrated Wellness Acquisition Corp (WEL) Peer Comparison – Compare with Others - Value Research</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Specialty Chemicals Stocks To Buy: Navin Fluorine, Rossari Among Nirmal Bang's Eight Picks With Up To 37% Upside — Full List Inside - NDTV Profit</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr"/>
-      <c r="Q19" s="2" t="inlineStr"/>
+          <t>Wonder Electricals Share Price Today After Sharp Fall - Univest</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>Btab uses artificial intelligence to link global manufacturers with U.S. business buyers - Stock Titan</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>Wonder Electricals Share Price Today: Market Cap and P/E - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 06:39:20 IST</t>
+          <t>2026-09-04 12:50:03 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -3131,64 +3163,60 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>CORDSCABLE.NS</t>
+          <t>PONNIERODE.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Cords Cable Industries Limited</t>
+          <t>Ponni Sugars (Erode) Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>323.8999938964844</v>
+        <v>402.8999938964844</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>323.8999938964844</v>
+        <v>402.8999938964844</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>287.2000122070312</v>
+        <v>385</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>302.8999938964844</v>
+        <v>386</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>315.5</v>
+        <v>398.6499938964844</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>302.8999938964844</v>
+        <v>386</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>259816</v>
+        <v>17691</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-3.99</v>
+        <v>-3.17</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Cords Cable Industries Share Price Gain With Valuation View - Univest</t>
+          <t>Ponni Sugars Share Price Today: Price Rise and Analysis - Univest</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Cords Cable Industries Share Price Gain With Valuation View - Univest</t>
+          <t>NXG Infrastructure Income Fund Holds Ground at $56.30 as Market Waits for Direction - Fear Greed Extreme - vinanet.vn</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Here's Why Cords Cable Industries (NSE:CORDSCABLE) Has Caught The Eye Of Investors - simplywall.st</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>Cords Cable Flags Routine Newspaper Disclosure to Exchange - TipRanks</t>
-        </is>
-      </c>
+          <t>NXG Infrastructure Income Fund Holds Ground at $56.30 as Market Waits for Direction - Fear Greed Extreme - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr"/>
       <c r="Q20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 06:39:20 IST</t>
+          <t>2026-09-04 12:50:03 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -3196,63 +3224,55 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>OLAELEC.NS</t>
+          <t>POWERMECH.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Ola Electric Mobility Limited</t>
+          <t>Power Mech Projects Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>39.34999847412109</v>
+        <v>2399.89990234375</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>39.70000076293945</v>
+        <v>2416</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>37.11000061035156</v>
+        <v>2331</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>37.47000122070312</v>
+        <v>2334</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>38.97999954223633</v>
+        <v>2399.800048828125</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>37.47000122070312</v>
+        <v>2334</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>66732839</v>
+        <v>37175</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-3.87</v>
+        <v>-2.74</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Ola Electric Share Price - Live NSE: OLAELEC Stock Price &amp; Chart - Upstox</t>
+          <t>Power Mech Projects Limited announces Annual dividend, payable on October 17, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Ola Electric Share Price - Live NSE: OLAELEC Stock Price &amp; Chart - Upstox</t>
+          <t>Power Mech Projects Limited announces Annual dividend, payable on October 17, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Ola Electric Heralds New ‘LFP Era’ as Gigafactory Ramp-Up Powers Thousands of EVs - theglobeandmail.com</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>Ola Electric Launches New Battery Energy Storage Portfolio in India - theglobeandmail.com</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>Ola Electric Files Q1 FY27 Monitoring Reports on IPO and QIP Proceeds - theglobeandmail.com</t>
-        </is>
-      </c>
+          <t>Power Mech Projects Publishes AGM Notice and E-Voting Details in Newspapers - TipRanks</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -439,14 +439,14 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="39" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 12:50:03 IST</t>
+          <t>2026-09-04 20:18:15 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -553,68 +553,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>JINDWORLD.NS</t>
+          <t>XTRANET.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Jindal Worldwide Limited</t>
+          <t>Xtranet Technologies Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>49.66999816894531</v>
+        <v>197.1999969482422</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>57.75</v>
+        <v>234.2400054931641</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>49.02000045776367</v>
+        <v>193.1100006103516</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>57.29000091552734</v>
+        <v>234.2400054931641</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>48.15000152587891</v>
+        <v>195.1999969482422</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>57.29000091552734</v>
+        <v>234.2400054931641</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>165843995</v>
+        <v>5584584</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>18.98</v>
+        <v>20</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Most Active Equities on September 3, 2026 at 4:00 PM - hdfcsky.com</t>
+          <t>XTRANET TECHNOLOGIES LTD Share Price - Upstox</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Most Active Equities on September 4, 2026 at 12:00 PM - hdfcsky.com</t>
+          <t>Xtranet Technologies Ltd (XTRANET) Share Price - businesstoday.in</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Jindal Worldwide seeks approval for ₹650 Cr rights issue at AGM - scanx.trade</t>
+          <t>Xtranet Technologies Ltd (XTRANET) Share Price - businesstoday.in</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Most Active Equities on September 4, 2026 at 12:00 PM - hdfcsky.com</t>
+          <t>XTRANET Share Price Today - XTRANET TECHNOLOGIES LTD Stock Price Live NSE/BSE - Univest</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Jindal Worldwide shares surge again, up about 30% in two sessions on EV showroom expansion plan - Business Upturn</t>
+          <t>Stocks to Watch Today: BSE, United Spirits, Hyundai Motor, XtraNet Tech, Autoline Industries, EMS, Ramco... - Moneycontrol.com</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 12:50:03 IST</t>
+          <t>2026-09-04 20:18:15 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -622,68 +622,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>NIACL.NS</t>
+          <t>JINDWORLD.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>The New India Assurance Company Limited</t>
+          <t>Jindal Worldwide Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>196.4900054931641</v>
+        <v>49.66999816894531</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>229.2200012207031</v>
+        <v>57.77999877929688</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>196.4900054931641</v>
+        <v>49.02000045776367</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>227.0700073242188</v>
+        <v>57.5099983215332</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>195.3300018310547</v>
+        <v>48.15000152587891</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>227.0700073242188</v>
+        <v>57.5099983215332</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>41018366</v>
+        <v>187907453</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>16.25</v>
+        <v>19.44</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>NSE targets listing on Sep 25, reports CNBC-TV18; IFCI, NIACL shares rise up to 11% - TradingView</t>
+          <t>Jindal Worldwide (JINDWORLD.NS) Edges Higher at ₹38.31; Key Support and Resistance in Focus - Dividend Growth Stocks - siam.in</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>NSE targets listing on Sep 25, reports CNBC-TV18; IFCI, NIACL shares rise up to 11% - TradingView</t>
+          <t>Most Active Equities on September 4, 2026 at 4:00 PM - HDFC Sky</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>NSE IPO Speculation Lifts IFCI, NIACL; Profit Booking Cuts Gains - hdfcsky.com</t>
+          <t>Jindal Worldwide shares hit 20% upper circuit as arm plans 100 electric scooter showrooms - TradingView</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>IFCI, NIACL stocks jump up to 14%; NSE IPO buzz lifts focus: Analysts share outlook - Business Today</t>
+          <t>News by CNBC TV18 on TradingView, 2026-09-04 — cnbctv:657850109094b:0 - TradingView</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>NSE IPO soon? NIACL, IFCI shares jump up to 11% on buzz over issue launch - TradingView</t>
+          <t>Jindal Worldwide stock hits upper circuit - What's behind the share price jump? - Livemint</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 12:50:03 IST</t>
+          <t>2026-09-04 20:18:15 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -691,46 +691,46 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>RESPONIND.NS</t>
+          <t>NRAIL.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Responsive Industries Limited</t>
+          <t>N R Agarwal Industries Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>151.25</v>
+        <v>498.9500122070312</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>176.1399993896484</v>
+        <v>595.25</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>151.25</v>
+        <v>496.0499877929688</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>173.0299987792969</v>
+        <v>584</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>151.8699951171875</v>
+        <v>496.0499877929688</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>173.0299987792969</v>
+        <v>584</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>22911336</v>
+        <v>157425</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>13.93</v>
+        <v>17.73</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Responsive Industries board to consider equity share buyback on Aug 14 - scanx.trade</t>
+          <t>NR Agarwal Industries Ltd. (NRAIL) Share Price Rises 12.36% Today - Univest</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Responsive Industries board to consider equity share buyback on Aug 14 - scanx.trade</t>
+          <t>NR Agarwal Industries Ltd. (NRAIL) Share Price Rises 12.36% Today - Univest</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr"/>
@@ -740,7 +740,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 12:50:03 IST</t>
+          <t>2026-09-04 20:18:15 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -760,44 +760,56 @@
         <v>35.13000106811523</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>40</v>
+        <v>40.88000106811523</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>34.20999908447266</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>39.5099983215332</v>
+        <v>40.34999847412109</v>
       </c>
       <c r="I5" s="2" t="n">
         <v>34.75</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>39.5099983215332</v>
+        <v>40.34999847412109</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>1244384</v>
+        <v>2380475</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>13.7</v>
+        <v>16.12</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Lancor Holdings Ltd. Share Price News and Stock Analysis - Univest</t>
+          <t>Lancor Holdings Limited (NSE:LANCORHOL) Shares Fly 25% But Investors Aren't Buying For Growth - simplywall.st</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Lancor Holdings Ltd. Share Price News and Stock Analysis - Univest</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
+          <t>LANCORHOL.NS Mar 2026 Earnings: EPS of ₹5.84 on Revenue of ₹14.0 Cr; Stock Gains 8.32 Points - Analyst Drop Coverage - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>Lancor Holdings Limited Sees Marginal Decline: Technical Resistance and Support Levels in Focus - SuperTrend - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>Lancor Holdings Faces Resistance: Stock Declines 2.62% Amid Sector Volatility - Elliott Wave Entry - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>LANCOR HOLDINGS LIMITED Share Price - Upstox</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 12:50:03 IST</t>
+          <t>2026-09-04 20:18:15 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -805,56 +817,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>MARSONS.NS</t>
+          <t>SVGLOBAL.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Marsons Limited</t>
+          <t>S V Global Mill Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>125.8899993896484</v>
+        <v>162</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>140.7299957275391</v>
+        <v>172.8099975585938</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>125.3000030517578</v>
+        <v>157.1499938964844</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>139.4400024414062</v>
+        <v>163.6199951171875</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>125.5299987792969</v>
+        <v>144.0099945068359</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>139.4400024414062</v>
+        <v>163.6199951171875</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>10070759</v>
+        <v>286297</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>11.08</v>
+        <v>13.62</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Marsons Limited Receives PGCIL Vendor Approval for Supply of Power Transformers - scanx.trade</t>
+          <t>S V Global Mill Ltd (SVGLOBAL) Profile, Company FAQs &amp; Facts, Industry, Sector, Employee Strength - Stocktwits</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Marsons Limited Receives PGCIL Vendor Approval for Supply of Power Transformers - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
+          <t>SV Global Mill Ltd. Share Price Rise Streak: Price Action - Univest</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>SV Global Mill Share Price Today: Stock Drops to Rs 124.30 - Univest</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>SV Global Mill Share Price gains 19.99% amid market focus - Univest</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>SV Global Mill Share Price today: price rise and valuation - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 12:50:03 IST</t>
+          <t>2026-09-04 20:18:15 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -862,46 +886,46 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>BIRLAPREC.NS</t>
+          <t>NAGREEKEXP.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Birla Precision Technologies Limited</t>
+          <t>Nagreeka Exports Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>53.25</v>
+        <v>21.10000038146973</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>59.79000091552734</v>
+        <v>25</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>52.72999954223633</v>
+        <v>20.80999946594238</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>57.15000152587891</v>
+        <v>24.10000038146973</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>51.66999816894531</v>
+        <v>21.29999923706055</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>57.15000152587891</v>
+        <v>24.10000038146973</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>2011222</v>
+        <v>411783</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>10.61</v>
+        <v>13.15</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Birla Precision Technologies Ltd. (BIRLAPREC) Share Price Rises 10.68% Today - Univest</t>
+          <t>CFEL Stock Price and Chart — NSE:CFEL - TradingView</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Birla Precision Technologies Ltd. (BIRLAPREC) Share Price Rises 10.68% Today - Univest</t>
+          <t>CFEL Stock Price and Chart — NSE:CFEL - TradingView</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr"/>
@@ -911,7 +935,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 12:50:03 IST</t>
+          <t>2026-09-04 20:18:15 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -919,68 +943,56 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>TBZ.NS</t>
+          <t>PCJEWELLER.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Tribhovandas Bhimji Zaveri Limited</t>
+          <t>PC Jeweller Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>456</v>
+        <v>10.60000038146973</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>480.8500061035156</v>
+        <v>12.17000007629395</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>456</v>
+        <v>10.51000022888184</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>480.8500061035156</v>
+        <v>11.85999965667725</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>437.1499938964844</v>
+        <v>10.52000045776367</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>480.8500061035156</v>
+        <v>11.85999965667725</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>3433517</v>
+        <v>1088882385</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>10</v>
+        <v>12.74</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Tribhovandas Bhimji Zaveri is now GRT's jewel - Finshots</t>
+          <t>PC Jewellers Share Price - Live NSE: PCJEWELLER Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Tribhovandas Bhimji Zaveri soars 58% in 4 days; zooms 107% from Aug low - Business Standard</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>Tribhovandas Bhimji Zaveri soars 58% in 4 days; zooms 107% from Aug low - Business Standard</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>56% Jump In 5 Sessions: Why Is Tribhovandas Bhimji Zaveri Stock Locked In 10% Upper Circuit Today? - NDTV Profit</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>TBZ shares zoom 20%, hit upper circuit after GRT Jewellers open offer - economictimes.com</t>
-        </is>
-      </c>
+          <t>PC Jewellers Share Price - Live NSE: PCJEWELLER Stock Price &amp; Chart - Upstox</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 12:50:03 IST</t>
+          <t>2026-09-04 20:18:15 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -988,56 +1000,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>RAMBHAJO.NS</t>
+          <t>BIRLAPREC.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Advit Jewels Limited</t>
+          <t>Birla Precision Technologies Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>249.8999938964844</v>
+        <v>53.25</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>267.5</v>
+        <v>59.79000091552734</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>247.0599975585938</v>
+        <v>52.72999954223633</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>264.6400146484375</v>
+        <v>57.91999816894531</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>244.2599945068359</v>
+        <v>51.66999816894531</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>264.6400146484375</v>
+        <v>57.91999816894531</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>1505092</v>
+        <v>2568069</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>8.34</v>
+        <v>12.1</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Advit Jewels Q1 Results: Earnings call audio now available online - scanx.trade</t>
+          <t>Birla Precision Technologies (BIRLAPREC.NS): Stock Eases Marginally, Nears Key Support Level - Symmetrical Triangle - vinanet.vn</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Advit Jewels Q1 Results: Earnings call audio now available online - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr"/>
-      <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr"/>
+          <t>Birla Precision Technologies Mar 2026 Earnings: Steady EPS Delivery Amid Modest Revenue Performance - Tangible Book Value - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>BIRLAPREC.NS Mar 2026 Earnings: Marginal EPS of ₹0.39 on Modest Revenue of ₹63.91 crore; Stock Slides 0.71% - ROA Comparison - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>Birla Precision Technologies Mar 2026 Earnings: Steady EPS Delivery Amid Modest Revenue Performance - Tangible Book Value - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>Birla Precision Technologies Mar 2026 Earnings: Modest Profitability Amidst Stable Revenue - Revenue Warning Signal - vinanet.vn</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 12:50:03 IST</t>
+          <t>2026-09-04 20:18:15 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1045,68 +1069,60 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>MOTISONS.NS</t>
+          <t>MARALOVER.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Motisons Jewellers Limited</t>
+          <t>Maral Overseas Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>15.21000003814697</v>
+        <v>55</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>17.5</v>
+        <v>65.69000244140625</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>15.21000003814697</v>
+        <v>55</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>16.39999961853027</v>
+        <v>61.83000183105469</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>15.36999988555908</v>
+        <v>55.2599983215332</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>16.39999961853027</v>
+        <v>61.83000183105469</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>103761387</v>
+        <v>313406</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>6.7</v>
+        <v>11.89</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Motisons Jewellers Q1FY27 net profit rises 38% to ₹110.5 crore - scanx.trade</t>
+          <t>Maral Overseas Limited Reports Zero Physical Share Transfer Requests Under SEBI Special Window - scanx.trade</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Vodafone Idea, Motisons, LEAP India Among Top NSE Movers - hdfcsky.com</t>
+          <t>Maral Overseas Limited Reports Zero Physical Share Transfer Requests Under SEBI Special Window - scanx.trade</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Vodafone Idea, Motisons, LEAP India Among Top NSE Movers - hdfcsky.com</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>Motisons Jewellers standalone net profit rises 37.61% in the June 2026 quarter - Business Standard</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>Motisons Jewellers shares jump 5% on heavy volumes after Q1 results: Here's what the numbers showed - Business Upturn</t>
-        </is>
-      </c>
+          <t>Maral Overseas schedules 37th AGM on August 25 via VC/OAVM - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 12:50:03 IST</t>
+          <t>2026-09-04 20:18:15 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1114,68 +1130,60 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>PURVA.NS</t>
+          <t>CYBERMEDIA.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Puravankara Limited</t>
+          <t>Cyber Media (India) Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>215</v>
+        <v>25.89999961853027</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>236</v>
+        <v>28.45000076293945</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>215</v>
+        <v>22.20000076293945</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>224.7299957275391</v>
+        <v>26.39999961853027</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>211.0899963378906</v>
+        <v>23.8799991607666</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>224.7299957275391</v>
+        <v>26.39999961853027</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>13276061</v>
+        <v>2156723</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>6.46</v>
+        <v>10.55</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>TTI Enterprise appoints Purva Sharegistry as new RTA - scanx.trade</t>
+          <t>Cyber Media (NSE: CYBERMEDIA) Price Analysis - Kalkine India</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Puravankara Ltd. Share Price Rise: Valuation and Sector - Univest</t>
+          <t>Cyber Media (NSE: CYBERMEDIA) Price Analysis - Kalkine India</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Puravankara Ltd. Share Price Rise: Valuation and Sector - Univest</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>What Drove Puravankara’s Q1 FY27 Profit Turnaround? Key Factors Explained - Trade Brains</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>Puravankara Moves AGM Online, Directs Offline Shareholders to Digital Annual Report - TipRanks</t>
-        </is>
-      </c>
+          <t>Number of employees of Cyber Media (India) Limited Rights 2025-29.08.25 For Shares – BSE:CYBER_RE - TradingView</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 12:50:03 IST</t>
+          <t>2026-09-04 20:18:15 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1183,68 +1191,64 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>AFFLE.NS</t>
+          <t>ZSARACOM.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Affle 3i Limited</t>
+          <t>Saraswati Commercial India Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1529</v>
+        <v>10096</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1620.699951171875</v>
+        <v>11600</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>1521</v>
+        <v>9808</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1611.300048828125</v>
+        <v>11302</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1519.199951171875</v>
+        <v>10227</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1611.300048828125</v>
+        <v>11302</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>650727</v>
+        <v>221</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>6.06</v>
+        <v>10.51</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Affle 3i Share Price: Buy, Hold or Sell Guide - Univest</t>
+          <t>Saraswati Commercial Share Price Rise on NBFC Valuation - Univest</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Affle 3i Share Price: Is It a Good Buy After Q1 FY27 Results? - Univest</t>
+          <t>Saraswati Commercial Share Price Rise on NBFC Valuation - Univest</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Affle 3i Share Price: Is It a Good Buy After Q1 FY27 Results? - Univest</t>
+          <t>Saraswati Commercial submits FY26 annual report to BSE - scanx.trade</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Affle 3i to participate in Elara Capital investor conference - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>Affle 3i holds investor meet with Stallion Asset Management - scanx.trade</t>
-        </is>
-      </c>
+          <t>Saraswati Commercial Q1FY27 net profit surges 169% YoY to ₹635.6 million - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 12:50:03 IST</t>
+          <t>2026-09-04 20:18:15 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1252,68 +1256,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>WELSPLSOL.NS</t>
+          <t>MASTERTR.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Welspun Specialty Solutions Limited</t>
+          <t>Master Trust Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>56.95000076293945</v>
+        <v>81.05000305175781</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>59.43999862670898</v>
+        <v>95.5</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>56.0099983215332</v>
+        <v>81.05000305175781</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>59.38000106811523</v>
+        <v>89.16000366210938</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>56.02000045776367</v>
+        <v>81.02999877929688</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>59.38000106811523</v>
+        <v>89.16000366210938</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>1434273</v>
+        <v>8359824</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>6</v>
+        <v>10.03</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>WELSPLSOL Stock Price and Chart — NSE:WELSPLSOL - TradingView</t>
+          <t>It's Down 26% But Master Trust Limited (NSE:MASTERTR) Could Be Riskier Than It Looks - simplywall.st</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Welspun Specialty Solutions (WELSPLSOL) Mar 2026 Earnings: Modest Profitability Amid Revenue Stability - Capex Guidance - vinanet.vn</t>
+          <t>Master Trust Limited Q2 2026 Earnings: Revenue Declines Marginally, EPS Holds at ₹10.6 - Consensus Forecast Report - vinanet.vn</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Shareholders Will Be Pleased With The Quality of Welspun Specialty Solutions' (NSE:WELSPLSOL) Earnings - simplywall.st</t>
+          <t>Master Trust Limited sees mild gains; support and resistance levels in focus - Price Surge Stocks - vinanet.vn</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Welspun Specialty Solutions Limited (WELSPLSOL.NS) Mar 2026 Earnings: Marginal Profitability Maintained on Steady Revenue - Revenue Growth Outlook - vinanet.vn</t>
+          <t>MASTERTR Stock Price and Chart — NSE:MASTERTR - TradingView</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>WELSPLSOL Mar 2026 Earnings: Modest Profitability Amidst Stable Revenue Run-Rate - Revenue Estimate Trend - vinanet.vn</t>
+          <t>Master Trust Limited (MASTERTR.NS) – Steady Gains Above Support Zone - Fear Greed Extreme - vinanet.vn</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 12:50:03 IST</t>
+          <t>2026-09-04 20:18:15 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1321,64 +1325,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>WELENT.NS</t>
+          <t>RHETAN.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Welspun Enterprises Limited</t>
+          <t>Rhetan TMT Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>761.7999877929688</v>
+        <v>25.42000007629395</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>825</v>
+        <v>25.42000007629395</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>757.4000244140625</v>
+        <v>25.40999984741211</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>810.5</v>
+        <v>25.42000007629395</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>764.75</v>
+        <v>23.11000061035156</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>810.5</v>
+        <v>25.42000007629395</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1719692</v>
+        <v>5455318</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>5.98</v>
+        <v>10</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Welspun Enterprises Share Price News: Fresh 52-Week Peak - Univest</t>
+          <t>Rhetan TMT stock surges 10% upper circuit; AGM on Sep 16 to consider and approve company borrowing limit to Rs. 300 crore for Business expansion - ThePrint</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Welspun Enterprises Share Price: fresh 52-week high update - Univest</t>
+          <t>Rhetan TMT Stock Hits Upper Circuit: Key Triggers &amp; Q1 Results - The Daily Jagran</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Welspun Enterprises Share Price: fresh 52-week high update - Univest</t>
+          <t>Small-cap stock under 50 hits 10% upper circuit despite stock market crash - Livemint</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Welspun Enterprises Ltd. Share Price at Fresh 52-Week High - Univest</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr"/>
+          <t>130% Return In 3 Years: Rhetan TMT Stock Jumps Post Q1 Result | Key Things To Know - Goodreturns</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>Rhetan TMT Ltd. Share Price Jumps to Fresh One-Year High - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 12:50:03 IST</t>
+          <t>2026-09-04 20:18:15 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1386,68 +1394,56 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>SKIPPER.NS</t>
+          <t>RAMBHAJO.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Skipper Limited</t>
+          <t>Advit Jewels Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>538.1500244140625</v>
+        <v>249.8999938964844</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>578.7999877929688</v>
+        <v>268.6799926757812</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>533.75</v>
+        <v>247.0599975585938</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>578.7999877929688</v>
+        <v>268.6799926757812</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>546.9000244140625</v>
+        <v>244.2599945068359</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>578.7999877929688</v>
+        <v>268.6799926757812</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>1388238</v>
+        <v>1915247</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>5.83</v>
+        <v>10</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Skipper Q1FY27 net profit rises 26.5% to ₹565M on infra surge - scanx.trade</t>
+          <t>ADVIT JEWELS Share Price update: fundamentals and peers - Univest</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Skipper Q1FY27 net profit rises 26.5% to ₹565M on infra surge - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>Skipper Shares Rise 3% on Rs 1,305 Cr T&amp;D Order Wins - Equitypandit</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>News by CNBC TV18 on TradingView, 2026-08-27 — cnbctv:6bc1348a7094b:0 - TradingView</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>50% Return in Six Months: This Stock Jumped 3% After Getting Rs 1,305 Crore New Project Order - NDTV Profit</t>
-        </is>
-      </c>
+          <t>ADVIT JEWELS Share Price update: fundamentals and peers - Univest</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr"/>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 12:50:03 IST</t>
+          <t>2026-09-04 20:18:15 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1455,64 +1451,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>ANGELONE.NS</t>
+          <t>UNITECH.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Angel One Limited</t>
+          <t>Unitech Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>295.1000061035156</v>
+        <v>3.710000038146973</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>308.3500061035156</v>
+        <v>4.079999923706055</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>294.75</v>
+        <v>3.710000038146973</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>302.1499938964844</v>
+        <v>4.079999923706055</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>286</v>
+        <v>3.710000038146973</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>302.1499938964844</v>
+        <v>4.079999923706055</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>25159255</v>
+        <v>14406516</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>5.65</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Angel One Stock And Indian Trading Platforms Facing A Volatile Market Test - simplywall.st</t>
+          <t>Unitech Ltd Share Price Today: price action and valuation - Univest</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Angel One Stock And Indian Trading Platforms Facing A Volatile Market Test - simplywall.st</t>
+          <t>Unitech Ltd Share Price Today: price action and valuation - Univest</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Should You Buy Angel One Shares On Monday To Be Eligible For 2nd Interim Dividend By Record Date? - Goodreturns</t>
+          <t>InvestingPro’s Fair Value warned of 54% drop in Unitech shares By Investing.com - Investing.com India</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Angel One Allots 3.49 Lakh Shares Under Employee Incentive Plan - TipRanks</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr"/>
+          <t>Unitech Group files FY26 BRSR; awards 10 Lot-5 tenders - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>Unitech appoints Giridhar Aramane as Chairman and Managing Director - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 12:50:03 IST</t>
+          <t>2026-09-04 20:18:15 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1520,60 +1520,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>SMLMAH.NS</t>
+          <t>AKI.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>SML Mahindra Limited</t>
+          <t>AKI India Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>5725</v>
+        <v>7.21999979019165</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>6094</v>
+        <v>7.21999979019165</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>5719.5</v>
+        <v>7.21999979019165</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>6049.5</v>
+        <v>7.21999979019165</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>5726</v>
+        <v>6.570000171661377</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>6049.5</v>
+        <v>7.21999979019165</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>226226</v>
+        <v>258805</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>5.65</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>SML Mahindra February CV Production Increases To 1,679 Units From 1,442 Units YoY - scanx.trade</t>
+          <t>Penny stock under 10 rupees: Upper circuit - Leather share jumps 74% in 4 sessions | Back-to-back surge for third day - TradingView</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>SML Mahindra Posts 40% Surge in August Vehicle Sales - TipRanks</t>
+          <t>Penny stock under 10 rupees: Upper circuit - Leather share jumps 74% in 4 sessions | Back-to-back surge for third day - TradingView</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>SML Mahindra Posts 40% Surge in August Vehicle Sales - TipRanks</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr"/>
-      <c r="Q17" s="2" t="inlineStr"/>
+          <t>AKI India Ltd Upgraded to Sell on Technical Improvements Despite Lingering Financial Challenges - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>AKI India Ltd leads gainers in 'B' group - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>Volume shocker stocks: Why share price of EMS, Expleo Solutions, Windlas Biotech, AKI India, Heritage Foods are up today - Livemint</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 12:50:03 IST</t>
+          <t>2026-09-04 20:18:15 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1581,64 +1589,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>INDORAMA.NS</t>
+          <t>KSR.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Indo Rama Synthetics (India) Limited</t>
+          <t>KSR Footwear Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>69.79000091552734</v>
+        <v>32.5</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>74.25</v>
+        <v>34.68999862670898</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>69.55000305175781</v>
+        <v>31.89999961853027</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>72.56999969482422</v>
+        <v>34.61000061035156</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>68.87000274658203</v>
+        <v>31.54000091552734</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>72.56999969482422</v>
+        <v>34.61000061035156</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>1298184</v>
+        <v>388523</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>5.37</v>
+        <v>9.73</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Indo Rama Synthetics (India) Ltd. (INDORAMA) Share Price Rises 10.14% Today - Univest</t>
+          <t>KSR Footwear Share Price: Alpa Wealth Buys 1.33% Stake - Univest</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Indo Rama Synthetics (India) Ltd. (INDORAMA) Share Price Rises 10.14% Today - Univest</t>
+          <t>Mark Pope shares not-so-subtle response to losing Mark Mitchell - On3</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Indorama Ventures posts strong 1H26 recovery as EBITDA jumps 61% - Thai Enquirer</t>
+          <t>KSR Footwear AGM passes FY26 results; promoters vote 100% in favour - scanx.trade</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Indorama Ventures Public Company Limited 2026 Q2 - Results - Earnings Call Presentation - Seeking Alpha</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr"/>
+          <t>Mark Pope shares not-so-subtle response to losing Mark Mitchell - On3</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>Kalen "Big K" Edwards Shares Words of Wisdom from the Changing Kentucky Trenches - On3</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 12:50:03 IST</t>
+          <t>2026-09-04 20:18:15 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1646,68 +1658,56 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>PAISALO.NS</t>
+          <t>JISLJALEQS.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Paisalo Digital Limited</t>
+          <t>Jain Irrigation Systems Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>71.65000152587891</v>
+        <v>28.29000091552734</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>74.05999755859375</v>
+        <v>32.38999938964844</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>70.05000305175781</v>
+        <v>28.25</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>74</v>
+        <v>30.8700008392334</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>70.27999877929688</v>
+        <v>28.15999984741211</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>74</v>
+        <v>30.8700008392334</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>19527382</v>
+        <v>29542567</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>5.29</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Paisalo Digital Share Price rises 5.78%: valuation view - Univest</t>
+          <t>Jain Irrigation (JISLDVREQS.NS) Slips Marginally to ₹21.0: Key Support and Resistance Levels in Focus - Volume Climax - siam.in</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Paisalo Digital Share Price rises 5.78%: valuation view - Univest</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>Paisalo Digital Operations and Finance Committee to review NCD issuance on September 5 - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>Paisalo Digital Ltd. Stock News - Value Research</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>Paisalo Digital Ltd. Share Price Today - Paisalo Digital Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
-        </is>
-      </c>
+          <t>Jain Irrigation (JISLDVREQS.NS) Slips Marginally to ₹21.0: Key Support and Resistance Levels in Focus - Volume Climax - siam.in</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr"/>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 12:50:03 IST</t>
+          <t>2026-09-04 20:18:15 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1715,68 +1715,56 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>CARBORUNIV.NS</t>
+          <t>CURAA.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Carborundum Universal Limited</t>
+          <t>Cura Technologies Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1078.699951171875</v>
+        <v>78.5</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1140.900024414062</v>
+        <v>78.5</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>1069.900024414062</v>
+        <v>60</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>1135</v>
+        <v>72.45999908447266</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1078</v>
+        <v>66.19999694824219</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1135</v>
+        <v>72.45999908447266</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>218121</v>
+        <v>2020</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>5.29</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Carborundum Universal Ltd. Share Price Rise: Price Action - Univest</t>
+          <t>D2C kitchenware startup Curaa raises Rs 40 crore led by 3one4 Capital - economictimes.com</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Carborundum Universal Share Price Rises 3.69%: Analysis - Univest</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>Carborundum Universal Share Price: 4.87% Price Rise Analysis - Univest</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>Carborundum Universal Share Price Rises 3.69%: Analysis - Univest</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>Carborundum Universal Ltd. Share Price Price Action View - Univest</t>
-        </is>
-      </c>
+          <t>D2C kitchenware startup Curaa raises Rs 40 crore led by 3one4 Capital - economictimes.com</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 12:50:03 IST</t>
+          <t>2026-09-04 20:18:15 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1784,51 +1772,63 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>PWL.NS</t>
+          <t>LALITHAA.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Physicswallah Limited</t>
+          <t>Lalithaa Jewellery Mart Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>123.370002746582</v>
+        <v>283</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>129.6999969482422</v>
+        <v>308.2999877929688</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>123.0299987792969</v>
+        <v>280.6000061035156</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>126.9000015258789</v>
+        <v>306.7000122070312</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>120.5999984741211</v>
+        <v>280.2999877929688</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>126.9000015258789</v>
+        <v>306.7000122070312</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>35587662</v>
+        <v>23778911</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>5.22</v>
+        <v>9.42</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>PW Gyaan-E Finance | 33+ Courses, Guides &amp; 200+ Skill Courses - PW</t>
+          <t>Shanti Gold International Buys 1.44 Lakh Shares In Lalithaa Jewellery Mart For ₹3.88 Crore - Sahi</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>PW Gyaan-E Finance | 33+ Courses, Guides &amp; 200+ Skill Courses - PW</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr"/>
-      <c r="P21" s="2" t="inlineStr"/>
-      <c r="Q21" s="2" t="inlineStr"/>
+          <t>Lalithaa Jewellery Mart launches 65th showroom in Chennai - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>Shanti Gold buys ₹3.88 crore stake in retail client Lalithaa Jewellery - Dealroom</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>Shanti Gold buys 42,130 more Lalithaa Jewellery shares for ₹1.11 crore - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>Lalithaa Jewellery shares make strong market debut at 32% premium; should you buy, sell or hold? - Moneycontrol.com</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1847,7 +1847,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -1953,7 +1953,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 12:50:03 IST</t>
+          <t>2026-09-04 20:18:15 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -1961,46 +1961,46 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>JAYNECOIND.NS</t>
+          <t>DYCL.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Jayaswal Neco Industries Limited</t>
+          <t>Dynamic Cables Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>92</v>
+        <v>541.9000244140625</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>94.37000274658203</v>
+        <v>546.7999877929688</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>85.22000122070312</v>
+        <v>484</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>86.76000213623047</v>
+        <v>487.8999938964844</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>98.68000030517578</v>
+        <v>544.2999877929688</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>86.76000213623047</v>
+        <v>487.8999938964844</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>39076238</v>
+        <v>1788207</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-12.08</v>
+        <v>-10.36</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>With EPS Growth And More, Jayaswal Neco Industries (NSE:JAYNECOIND) Makes An Interesting Case - simplywall.st</t>
+          <t>Dynamic Cables (NSE: DYCL) Stock Analysis - Kalkine India</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>With EPS Growth And More, Jayaswal Neco Industries (NSE:JAYNECOIND) Makes An Interesting Case - simplywall.st</t>
+          <t>Dynamic Cables (NSE: DYCL) Stock Analysis - Kalkine India</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr"/>
@@ -2010,7 +2010,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 12:50:03 IST</t>
+          <t>2026-09-04 20:18:15 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -2018,46 +2018,46 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UGARSUGAR.NS</t>
+          <t>JAYNECOIND.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>The Ugar Sugar Works Limited</t>
+          <t>Jayaswal Neco Industries Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>58.40000152587891</v>
+        <v>92</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>58.5</v>
+        <v>94.37000274658203</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>53.43000030517578</v>
+        <v>85.22000122070312</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>53.84000015258789</v>
+        <v>89.04000091552734</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>58.56000137329102</v>
+        <v>98.68000030517578</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>53.84000015258789</v>
+        <v>89.04000091552734</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>1106436</v>
+        <v>49816021</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-8.06</v>
+        <v>-9.77</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Ugar Sugar Works director Hari Athawale retires, Prafulla Shirgaokar resigns from board - ChiniMandi</t>
+          <t>With EPS Growth And More, Jayaswal Neco Industries (NSE:JAYNECOIND) Makes An Interesting Case - simplywall.st</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Ugar Sugar Works director Hari Athawale retires, Prafulla Shirgaokar resigns from board - ChiniMandi</t>
+          <t>With EPS Growth And More, Jayaswal Neco Industries (NSE:JAYNECOIND) Makes An Interesting Case - simplywall.st</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr"/>
@@ -2067,7 +2067,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 12:50:03 IST</t>
+          <t>2026-09-04 20:18:15 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -2075,68 +2075,64 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>DYCL.NS</t>
+          <t>UGARSUGAR.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Dynamic Cables Limited</t>
+          <t>The Ugar Sugar Works Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>541.9000244140625</v>
+        <v>58.40000152587891</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>546.7999877929688</v>
+        <v>58.5</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>500</v>
+        <v>53.0099983215332</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>505.25</v>
+        <v>53.34999847412109</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>544.2999877929688</v>
+        <v>58.56000137329102</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>505.25</v>
+        <v>53.34999847412109</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>994101</v>
+        <v>1343466</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-7.17</v>
+        <v>-8.9</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>We Ran A Stock Scan For Earnings Growth And Dynamic Cables (NSE:DYCL) Passed With Ease - simplywall.st</t>
+          <t>Ugar Sugar Works (NSE: UGARSUGAR) Analysis - Kalkine India</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Dynamic Cables (DYCL.NS): Modest Uptick Mirrors Cautious Sector Optimism - Reversal Setup Alerts - vinanet.vn</t>
+          <t>Ugar Sugar Works (NSE: UGARSUGAR) Analysis - Kalkine India</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Dynamic Cables Limited Confirms No Share Encumbrance by Promoters for FY26 - scanx.trade</t>
+          <t>The Ugar Sugar Works Share Price Today: Fall and Analysis - Univest</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Dynamic Cables Limited (DYCL.NS) Q2 2026 Earnings: Revenue Growth Drivers and Operational Resilience - ROA Comparison - vinanet.vn</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>Dynamic Cables Limited Receives CRISIL Credit Rating Reaffirmation for Rs. 350 Crore Banking Facilities - scanx.trade</t>
-        </is>
-      </c>
+          <t>Ugar Sugar Works director Hari Athawale retires, Prafulla Shirgaokar resigns from board - ChiniMandi</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 12:50:03 IST</t>
+          <t>2026-09-04 20:18:15 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -2144,68 +2140,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>POLYCAB.NS</t>
+          <t>JAYKAY.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Polycab India Limited</t>
+          <t>Jaykay Enterprises Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>8500</v>
+        <v>165.3699951171875</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>8500</v>
+        <v>167.8800048828125</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>8287.5</v>
+        <v>151.7599945068359</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>8308.5</v>
+        <v>153.6900024414062</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>8807.5</v>
+        <v>166.4600067138672</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>8308.5</v>
+        <v>153.6900024414062</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>1026763</v>
+        <v>470343</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-5.67</v>
+        <v>-7.67</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Polycab, KEI Industries shares crash up to 9% after UltraTech Cement enters wires &amp; cables business. What - economictimes.com</t>
+          <t>Jaykay Enterprises board meets May 27 to approve FY26 results - scanx.trade</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>RR Kabel, KEI Industries, Polycab shares sink up to 8%; Nuvama lists preferred picks - Business Today</t>
+          <t>Federal-Mogul Goetze (India) Ltd leads losers in 'B' group - Business Standard</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Polycab, KEI Industries Shares up to 8% as Ultratech Enters Wires &amp; Cables Business with Ultravolt - India Infoline</t>
+          <t>Jaykay Enterprises files Letter of Offer for ₹154.28 crore rights issue - scanx.trade</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Cable stocks crash up to 6% as UltraTech launches Ultravolt; Polycab, KEI, RR Kabel among top losers - Moneycontrol.com</t>
+          <t>Jaykay Enterprises schedules 80th AGM for Sep 29 via video conferencing - scanx.trade</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>Copper Shock Hits Cables Stocks: Polycab, Finolex, RR Kabel Slide Up To 6% After Price Hikes - NDTV Profit</t>
+          <t>Jaykay Enterprises Ltd. Key Financial Ratios – Valuation, Profitability &amp; More - Value Research</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 12:50:03 IST</t>
+          <t>2026-09-04 20:18:15 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2213,68 +2209,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>UTTAMSUGAR.NS</t>
+          <t>HIKAL.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Uttam Sugar Mills Limited</t>
+          <t>Hikal Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>300.8999938964844</v>
+        <v>234</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>302</v>
+        <v>236.7400054931641</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>281.0499877929688</v>
+        <v>220.1000061035156</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>283.2000122070312</v>
+        <v>222.3000030517578</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>299</v>
+        <v>240.3600006103516</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>283.2000122070312</v>
+        <v>222.3000030517578</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>231891</v>
+        <v>5351852</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-5.28</v>
+        <v>-7.51</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Uttam Sugar Mills Share Price Today: 8.75% rise - Univest</t>
+          <t>Hikal Ltd Shares Hit Intraday Low Amid Price Pressure on 4 Sep 2026 - MarketsMojo</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Uttam Sugar Mills Share Price Today: 8.75% rise - Univest</t>
+          <t>Hikal Ltd Shares Hit Intraday Low Amid Price Pressure on 4 Sep 2026 - MarketsMojo</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Uttam Sugar Mills Share Price: Technical, Fundamental View - Univest</t>
+          <t>Hikal Ltd. Share Price Rise: Price Action and Fundamentals - Univest</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Uttam Sugar Mills Ltd. Share Price Today Near 52-Week High - Univest</t>
+          <t>Don't Race Out To Buy Hikal Limited (NSE:HIKAL) Just Because It's Going Ex-Dividend - simplywall.st</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>Uttam Sugar Mills Q1 Net Profit Plummets 94.69% YoY to ₹85 lakh - Sahi</t>
+          <t>Hikal files FY26 sustainability report with ESG metrics - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 12:50:03 IST</t>
+          <t>2026-09-04 20:18:15 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2282,68 +2278,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>RNBDENIMS.NS</t>
+          <t>AUTOIND.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>R&amp;B Denims Limited</t>
+          <t>Autoline Industries Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>10.8100004196167</v>
+        <v>94</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>10.8100004196167</v>
+        <v>95.90000152587891</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>10.27000045776367</v>
+        <v>85.20999908447266</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>10.27000045776367</v>
+        <v>86.44999694824219</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>10.8100004196167</v>
+        <v>92.75</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>10.27000045776367</v>
+        <v>86.44999694824219</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>406522</v>
+        <v>591037</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-5</v>
+        <v>-6.79</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>RNBDENIMS Stock Price and Chart — NSE:RNBDENIMS - TradingView</t>
+          <t>Autoline Industries Share Price Rise; Valuation in Focus - Univest</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>R&amp;B Denims (RNBDENIMS.NS) Slips 1.5%: Testing Key Support Near ₹9.89 - Defined Outcome ETF - vinanet.vn</t>
+          <t>Autoline Industries AUTOIND 30th AGM Notice September 2026 - Kalkine India</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>R&amp;B Denims Limited Allots Bonus Shares in 1:2 Ratio with Record Date April 03, 2026 - scanx.trade</t>
+          <t>Autoline Industries Wins ₹100 Crore Tata Motors Order - HDFC Sky</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>R&amp;B Denims (RNBDENIMS.NS) Slips 1.5%: Testing Key Support Near ₹9.89 - Defined Outcome ETF - vinanet.vn</t>
+          <t>ISTLTD Stock Price and Chart — NSE:ISTLTD - TradingView</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>R&amp;B Denims Limited Sets Record Date April 3, 2026 for 1:2 Bonus Equity Shares - scanx.trade</t>
+          <t>Autoline Industries Ltd. Share Price: Near 52-Week High - Univest</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 12:50:03 IST</t>
+          <t>2026-09-04 20:18:15 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2351,68 +2347,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>PAR.NS</t>
+          <t>RRKABEL.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Par Drugs And Chemicals Limited</t>
+          <t>R R Kabel Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>168</v>
+        <v>2550</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>168</v>
+        <v>2609</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>156.7100067138672</v>
+        <v>2374.39990234375</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>156.7100067138672</v>
+        <v>2454.10009765625</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>164.9499969482422</v>
+        <v>2617.699951171875</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>156.7100067138672</v>
+        <v>2454.10009765625</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>9717</v>
+        <v>2596647</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-5</v>
+        <v>-6.25</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Alliance Select Foods International Announces Equity Restructuring For Common Shares Par Value Reduction To 0.10 Pesos Per Share - TradingView</t>
+          <t>RR Kabel, KEI Industries, Polycab India shares tumble; JM Financial downgrades stocks, revises targets - businesstoday.in</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Par Pacific (NYSE: PARR) officer lines up new stock sale - Stock Titan</t>
+          <t>RR Kabel, KEI Industries, Polycab India shares tumble; JM Financial downgrades stocks, revises targets - businesstoday.in</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Symbiotec Pharmalab makes tepid market debut, lists at par with IPO price - Business Standard</t>
+          <t>RR Kabel Share Price Near 52-Week High Analysis - Univest</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Strategy’s (MSTR) STRC remains below par as Strive’s SATA attracts investors - coindesk.com</t>
+          <t>RR Kabel Share Price at fresh 52-week high: analysis - Univest</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>GFL Environmental Inc. Subordinate voting shares no par value - ADR Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>RR Kabel Share Price Falls 2.72%: Price, Valuation View - Univest</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 12:50:03 IST</t>
+          <t>2026-09-04 20:18:15 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2420,68 +2416,64 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>HIKAL.NS</t>
+          <t>LANDSMILL.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Hikal Limited</t>
+          <t>Landsmill Green Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>234</v>
+        <v>0.6700000166893005</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>236.7400054931641</v>
+        <v>0.7099999785423279</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>226.1999969482422</v>
+        <v>0.6299999952316284</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>230.0200042724609</v>
+        <v>0.6299999952316284</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>240.3600006103516</v>
+        <v>0.6700000166893005</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>230.0200042724609</v>
+        <v>0.6299999952316284</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>3668424</v>
+        <v>10120631</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-4.3</v>
+        <v>-5.97</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Hikal Ltd. Share Price Rise: Price Action and Fundamentals - Univest</t>
+          <t>Landsmill Green - 14 penny stocks plunge up to 85% in 6 months. Are you holding any? - economictimes.com</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Hikal Ltd. Share Price Rise: Price Action and Fundamentals - Univest</t>
+          <t>Landsmill Green board to delete FMCG object, close subsidiary on Sep 4 - scanx.trade</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Don't Race Out To Buy Hikal Limited (NSE:HIKAL) Just Because It's Going Ex-Dividend - simplywall.st</t>
+          <t>Landsmill Green Q1 Results: Net profit up 987% YoY to ₹85.4 lakh - scanx.trade</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Hikal files FY26 sustainability report with ESG metrics - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>Hikal Q1 Consolidated Net Loss Narrows to ₹7.4 Crore; Revenue At ₹403 Crore - Sahi</t>
-        </is>
-      </c>
+          <t>Landsmill Green board to delete FMCG object, close subsidiary on Sep 4 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 12:50:03 IST</t>
+          <t>2026-09-04 20:18:15 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2489,68 +2481,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>DWARKESH.NS</t>
+          <t>POLYCAB.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Dwarikesh Sugar Industries Limited</t>
+          <t>Polycab India Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>49.40999984741211</v>
+        <v>8500</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>49.40999984741211</v>
+        <v>8500</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>47.13999938964844</v>
+        <v>8250</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>47.25</v>
+        <v>8300</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>49.31999969482422</v>
+        <v>8807.5</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>47.25</v>
+        <v>8300</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>1456612</v>
+        <v>1559219</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-4.2</v>
+        <v>-5.76</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Dwarikesh Sugar Industries: Promoter Gautam Morarka Increases Stake to 15.22% - scanx.trade</t>
+          <t>Polycab, KEI Industries shares crash up to 9% after UltraTech Cement enters wires &amp; cables business. What - economictimes.com</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>AI: The Tech ‘Go-Direct’ Ethos Meets Grassroots AI Revolt. AI-RTZ #1198 - AI: Reset to Zero</t>
+          <t>Polycab falls 7% on UltraTech's foray into wires and cables even as JPMorgan allays fears; should you buy,... - Moneycontrol.com</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Dwarikesh Sugar Industries Share Price Rises 8.3% Today - Univest</t>
+          <t>Polycab, KEI Industries Shares up to 8% as Ultratech Enters Wires &amp; Cables Business with Ultravolt - India Infoline</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Dwarkesh Patels’s wildly popular but dangerously misleading account of the OpenAI Hugging Face incident - Marcus on AI | Substack</t>
+          <t>Copper Shock Hits Cables Stocks: Polycab, Finolex, RR Kabel Slide Up To 6% After Price Hikes - NDTV Profit</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>OpenAI-Hugging Face controversy deepens as experts debate Dwarkesh Patel's 'AI civilisation' claims - Moneycontrol.com</t>
+          <t>Polycab valuations correcting to these levels will be a buying opportunity, JPMorgan says - CNBC TV18</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 12:50:03 IST</t>
+          <t>2026-09-04 20:18:15 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2558,68 +2550,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>SYNCOMF.NS</t>
+          <t>SKYWAYS.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Syncom Formulations (India) Limited</t>
+          <t>Skyways Air Services Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>20.93000030517578</v>
+        <v>131.5</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>21.8799991607666</v>
+        <v>133.6499938964844</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>20.04999923706055</v>
+        <v>120.0999984741211</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>20.54000091552734</v>
+        <v>122.7200012207031</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>21.36000061035156</v>
+        <v>130.0599975585938</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>20.54000091552734</v>
+        <v>122.7200012207031</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>11553212</v>
+        <v>8334295</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-3.84</v>
+        <v>-5.64</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Here's Why Syncom Formulations (India) (NSE:SYNCOMF) Has Caught The Eye Of Investors - simplywall.st</t>
+          <t>Skyways Air Services shares list at 9% discount to IPO price on NSE, BSE - Moneycontrol.com</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Syncom Formulations Sees Minor Pullback, Holds Above Key Support at ₹13.27 - Last Point Support - vinanet.vn</t>
+          <t>Skyways Air Services Shares List 10% Below IPO Price; Defies Grey Market Expectations - BW Businessworld</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Syncom Formulations (India) Limited Acquires Commercial Property from HDFC Bank Ltd for ₹57,26,00,000 - scanx.trade</t>
+          <t>Skyways Air Services shares defy GMP expectations, list at 10% discount - Business Standard</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>SYNCOMF.NS Q2 2025 Earnings: Robust Revenue Growth of 76% YoY Despite Marginal Stock Dip - Tax Rate Impact - vinanet.vn</t>
+          <t>Skyways Air Services tumble over 10% on market debut - BusinessLine</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>SYNCOMF Stock Price and Chart — NSE:SYNCOMF - TradingView</t>
+          <t>Skyways Air Services listing: Shares list at 10.1% discount compare to IPO price on NSE - Upstox</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 12:50:03 IST</t>
+          <t>2026-09-04 20:18:15 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2627,68 +2619,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>DBOL.NS</t>
+          <t>ANTELOPUS.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Dhampur Bio Organics Limited</t>
+          <t>Antelopus Selan Energy Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>128.9600067138672</v>
+        <v>1001</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>128.9600067138672</v>
+        <v>1028.800048828125</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>124</v>
+        <v>925.2000122070312</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>124.6900024414062</v>
+        <v>957.1500244140625</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>129.6399993896484</v>
+        <v>1013.299987792969</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>124.6900024414062</v>
+        <v>957.1500244140625</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>181551</v>
+        <v>4816041</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-3.82</v>
+        <v>-5.54</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Dhampur Bio Organics promoters confirm no share encumbrance in FY26 - scanx.trade</t>
+          <t>Antelopus Selan Energy shares rally 20% to 52-week high; what investors need to know - Upstox</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Dhampur Bio Organics promoters confirm no share encumbrance in FY26 - scanx.trade</t>
+          <t>Why did Antelopus Selan Energy's shares jump over 32% in 4 days? | The stock has rallied 636% in 5 years | Inshorts - Inshorts</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Dhampur Bio Organics Share Price, Valuation, Sector View - Univest</t>
+          <t>Antelopus Selan Energy share price up over 32% up in 3 days - What's behind continuous stock jump? Details here - Livemint</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Sonitron acquires 40,000 Dhampur Bio Organics shares in open market - scanx.trade</t>
+          <t>Multibagger Smallcap Stock Jumps Over 15% In Trade. Here's Why - NDTV Profit</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>PHAT Q2 2026 Earnings: Narrower Loss Beats Estimates, Shares Gain 4.36% - Earnings Yield Spread - vinanet.vn</t>
+          <t>Antelopus Selan Energy promoter declares no encumbrance in FY26 - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 12:50:03 IST</t>
+          <t>2026-09-04 20:18:15 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2696,68 +2688,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>ATHERENERG.NS</t>
+          <t>TCC.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Ather Energy Limited</t>
+          <t>TCC Concept Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1644</v>
+        <v>47.33000183105469</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1644.5</v>
+        <v>49.22000122070312</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>1573.5</v>
+        <v>43.79999923706055</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>1576.5</v>
+        <v>44.09999847412109</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1638.900024414062</v>
+        <v>46.62599945068359</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1576.5</v>
+        <v>44.09999847412109</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>3222709</v>
+        <v>578461</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-3.81</v>
+        <v>-5.42</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>ATHER ENERGY LIMITED Share Price - Live NSE: ATHERENERG Stock Price &amp; Chart - Upstox</t>
+          <t>TCC Concept signs MOU for 60 MW data centre campus in Pune - scanx.trade</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>ATHER ENERGY Share Price: Today's 2.45% Decline - Univest</t>
+          <t>Taiwan Cement stock falls as volume and margins draw focus - ad-hoc-news.de</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>When Can We Expect A Profit From Ather Energy Limited (NSE:ATHERENERG)? - simplywall.st</t>
+          <t>Volume Gainers as of 12:25 PM IST, Mumbai, August 26: Indo Thai Securities, TCC Concept Lead Trading Surge - HDFC Sky</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Ather Energy shares climb to all-time high, rising 17% above Hero MotoCorp block price - TechStock²</t>
+          <t>TCC CONCEPT Consolidated June 2026 Net Sales at Rs 128.28 crore, up 480.19% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>Ather Energy Share Price Rise: Market Cap and Valuation - Univest</t>
+          <t>TCC Concept fixes September 4 record date for 1:5 share split - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 12:50:03 IST</t>
+          <t>2026-09-04 20:18:15 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2765,68 +2757,64 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>EMIL.NS</t>
+          <t>MAKERSL.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Electronics Mart India Limited</t>
+          <t>Makers Laboratories Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>175.3999938964844</v>
+        <v>206.8500061035156</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>176.6699981689453</v>
+        <v>206.8500061035156</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>168.9299926757812</v>
+        <v>188.3999938964844</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>169.7200012207031</v>
+        <v>189.8999938964844</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>176.1600036621094</v>
+        <v>200.7700042724609</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>169.7200012207031</v>
+        <v>189.8999938964844</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>753170</v>
+        <v>6513</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-3.66</v>
+        <v>-5.41</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Pentagon official overseeing military AI sold millions worth of stock in AI firm - The Guardian</t>
+          <t>Makers Laboratories Share Price rise: fundamentals and peers - Univest</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Top Pentagon AI Official Sold Millions in Perplexity Stock, Disclosures Show - Decrypt</t>
+          <t>Makers Laboratories Share Price rise: fundamentals and peers - Univest</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Electronics Mart India Share Price Within 2% of 52W High - Univest</t>
+          <t>Makers Laboratories Ltd. (MAKERSL) Fundamental and Financial Data - Stocktwits</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Most Active Equities, August 10, 2026, 3:30 PM IST - hdfcsky.com</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>Earnings Update: Here's Why Analysts Just Lifted Their Electronics Mart India Limited (NSE:EMIL) Price Target To ₹186 - simplywall.st</t>
-        </is>
-      </c>
+          <t>Makers Laboratories Q1 Results: Consolidated Net Profit Surges 244% YoY to ₹150.43 lacs - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 12:50:03 IST</t>
+          <t>2026-09-04 20:18:15 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2834,51 +2822,51 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>FIVESTAR.NS</t>
+          <t>DHAMPURSUG.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Five-Star Business Finance Limited</t>
+          <t>Dhampur Sugar Mills Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>538</v>
+        <v>176.4499969482422</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>538</v>
+        <v>176.4499969482422</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>512.5</v>
+        <v>165.6300048828125</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>515.25</v>
+        <v>167.5899963378906</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>534.5999755859375</v>
+        <v>177.0500030517578</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>515.25</v>
+        <v>167.5899963378906</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>554474</v>
+        <v>831577</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-3.62</v>
+        <v>-5.34</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Five-Star Business Finance Limited Appoints Sreeram Ranganathan Iyer as A Non­ Executive Independent Director, Effective July 25, 2026 - marketscreener.com</t>
+          <t>Dhampur Sugar Mills Ltd. Share Price: 52-Week High Focus - Univest</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Five-Star Business Finance Limited Appoints Sreeram Ranganathan Iyer as A Non­ Executive Independent Director, Effective July 25, 2026 - marketscreener.com</t>
+          <t>Dhampur Sugar Mills net profit rises 569% to ₹6.09 crore in Q1FY27 - scanx.trade</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Five Star Business Finance Submits Business Responsibility and Sustainability Report for FY 2025-26 - scanx.trade</t>
+          <t>Dhampur Sugar Mills net profit rises 569% to ₹6.09 crore in Q1FY27 - scanx.trade</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr"/>
@@ -2887,7 +2875,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 12:50:03 IST</t>
+          <t>2026-09-04 20:18:15 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2895,68 +2883,64 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>EBGNG.NS</t>
+          <t>ANNAPURNA.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>GNG Electronics Limited</t>
+          <t>Annapurna Swadisht Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>622</v>
+        <v>151.4499969482422</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>633.4000244140625</v>
+        <v>151.4499969482422</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>598</v>
+        <v>139</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>600</v>
+        <v>140.1999969482422</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>622.0999755859375</v>
+        <v>147.7799987792969</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>600</v>
+        <v>140.1999969482422</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>572288</v>
+        <v>96796</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-3.55</v>
+        <v>-5.13</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Should You Be Adding GNG Electronics (NSE:EBGNG) To Your Watchlist Today? - simplywall.st</t>
+          <t>Annapurna Swadisht Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>GNG Electronics Schedules 20th AGM and Releases FY 2025-26 Annual Report - TipRanks</t>
+          <t>Annapurna Studios expands distribution slate with Dulquer Salmaan’s I’m Game, Karthi’s Sardar 2 and... - Moneycontrol.com</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>GNG Electronics Limited (NSE: EBGNG) Stock Price, News &amp; Analysis - Kalkine</t>
+          <t>Annapurna gets ‘Annapurna Bhandar’ benefits: Mamata Banerjee thanks CM Suvendu and leaves one wondering - Bhaskar English</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>GNG Electronics reports 32% revenue surge in Q1FY27 on margin expansion - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>GNG Electronics Schedules 20th AGM and Releases FY 2025-26 Annual Report - TipRanks</t>
-        </is>
-      </c>
+          <t>Annapurna Studios expands distribution slate with Dulquer Salmaan’s I’m Game, Karthi’s Sardar 2 and... - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 12:50:03 IST</t>
+          <t>2026-09-04 20:18:15 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -2964,60 +2948,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>MACPOWER.NS</t>
+          <t>TARMAT.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Macpower CNC Machines Limited</t>
+          <t>Tarmat Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1955.800048828125</v>
+        <v>64.48999786376953</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>1960</v>
+        <v>64.79000091552734</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>1868.300048828125</v>
+        <v>60.54999923706055</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>1878.599975585938</v>
+        <v>61.22999954223633</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1944.099975585938</v>
+        <v>64.48999786376953</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1878.599975585938</v>
+        <v>61.22999954223633</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>23752</v>
+        <v>36266</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-3.37</v>
+        <v>-5.06</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Macpower CNC Machines Ltd is Rated Hold - MarketsMojo</t>
+          <t>Tarmat schedules AGM to approve board reappointments and salary hikes - scanx.trade</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Macpower CNC Machines Ltd is Rated Hold - MarketsMojo</t>
+          <t>Tarmat schedules AGM to approve board reappointments and salary hikes - scanx.trade</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Rs 21,932 cr opportunity: 2 stocks powering India’s next manufacturing wave - financialexpress.com</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr"/>
-      <c r="Q17" s="2" t="inlineStr"/>
+          <t>Tarmat Ltd. Financials – Balance Sheet, Profit &amp; Loss, Cash Flow - Value Research</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>Tarmat Ltd. Share Price rise with market cap at Rs 128.43 Cr - Univest</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>Tarmat consolidated net profit rises 121.74% in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 12:50:03 IST</t>
+          <t>2026-09-04 20:18:15 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -3025,68 +3017,60 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>GRAVITA.NS</t>
+          <t>NIRAJISPAT.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Gravita India Limited</t>
+          <t>Niraj Ispat Industries Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1684.800048828125</v>
+        <v>387.7999877929688</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>1696.599975585938</v>
+        <v>387.7999877929688</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>1626.900024414062</v>
+        <v>387.7999877929688</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>1630</v>
+        <v>387.7999877929688</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1684.800048828125</v>
+        <v>408.2000122070312</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1630</v>
+        <v>387.7999877929688</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>255828</v>
+        <v>601</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-3.25</v>
+        <v>-5</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Gravita India closes books for AGM from Sep 22 to Sep 28 - scanx.trade</t>
+          <t>Niraj (NIRAJISPAT.NS) Stock: Closes with Little Net Change at ₹216.00 in the Available Record; Range Check: the Price Remains Bounded by the Supplied Support and Resistance for the Current Session - ALMA Signal - siam.in</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Gravita India closes books for AGM from Sep 22 to Sep 28 - scanx.trade</t>
+          <t>Precision Wires and 11 Other Stocks That Hit the 20% Upper Circuit Today; Are You Holding Any? - tradebrains.in</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Gravita India approves ₹100 Cr corporate guarantee for subsidiary RMIL - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>Gravita India to add 59,200 MTPA copper recycling capacity at Mundra with ₹64 crore capex - CNBC TV18</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>Gravita India schedules physical investor meet in Jaipur on Sep 2 - scanx.trade</t>
-        </is>
-      </c>
+          <t>Precision Wires and 11 Other Stocks That Hit the 20% Upper Circuit Today; Are You Holding Any? - tradebrains.in</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 12:50:03 IST</t>
+          <t>2026-09-04 20:18:15 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -3094,68 +3078,64 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>WEL.NS</t>
+          <t>KJMCFIN.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Wonder Electricals Limited</t>
+          <t>KJMC Financial Services Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>79.25</v>
+        <v>66.79000091552734</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>79.25</v>
+        <v>68</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>75.41000366210938</v>
+        <v>63.13999938964844</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>76.83000183105469</v>
+        <v>63.13999938964844</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>79.37000274658203</v>
+        <v>66.45999908447266</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>76.83000183105469</v>
+        <v>63.13999938964844</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>914005</v>
+        <v>2504</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-3.2</v>
+        <v>-5</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Integrated Wellness Acquisition Corp (WEL) Peer Comparison – Compare with Others - Value Research</t>
+          <t>KJMC Financial Services Ltd. (KJMCFIN) Share Price Today, Quote, Latest Discussions, Interactive Chart and News - Stocktwits</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Integrated Wellness Acquisition Corp (WEL) Peer Comparison – Compare with Others - Value Research</t>
+          <t>KJMC Financial Services Ltd. (KJMCFIN) Fundamental and Financial Data - Stocktwits</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Wonder Electricals Share Price Today After Sharp Fall - Univest</t>
+          <t>KJMC Financial Services Ltd. (KJMCFIN) Fundamental and Financial Data - Stocktwits</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Btab uses artificial intelligence to link global manufacturers with U.S. business buyers - Stock Titan</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>Wonder Electricals Share Price Today: Market Cap and P/E - Univest</t>
-        </is>
-      </c>
+          <t>KJMC Financial Services Ltd. (KJMCFIN) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 12:50:03 IST</t>
+          <t>2026-09-04 20:18:15 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -3163,60 +3143,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>PONNIERODE.NS</t>
+          <t>ANNU.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Ponni Sugars (Erode) Limited</t>
+          <t>Annu Projects Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>402.8999938964844</v>
+        <v>68.23000335693359</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>402.8999938964844</v>
+        <v>69</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>385</v>
+        <v>68.23000335693359</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>386</v>
+        <v>68.23000335693359</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>398.6499938964844</v>
+        <v>71.81999969482422</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>386</v>
+        <v>68.23000335693359</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>17691</v>
+        <v>412213</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-3.17</v>
+        <v>-5</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Ponni Sugars Share Price Today: Price Rise and Analysis - Univest</t>
+          <t>Weak market debut: Annu Projects shares list at over 27% discount to its IPO price - Moneycontrol.com</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>NXG Infrastructure Income Fund Holds Ground at $56.30 as Market Waits for Direction - Fear Greed Extreme - vinanet.vn</t>
+          <t>ANNU PROJECTS LIMITED Share Price - Upstox</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>NXG Infrastructure Income Fund Holds Ground at $56.30 as Market Waits for Direction - Fear Greed Extreme - vinanet.vn</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr"/>
-      <c r="Q20" s="2" t="inlineStr"/>
+          <t>ANNU PROJECTS LIMITED Share Price - Upstox</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>Weak Start! Annu Projects shares list at 27% discount to IPO price - economictimes.com</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>Annu Projects Shares List at 27% Discount on NSE - Groww</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 12:50:03 IST</t>
+          <t>2026-09-04 20:18:15 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -3224,55 +3212,63 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>POWERMECH.NS</t>
+          <t>RNBDENIMS.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Power Mech Projects Limited</t>
+          <t>R&amp;B Denims Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>2399.89990234375</v>
+        <v>10.8100004196167</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>2416</v>
+        <v>10.8100004196167</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>2331</v>
+        <v>10.27000045776367</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>2334</v>
+        <v>10.27000045776367</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>2399.800048828125</v>
+        <v>10.8100004196167</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>2334</v>
+        <v>10.27000045776367</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>37175</v>
+        <v>424488</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-2.74</v>
+        <v>-5</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Power Mech Projects Limited announces Annual dividend, payable on October 17, 2026 - marketscreener.com</t>
+          <t>RNBDENIMS Stock Price and Chart — NSE:RNBDENIMS - TradingView</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Power Mech Projects Limited announces Annual dividend, payable on October 17, 2026 - marketscreener.com</t>
+          <t>R&amp;B Denims (RNBDENIMS.NS) Slips 1.5%: Testing Key Support Near ₹9.89 - Defined Outcome ETF - vinanet.vn</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Power Mech Projects Publishes AGM Notice and E-Voting Details in Newspapers - TipRanks</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr"/>
-      <c r="Q21" s="2" t="inlineStr"/>
+          <t>R&amp;B Denims Schedules EGM for March 13 to Approve Stock Split and Corporate Actions - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>R&amp;B Denims (RNBDENIMS.NS) Slips 1.5%: Testing Key Support Near ₹9.89 - Defined Outcome ETF - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>R&amp;B Denims Limited (RNBDENIMS.NS) Faces Selling Pressure, Holds Above Key Support - Institutional Sentiment - vinanet.vn</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -439,7 +439,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="39" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 20:18:15 IST</t>
+          <t>2026-09-07 12:56:35 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -553,68 +553,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>XTRANET.NS</t>
+          <t>ALKALI.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Xtranet Technologies Limited</t>
+          <t>Alkali Metals Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>197.1999969482422</v>
+        <v>69.98999786376953</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>234.2400054931641</v>
+        <v>78.66000366210938</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>193.1100006103516</v>
+        <v>68</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>234.2400054931641</v>
+        <v>78.66000366210938</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>195.1999969482422</v>
+        <v>65.55000305175781</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>234.2400054931641</v>
+        <v>78.66000366210938</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>5584584</v>
+        <v>70547</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>20</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>XTRANET TECHNOLOGIES LTD Share Price - Upstox</t>
+          <t>Momentum Stocks: Alkali Metals, Deepak Builders jump up to 15% on sheer momentum - Moneycontrol.com</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Xtranet Technologies Ltd (XTRANET) Share Price - businesstoday.in</t>
+          <t>Alkali Metals and Deepak Builders Surge on Momentum Trading - whalesbook.com</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Xtranet Technologies Ltd (XTRANET) Share Price - businesstoday.in</t>
+          <t>Lords Chloro Alkali Commissions 14.5 MW Solar Plant; Shares Rise 1.33% - HDFC Sky</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>XTRANET Share Price Today - XTRANET TECHNOLOGIES LTD Stock Price Live NSE/BSE - Univest</t>
+          <t>Tuticorin Alkali Chemicals schedules 53rd AGM for September 25, 2026 - scanx.trade</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Stocks to Watch Today: BSE, United Spirits, Hyundai Motor, XtraNet Tech, Autoline Industries, EMS, Ramco... - Moneycontrol.com</t>
+          <t>Don't Buy Alkali Metals Limited (NSE:ALKALI) For Its Next Dividend Without Doing These Checks - simplywall.st</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 20:18:15 IST</t>
+          <t>2026-09-07 12:56:35 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -622,68 +622,60 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>JINDWORLD.NS</t>
+          <t>PKTEA.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Jindal Worldwide Limited</t>
+          <t>The Peria Karamalai Tea &amp; Produce Company Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>49.66999816894531</v>
+        <v>808</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>57.77999877929688</v>
+        <v>963.1500244140625</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>49.02000045776367</v>
+        <v>808</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>57.5099983215332</v>
+        <v>963.1500244140625</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>48.15000152587891</v>
+        <v>802.6500244140625</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>57.5099983215332</v>
+        <v>963.1500244140625</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>187907453</v>
+        <v>10527</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>19.44</v>
+        <v>20</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Jindal Worldwide (JINDWORLD.NS) Edges Higher at ₹38.31; Key Support and Resistance in Focus - Dividend Growth Stocks - siam.in</t>
+          <t>The Peria Karamalai Tea &amp; Produce Company Limited (NSE: PKTEA) Gains 20% as Stock Movement Draws Market Attention - Kalkine India</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Most Active Equities on September 4, 2026 at 4:00 PM - HDFC Sky</t>
+          <t>The Peria Karamalai Tea &amp; Produce Company Limited (NSE: PKTEA) Gains 20% as Stock Movement Draws Market Attention - Kalkine India</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Jindal Worldwide shares hit 20% upper circuit as arm plans 100 electric scooter showrooms - TradingView</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>News by CNBC TV18 on TradingView, 2026-09-04 — cnbctv:657850109094b:0 - TradingView</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>Jindal Worldwide stock hits upper circuit - What's behind the share price jump? - Livemint</t>
-        </is>
-      </c>
+          <t>THE P K TEA PROD CO LTD Share Price - Upstox</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 20:18:15 IST</t>
+          <t>2026-09-07 12:56:35 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -691,56 +683,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>NRAIL.NS</t>
+          <t>ANDHRAPAP.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>N R Agarwal Industries Limited</t>
+          <t>ANDHRA PAPER LIMITED</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>498.9500122070312</v>
+        <v>64.09999847412109</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>595.25</v>
+        <v>77.33999633789062</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>496.0499877929688</v>
+        <v>61.9900016784668</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>584</v>
+        <v>76.19999694824219</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>496.0499877929688</v>
+        <v>64.44999694824219</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>584</v>
+        <v>76.19999694824219</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>157425</v>
+        <v>21270613</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>17.73</v>
+        <v>18.23</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>NR Agarwal Industries Ltd. (NRAIL) Share Price Rises 12.36% Today - Univest</t>
+          <t>Andhra Paper Rises 3.3% to ₹61.93: Key Levels to Watch - Short Setup Alerts - siam.in</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>NR Agarwal Industries Ltd. (NRAIL) Share Price Rises 12.36% Today - Univest</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr"/>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
+          <t>APPCB imposes ₹21 crore environmental compensation on Andhra Paper Limited - The Hindu</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>APPCB imposes ₹21 crore environmental compensation on Andhra Paper Limited - The Hindu</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh Deputy CM Pawan Kalyan directs APPCB to initiate action against Andhra Paper Limited for ‘polluting’ Godavari river - The Hindu</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>Andhra Paper reappoints Saurabh Bangur as MD for five years - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 20:18:15 IST</t>
+          <t>2026-09-07 12:56:35 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -748,68 +752,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>LANCORHOL.NS</t>
+          <t>XTRANET.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Lancor Holdings Limited</t>
+          <t>Xtranet Technologies Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>35.13000106811523</v>
+        <v>242</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>40.88000106811523</v>
+        <v>280</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>34.20999908447266</v>
+        <v>236.5800018310547</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>40.34999847412109</v>
+        <v>273.9800109863281</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>34.75</v>
+        <v>234.2400054931641</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>40.34999847412109</v>
+        <v>273.9800109863281</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>2380475</v>
+        <v>11559377</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>16.12</v>
+        <v>16.97</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Lancor Holdings Limited (NSE:LANCORHOL) Shares Fly 25% But Investors Aren't Buying For Growth - simplywall.st</t>
+          <t>XTRANET TECHNOLOGIES LTD Share Price - Upstox</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>LANCORHOL.NS Mar 2026 Earnings: EPS of ₹5.84 on Revenue of ₹14.0 Cr; Stock Gains 8.32 Points - Analyst Drop Coverage - vinanet.vn</t>
+          <t>XTRANET TECHNOLOGIES LTD Share Price - Upstox</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Lancor Holdings Limited Sees Marginal Decline: Technical Resistance and Support Levels in Focus - SuperTrend - vinanet.vn</t>
+          <t>Xtranet Technologies Ltd (XTRANET) Share Price - Business Today</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Lancor Holdings Faces Resistance: Stock Declines 2.62% Amid Sector Volatility - Elliott Wave Entry - vinanet.vn</t>
+          <t>XTRANET Technologies Share Price Today after 9.86% gain - Univest</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>LANCOR HOLDINGS LIMITED Share Price - Upstox</t>
+          <t>1,970,100 Equity Shares of Xtranet Technologies Limited are subject to a Lock-Up Agreement Ending on 26-AUG-2026. - marketscreener.com</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 20:18:15 IST</t>
+          <t>2026-09-07 12:56:35 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -817,68 +821,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>SVGLOBAL.NS</t>
+          <t>DBEIL.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>S V Global Mill Limited</t>
+          <t>Deepak Builders &amp; Engineers India Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>162</v>
+        <v>6.610000133514404</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>172.8099975585938</v>
+        <v>7.710000038146973</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>157.1499938964844</v>
+        <v>6.610000133514404</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>163.6199951171875</v>
+        <v>7.440000057220459</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>144.0099945068359</v>
+        <v>6.429999828338623</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>163.6199951171875</v>
+        <v>7.440000057220459</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>286297</v>
+        <v>2025752</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>13.62</v>
+        <v>15.71</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>S V Global Mill Ltd (SVGLOBAL) Profile, Company FAQs &amp; Facts, Industry, Sector, Employee Strength - Stocktwits</t>
+          <t>Deepak Builders &amp; Engineers India Limited's (NSE:DBEIL) Stock Has Shown Weakness Lately But Financial Prospects Look Decent: Is The Market Wrong? - simplywall.st</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>SV Global Mill Ltd. Share Price Rise Streak: Price Action - Univest</t>
+          <t>Deepak Builders &amp; Engineers India (DBEIL.NS) Slides 4.93% – Key Support at ₹7.69 in Focus - PCR Spike - vinanet.vn</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>SV Global Mill Share Price Today: Stock Drops to Rs 124.30 - Univest</t>
+          <t>Deepak Builders Dispatches Postal Ballot Notice for 1:10 Stock Split Approval - scanx.trade</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>SV Global Mill Share Price gains 19.99% amid market focus - Univest</t>
+          <t>DEEPAK BUILDERS &amp; ENG I L Share Price - Upstox</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>SV Global Mill Share Price today: price rise and valuation - Univest</t>
+          <t>Deepak Builders &amp; Engineers India (DBEIL.NS) Slides 4.93% – Key Support at ₹7.69 in Focus - PCR Spike - vinanet.vn</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 20:18:15 IST</t>
+          <t>2026-09-07 12:56:35 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -886,56 +890,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>NAGREEKEXP.NS</t>
+          <t>GNRL.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Nagreeka Exports Limited</t>
+          <t>Gujarat Natural Resources Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>21.10000038146973</v>
+        <v>100</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>25</v>
+        <v>113.75</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>20.80999946594238</v>
+        <v>100</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>24.10000038146973</v>
+        <v>113.5899963378906</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>21.29999923706055</v>
+        <v>99.26999664306641</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>24.10000038146973</v>
+        <v>113.5899963378906</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>411783</v>
+        <v>2021677</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>13.15</v>
+        <v>14.43</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>CFEL Stock Price and Chart — NSE:CFEL - TradingView</t>
+          <t>GNRL Jun 2026 Earnings: EPS of ₹0.69 Reported with Nil Revenue; Stock Falls 6.87% - Earnings Whisper Number - siam.in</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>CFEL Stock Price and Chart — NSE:CFEL - TradingView</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr"/>
-      <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr"/>
+          <t>Gujarat (GNRL.NS) Outlook: Finishes 0.29% Lower at ₹101.60 on the Day; Key Range: Price Remains Between ₹96.52 Support and ₹106.68 Resistance in the Latest Session - High Conviction Picks - siam.in</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>Gujarat Natural Resources Share Price Rises 8.06% Today - Univest</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>Gujarat (GNRL.NS) Outlook: Finishes 0.29% Lower at ₹101.60 on the Day; Key Range: Price Remains Between ₹96.52 Support and ₹106.68 Resistance in the Latest Session - High Conviction Picks - siam.in</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>GNRL.NS Jun 2026 Earnings: EPS at ₹0.69 Despite Nil Revenue; Shares Slip 2.72% - Analyst Coverage Count - siam.in</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 20:18:15 IST</t>
+          <t>2026-09-07 12:56:35 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -952,28 +968,28 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>10.60000038146973</v>
+        <v>12.28999996185303</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>12.17000007629395</v>
+        <v>13.68000030517578</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>10.51000022888184</v>
+        <v>12.21000003814697</v>
       </c>
       <c r="H8" s="2" t="n">
+        <v>13.52000045776367</v>
+      </c>
+      <c r="I8" s="2" t="n">
         <v>11.85999965667725</v>
       </c>
-      <c r="I8" s="2" t="n">
-        <v>10.52000045776367</v>
-      </c>
       <c r="J8" s="2" t="n">
-        <v>11.85999965667725</v>
+        <v>13.52000045776367</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>1088882385</v>
+        <v>1551586213</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>12.74</v>
+        <v>14</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
@@ -982,17 +998,29 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>PC Jewellers Share Price - Live NSE: PCJEWELLER Stock Price &amp; Chart - Upstox</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr"/>
-      <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr"/>
+          <t>PC Jeweller Stock Update: Shares Jump 11% on Debt Repayment Progress - LatestLY</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>Pc Jeweller Stock Price Forecast. Should You Buy PCJEWELLER.NS? - StockInvest.us</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>PC Jeweller (PCJEWELLER) Share Price Falls 5.09% Today; Stock Analysis and Valuation Check - Univest</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>Most Active Equities, August 11, 2026, 3:30 PM IST - HDFC Sky</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 20:18:15 IST</t>
+          <t>2026-09-07 12:56:35 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1000,68 +1028,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>BIRLAPREC.NS</t>
+          <t>CENTUM.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Birla Precision Technologies Limited</t>
+          <t>Centum Electronics Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>53.25</v>
+        <v>3778.199951171875</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>59.79000091552734</v>
+        <v>4341</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>52.72999954223633</v>
+        <v>3778.199951171875</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>57.91999816894531</v>
+        <v>4253.2998046875</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>51.66999816894531</v>
+        <v>3767.300048828125</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>57.91999816894531</v>
+        <v>4253.2998046875</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>2568069</v>
+        <v>249894</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>12.1</v>
+        <v>12.9</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Birla Precision Technologies (BIRLAPREC.NS): Stock Eases Marginally, Nears Key Support Level - Symmetrical Triangle - vinanet.vn</t>
+          <t>Centum Electronics Share Price Today Near One-Year High - Univest</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Birla Precision Technologies Mar 2026 Earnings: Steady EPS Delivery Amid Modest Revenue Performance - Tangible Book Value - vinanet.vn</t>
+          <t>Centum Electronics Share Price Today Near One-Year High - Univest</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>BIRLAPREC.NS Mar 2026 Earnings: Marginal EPS of ₹0.39 on Modest Revenue of ₹63.91 crore; Stock Slides 0.71% - ROA Comparison - vinanet.vn</t>
+          <t>Centum Electronics Ltd. Stock News - Value Research</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Birla Precision Technologies Mar 2026 Earnings: Steady EPS Delivery Amid Modest Revenue Performance - Tangible Book Value - vinanet.vn</t>
+          <t>Centum Electronics to Host Virtual Analyst and Investor Meet on September 9 - theglobeandmail.com</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>Birla Precision Technologies Mar 2026 Earnings: Modest Profitability Amidst Stable Revenue - Revenue Warning Signal - vinanet.vn</t>
+          <t>Centum Electronics Ltd. Share Price Today: key stock move - Univest</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 20:18:15 IST</t>
+          <t>2026-09-07 12:56:35 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1069,60 +1097,64 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>MARALOVER.NS</t>
+          <t>THEMISMED.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Maral Overseas Limited</t>
+          <t>Themis Medicare Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>55</v>
+        <v>121.379997253418</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>65.69000244140625</v>
+        <v>136.25</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>55</v>
+        <v>119.1699981689453</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>61.83000183105469</v>
+        <v>135.8899993896484</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>55.2599983215332</v>
+        <v>120.4199981689453</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>61.83000183105469</v>
+        <v>135.8899993896484</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>313406</v>
+        <v>2052487</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>11.89</v>
+        <v>12.85</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Maral Overseas Limited Reports Zero Physical Share Transfer Requests Under SEBI Special Window - scanx.trade</t>
+          <t>Themis Medicare Holds Gains at ₹104.51: Key Levels to Monitor for THEMISMED.NS - Jurik MA - siam.in</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Maral Overseas Limited Reports Zero Physical Share Transfer Requests Under SEBI Special Window - scanx.trade</t>
+          <t>THEMISMED Share Price News: Price Action and Fundamentals - Univest</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Maral Overseas schedules 37th AGM on August 25 via VC/OAVM - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr"/>
+          <t>THEMISMED Share Price News: Price Action and Fundamentals - Univest</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>Themis Medicare Share Price Today: price rise and valuation - Univest</t>
+        </is>
+      </c>
       <c r="Q10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 20:18:15 IST</t>
+          <t>2026-09-07 12:56:35 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1130,60 +1162,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>CYBERMEDIA.NS</t>
+          <t>ARFIN.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Cyber Media (India) Limited</t>
+          <t>Arfin India Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>25.89999961853027</v>
+        <v>88.69999694824219</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>28.45000076293945</v>
+        <v>97.44000244140625</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>22.20000076293945</v>
+        <v>87.72000122070312</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>26.39999961853027</v>
+        <v>97.33000183105469</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>23.8799991607666</v>
+        <v>87.23999786376953</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>26.39999961853027</v>
+        <v>97.33000183105469</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>2156723</v>
+        <v>2916534</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>10.55</v>
+        <v>11.57</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Cyber Media (NSE: CYBERMEDIA) Price Analysis - Kalkine India</t>
+          <t>Arfin India sets September 19 date for 34th AGM and e-voting - scanx.trade</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Cyber Media (NSE: CYBERMEDIA) Price Analysis - Kalkine India</t>
+          <t>Mufin Green Finance: செப்டம்பர் 28-ல் முக்கிய பொதுக்குழு கூட்டம்! லாபம் **39%** உயர்வு - whalesbook.com</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Number of employees of Cyber Media (India) Limited Rights 2025-29.08.25 For Shares – BSE:CYBER_RE - TradingView</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr"/>
-      <c r="Q11" s="2" t="inlineStr"/>
+          <t>Arfin (ARFIN.NS) Q2 2026 Earnings: The Company Releases Its Current Earnings Data under the Current Snapshot; Trading Move: Shares Move 0.68% Up for the Current Session - Revenue Recognition Risk - siam.in</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>Arfin India Consolidated June 2026 Net Sales at Rs 212.77 crore, up 95.46% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>Arfin India consolidated net profit rises 276.85% in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 20:18:15 IST</t>
+          <t>2026-09-07 12:56:35 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1191,64 +1231,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>ZSARACOM.NS</t>
+          <t>UDAYJEW.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Saraswati Commercial India Limited</t>
+          <t>Uday Jewellery Industries Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>10096</v>
+        <v>168.3999938964844</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>11600</v>
+        <v>168.3999938964844</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>9808</v>
+        <v>148</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>11302</v>
+        <v>158</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>10227</v>
+        <v>143</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>11302</v>
+        <v>158</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>221</v>
+        <v>170308</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>10.51</v>
+        <v>10.49</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Saraswati Commercial Share Price Rise on NBFC Valuation - Univest</t>
+          <t>Technical Analysis of Uday Jewellery Industries Ltd. (NSE:UDAYJEW) - TradingView</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Saraswati Commercial Share Price Rise on NBFC Valuation - Univest</t>
+          <t>Uday Jewellery Industries Share Price Rises 8.82% Today - Univest</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Saraswati Commercial submits FY26 annual report to BSE - scanx.trade</t>
+          <t>Uday Jewellery Industries Share Price Rises 8.82% Today - Univest</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Saraswati Commercial Q1FY27 net profit surges 169% YoY to ₹635.6 million - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr"/>
+          <t>Uday Jewellery Industries Ltd. (UDAYJEW) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>Uday Jewellery Promoters Acquire 73.34 Lakh Shares Through Merger Scheme - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 20:18:15 IST</t>
+          <t>2026-09-07 12:56:35 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1256,68 +1300,56 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>MASTERTR.NS</t>
+          <t>CURAA.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Master Trust Limited</t>
+          <t>Cura Technologies Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>81.05000305175781</v>
+        <v>76</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>95.5</v>
+        <v>80</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>81.05000305175781</v>
+        <v>76</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>89.16000366210938</v>
+        <v>80</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>81.02999877929688</v>
+        <v>72.45999908447266</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>89.16000366210938</v>
+        <v>80</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>8359824</v>
+        <v>1681</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>10.03</v>
+        <v>10.41</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>It's Down 26% But Master Trust Limited (NSE:MASTERTR) Could Be Riskier Than It Looks - simplywall.st</t>
+          <t>D2C kitchenware startup Curaa raises Rs 40 crore led by 3one4 Capital - The Economic Times</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Master Trust Limited Q2 2026 Earnings: Revenue Declines Marginally, EPS Holds at ₹10.6 - Consensus Forecast Report - vinanet.vn</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>Master Trust Limited sees mild gains; support and resistance levels in focus - Price Surge Stocks - vinanet.vn</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>MASTERTR Stock Price and Chart — NSE:MASTERTR - TradingView</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>Master Trust Limited (MASTERTR.NS) – Steady Gains Above Support Zone - Fear Greed Extreme - vinanet.vn</t>
-        </is>
-      </c>
+          <t>D2C kitchenware startup Curaa raises Rs 40 crore led by 3one4 Capital - The Economic Times</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr"/>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 20:18:15 IST</t>
+          <t>2026-09-07 12:56:35 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1325,68 +1357,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>RHETAN.NS</t>
+          <t>STAR.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Rhetan TMT Limited</t>
+          <t>Strides Pharma Science Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>25.42000007629395</v>
+        <v>1058.699951171875</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>25.42000007629395</v>
+        <v>1171.300048828125</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>25.40999984741211</v>
+        <v>1045</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>25.42000007629395</v>
+        <v>1168.199951171875</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>23.11000061035156</v>
+        <v>1059.599975585938</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>25.42000007629395</v>
+        <v>1168.199951171875</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>5455318</v>
+        <v>1010895</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>10</v>
+        <v>10.25</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Rhetan TMT stock surges 10% upper circuit; AGM on Sep 16 to consider and approve company borrowing limit to Rs. 300 crore for Business expansion - ThePrint</t>
+          <t>Asia tech shares rally, others hesitant as oil rises - The Star</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Rhetan TMT Stock Hits Upper Circuit: Key Triggers &amp; Q1 Results - The Daily Jagran</t>
+          <t>Asia tech shares rally, others hesitant as oil rises - The Star</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Small-cap stock under 50 hits 10% upper circuit despite stock market crash - Livemint</t>
+          <t>Evan, formerly ENHYPEN’s Heeseung, reveals his cancer battle for the first time - t2ONLINE</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>130% Return In 3 Years: Rhetan TMT Stock Jumps Post Q1 Result | Key Things To Know - Goodreturns</t>
+          <t>5-Star Analyst Resets Intel Stock Price Target on Weaker PC Demand - TradingView</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>Rhetan TMT Ltd. Share Price Jumps to Fresh One-Year High - Univest</t>
+          <t>Forget Rolls-Royce shares: OXB is a rising FTSE 250 star tipped to gain 68% in the coming year! - The Twelfth Magpie</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 20:18:15 IST</t>
+          <t>2026-09-07 12:56:35 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1394,56 +1426,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>RAMBHAJO.NS</t>
+          <t>RADHIKAJWE.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Advit Jewels Limited</t>
+          <t>Radhika Jeweltech Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>249.8999938964844</v>
+        <v>84.62000274658203</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>268.6799926757812</v>
+        <v>93.76000213623047</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>247.0599975585938</v>
+        <v>84.61000061035156</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>268.6799926757812</v>
+        <v>91.65000152587891</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>244.2599945068359</v>
+        <v>83.16000366210938</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>268.6799926757812</v>
+        <v>91.65000152587891</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>1915247</v>
+        <v>16755953</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>10</v>
+        <v>10.21</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>ADVIT JEWELS Share Price update: fundamentals and peers - Univest</t>
+          <t>Here's Why Radhika Jeweltech (NSE:RADHIKAJWE) Has Caught The Eye Of Investors - simplywall.st</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>ADVIT JEWELS Share Price update: fundamentals and peers - Univest</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr"/>
-      <c r="P15" s="2" t="inlineStr"/>
-      <c r="Q15" s="2" t="inlineStr"/>
+          <t>Radhika Jeweltech (RADHIKAJWE.NS) Gains 5.15% as Bullish Momentum Builds - Virgin POC - siam.in</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>Radhika Jeweltech (RADHIKAJWE.NS) Gains 5.15% as Bullish Momentum Builds - Virgin POC - siam.in</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>Radhika Jeweltech Holds Steady Near Support; Resistance at ₹58.24 in Focus - Stock Analysis - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>RADHIKAJWE Stock Price and Chart — NSE:RADHIKAJWE - TradingView</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 20:18:15 IST</t>
+          <t>2026-09-07 12:56:35 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1451,68 +1495,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>UNITECH.NS</t>
+          <t>HIKAL.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Unitech Limited</t>
+          <t>Hikal Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>3.710000038146973</v>
+        <v>222.0099945068359</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>4.079999923706055</v>
+        <v>257</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>3.710000038146973</v>
+        <v>218.8200073242188</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>4.079999923706055</v>
+        <v>244.6799926757812</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>3.710000038146973</v>
+        <v>222.3000030517578</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>4.079999923706055</v>
+        <v>244.6799926757812</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>14406516</v>
+        <v>14712371</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>9.970000000000001</v>
+        <v>10.07</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Unitech Ltd Share Price Today: price action and valuation - Univest</t>
+          <t>Hikal FY26 net loss of ₹49 crore on exceptional items - scanx.trade</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Unitech Ltd Share Price Today: price action and valuation - Univest</t>
+          <t>Hikal FY26 net loss of ₹49 crore on exceptional items - scanx.trade</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>InvestingPro’s Fair Value warned of 54% drop in Unitech shares By Investing.com - Investing.com India</t>
+          <t>Hikal Ltd. Share Price Rise: Price Action and Fundamentals - Univest</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Unitech Group files FY26 BRSR; awards 10 Lot-5 tenders - scanx.trade</t>
+          <t>Don't Race Out To Buy Hikal Limited (NSE:HIKAL) Just Because It's Going Ex-Dividend - simplywall.st</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>Unitech appoints Giridhar Aramane as Chairman and Managing Director - scanx.trade</t>
+          <t>Hikal Ltd Shares Hit Intraday Low Amid Price Pressure on 4 Sep 2026 - MarketsMojo</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 20:18:15 IST</t>
+          <t>2026-09-07 12:56:35 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1520,68 +1564,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>AKI.NS</t>
+          <t>FCL.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>AKI India Limited</t>
+          <t>Fineotex Chemical Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>7.21999979019165</v>
+        <v>52.25</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>7.21999979019165</v>
+        <v>56.65999984741211</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>7.21999979019165</v>
+        <v>52.18999862670898</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>7.21999979019165</v>
+        <v>56.65999984741211</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>6.570000171661377</v>
+        <v>51.5099983215332</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>7.21999979019165</v>
+        <v>56.65999984741211</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>258805</v>
+        <v>36901422</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>9.890000000000001</v>
+        <v>10</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Penny stock under 10 rupees: Upper circuit - Leather share jumps 74% in 4 sessions | Back-to-back surge for third day - TradingView</t>
+          <t>Why FINEOS Corporation (ASX: FCL) Could Be a Stock to Watch Into the Final Months of 2026 - Kalkine</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Penny stock under 10 rupees: Upper circuit - Leather share jumps 74% in 4 sessions | Back-to-back surge for third day - TradingView</t>
+          <t>Why FINEOS Corporation (ASX: FCL) Could Be a Stock to Watch Into the Final Months of 2026 - Kalkine</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>AKI India Ltd Upgraded to Sell on Technical Improvements Despite Lingering Financial Challenges - MarketsMojo</t>
+          <t>Average basic shares outstanding of FCL-X FIRE SAFETY INC – TSXV:FCLX - TradingView</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>AKI India Ltd leads gainers in 'B' group - Business Standard</t>
+          <t>Full Circle Lithium Rebrands as FCL-X Fire &amp; Safety Inc. and Provides Corporate Update - Stock Titan</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>Volume shocker stocks: Why share price of EMS, Expleo Solutions, Windlas Biotech, AKI India, Heritage Foods are up today - Livemint</t>
+          <t>Fineos (ASX:FCL) Shares Edge Lower Amid Weaker Technology Sector Sentiment - Kalkine</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 20:18:15 IST</t>
+          <t>2026-09-07 12:56:35 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1589,68 +1633,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>KSR.NS</t>
+          <t>BODALCHEM.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>KSR Footwear Limited</t>
+          <t>Bodal Chemicals Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>32.5</v>
+        <v>168</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>34.68999862670898</v>
+        <v>171.1799926757812</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>31.89999961853027</v>
+        <v>162.8000030517578</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>34.61000061035156</v>
+        <v>171.1799926757812</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>31.54000091552734</v>
+        <v>155.6199951171875</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>34.61000061035156</v>
+        <v>171.1799926757812</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>388523</v>
+        <v>4822306</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>9.73</v>
+        <v>10</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>KSR Footwear Share Price: Alpa Wealth Buys 1.33% Stake - Univest</t>
+          <t>With EPS Growth And More, Bodal Chemicals (NSE:BODALCHEM) Makes An Interesting Case - simplywall.st</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Mark Pope shares not-so-subtle response to losing Mark Mitchell - On3</t>
+          <t>Bodal Chemicals Sets Virtual AGM to Approve FY26 Accounts and Board Changes - TipRanks</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>KSR Footwear AGM passes FY26 results; promoters vote 100% in favour - scanx.trade</t>
+          <t>Bodal Chemicals Share Price news with valuation context - Univest</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Mark Pope shares not-so-subtle response to losing Mark Mitchell - On3</t>
+          <t>Bodal Chemicals Ltd. (BODALCHEM) Share Price Rises 9.21% Today; Key Levels, Valuation and Peer View - Univest</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>Kalen "Big K" Edwards Shares Words of Wisdom from the Changing Kentucky Trenches - On3</t>
+          <t>Bodal Chemicals Sets Virtual AGM to Approve FY26 Accounts and Board Changes - TipRanks</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 20:18:15 IST</t>
+          <t>2026-09-07 12:56:35 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1658,56 +1702,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>JISLJALEQS.NS</t>
+          <t>TBZ.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Jain Irrigation Systems Limited</t>
+          <t>Tribhovandas Bhimji Zaveri Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>28.29000091552734</v>
+        <v>528.9000244140625</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>32.38999938964844</v>
+        <v>528.9000244140625</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>28.25</v>
+        <v>528.9000244140625</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>30.8700008392334</v>
+        <v>528.9000244140625</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>28.15999984741211</v>
+        <v>480.8500061035156</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>30.8700008392334</v>
+        <v>528.9000244140625</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>29542567</v>
+        <v>281857</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>9.619999999999999</v>
+        <v>9.99</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Jain Irrigation (JISLDVREQS.NS) Slips Marginally to ₹21.0: Key Support and Resistance Levels in Focus - Volume Climax - siam.in</t>
+          <t>Jewellery Stocks In Focus: PC Jeweller Surges 15%, TBZ Hits 10% Upper Circuit; Shankesh Gains 8% — Know Why - NDTV Profit</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Jain Irrigation (JISLDVREQS.NS) Slips Marginally to ₹21.0: Key Support and Resistance Levels in Focus - Volume Climax - siam.in</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr"/>
-      <c r="P19" s="2" t="inlineStr"/>
-      <c r="Q19" s="2" t="inlineStr"/>
+          <t>Jewellery Stocks In Focus: PC Jeweller Surges 15%, TBZ Hits 10% Upper Circuit; Shankesh Gains 8% — Know Why - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>Multibagger stock: Why TBZ shares are locked at 20% upper circuit - Business Standard</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>Tribhovandas Bhimji Zaveri is now GRT's jewel - Finshots</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>TBZ shares zoom 20%, hit upper circuit after GRT Jewellers open offer - The Economic Times</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 20:18:15 IST</t>
+          <t>2026-09-07 12:56:35 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1715,56 +1771,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>CURAA.NS</t>
+          <t>DHATRE.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Cura Technologies Limited</t>
+          <t>Dhatre Udyog Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>78.5</v>
+        <v>4.349999904632568</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>78.5</v>
+        <v>5.170000076293945</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>60</v>
+        <v>4.210000038146973</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>72.45999908447266</v>
+        <v>4.75</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>66.19999694824219</v>
+        <v>4.329999923706055</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>72.45999908447266</v>
+        <v>4.75</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>2020</v>
+        <v>105820</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>9.460000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>D2C kitchenware startup Curaa raises Rs 40 crore led by 3one4 Capital - economictimes.com</t>
+          <t>DHATRE Stock Price and Chart — NSE:DHATRE - TradingView</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>D2C kitchenware startup Curaa raises Rs 40 crore led by 3one4 Capital - economictimes.com</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr"/>
-      <c r="P20" s="2" t="inlineStr"/>
-      <c r="Q20" s="2" t="inlineStr"/>
+          <t>Dhatre Udyog corrects 31st AGM time to 11 am on Sept 26 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>Dhatre Udyog Q1FY26 net profit hits ₹573 lakh on OCI surge - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>Dhatre Udyog Ltd. (DHATRE) Profile, Company FAQs &amp; Facts, Industry, Sector, Employee Strength - Stocktwits</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>Dhatre Udyog Q1 FY27 Results: Revenue and PAT Highlights - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 20:18:15 IST</t>
+          <t>2026-09-07 12:56:35 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1772,61 +1840,61 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>LALITHAA.NS</t>
+          <t>MMP.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Lalithaa Jewellery Mart Limited</t>
+          <t>MMP Industries Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>283</v>
+        <v>405.8999938964844</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>308.2999877929688</v>
+        <v>455.6000061035156</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>280.6000061035156</v>
+        <v>404.5</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>306.7000122070312</v>
+        <v>443.1499938964844</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>280.2999877929688</v>
+        <v>404.1499938964844</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>306.7000122070312</v>
+        <v>443.1499938964844</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>23778911</v>
+        <v>301815</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>9.42</v>
+        <v>9.65</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Shanti Gold International Buys 1.44 Lakh Shares In Lalithaa Jewellery Mart For ₹3.88 Crore - Sahi</t>
+          <t>MMP Industries confirms no encumbrance on promoter shares in FY26 - scanx.trade</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Lalithaa Jewellery Mart launches 65th showroom in Chennai - scanx.trade</t>
+          <t>MMP Industries confirms no encumbrance on promoter shares in FY26 - scanx.trade</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Shanti Gold buys ₹3.88 crore stake in retail client Lalithaa Jewellery - Dealroom</t>
+          <t>MMP Industries Drops 2.6% to ₹383.25; Support at ₹364.09 Holds Key - Option Strike Build - siam.in</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Shanti Gold buys 42,130 more Lalithaa Jewellery shares for ₹1.11 crore - scanx.trade</t>
+          <t>MMP Industries Share Price Rises 8.51%: Price, Valuation - Univest</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>Lalithaa Jewellery shares make strong market debut at 32% premium; should you buy, sell or hold? - Moneycontrol.com</t>
+          <t>MMP Industries Consolidated June 2026 Net Sales at Rs 232.60 crore, up 26.9% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
     </row>
@@ -1847,14 +1915,14 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
@@ -1953,7 +2021,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 20:18:15 IST</t>
+          <t>2026-09-07 12:56:35 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -1961,56 +2029,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>DYCL.NS</t>
+          <t>HEG.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Dynamic Cables Limited</t>
+          <t>HEG Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>541.9000244140625</v>
+        <v>260</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>546.7999877929688</v>
+        <v>273</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>484</v>
+        <v>250</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>487.8999938964844</v>
+        <v>265.5499877929688</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>544.2999877929688</v>
+        <v>728.25</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>487.8999938964844</v>
+        <v>265.5499877929688</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>1788207</v>
+        <v>2092808</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-10.36</v>
+        <v>-63.54</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Dynamic Cables (NSE: DYCL) Stock Analysis - Kalkine India</t>
+          <t>HEG Demerger Record Date Today. What It Means For Shareholders? All You Need To Know - NDTV Profit</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Dynamic Cables (NSE: DYCL) Stock Analysis - Kalkine India</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
+          <t>Did HEG shares really crash 64% in one day? Here’s how the demerger math works - The Economic Times</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Did HEG shares really crash 64% in one day? Here’s how the demerger math works - The Economic Times</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>HEG demerger news: Record date today | Ratio, latest updates, other details in 5 points - Livemint</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>HEG Advanced Material shares see discovered price of ₹260 on the bourses; Here's what you need to know - CNBC TV18</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 20:18:15 IST</t>
+          <t>2026-09-07 12:56:35 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -2018,56 +2098,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>JAYNECOIND.NS</t>
+          <t>ICDSLTD.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Jayaswal Neco Industries Limited</t>
+          <t>ICDS Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>92</v>
+        <v>71.55999755859375</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>94.37000274658203</v>
+        <v>77.69000244140625</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>85.22000122070312</v>
+        <v>64.30999755859375</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>89.04000091552734</v>
+        <v>65.18000030517578</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>98.68000030517578</v>
+        <v>71.44999694824219</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>89.04000091552734</v>
+        <v>65.18000030517578</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>49816021</v>
+        <v>94965</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-9.77</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>With EPS Growth And More, Jayaswal Neco Industries (NSE:JAYNECOIND) Makes An Interesting Case - simplywall.st</t>
+          <t>ICDS Limited (ICDSLTD.NS) Surges Over 7.8%: Strong Momentum or Resistance Ahead? - Bear Pennant - vinanet.vn</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>With EPS Growth And More, Jayaswal Neco Industries (NSE:JAYNECOIND) Makes An Interesting Case - simplywall.st</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
+          <t>ICDS Limited (ICDSLTD.NS): Mild Decline Amid Consolidation, Key Levels Hold - Value ETF - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>ICDS Ltd Sees Decline: Stock Slips 3.85% Amidst Key Support Test - Day Trade Opportunities - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>ICDS Share Price - Live NSE: ICDSLTD Stock Price &amp; Chart - Upstox</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>ICDSLTD Stock Price and Chart — NSE:ICDSLTD - TradingView</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 20:18:15 IST</t>
+          <t>2026-09-07 12:56:35 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -2075,64 +2167,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>UGARSUGAR.NS</t>
+          <t>SVGLOBAL.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>The Ugar Sugar Works Limited</t>
+          <t>S V Global Mill Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>58.40000152587891</v>
+        <v>160</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>58.5</v>
+        <v>160</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>53.0099983215332</v>
+        <v>152</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>53.34999847412109</v>
+        <v>152</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>58.56000137329102</v>
+        <v>163.6199951171875</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>53.34999847412109</v>
+        <v>152</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1343466</v>
+        <v>15396</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-8.9</v>
+        <v>-7.1</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Ugar Sugar Works (NSE: UGARSUGAR) Analysis - Kalkine India</t>
+          <t>S V Global Mill Ltd (SVGLOBAL) Profile, Company FAQs &amp; Facts, Industry, Sector, Employee Strength - Stocktwits</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Ugar Sugar Works (NSE: UGARSUGAR) Analysis - Kalkine India</t>
+          <t>SV Global Mill Ltd. Share Price Rise Streak: Price Action - Univest</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>The Ugar Sugar Works Share Price Today: Fall and Analysis - Univest</t>
+          <t>SV Global Mill Share Price gains 19.99% amid market focus - Univest</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Ugar Sugar Works director Hari Athawale retires, Prafulla Shirgaokar resigns from board - ChiniMandi</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr"/>
+          <t>SV Global Mill Share Price today: price rise and valuation - Univest</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>SV Global Mill Ltd. Share Price Fall and Stock Analysis - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 20:18:15 IST</t>
+          <t>2026-09-07 12:56:35 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -2140,68 +2236,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>JAYKAY.NS</t>
+          <t>NAGREEKEXP.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Jaykay Enterprises Limited</t>
+          <t>Nagreeka Exports Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>165.3699951171875</v>
+        <v>22.67000007629395</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>167.8800048828125</v>
+        <v>23.8700008392334</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>151.7599945068359</v>
+        <v>22.20000076293945</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>153.6900024414062</v>
+        <v>22.5</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>166.4600067138672</v>
+        <v>24.10000038146973</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>153.6900024414062</v>
+        <v>22.5</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>470343</v>
+        <v>46834</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-7.67</v>
+        <v>-6.64</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Jaykay Enterprises board meets May 27 to approve FY26 results - scanx.trade</t>
+          <t>Nagreeka Exports Limited (NSE: NAGREEKEXP) Falls 5.23% as Stock Movement Draws Market Attention - Kalkine India</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Federal-Mogul Goetze (India) Ltd leads losers in 'B' group - Business Standard</t>
+          <t>Nagreeka Exports Limited (NSE: NAGREEKEXP) Falls 5.23% as Stock Movement Draws Market Attention - Kalkine India</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Jaykay Enterprises files Letter of Offer for ₹154.28 crore rights issue - scanx.trade</t>
+          <t>Nagreeka Exports Holds Near ₹21.3: Consolidation Persists for NAGREEKEXP on NSE - Rounding Top - siam.in</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Jaykay Enterprises schedules 80th AGM for Sep 29 via video conferencing - scanx.trade</t>
+          <t>CFEL Stock Price and Chart — NSE:CFEL - TradingView</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>Jaykay Enterprises Ltd. Key Financial Ratios – Valuation, Profitability &amp; More - Value Research</t>
+          <t>Nagreeka Exports files revised FY26 annual report to fix clerical error - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 20:18:15 IST</t>
+          <t>2026-09-07 12:56:35 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2209,68 +2305,56 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>HIKAL.NS</t>
+          <t>RPEL.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Hikal Limited</t>
+          <t>Raghav Productivity Enhancers Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>234</v>
+        <v>1819.099975585938</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>236.7400054931641</v>
+        <v>1821.5</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>220.1000061035156</v>
+        <v>1635.599975585938</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>222.3000030517578</v>
+        <v>1687.199951171875</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>240.3600006103516</v>
+        <v>1807.199951171875</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>222.3000030517578</v>
+        <v>1687.199951171875</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>5351852</v>
+        <v>227646</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-7.51</v>
+        <v>-6.64</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Hikal Ltd Shares Hit Intraday Low Amid Price Pressure on 4 Sep 2026 - MarketsMojo</t>
+          <t>Raghav Productivity Enhancers Ltd. Share Price Near High - Univest</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Hikal Ltd Shares Hit Intraday Low Amid Price Pressure on 4 Sep 2026 - MarketsMojo</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>Hikal Ltd. Share Price Rise: Price Action and Fundamentals - Univest</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>Don't Race Out To Buy Hikal Limited (NSE:HIKAL) Just Because It's Going Ex-Dividend - simplywall.st</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>Hikal files FY26 sustainability report with ESG metrics - scanx.trade</t>
-        </is>
-      </c>
+          <t>Raghav Productivity Enhancers Ltd. Share Price Near High - Univest</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 20:18:15 IST</t>
+          <t>2026-09-07 12:56:35 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2278,68 +2362,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>AUTOIND.NS</t>
+          <t>SAICAPI.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Autoline Industries Limited</t>
+          <t>Sai Capital Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>94</v>
+        <v>158.3399963378906</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>95.90000152587891</v>
+        <v>158.3399963378906</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>85.20999908447266</v>
+        <v>147.9299926757812</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>86.44999694824219</v>
+        <v>147.9299926757812</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>92.75</v>
+        <v>157.5599975585938</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>86.44999694824219</v>
+        <v>147.9299926757812</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>591037</v>
+        <v>91</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-6.79</v>
+        <v>-6.11</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Autoline Industries Share Price Rise; Valuation in Focus - Univest</t>
+          <t>SAICAPI Stock Price and Chart — NSE:SAICAPI - TradingView</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Autoline Industries AUTOIND 30th AGM Notice September 2026 - Kalkine India</t>
+          <t>SAICAPI Stock Price and Chart — NSE:SAICAPI - TradingView</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Autoline Industries Wins ₹100 Crore Tata Motors Order - HDFC Sky</t>
+          <t>Sai Capital Ltd. (SAICAPI) News, Articles, Events &amp; Latest Updates - Stocktwits</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>ISTLTD Stock Price and Chart — NSE:ISTLTD - TradingView</t>
+          <t>Sai Capital Q1 Results: Standalone and consolidated financials approved - scanx.trade</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>Autoline Industries Ltd. Share Price: Near 52-Week High - Univest</t>
+          <t>Sai Capital Ltd. (SAICAPI) Share Price Today, Quote, Latest Discussions, Interactive Chart and News - Stocktwits</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 20:18:15 IST</t>
+          <t>2026-09-07 12:56:35 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2347,68 +2431,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>RRKABEL.NS</t>
+          <t>TCC.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>R R Kabel Limited</t>
+          <t>TCC Concept Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2550</v>
+        <v>44</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>2609</v>
+        <v>44.47000122070312</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>2374.39990234375</v>
+        <v>40.70999908447266</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>2454.10009765625</v>
+        <v>41.40999984741211</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2617.699951171875</v>
+        <v>44.09999847412109</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>2454.10009765625</v>
+        <v>41.40999984741211</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>2596647</v>
+        <v>406600</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-6.25</v>
+        <v>-6.1</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>RR Kabel, KEI Industries, Polycab India shares tumble; JM Financial downgrades stocks, revises targets - businesstoday.in</t>
+          <t>TCC CONCPAR: Shareholders Board Members Managers and Company Profile | INE887D01016 - marketscreener.com</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>RR Kabel, KEI Industries, Polycab India shares tumble; JM Financial downgrades stocks, revises targets - businesstoday.in</t>
+          <t>TCC CONCPAR: Shareholders Board Members Managers and Company Profile | INE887D01016 - marketscreener.com</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>RR Kabel Share Price Near 52-Week High Analysis - Univest</t>
+          <t>TCC Concept Stock Falls: Key Levels to Watch - Kalkine India</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>RR Kabel Share Price at fresh 52-week high: analysis - Univest</t>
+          <t>TCC CONCEPT Consolidated June 2026 Net Sales at Rs 128.28 crore, up 480.19% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>RR Kabel Share Price Falls 2.72%: Price, Valuation View - Univest</t>
+          <t>TCC Concept fixes September 4 record date for 1:5 share split - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 20:18:15 IST</t>
+          <t>2026-09-07 12:56:35 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2416,64 +2500,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>LANDSMILL.NS</t>
+          <t>PVRINOX.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Landsmill Green Limited</t>
+          <t>PVR INOX Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.6700000166893005</v>
+        <v>1199.099975585938</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.7099999785423279</v>
+        <v>1199.099975585938</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.6299999952316284</v>
+        <v>1125.699951171875</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.6299999952316284</v>
+        <v>1162.300048828125</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0.6700000166893005</v>
+        <v>1227.199951171875</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.6299999952316284</v>
+        <v>1162.300048828125</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>10120631</v>
+        <v>2523836</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-5.97</v>
+        <v>-5.29</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Landsmill Green - 14 penny stocks plunge up to 85% in 6 months. Are you holding any? - economictimes.com</t>
+          <t>PVR INOX Limited (NSE: PVRINOX) Falls 6.79% as Stock Movement Draws Market Attention - Kalkine India</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Landsmill Green board to delete FMCG object, close subsidiary on Sep 4 - scanx.trade</t>
+          <t>PVR INOX Limited (NSE: PVRINOX) Falls 6.79% as Stock Movement Draws Market Attention - Kalkine India</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Landsmill Green Q1 Results: Net profit up 987% YoY to ₹85.4 lakh - scanx.trade</t>
+          <t>PVR Inox Share Price - Live NSE: PVRINOX Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Landsmill Green board to delete FMCG object, close subsidiary on Sep 4 - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr"/>
+          <t>PVRINOX Outlook for the Week - equitypandit.com</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>PVR INOX Limited announces an Equity Buyback for 2,068,965 shares, representing 2.11% for INR 3,000 million. - marketscreener.com</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 20:18:15 IST</t>
+          <t>2026-09-07 12:56:35 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2481,68 +2569,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>POLYCAB.NS</t>
+          <t>ANNU.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Polycab India Limited</t>
+          <t>Annu Projects Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>8500</v>
+        <v>64.81999969482422</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>8500</v>
+        <v>64.81999969482422</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>8250</v>
+        <v>64.81999969482422</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>8300</v>
+        <v>64.81999969482422</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>8807.5</v>
+        <v>68.23000335693359</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>8300</v>
+        <v>64.81999969482422</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>1559219</v>
+        <v>102987</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-5.76</v>
+        <v>-5</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Polycab, KEI Industries shares crash up to 9% after UltraTech Cement enters wires &amp; cables business. What - economictimes.com</t>
+          <t>Weak market debut: Annu Projects shares list at over 27% discount to its IPO price - Moneycontrol.com</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Polycab falls 7% on UltraTech's foray into wires and cables even as JPMorgan allays fears; should you buy,... - Moneycontrol.com</t>
+          <t>Annu Projects Ltd. Share Price Today - Annu Projects Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Polycab, KEI Industries Shares up to 8% as Ultratech Enters Wires &amp; Cables Business with Ultravolt - India Infoline</t>
+          <t>Annu Projects Shares List at 27% Discount on NSE - Groww</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Copper Shock Hits Cables Stocks: Polycab, Finolex, RR Kabel Slide Up To 6% After Price Hikes - NDTV Profit</t>
+          <t>Total common shares outstanding of Annu Projects Limited – NSE:ANNU - TradingView</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>Polycab valuations correcting to these levels will be a buying opportunity, JPMorgan says - CNBC TV18</t>
+          <t>Annu Projects Ltd. Share Price Today - Annu Projects Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 20:18:15 IST</t>
+          <t>2026-09-07 12:56:35 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2550,68 +2638,64 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>SKYWAYS.NS</t>
+          <t>NIRAJISPAT.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Skyways Air Services Limited</t>
+          <t>Niraj Ispat Industries Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>131.5</v>
+        <v>368.4500122070312</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>133.6499938964844</v>
+        <v>368.4500122070312</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>120.0999984741211</v>
+        <v>368.4500122070312</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>122.7200012207031</v>
+        <v>368.4500122070312</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>130.0599975585938</v>
+        <v>387.7999877929688</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>122.7200012207031</v>
+        <v>368.4500122070312</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>8334295</v>
+        <v>70</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-5.64</v>
+        <v>-4.99</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Skyways Air Services shares list at 9% discount to IPO price on NSE, BSE - Moneycontrol.com</t>
+          <t>Niraj (NIRAJISPAT.NS) Price Update: Ends Down by 3.00% at ₹205.65 for the Current Session - siam.in</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Skyways Air Services Shares List 10% Below IPO Price; Defies Grey Market Expectations - BW Businessworld</t>
+          <t>Precision Wires and 11 Other Stocks That Hit the 20% Upper Circuit Today; Are You Holding Any? - Trade Brains</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Skyways Air Services shares defy GMP expectations, list at 10% discount - Business Standard</t>
+          <t>Niraj (NIRAJISPAT.NS) Session: Finishes Nearly Flat at ₹216.00; Levels: the ₹205.20 to ₹226.80 Range Remains in Focus in the Available Record - PSAR Stop - siam.in</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Skyways Air Services tumble over 10% on market debut - BusinessLine</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>Skyways Air Services listing: Shares list at 10.1% discount compare to IPO price on NSE - Upstox</t>
-        </is>
-      </c>
+          <t>Precision Wires and 11 Other Stocks That Hit the 20% Upper Circuit Today; Are You Holding Any? - Trade Brains</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 20:18:15 IST</t>
+          <t>2026-09-07 12:56:35 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2619,68 +2703,56 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>ANTELOPUS.NS</t>
+          <t>BIRLACABLE.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Antelopus Selan Energy Limited</t>
+          <t>Birla Cable Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1001</v>
+        <v>395</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1028.800048828125</v>
+        <v>395</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>925.2000122070312</v>
+        <v>357.75</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>957.1500244140625</v>
+        <v>357.75</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1013.299987792969</v>
+        <v>376.5499877929688</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>957.1500244140625</v>
+        <v>357.75</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>4816041</v>
+        <v>763650</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-5.54</v>
+        <v>-4.99</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Antelopus Selan Energy shares rally 20% to 52-week high; what investors need to know - Upstox</t>
+          <t>Birla Cable Limited Files Quarterly Compliance Certificate for Q4 FY26 Under SEBI Regulations - scanx.trade</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Why did Antelopus Selan Energy's shares jump over 32% in 4 days? | The stock has rallied 636% in 5 years | Inshorts - Inshorts</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>Antelopus Selan Energy share price up over 32% up in 3 days - What's behind continuous stock jump? Details here - Livemint</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>Multibagger Smallcap Stock Jumps Over 15% In Trade. Here's Why - NDTV Profit</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>Antelopus Selan Energy promoter declares no encumbrance in FY26 - scanx.trade</t>
-        </is>
-      </c>
+          <t>Birla Cable Limited Files Quarterly Compliance Certificate for Q4 FY26 Under SEBI Regulations - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 20:18:15 IST</t>
+          <t>2026-09-07 12:56:35 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2688,68 +2760,64 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>TCC.NS</t>
+          <t>CALSOFT.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>TCC Concept Limited</t>
+          <t>California Software Company Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>47.33000183105469</v>
+        <v>38.93999862670898</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>49.22000122070312</v>
+        <v>38.93999862670898</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>43.79999923706055</v>
+        <v>38.93999862670898</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>44.09999847412109</v>
+        <v>38.93999862670898</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>46.62599945068359</v>
+        <v>40.97999954223633</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>44.09999847412109</v>
+        <v>38.93999862670898</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>578461</v>
+        <v>62294</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-5.42</v>
+        <v>-4.98</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>TCC Concept signs MOU for 60 MW data centre campus in Pune - scanx.trade</t>
+          <t>CALSOFT Stock Price and Chart — NSE:CALSOFT - TradingView</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Taiwan Cement stock falls as volume and margins draw focus - ad-hoc-news.de</t>
+          <t>California Software profit rises to ₹411.64 lakh in Q1FY27 - scanx.trade</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Volume Gainers as of 12:25 PM IST, Mumbai, August 26: Indo Thai Securities, TCC Concept Lead Trading Surge - HDFC Sky</t>
+          <t>California Software profit rises to ₹411.64 lakh in Q1FY27 - scanx.trade</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>TCC CONCEPT Consolidated June 2026 Net Sales at Rs 128.28 crore, up 480.19% Y-o-Y - Moneycontrol.com</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>TCC Concept fixes September 4 record date for 1:5 share split - scanx.trade</t>
-        </is>
-      </c>
+          <t>GRMN Q2 2026 Earnings: EPS Blowout Beats Estimates by 22.72%, Yet Shares Slip 1.61% - Pre-Earnings Setup - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 20:18:15 IST</t>
+          <t>2026-09-07 12:56:35 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2757,64 +2825,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>MAKERSL.NS</t>
+          <t>SUPTANERY.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Makers Laboratories Limited</t>
+          <t>Super Tannery Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>206.8500061035156</v>
+        <v>12.59000015258789</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>206.8500061035156</v>
+        <v>12.59000015258789</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>188.3999938964844</v>
+        <v>12.59000015258789</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>189.8999938964844</v>
+        <v>12.59000015258789</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>200.7700042724609</v>
+        <v>13.25</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>189.8999938964844</v>
+        <v>12.59000015258789</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>6513</v>
+        <v>38042</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-5.41</v>
+        <v>-4.98</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Makers Laboratories Share Price rise: fundamentals and peers - Univest</t>
+          <t>SUPTANERY Stock Price and Chart — NSE:SUPTANERY - TradingView</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Makers Laboratories Share Price rise: fundamentals and peers - Univest</t>
+          <t>Super Tannery Ltd. (SUPTANERY) Profile, Company FAQs &amp; Facts, Industry, Sector, Employee Strength - Stocktwits</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Makers Laboratories Ltd. (MAKERSL) Fundamental and Financial Data - Stocktwits</t>
+          <t>SUPTANERY Historical Data - equitypandit.com</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Makers Laboratories Q1 Results: Consolidated Net Profit Surges 244% YoY to ₹150.43 lacs - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr"/>
+          <t>Super Tannery Ltd. (SUPTANERY) Profile, Company FAQs &amp; Facts, Industry, Sector, Employee Strength - Stocktwits</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>Super Tannery Ltd. (SUPTANERY) Fundamental and Financial Data - Stocktwits</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 20:18:15 IST</t>
+          <t>2026-09-07 12:56:35 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2822,60 +2894,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>DHAMPURSUG.NS</t>
+          <t>BURNPUR.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Dhampur Sugar Mills Limited</t>
+          <t>Burnpur Cement Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>176.4499969482422</v>
+        <v>22.6299991607666</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>176.4499969482422</v>
+        <v>22.6299991607666</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>165.6300048828125</v>
+        <v>20.48999977111816</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>167.5899963378906</v>
+        <v>20.48999977111816</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>177.0500030517578</v>
+        <v>21.55999946594238</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>167.5899963378906</v>
+        <v>20.48999977111816</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>831577</v>
+        <v>371470</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-5.34</v>
+        <v>-4.96</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Dhampur Sugar Mills Ltd. Share Price: 52-Week High Focus - Univest</t>
+          <t>Burnpur Cement dispatches web links for 40th AGM and FY26 annual report - scanx.trade</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Dhampur Sugar Mills net profit rises 569% to ₹6.09 crore in Q1FY27 - scanx.trade</t>
+          <t>Price Band Hitters on September 7, 2026 at 12:00 PM - HDFC Sky</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Dhampur Sugar Mills net profit rises 569% to ₹6.09 crore in Q1FY27 - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr"/>
-      <c r="Q15" s="2" t="inlineStr"/>
+          <t>Burnpur Cement Share Price - Upstox</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>Burnpur Cement Ltd Locks at Upper Circuit With 4.96% Gain — Buyers Queue, Sellers Absent - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>Burnpur Cement FY26 Results: Net loss widens 87% to ₹792 crore - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 20:18:15 IST</t>
+          <t>2026-09-07 12:56:35 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2883,64 +2963,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>ANNAPURNA.NS</t>
+          <t>ELITECON.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Annapurna Swadisht Limited</t>
+          <t>Elitecon International Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>151.4499969482422</v>
+        <v>8.25</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>151.4499969482422</v>
+        <v>8.909999847412109</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>139</v>
+        <v>8.25</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>140.1999969482422</v>
+        <v>8.25</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>147.7799987792969</v>
+        <v>8.680000305175781</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>140.1999969482422</v>
+        <v>8.25</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>96796</v>
+        <v>3864394</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-5.13</v>
+        <v>-4.95</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Annapurna Swadisht Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>Elitecon International Fined ₹1.12 Lakh by BSE for Late Financial Results Submission - scanx.trade</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Annapurna Studios expands distribution slate with Dulquer Salmaan’s I’m Game, Karthi’s Sardar 2 and... - Moneycontrol.com</t>
+          <t>Elitecon International Fined ₹1.12 Lakh by BSE for Late Financial Results Submission - scanx.trade</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Annapurna gets ‘Annapurna Bhandar’ benefits: Mamata Banerjee thanks CM Suvendu and leaves one wondering - Bhaskar English</t>
+          <t>Elitecon International Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Annapurna Studios expands distribution slate with Dulquer Salmaan’s I’m Game, Karthi’s Sardar 2 and... - Moneycontrol.com</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr"/>
+          <t>Small-cap stock under Rs.50 hits 5% upper circuit following stock market rebound - TradingView</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>Elitecon International Declines 4.92% to ₹11.2: Support at ₹10.64 Holds Key - Jurik MA - siam.in</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 20:18:15 IST</t>
+          <t>2026-09-07 12:56:35 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -2948,68 +3032,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>TARMAT.NS</t>
+          <t>TIJARIA.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Tarmat Limited</t>
+          <t>Tijaria Polypipes Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>64.48999786376953</v>
+        <v>9.739999771118164</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>64.79000091552734</v>
+        <v>9.800000190734863</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>60.54999923706055</v>
+        <v>9.069999694824219</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>61.22999954223633</v>
+        <v>9.069999694824219</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>64.48999786376953</v>
+        <v>9.539999961853027</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>61.22999954223633</v>
+        <v>9.069999694824219</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>36266</v>
+        <v>141636</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-5.06</v>
+        <v>-4.93</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Tarmat schedules AGM to approve board reappointments and salary hikes - scanx.trade</t>
+          <t>Tijaria Polypipes (NSE: TIJARIA) Gains Momentum - Kalkine India</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Tarmat schedules AGM to approve board reappointments and salary hikes - scanx.trade</t>
+          <t>Tijaria Polypipes Ltd Locks at Upper Circuit With 4.95% Gain — Buyers Queue, Sellers Absent - MarketsMojo</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Tarmat Ltd. Financials – Balance Sheet, Profit &amp; Loss, Cash Flow - Value Research</t>
+          <t>Tijaria Polypipes Ltd Locks at Upper Circuit With 4.95% Gain — Buyers Queue, Sellers Absent - MarketsMojo</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Tarmat Ltd. Share Price rise with market cap at Rs 128.43 Cr - Univest</t>
+          <t>Tijaria Polypipes (NSE: TIJARIA) Sees Sharp Upmove - Kalkine India</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>Tarmat consolidated net profit rises 121.74% in the June 2026 quarter - Business Standard</t>
+          <t>Tijaria Polypipes posts ₹36.11 crore loss in Q1FY27 as revenue remains zero - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 20:18:15 IST</t>
+          <t>2026-09-07 12:56:35 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -3017,60 +3101,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>NIRAJISPAT.NS</t>
+          <t>EASTSILK.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Niraj Ispat Industries Limited</t>
+          <t>Eastern Silk Industries Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>387.7999877929688</v>
+        <v>60.79999923706055</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>387.7999877929688</v>
+        <v>60.79999923706055</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>387.7999877929688</v>
+        <v>58.02000045776367</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>387.7999877929688</v>
+        <v>58.04000091552734</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>408.2000122070312</v>
+        <v>61</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>387.7999877929688</v>
+        <v>58.04000091552734</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>601</v>
+        <v>330</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-5</v>
+        <v>-4.85</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Niraj (NIRAJISPAT.NS) Stock: Closes with Little Net Change at ₹216.00 in the Available Record; Range Check: the Price Remains Bounded by the Supplied Support and Resistance for the Current Session - ALMA Signal - siam.in</t>
+          <t>Eastern Silk Industries Limited Schedules Board Meeting on May 27, 2026 to Approve FY26 Audited Financial Results - scanx.trade</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Precision Wires and 11 Other Stocks That Hit the 20% Upper Circuit Today; Are You Holding Any? - tradebrains.in</t>
+          <t>EASTSILK Q2 2026 Earnings: Revenue Grows 8.48% to ₹23.71 Crore, but EPS Loss of ₹27.2 Dents Sentiment - siam.in</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Precision Wires and 11 Other Stocks That Hit the 20% Upper Circuit Today; Are You Holding Any? - tradebrains.in</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr"/>
-      <c r="Q18" s="2" t="inlineStr"/>
+          <t>EASTSILK Q2 2026 Earnings: Revenue Grows 8.48% to ₹23.71 Crore, but EPS Loss of ₹27.2 Dents Sentiment - siam.in</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Silk Industries Trades Flat Near ₹50.5; Key Support and Resistance Levels in Focus - Beta Neutral Pair - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Silk Industries Limited Announces Q3 FY26 Financial Results - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 20:18:15 IST</t>
+          <t>2026-09-07 12:56:35 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -3078,64 +3170,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>KJMCFIN.NS</t>
+          <t>PIONRINV.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>KJMC Financial Services Limited</t>
+          <t>Pioneer Investcorp Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>66.79000091552734</v>
+        <v>79.75</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>68</v>
+        <v>79.84999847412109</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>63.13999938964844</v>
+        <v>79.75</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>63.13999938964844</v>
+        <v>79.84999847412109</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>66.45999908447266</v>
+        <v>83.88999938964844</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>63.13999938964844</v>
+        <v>79.84999847412109</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>2504</v>
+        <v>1426</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-5</v>
+        <v>-4.82</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>KJMC Financial Services Ltd. (KJMCFIN) Share Price Today, Quote, Latest Discussions, Interactive Chart and News - Stocktwits</t>
+          <t>Pioneer Investcorp Limited (PIONRINV.NS) Mar 2026 Earnings: EPS of ₹2.18 Reported Amid Modest Revenue; Stock Declines 3.55% - Revenue Growth Report - vinanet.vn</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>KJMC Financial Services Ltd. (KJMCFIN) Fundamental and Financial Data - Stocktwits</t>
+          <t>Pioneer Investcorp Limited (PIONRINV.NS) Mar 2026 Earnings: EPS of ₹2.18 Reported Amid Modest Revenue; Stock Declines 3.55% - Revenue Growth Report - vinanet.vn</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>KJMC Financial Services Ltd. (KJMCFIN) Fundamental and Financial Data - Stocktwits</t>
+          <t>Technical Analysis of Pioneer Investcorp Limited (NSE:PIONRINV) - TradingView</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>KJMC Financial Services Ltd. (KJMCFIN) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr"/>
+          <t>Pioneer Investcorp (PIONRINV.NS) Slips 3.26%: Support at ₹85.5 in Focus - Momentum Surge Alerts - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>Pioneer Investcorp Limited (PIONRINV.NS) Mar 2026 Earnings: Net Profit Scales Higher – EPS of ₹2.18; Revenue at ₹1.9 Crore - Performance Review - vinanet.vn</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 20:18:15 IST</t>
+          <t>2026-09-07 12:56:35 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -3143,68 +3239,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>ANNU.NS</t>
+          <t>DIVGIITTS.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Annu Projects Limited</t>
+          <t>Divgi Torqtransfer Systems Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>68.23000335693359</v>
+        <v>1242</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>69</v>
+        <v>1285.199951171875</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>68.23000335693359</v>
+        <v>1155.199951171875</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>68.23000335693359</v>
+        <v>1176.5</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>71.81999969482422</v>
+        <v>1235.800048828125</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>68.23000335693359</v>
+        <v>1176.5</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>412213</v>
+        <v>167874</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-5</v>
+        <v>-4.8</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Weak market debut: Annu Projects shares list at over 27% discount to its IPO price - Moneycontrol.com</t>
+          <t>Divgi (DIVGIITTS.NS) Session: Finishes 2.96% Down at ₹1,226.05; Level Watch: the Supplied Trading Band Runs From ₹1,164.75 to ₹1,287.35 in Latest Trading - Momentum Trade - siam.in</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>ANNU PROJECTS LIMITED Share Price - Upstox</t>
+          <t>Divgi TorqTransfer Systems to Meet Investors in Non-Deal Roadshow - TipRanks</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ANNU PROJECTS LIMITED Share Price - Upstox</t>
+          <t>Divgi Torqtransfer Slips 0.99% to ₹1219.75: Key Support and Resistance Levels in Focus - Sector Leader Stocks - siam.in</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Weak Start! Annu Projects shares list at 27% discount to IPO price - economictimes.com</t>
+          <t>Divgi Torqtransfer Systems Share Price Hits One-Year High - Univest</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Annu Projects Shares List at 27% Discount on NSE - Groww</t>
+          <t>Divgi TorqTransfer Stock Surges 13% As Q1 FY27 PAT Jumps 183% To ₹25.2 Cr - Trade Brains</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04 20:18:15 IST</t>
+          <t>2026-09-07 12:56:35 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -3212,61 +3308,61 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>RNBDENIMS.NS</t>
+          <t>BETA.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>R&amp;B Denims Limited</t>
+          <t>Beta Drugs Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>10.8100004196167</v>
+        <v>2204</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>10.8100004196167</v>
+        <v>2204</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>10.27000045776367</v>
+        <v>2087.89990234375</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>10.27000045776367</v>
+        <v>2114.60009765625</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>10.8100004196167</v>
+        <v>2218.5</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>10.27000045776367</v>
+        <v>2114.60009765625</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>424488</v>
+        <v>34067</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-5</v>
+        <v>-4.68</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>RNBDENIMS Stock Price and Chart — NSE:RNBDENIMS - TradingView</t>
+          <t>Beta bionics CEO Sean Saint sells $113,258 in company stock - Investing.com India</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>R&amp;B Denims (RNBDENIMS.NS) Slips 1.5%: Testing Key Support Near ₹9.89 - Defined Outcome ETF - vinanet.vn</t>
+          <t>Beta Technologies terminates security control agreement with US Defense Department - scanx.trade</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>R&amp;B Denims Schedules EGM for March 13 to Approve Stock Split and Corporate Actions - scanx.trade</t>
+          <t>Beta Technologies terminates security control agreement with US Defense Department - scanx.trade</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>R&amp;B Denims (RNBDENIMS.NS) Slips 1.5%: Testing Key Support Near ₹9.89 - Defined Outcome ETF - vinanet.vn</t>
+          <t>What Is the Beta of a Stock? Meaning &amp; Formula - Britannica</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>R&amp;B Denims Limited (RNBDENIMS.NS) Faces Selling Pressure, Holds Above Key Support - Institutional Sentiment - vinanet.vn</t>
+          <t>Independent Director of BETA Technologies Picks Up 1.5% More Stock - simplywall.st</t>
         </is>
       </c>
     </row>

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -439,14 +439,14 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="37" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 12:56:35 IST</t>
+          <t>2026-09-07 21:31:37 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -553,68 +553,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>ALKALI.NS</t>
+          <t>UDAYJEW.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Alkali Metals Limited</t>
+          <t>Uday Jewellery Industries Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>69.98999786376953</v>
+        <v>168.3999938964844</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>78.66000366210938</v>
+        <v>171.6000061035156</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>68</v>
+        <v>148</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>78.66000366210938</v>
+        <v>167.5800018310547</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>65.55000305175781</v>
+        <v>143</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>78.66000366210938</v>
+        <v>167.5800018310547</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>70547</v>
+        <v>638450</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>20</v>
+        <v>17.19</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Momentum Stocks: Alkali Metals, Deepak Builders jump up to 15% on sheer momentum - Moneycontrol.com</t>
+          <t>Uday Jewellery Industries Share Price Rises 8.82% Today - Univest</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Alkali Metals and Deepak Builders Surge on Momentum Trading - whalesbook.com</t>
+          <t>Uday Jewellery Industries Share Price Rises 8.82% Today - Univest</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Lords Chloro Alkali Commissions 14.5 MW Solar Plant; Shares Rise 1.33% - HDFC Sky</t>
+          <t>Uday Jewellery Industries Ltd. (UDAYJEW) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Tuticorin Alkali Chemicals schedules 53rd AGM for September 25, 2026 - scanx.trade</t>
+          <t>Technical Analysis of Uday Jewellery Industries Ltd. (NSE:UDAYJEW) - TradingView</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Don't Buy Alkali Metals Limited (NSE:ALKALI) For Its Next Dividend Without Doing These Checks - simplywall.st</t>
+          <t>Uday Jewellery Promoters Acquire 73.34 Lakh Shares Through Merger Scheme - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 12:56:35 IST</t>
+          <t>2026-09-07 21:31:37 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -622,60 +622,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>PKTEA.NS</t>
+          <t>CENTUM.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>The Peria Karamalai Tea &amp; Produce Company Limited</t>
+          <t>Centum Electronics Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>808</v>
+        <v>3778.199951171875</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>963.1500244140625</v>
+        <v>4420</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>808</v>
+        <v>3778.199951171875</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>963.1500244140625</v>
+        <v>4376.89990234375</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>802.6500244140625</v>
+        <v>3767.300048828125</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>963.1500244140625</v>
+        <v>4376.89990234375</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>10527</v>
+        <v>826784</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>20</v>
+        <v>16.18</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>The Peria Karamalai Tea &amp; Produce Company Limited (NSE: PKTEA) Gains 20% as Stock Movement Draws Market Attention - Kalkine India</t>
+          <t>Centum Electronics Share Price Today Near One-Year High - Univest</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>The Peria Karamalai Tea &amp; Produce Company Limited (NSE: PKTEA) Gains 20% as Stock Movement Draws Market Attention - Kalkine India</t>
+          <t>Centum Electronics Share Price Today Near One-Year High - Univest</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>THE P K TEA PROD CO LTD Share Price - Upstox</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
+          <t>Centum Electronics Ltd. Stock News - Value Research</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>Centum Electronics Ltd. Share Price Today: key stock move - Univest</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>CTUM stock gains on Nairobi exchange as investors watch Centum fundamentals - AD HOC NEWS</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 12:56:35 IST</t>
+          <t>2026-09-07 21:31:37 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -683,68 +691,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>ANDHRAPAP.NS</t>
+          <t>MITTAL.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>ANDHRA PAPER LIMITED</t>
+          <t>Mittal Life Style Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>64.09999847412109</v>
+        <v>0.8199999928474426</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>77.33999633789062</v>
+        <v>0.9599999785423279</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>61.9900016784668</v>
+        <v>0.8100000023841858</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>76.19999694824219</v>
+        <v>0.9200000166893005</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>64.44999694824219</v>
+        <v>0.800000011920929</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>76.19999694824219</v>
+        <v>0.9200000166893005</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>21270613</v>
+        <v>11565075</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>18.23</v>
+        <v>15</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Andhra Paper Rises 3.3% to ₹61.93: Key Levels to Watch - Short Setup Alerts - siam.in</t>
+          <t>Mittal Life Style Limited (NSE: MITTAL) Gains 13.75% as Stock Movement Draws Market Attention - Kalkine India</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>APPCB imposes ₹21 crore environmental compensation on Andhra Paper Limited - The Hindu</t>
+          <t>Mittal Life Style Limited (NSE: MITTAL) Gains 13.75% as Stock Movement Draws Market Attention - Kalkine India</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>APPCB imposes ₹21 crore environmental compensation on Andhra Paper Limited - The Hindu</t>
+          <t>BCL Industries Promoter Rajinder Mittal Continues Share Acquisition Spree - scanx.trade</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Andhra Pradesh Deputy CM Pawan Kalyan directs APPCB to initiate action against Andhra Paper Limited for ‘polluting’ Godavari river - The Hindu</t>
+          <t>Divya Mittal’s digital diary: 'Don’t fight the Sirens. Tie yourself to the mast' - The Times of India</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Andhra Paper reappoints Saurabh Bangur as MD for five years - scanx.trade</t>
+          <t>"Hate This": Cancer Survivor Chhavi Mittal Shares Health Update After Fibroid Surgery - NDTV</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 12:56:35 IST</t>
+          <t>2026-09-07 21:31:37 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -752,68 +760,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>XTRANET.NS</t>
+          <t>GNRL.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Xtranet Technologies Limited</t>
+          <t>Gujarat Natural Resources Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>242</v>
+        <v>100</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>280</v>
+        <v>116.3300018310547</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>236.5800018310547</v>
+        <v>100</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>273.9800109863281</v>
+        <v>113.9599990844727</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>234.2400054931641</v>
+        <v>99.26999664306641</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>273.9800109863281</v>
+        <v>113.9599990844727</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>11559377</v>
+        <v>3632884</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>16.97</v>
+        <v>14.8</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>XTRANET TECHNOLOGIES LTD Share Price - Upstox</t>
+          <t>GNRL Jun 2026 Earnings: EPS of ₹0.69 Reported with Nil Revenue; Stock Falls 6.87% - Earnings Whisper Number - siam.in</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>XTRANET TECHNOLOGIES LTD Share Price - Upstox</t>
+          <t>GNRL Shares Surge 12% As Post-Monsoon Drilling Program Resumes - Trade Brains</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Xtranet Technologies Ltd (XTRANET) Share Price - Business Today</t>
+          <t>GNRL.NS Jun 2026 Earnings: EPS at ₹0.69 Despite Nil Revenue; Shares Slip 2.72% - Analyst Coverage Count - siam.in</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>XTRANET Technologies Share Price Today after 9.86% gain - Univest</t>
+          <t>Gujarat Natural Resources Share Price Rises 13.47% Today - Univest</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>1,970,100 Equity Shares of Xtranet Technologies Limited are subject to a Lock-Up Agreement Ending on 26-AUG-2026. - marketscreener.com</t>
+          <t>Gujarat Natural Resources Share Price Rises 8.06% Today - Univest</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 12:56:35 IST</t>
+          <t>2026-09-07 21:31:37 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -821,68 +829,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>DBEIL.NS</t>
+          <t>RADHIKAJWE.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Deepak Builders &amp; Engineers India Limited</t>
+          <t>Radhika Jeweltech Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>6.610000133514404</v>
+        <v>84.62000274658203</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>7.710000038146973</v>
+        <v>97.40000152587891</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>6.610000133514404</v>
+        <v>84.61000061035156</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>7.440000057220459</v>
+        <v>94.27999877929688</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>6.429999828338623</v>
+        <v>83.16000366210938</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>7.440000057220459</v>
+        <v>94.27999877929688</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>2025752</v>
+        <v>31904994</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>15.71</v>
+        <v>13.37</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Deepak Builders &amp; Engineers India Limited's (NSE:DBEIL) Stock Has Shown Weakness Lately But Financial Prospects Look Decent: Is The Market Wrong? - simplywall.st</t>
+          <t>Here's Why Radhika Jeweltech (NSE:RADHIKAJWE) Has Caught The Eye Of Investors - simplywall.st</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Deepak Builders &amp; Engineers India (DBEIL.NS) Slides 4.93% – Key Support at ₹7.69 in Focus - PCR Spike - vinanet.vn</t>
+          <t>Radhika Jeweltech Surges 13%: Key Levels and Momentum Analysis - Channel Breakout - vinanet.vn</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Deepak Builders Dispatches Postal Ballot Notice for 1:10 Stock Split Approval - scanx.trade</t>
+          <t>Radhika Jeweltech (RADHIKAJWE.NS) Eases Marginally: Key Support and Resistance Levels in Focus - Factor Timing - vinanet.vn</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>DEEPAK BUILDERS &amp; ENG I L Share Price - Upstox</t>
+          <t>RADHIKAJWE Stock Price and Chart — NSE:RADHIKAJWE - TradingView</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>Deepak Builders &amp; Engineers India (DBEIL.NS) Slides 4.93% – Key Support at ₹7.69 in Focus - PCR Spike - vinanet.vn</t>
+          <t>RADHIKAJWE Share Price Today - Radhika Jeweltech Ltd. Stock Price Live NSE/BSE - Univest</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 12:56:35 IST</t>
+          <t>2026-09-07 21:31:37 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -890,68 +898,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>GNRL.NS</t>
+          <t>RIR.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Gujarat Natural Resources Limited</t>
+          <t>RIR Power Electronics Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>100</v>
+        <v>175.0399932861328</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>113.75</v>
+        <v>203.8300018310547</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>100</v>
+        <v>175.0399932861328</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>113.5899963378906</v>
+        <v>191.9499969482422</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>99.26999664306641</v>
+        <v>169.8600006103516</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>113.5899963378906</v>
+        <v>191.9499969482422</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>2021677</v>
+        <v>11233563</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>14.43</v>
+        <v>13</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>GNRL Jun 2026 Earnings: EPS of ₹0.69 Reported with Nil Revenue; Stock Falls 6.87% - Earnings Whisper Number - siam.in</t>
+          <t>RIR Power Electronics Limited (NSE: RIR) Gains 11.90% as Stock Movement Draws Market Attention - Kalkine India</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Gujarat (GNRL.NS) Outlook: Finishes 0.29% Lower at ₹101.60 on the Day; Key Range: Price Remains Between ₹96.52 Support and ₹106.68 Resistance in the Latest Session - High Conviction Picks - siam.in</t>
+          <t>RIR Power Electronics Limited (NSE: RIR) Gains 11.90% as Stock Movement Draws Market Attention - Kalkine India</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Gujarat Natural Resources Share Price Rises 8.06% Today - Univest</t>
+          <t>Volume shocker stocks today: Why Innovassynth, RIR Power, Pashupati Cotspin, Zydus Wellness are soaring - Details here - Livemint</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Gujarat (GNRL.NS) Outlook: Finishes 0.29% Lower at ₹101.60 on the Day; Key Range: Price Remains Between ₹96.52 Support and ₹106.68 Resistance in the Latest Session - High Conviction Picks - siam.in</t>
+          <t>RIR Share Price Rises 11.78%: Price and Valuation - Univest</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>GNRL.NS Jun 2026 Earnings: EPS at ₹0.69 Despite Nil Revenue; Shares Slip 2.72% - Analyst Coverage Count - siam.in</t>
+          <t>RIR Power Electronics sets Sept 22 record date for final dividend - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 12:56:35 IST</t>
+          <t>2026-09-07 21:31:37 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -959,68 +967,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>PCJEWELLER.NS</t>
+          <t>SYRMA.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>PC Jeweller Limited</t>
+          <t>Syrma SGS Technology Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>12.28999996185303</v>
+        <v>1458.5</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>13.68000030517578</v>
+        <v>1645</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>12.21000003814697</v>
+        <v>1458.300048828125</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>13.52000045776367</v>
+        <v>1634.800048828125</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>11.85999965667725</v>
+        <v>1457.300048828125</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>13.52000045776367</v>
+        <v>1634.800048828125</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>1551586213</v>
+        <v>13076470</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>14</v>
+        <v>12.18</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>PC Jewellers Share Price - Live NSE: PCJEWELLER Stock Price &amp; Chart - Upstox</t>
+          <t>Record High: Syrma SGS Technology shares extend gains for third-consecutive day, surge nearly 12% — Here's why - CNBC TV18</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>PC Jeweller Stock Update: Shares Jump 11% on Debt Repayment Progress - LatestLY</t>
+          <t>Smallcap 500 index hits 52-week high; Syrma, Strides, Avalon soar up to 12% - Business Standard</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Pc Jeweller Stock Price Forecast. Should You Buy PCJEWELLER.NS? - StockInvest.us</t>
+          <t>Zydus Wellness, Syrma SGS, PVR Inox shares spurt amid heavy volumes; check full list - Upstox</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>PC Jeweller (PCJEWELLER) Share Price Falls 5.09% Today; Stock Analysis and Valuation Check - Univest</t>
+          <t>Smallcap 500 index hits 52-week high; Syrma, Strides, Avalon soar up to 12% - Business Standard</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Most Active Equities, August 11, 2026, 3:30 PM IST - HDFC Sky</t>
+          <t>Syrma SGS Technology Stock Surges Over 3% After ECMS Application Gets Approved By Govt - NDTV Profit</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 12:56:35 IST</t>
+          <t>2026-09-07 21:31:37 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1028,68 +1036,56 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>CENTUM.NS</t>
+          <t>ANUHPHR.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Centum Electronics Limited</t>
+          <t>Anuh Pharma Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>3778.199951171875</v>
+        <v>82.69999694824219</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>4341</v>
+        <v>91.80000305175781</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>3778.199951171875</v>
+        <v>82</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>4253.2998046875</v>
+        <v>90.29000091552734</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>3767.300048828125</v>
+        <v>81.09999847412109</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>4253.2998046875</v>
+        <v>90.29000091552734</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>249894</v>
+        <v>1068438</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>12.9</v>
+        <v>11.33</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Centum Electronics Share Price Today Near One-Year High - Univest</t>
+          <t>Anuh (ANUHPHR.NS) Update: Falls 1.28% to ₹77.82 in the Latest Reading; Price Context: the Supplied Trading Band Runs From ₹73.93 to ₹81.71 in the Available Record - Volume Gap - siam.in</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Centum Electronics Share Price Today Near One-Year High - Univest</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>Centum Electronics Ltd. Stock News - Value Research</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>Centum Electronics to Host Virtual Analyst and Investor Meet on September 9 - theglobeandmail.com</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>Centum Electronics Ltd. Share Price Today: key stock move - Univest</t>
-        </is>
-      </c>
+          <t>Anuh (ANUHPHR.NS) Update: Falls 1.28% to ₹77.82 in the Latest Reading; Price Context: the Supplied Trading Band Runs From ₹73.93 to ₹81.71 in the Available Record - Volume Gap - siam.in</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 12:56:35 IST</t>
+          <t>2026-09-07 21:31:37 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1097,64 +1093,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>THEMISMED.NS</t>
+          <t>STAR.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Themis Medicare Limited</t>
+          <t>Strides Pharma Science Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>121.379997253418</v>
+        <v>1058.699951171875</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>136.25</v>
+        <v>1187.599975585938</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>119.1699981689453</v>
+        <v>1045</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>135.8899993896484</v>
+        <v>1178.800048828125</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>120.4199981689453</v>
+        <v>1059.599975585938</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>135.8899993896484</v>
+        <v>1178.800048828125</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>2052487</v>
+        <v>2617100</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>12.85</v>
+        <v>11.25</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Themis Medicare Holds Gains at ₹104.51: Key Levels to Monitor for THEMISMED.NS - Jurik MA - siam.in</t>
+          <t>Asia tech shares rally, others hesitant as oil rises - The Star</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>THEMISMED Share Price News: Price Action and Fundamentals - Univest</t>
+          <t>Barbara Eden, 95, shares health update after dropping out of festival at last minute - The Independent</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>THEMISMED Share Price News: Price Action and Fundamentals - Univest</t>
+          <t>Northern Star Resources Director Jeffrey Quartermaine Acquires 10,000 Shares On-Market - kalkine.com.au</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Themis Medicare Share Price Today: price rise and valuation - Univest</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr"/>
+          <t>Evan, formerly ENHYPEN’s Heeseung, reveals his cancer battle for the first time - t2ONLINE</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>5-Star Analyst Resets Intel Stock Price Target on Weaker PC Demand - TradingView</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 12:56:35 IST</t>
+          <t>2026-09-07 21:31:37 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1162,68 +1162,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>ARFIN.NS</t>
+          <t>SUNSHIEL.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Arfin India Limited</t>
+          <t>Sunshield Chemicals Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>88.69999694824219</v>
+        <v>1175</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>97.44000244140625</v>
+        <v>1275</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>87.72000122070312</v>
+        <v>1155</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>97.33000183105469</v>
+        <v>1268.599975585938</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>87.23999786376953</v>
+        <v>1144.900024414062</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>97.33000183105469</v>
+        <v>1268.599975585938</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>2916534</v>
+        <v>13356</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>11.57</v>
+        <v>10.8</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Arfin India sets September 19 date for 34th AGM and e-voting - scanx.trade</t>
+          <t>SUNSHIEL Stock Price and Chart — NSE:SUNSHIEL - TradingView</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Mufin Green Finance: செப்டம்பர் 28-ல் முக்கிய பொதுக்குழு கூட்டம்! லாபம் **39%** உயர்வு - whalesbook.com</t>
+          <t>Sunshield Chemicals Share Price: valuation and sector view - Univest</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Arfin (ARFIN.NS) Q2 2026 Earnings: The Company Releases Its Current Earnings Data under the Current Snapshot; Trading Move: Shares Move 0.68% Up for the Current Session - Revenue Recognition Risk - siam.in</t>
+          <t>Sunshield Chemicals Share Price: valuation and sector view - Univest</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Arfin India Consolidated June 2026 Net Sales at Rs 212.77 crore, up 95.46% Y-o-Y - Moneycontrol.com</t>
+          <t>Free float of Sunshield Chemicals Limited – NSE:SUNSHIEL - TradingView</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>Arfin India consolidated net profit rises 276.85% in the June 2026 quarter - Business Standard</t>
+          <t>Sunshield Chemicals Ltd. (SUNSHIEL) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 12:56:35 IST</t>
+          <t>2026-09-07 21:31:37 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1231,68 +1231,56 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>UDAYJEW.NS</t>
+          <t>VENUSPIPES.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Uday Jewellery Industries Limited</t>
+          <t>Venus Pipes &amp; Tubes Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>168.3999938964844</v>
+        <v>1639.800048828125</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>168.3999938964844</v>
+        <v>1821</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>148</v>
+        <v>1639.800048828125</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>158</v>
+        <v>1805.400024414062</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>143</v>
+        <v>1631</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>158</v>
+        <v>1805.400024414062</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>170308</v>
+        <v>603232</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>10.49</v>
+        <v>10.69</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Technical Analysis of Uday Jewellery Industries Ltd. (NSE:UDAYJEW) - TradingView</t>
+          <t>Venus Pipes &amp; Tubes Gains 1.22% to ₹1596.5: Stock Approaches Key Resistance on NSE - Trading Ideas - siam.in</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Uday Jewellery Industries Share Price Rises 8.82% Today - Univest</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>Uday Jewellery Industries Share Price Rises 8.82% Today - Univest</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>Uday Jewellery Industries Ltd. (UDAYJEW) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>Uday Jewellery Promoters Acquire 73.34 Lakh Shares Through Merger Scheme - scanx.trade</t>
-        </is>
-      </c>
+          <t>Venus Pipes &amp; Tubes Gains 1.22% to ₹1596.5: Stock Approaches Key Resistance on NSE - Trading Ideas - siam.in</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 12:56:35 IST</t>
+          <t>2026-09-07 21:31:37 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1300,56 +1288,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>CURAA.NS</t>
+          <t>THEMISMED.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Cura Technologies Limited</t>
+          <t>Themis Medicare Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>76</v>
+        <v>121.379997253418</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>80</v>
+        <v>140.6000061035156</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>76</v>
+        <v>119.1699981689453</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>80</v>
+        <v>133.0700073242188</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>72.45999908447266</v>
+        <v>120.4199981689453</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>80</v>
+        <v>133.0700073242188</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>1681</v>
+        <v>4732288</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>10.41</v>
+        <v>10.5</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>D2C kitchenware startup Curaa raises Rs 40 crore led by 3one4 Capital - The Economic Times</t>
+          <t>Themis Medicare Holds Gains at ₹104.51: Key Levels to Monitor for THEMISMED.NS - Jurik MA - siam.in</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>D2C kitchenware startup Curaa raises Rs 40 crore led by 3one4 Capital - The Economic Times</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr"/>
-      <c r="P13" s="2" t="inlineStr"/>
-      <c r="Q13" s="2" t="inlineStr"/>
+          <t>Themis Medicare Says No Undisclosed News Behind Share Volume Surge - TipRanks</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>THEMISMED Share Price News: Price Action and Fundamentals - Univest</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>Themis Medicare Share Price Today: price rise and valuation - Univest</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>Themis Medicare Says No Undisclosed News Behind Share Volume Surge - TipRanks</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 12:56:35 IST</t>
+          <t>2026-09-07 21:31:37 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1357,68 +1357,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>STAR.NS</t>
+          <t>MGEL.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Strides Pharma Science Limited</t>
+          <t>Mangalam Global Enterprise Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1058.699951171875</v>
+        <v>14.85999965667725</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1171.300048828125</v>
+        <v>17.07999992370605</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>1045</v>
+        <v>13</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>1168.199951171875</v>
+        <v>15.72000026702881</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1059.599975585938</v>
+        <v>14.23999977111816</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1168.199951171875</v>
+        <v>15.72000026702881</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1010895</v>
+        <v>1420121</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>10.25</v>
+        <v>10.39</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Asia tech shares rally, others hesitant as oil rises - The Star</t>
+          <t>MGEL appoints Darshak Mehta as CEO of NEAT Everyday - Business Standard</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Asia tech shares rally, others hesitant as oil rises - The Star</t>
+          <t>Mangalam Global changes designation of director - scanx.trade</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Evan, formerly ENHYPEN’s Heeseung, reveals his cancer battle for the first time - t2ONLINE</t>
+          <t>Mangalam (MGEL.NS) Quarterly Figures: Available Data Shows the Latest Reported Performance in the Latest Reading; Market Move: Shares Finish 0.88% Lower in the Latest Session - Pretax Income Report - siam.in</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5-Star Analyst Resets Intel Stock Price Target on Weaker PC Demand - TradingView</t>
+          <t>Mangalam Global Enterprise Limited Announces Appointment of Darshak Mehta to Chief Executive Officer for the Brand 'NEAT EVERYDAY', Effective September 01, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>Forget Rolls-Royce shares: OXB is a rising FTSE 250 star tipped to gain 68% in the coming year! - The Twelfth Magpie</t>
+          <t>Mangalam Global changes designation of director - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 12:56:35 IST</t>
+          <t>2026-09-07 21:31:37 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1426,68 +1426,56 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>RADHIKAJWE.NS</t>
+          <t>ORIENTPPR.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Radhika Jeweltech Limited</t>
+          <t>Orient Paper &amp; Industries Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>84.62000274658203</v>
+        <v>17.03000068664551</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>93.76000213623047</v>
+        <v>19.28000068664551</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>84.61000061035156</v>
+        <v>16.85000038146973</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>91.65000152587891</v>
+        <v>18.80999946594238</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>83.16000366210938</v>
+        <v>17.07999992370605</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>91.65000152587891</v>
+        <v>18.80999946594238</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>16755953</v>
+        <v>2023696</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>10.21</v>
+        <v>10.13</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Here's Why Radhika Jeweltech (NSE:RADHIKAJWE) Has Caught The Eye Of Investors - simplywall.st</t>
+          <t>BioMarin (BMRN) Earnings Update: The EPS Result Is Above Expectation in the Current Update; Latest Reaction: The Stock Records a 1.45% Decrease in Latest Trading - EPS Consistency Score - vinanet.vn</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Radhika Jeweltech (RADHIKAJWE.NS) Gains 5.15% as Bullish Momentum Builds - Virgin POC - siam.in</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>Radhika Jeweltech (RADHIKAJWE.NS) Gains 5.15% as Bullish Momentum Builds - Virgin POC - siam.in</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>Radhika Jeweltech Holds Steady Near Support; Resistance at ₹58.24 in Focus - Stock Analysis - vinanet.vn</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>RADHIKAJWE Stock Price and Chart — NSE:RADHIKAJWE - TradingView</t>
-        </is>
-      </c>
+          <t>BioMarin (BMRN) Earnings Update: The EPS Result Is Above Expectation in the Current Update; Latest Reaction: The Stock Records a 1.45% Decrease in Latest Trading - EPS Consistency Score - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr"/>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 12:56:35 IST</t>
+          <t>2026-09-07 21:31:37 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1495,68 +1483,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>HIKAL.NS</t>
+          <t>BODALCHEM.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Hikal Limited</t>
+          <t>Bodal Chemicals Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>222.0099945068359</v>
+        <v>168</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>257</v>
+        <v>171.1799926757812</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>218.8200073242188</v>
+        <v>162.8000030517578</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>244.6799926757812</v>
+        <v>171.1799926757812</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>222.3000030517578</v>
+        <v>155.6199951171875</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>244.6799926757812</v>
+        <v>171.1799926757812</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>14712371</v>
+        <v>4910182</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>10.07</v>
+        <v>10</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Hikal FY26 net loss of ₹49 crore on exceptional items - scanx.trade</t>
+          <t>With EPS Growth And More, Bodal Chemicals (NSE:BODALCHEM) Makes An Interesting Case - simplywall.st</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Hikal FY26 net loss of ₹49 crore on exceptional items - scanx.trade</t>
+          <t>Bodal Chemicals Sets Virtual AGM to Approve FY26 Accounts and Board Changes - TipRanks</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Hikal Ltd. Share Price Rise: Price Action and Fundamentals - Univest</t>
+          <t>Bodal Chemicals Share Price news with valuation context - Univest</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Don't Race Out To Buy Hikal Limited (NSE:HIKAL) Just Because It's Going Ex-Dividend - simplywall.st</t>
+          <t>Bodal Chemicals Ltd. (BODALCHEM) Share Price Rises 9.21% Today; Key Levels, Valuation and Peer View - Univest</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>Hikal Ltd Shares Hit Intraday Low Amid Price Pressure on 4 Sep 2026 - MarketsMojo</t>
+          <t>Bodal Chemicals Sets Virtual AGM to Approve FY26 Accounts and Board Changes - TipRanks</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 12:56:35 IST</t>
+          <t>2026-09-07 21:31:37 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1591,19 +1579,19 @@
         <v>56.65999984741211</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>36901422</v>
+        <v>41997933</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>10</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Why FINEOS Corporation (ASX: FCL) Could Be a Stock to Watch Into the Final Months of 2026 - Kalkine</t>
+          <t>Why FINEOS Corporation (ASX: FCL) Could Be a Stock to Watch Into the Final Months of 2026 - kalkine.com.au</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Why FINEOS Corporation (ASX: FCL) Could Be a Stock to Watch Into the Final Months of 2026 - Kalkine</t>
+          <t>FINEOS Corporation (ASX: FCL) — Is This Insurance Software Stock Worth a Place on Your Watchlist? - kalkine.com.au</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -1613,19 +1601,19 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
+          <t>FINEOS Corporation (ASX: FCL) — Is This Insurance Software Stock Worth a Place on Your Watchlist? - kalkine.com.au</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
           <t>Full Circle Lithium Rebrands as FCL-X Fire &amp; Safety Inc. and Provides Corporate Update - Stock Titan</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>Fineos (ASX:FCL) Shares Edge Lower Amid Weaker Technology Sector Sentiment - Kalkine</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 12:56:35 IST</t>
+          <t>2026-09-07 21:31:37 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1633,68 +1621,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>BODALCHEM.NS</t>
+          <t>TBZ.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Bodal Chemicals Limited</t>
+          <t>Tribhovandas Bhimji Zaveri Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>168</v>
+        <v>528.9000244140625</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>171.1799926757812</v>
+        <v>528.9000244140625</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>162.8000030517578</v>
+        <v>528.9000244140625</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>171.1799926757812</v>
+        <v>528.9000244140625</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>155.6199951171875</v>
+        <v>480.8500061035156</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>171.1799926757812</v>
+        <v>528.9000244140625</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>4822306</v>
+        <v>318752</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>With EPS Growth And More, Bodal Chemicals (NSE:BODALCHEM) Makes An Interesting Case - simplywall.st</t>
+          <t>TBZ shares jump 72% in six sessions: What's driving the rally? - Business Today</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Bodal Chemicals Sets Virtual AGM to Approve FY26 Accounts and Board Changes - TipRanks</t>
+          <t>TBZ shares jump 72% in six sessions: What's driving the rally? - Business Today</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Bodal Chemicals Share Price news with valuation context - Univest</t>
+          <t>Jewellery Stocks In Focus: PC Jeweller Surges 15%, TBZ Hits 10% Upper Circuit; Shankesh Gains 8% — Know Why - NDTV Profit</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Bodal Chemicals Ltd. (BODALCHEM) Share Price Rises 9.21% Today; Key Levels, Valuation and Peer View - Univest</t>
+          <t>Multibagger stock: Why TBZ shares are locked at 20% upper circuit - Business Standard</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>Bodal Chemicals Sets Virtual AGM to Approve FY26 Accounts and Board Changes - TipRanks</t>
+          <t>Tribhovandas Bhimji Zaveri is now GRT's jewel - Finshots</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 12:56:35 IST</t>
+          <t>2026-09-07 21:31:37 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1702,68 +1690,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>TBZ.NS</t>
+          <t>AKI.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Tribhovandas Bhimji Zaveri Limited</t>
+          <t>AKI India Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>528.9000244140625</v>
+        <v>7.940000057220459</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>528.9000244140625</v>
+        <v>7.940000057220459</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>528.9000244140625</v>
+        <v>7.940000057220459</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>528.9000244140625</v>
+        <v>7.940000057220459</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>480.8500061035156</v>
+        <v>7.21999979019165</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>528.9000244140625</v>
+        <v>7.940000057220459</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>281857</v>
+        <v>701339</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>9.99</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Jewellery Stocks In Focus: PC Jeweller Surges 15%, TBZ Hits 10% Upper Circuit; Shankesh Gains 8% — Know Why - NDTV Profit</t>
+          <t>Penny stock under 10 rupees: Upper circuit - Leather share jumps 74% in 4 sessions | Back-to-back surge for third day - TradingView</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Jewellery Stocks In Focus: PC Jeweller Surges 15%, TBZ Hits 10% Upper Circuit; Shankesh Gains 8% — Know Why - NDTV Profit</t>
+          <t>Penny stock under 10 rupees: Upper circuit - Leather share jumps 74% in 4 sessions | Back-to-back surge for third day - TradingView</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Multibagger stock: Why TBZ shares are locked at 20% upper circuit - Business Standard</t>
+          <t>AKI India Ltd leads gainers in 'B' group - Business Standard</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Tribhovandas Bhimji Zaveri is now GRT's jewel - Finshots</t>
+          <t>AKI India Ltd Upgraded to Sell on Technical Improvements Despite Lingering Financial Challenges - MarketsMojo</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>TBZ shares zoom 20%, hit upper circuit after GRT Jewellers open offer - The Economic Times</t>
+          <t>Volume shocker stocks: Why share price of EMS, Expleo Solutions, Windlas Biotech, AKI India, Heritage Foods are up today - Livemint</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 12:56:35 IST</t>
+          <t>2026-09-07 21:31:37 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1771,68 +1759,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>DHATRE.NS</t>
+          <t>KABRAEXTRU.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Dhatre Udyog Limited</t>
+          <t>Kabra Extrusion Technik Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>4.349999904632568</v>
+        <v>587</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>5.170000076293945</v>
+        <v>642</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>4.210000038146973</v>
+        <v>587</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>4.75</v>
+        <v>634.5</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>4.329999923706055</v>
+        <v>579.1500244140625</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>4.75</v>
+        <v>634.5</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>105820</v>
+        <v>758781</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>9.699999999999999</v>
+        <v>9.56</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>DHATRE Stock Price and Chart — NSE:DHATRE - TradingView</t>
+          <t>Kabra Extrusion Technik Gains 5.93% to ₹513, Approaches Key Resistance at ₹538.65 - Strangle Setup - siam.in</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Dhatre Udyog corrects 31st AGM time to 11 am on Sept 26 - scanx.trade</t>
+          <t>Kabra Extrusion Technik Surges 9% After Receiving Letter Of Nomination From Vietnamese Auto OEM - Trade Brains</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Dhatre Udyog Q1FY26 net profit hits ₹573 lakh on OCI surge - scanx.trade</t>
+          <t>Kabra Extrusiontechnik Share Price rises 8.59%: analysis - Univest</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Dhatre Udyog Ltd. (DHATRE) Profile, Company FAQs &amp; Facts, Industry, Sector, Employee Strength - Stocktwits</t>
+          <t>Kabra Extrusiontechnik Ltd. (KABRAEXTRU) Share Price Rises 8.33% Today - Univest</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Dhatre Udyog Q1 FY27 Results: Revenue and PAT Highlights - Univest</t>
+          <t>Kabra Extrusion Technik Slips 2.21% to ₹509: Support Zone in Focus as Resistance Caps Upside - Low Vol ETF - siam.in</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 12:56:35 IST</t>
+          <t>2026-09-07 21:31:37 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1840,61 +1828,61 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>MMP.NS</t>
+          <t>SAKAR.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>MMP Industries Limited</t>
+          <t>Sakar Healthcare Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>405.8999938964844</v>
+        <v>1021</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>455.6000061035156</v>
+        <v>1124</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>404.5</v>
+        <v>1018.950012207031</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>443.1499938964844</v>
+        <v>1109.199951171875</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>404.1499938964844</v>
+        <v>1013.900024414062</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>443.1499938964844</v>
+        <v>1109.199951171875</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>301815</v>
+        <v>339493</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>9.65</v>
+        <v>9.4</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>MMP Industries confirms no encumbrance on promoter shares in FY26 - scanx.trade</t>
+          <t>Sakar Healthcare FY26 net profit rises 74% to ₹3048.46 lakh - scanx.trade</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>MMP Industries confirms no encumbrance on promoter shares in FY26 - scanx.trade</t>
+          <t>Sakar Healthcare FY26 net profit rises 74% to ₹3048.46 lakh - scanx.trade</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>MMP Industries Drops 2.6% to ₹383.25; Support at ₹364.09 Holds Key - Option Strike Build - siam.in</t>
+          <t>192.61% Stock Return, 82.3% Profit Growth: What’s Driving Sakar Healthcare Ltd’s Multibagger Rerating? - MarketsMojo</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>MMP Industries Share Price Rises 8.51%: Price, Valuation - Univest</t>
+          <t>Sakar Healthcare Ltd. Share Price Today: Valuation Check - Univest</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>MMP Industries Consolidated June 2026 Net Sales at Rs 232.60 crore, up 26.9% Y-o-Y - Moneycontrol.com</t>
+          <t>Sakar Healthcare Ltd Technical Momentum Shifts Signal Bullish Outlook - MarketsMojo</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1903,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -2021,7 +2009,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 12:56:35 IST</t>
+          <t>2026-09-07 21:31:37 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -2029,68 +2017,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>HEG.NS</t>
+          <t>SAICAPI.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>HEG Limited</t>
+          <t>Sai Capital Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>260</v>
+        <v>158.3399963378906</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>273</v>
+        <v>158.3399963378906</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>250</v>
+        <v>133.5</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>265.5499877929688</v>
+        <v>141.6000061035156</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>728.25</v>
+        <v>157.5599975585938</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>265.5499877929688</v>
+        <v>141.6000061035156</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>2092808</v>
+        <v>899</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-63.54</v>
+        <v>-10.13</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>HEG Demerger Record Date Today. What It Means For Shareholders? All You Need To Know - NDTV Profit</t>
+          <t>SAICAPI Stock Price and Chart — NSE:SAICAPI - TradingView</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Did HEG shares really crash 64% in one day? Here’s how the demerger math works - The Economic Times</t>
+          <t>SAICAPI Stock Price and Chart — NSE:SAICAPI - TradingView</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Did HEG shares really crash 64% in one day? Here’s how the demerger math works - The Economic Times</t>
+          <t>Sai Capital Ltd. (SAICAPI) News, Articles, Events &amp; Latest Updates - Stocktwits</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>HEG demerger news: Record date today | Ratio, latest updates, other details in 5 points - Livemint</t>
+          <t>Sai Capital Ltd. (SAICAPI) Share Price Today, Quote, Latest Discussions, Interactive Chart and News - Stocktwits</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>HEG Advanced Material shares see discovered price of ₹260 on the bourses; Here's what you need to know - CNBC TV18</t>
+          <t>Sai Capital Q1 Results: Standalone and consolidated financials approved - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 12:56:35 IST</t>
+          <t>2026-09-07 21:31:37 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -2098,68 +2086,64 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>ICDSLTD.NS</t>
+          <t>LANDSMILL.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>ICDS Limited</t>
+          <t>Landsmill Green Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>71.55999755859375</v>
+        <v>0.6399999856948853</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>77.69000244140625</v>
+        <v>0.6399999856948853</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>64.30999755859375</v>
+        <v>0.5799999833106995</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>65.18000030517578</v>
+        <v>0.5799999833106995</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>71.44999694824219</v>
+        <v>0.6299999952316284</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>65.18000030517578</v>
+        <v>0.5799999833106995</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>94965</v>
+        <v>6337105</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-8.779999999999999</v>
+        <v>-7.94</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>ICDS Limited (ICDSLTD.NS) Surges Over 7.8%: Strong Momentum or Resistance Ahead? - Bear Pennant - vinanet.vn</t>
+          <t>Landsmill Green promoter declares no share encumbrance in FY26 - scanx.trade</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>ICDS Limited (ICDSLTD.NS): Mild Decline Amid Consolidation, Key Levels Hold - Value ETF - vinanet.vn</t>
+          <t>Landsmill Green promoter declares no share encumbrance in FY26 - scanx.trade</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ICDS Ltd Sees Decline: Stock Slips 3.85% Amidst Key Support Test - Day Trade Opportunities - vinanet.vn</t>
+          <t>Landsmill Green Limited Falls to 52-Week Low of Rs 0.65 as Sell-Off Deepens - MarketsMojo</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>ICDS Share Price - Live NSE: ICDSLTD Stock Price &amp; Chart - Upstox</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>ICDSLTD Stock Price and Chart — NSE:ICDSLTD - TradingView</t>
-        </is>
-      </c>
+          <t>Landsmill Green - 14 penny stocks plunge up to 85% in 6 months. Are you holding any? - The Economic Times</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 12:56:35 IST</t>
+          <t>2026-09-07 21:31:37 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -2167,68 +2151,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>SVGLOBAL.NS</t>
+          <t>SKYWAYS.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>S V Global Mill Limited</t>
+          <t>Skyways Air Services Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>160</v>
+        <v>122.5</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>160</v>
+        <v>123.0899963378906</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>152</v>
+        <v>112</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>152</v>
+        <v>113.9100036621094</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>163.6199951171875</v>
+        <v>122.7200012207031</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>152</v>
+        <v>113.9100036621094</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>15396</v>
+        <v>9717767</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-7.1</v>
+        <v>-7.18</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>S V Global Mill Ltd (SVGLOBAL) Profile, Company FAQs &amp; Facts, Industry, Sector, Employee Strength - Stocktwits</t>
+          <t>Skyways Air Services shares list at 9% discount to IPO price on NSE, BSE - Moneycontrol.com</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>SV Global Mill Ltd. Share Price Rise Streak: Price Action - Univest</t>
+          <t>Skyways Air Services sets ₹0.65 per share dividend record date - scanx.trade</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>SV Global Mill Share Price gains 19.99% amid market focus - Univest</t>
+          <t>Skyways Air Services shares defy GMP expectations, list at 10% discount - Business Standard</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>SV Global Mill Share Price today: price rise and valuation - Univest</t>
+          <t>Skyways Air Services tumble over 10% on market debut - BusinessLine</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>SV Global Mill Ltd. Share Price Fall and Stock Analysis - Univest</t>
+          <t>Skyways Air Services shares list at 10% discount to IPO price, miss Street expectations - Fortune India</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 12:56:35 IST</t>
+          <t>2026-09-07 21:31:37 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -2236,68 +2220,64 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>NAGREEKEXP.NS</t>
+          <t>PAVNAIND.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Nagreeka Exports Limited</t>
+          <t>Pavna Industries Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>22.67000007629395</v>
+        <v>17.60000038146973</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>23.8700008392334</v>
+        <v>17.60000038146973</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>22.20000076293945</v>
+        <v>15.35999965667725</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>22.5</v>
+        <v>16.09000015258789</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>24.10000038146973</v>
+        <v>17.21999931335449</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>22.5</v>
+        <v>16.09000015258789</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>46834</v>
+        <v>304082</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-6.64</v>
+        <v>-6.56</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Nagreeka Exports Limited (NSE: NAGREEKEXP) Falls 5.23% as Stock Movement Draws Market Attention - Kalkine India</t>
+          <t>Pavna Industries Limited agreed to acquire 52.38% stake in Pavna Electric Systems Private Limited for INR 1.7 million. - marketscreener.com</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Nagreeka Exports Limited (NSE: NAGREEKEXP) Falls 5.23% as Stock Movement Draws Market Attention - Kalkine India</t>
+          <t>Pavna Industries Reshapes Subsidiary Portfolio With New Acquisition and Divestments - TipRanks</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Nagreeka Exports Holds Near ₹21.3: Consolidation Persists for NAGREEKEXP on NSE - Rounding Top - siam.in</t>
+          <t>Pavna Industries Reshapes Portfolio With New Subsidiary, Divests Two Units - TipRanks</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>CFEL Stock Price and Chart — NSE:CFEL - TradingView</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>Nagreeka Exports files revised FY26 annual report to fix clerical error - scanx.trade</t>
-        </is>
-      </c>
+          <t>Pavna Industries Reshapes Subsidiary Portfolio With New Acquisition and Divestments - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 12:56:35 IST</t>
+          <t>2026-09-07 21:31:37 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2305,56 +2285,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>RPEL.NS</t>
+          <t>TIMEX.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Raghav Productivity Enhancers Limited</t>
+          <t>Timex Group India Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1819.099975585938</v>
+        <v>672.0999755859375</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1821.5</v>
+        <v>672.1500244140625</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>1635.599975585938</v>
+        <v>617.5999755859375</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>1687.199951171875</v>
+        <v>628.2999877929688</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1807.199951171875</v>
+        <v>669.8499755859375</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1687.199951171875</v>
+        <v>628.2999877929688</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>227646</v>
+        <v>615682</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-6.64</v>
+        <v>-6.2</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Raghav Productivity Enhancers Ltd. Share Price Near High - Univest</t>
+          <t>Stock Market Today | Share Market News | Sensex Today | BSE/NSE Live - NDTV Profit</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Raghav Productivity Enhancers Ltd. Share Price Near High - Univest</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
+          <t>Stock Market Today | Share Market News | Sensex Today | BSE/NSE Live - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>Timex Group India Limited: Target Price Consensus and Analysts Recommendations | TIMEX | INE064A01026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Timex Group India Share Price: 5.42% Fall Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>Timex Group India Gains 5.12% to ₹656.0: Stock Approaches Key Resistance at ₹688.8 - Price Target - siam.in</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 12:56:35 IST</t>
+          <t>2026-09-07 21:31:37 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2362,68 +2354,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>SAICAPI.NS</t>
+          <t>LPDC.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Sai Capital Limited</t>
+          <t>Landmark Property Development Company Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>158.3399963378906</v>
+        <v>6.570000171661377</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>158.3399963378906</v>
+        <v>6.920000076293945</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>147.9299926757812</v>
+        <v>6.050000190734863</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>147.9299926757812</v>
+        <v>6.320000171661377</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>157.5599975585938</v>
+        <v>6.730000019073486</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>147.9299926757812</v>
+        <v>6.320000171661377</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>91</v>
+        <v>188005</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-6.11</v>
+        <v>-6.09</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>SAICAPI Stock Price and Chart — NSE:SAICAPI - TradingView</t>
+          <t>LPDC Q4 FY2026 Earnings: Modest Profit Amid Sluggish Revenue; Stock Declines 1.94% - Earnings Call Transcript - vinanet.vn</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>SAICAPI Stock Price and Chart — NSE:SAICAPI - TradingView</t>
+          <t>Landmark Property Development (LPDC.NS) Edges Higher; Support and Resistance in Focus - Day Trade Opportunities - vinanet.vn</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Sai Capital Ltd. (SAICAPI) News, Articles, Events &amp; Latest Updates - Stocktwits</t>
+          <t>Landmark Property Development (LPDC) Retraces Slightly Amid Low Volume; Support at ₹6.46 in Focus - Statistical Arbitrage - vinanet.vn</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Sai Capital Q1 Results: Standalone and consolidated financials approved - scanx.trade</t>
+          <t>LPDC Stock Price and Chart — NSE:LPDC - TradingView</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>Sai Capital Ltd. (SAICAPI) Share Price Today, Quote, Latest Discussions, Interactive Chart and News - Stocktwits</t>
+          <t>Landmark Property Development (LPDC.NS) Edges Lower; Support and Resistance Levels in Focus - Buyback Factor - vinanet.vn</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 12:56:35 IST</t>
+          <t>2026-09-07 21:31:37 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2431,68 +2423,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>TCC.NS</t>
+          <t>ICDSLTD.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>TCC Concept Limited</t>
+          <t>ICDS Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>44</v>
+        <v>71.55999755859375</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>44.47000122070312</v>
+        <v>77.69000244140625</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>40.70999908447266</v>
+        <v>64.30999755859375</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>41.40999984741211</v>
+        <v>67.31999969482422</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>44.09999847412109</v>
+        <v>71.44999694824219</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>41.40999984741211</v>
+        <v>67.31999969482422</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>406600</v>
+        <v>120496</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-6.1</v>
+        <v>-5.78</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>TCC CONCPAR: Shareholders Board Members Managers and Company Profile | INE887D01016 - marketscreener.com</t>
+          <t>ICDS Limited (ICDSLTD.NS) Surges Over 7.8%: Strong Momentum or Resistance Ahead? - Bear Pennant - vinanet.vn</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>TCC CONCPAR: Shareholders Board Members Managers and Company Profile | INE887D01016 - marketscreener.com</t>
+          <t>ICDS Limited (ICDSLTD.NS): Mild Decline Amid Consolidation, Key Levels Hold - Value ETF - vinanet.vn</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>TCC Concept Stock Falls: Key Levels to Watch - Kalkine India</t>
+          <t>ICDS Ltd Sees Decline: Stock Slips 3.85% Amidst Key Support Test - Day Trade Opportunities - vinanet.vn</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>TCC CONCEPT Consolidated June 2026 Net Sales at Rs 128.28 crore, up 480.19% Y-o-Y - Moneycontrol.com</t>
+          <t>ICDS Share Price - Live NSE: ICDSLTD Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>TCC Concept fixes September 4 record date for 1:5 share split - scanx.trade</t>
+          <t>ICDSLTD Stock Price and Chart — NSE:ICDSLTD - TradingView</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 12:56:35 IST</t>
+          <t>2026-09-07 21:31:37 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2518,19 +2510,19 @@
         <v>1125.699951171875</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1162.300048828125</v>
+        <v>1156.5</v>
       </c>
       <c r="I9" s="2" t="n">
         <v>1227.199951171875</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1162.300048828125</v>
+        <v>1156.5</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>2523836</v>
+        <v>3208260</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-5.29</v>
+        <v>-5.76</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
@@ -2539,7 +2531,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>PVR INOX Limited (NSE: PVRINOX) Falls 6.79% as Stock Movement Draws Market Attention - Kalkine India</t>
+          <t>PVR Inox Denies Rs 200-Crore Kickback Allegations in Stock Exchange Filing - Whalesbook</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -2549,7 +2541,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>PVRINOX Outlook for the Week - equitypandit.com</t>
+          <t>PVRINOX Outlook for the Week - Equitypandit</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -2561,7 +2553,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 12:56:35 IST</t>
+          <t>2026-09-07 21:31:37 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2569,68 +2561,56 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>ANNU.NS</t>
+          <t>TCPLPACK.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Annu Projects Limited</t>
+          <t>TCPL Packaging Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>64.81999969482422</v>
+        <v>4140</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>64.81999969482422</v>
+        <v>4140</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>64.81999969482422</v>
+        <v>3800</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>64.81999969482422</v>
+        <v>3862.39990234375</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>68.23000335693359</v>
+        <v>4091.89990234375</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>64.81999969482422</v>
+        <v>3862.39990234375</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>102987</v>
+        <v>34745</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-5</v>
+        <v>-5.61</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Weak market debut: Annu Projects shares list at over 27% discount to its IPO price - Moneycontrol.com</t>
+          <t>TCPL Packaging Ltd. (TCPLPACK) Share Price Today: Price Action Analysis - Univest</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Annu Projects Ltd. Share Price Today - Annu Projects Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>Annu Projects Shares List at 27% Discount on NSE - Groww</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>Total common shares outstanding of Annu Projects Limited – NSE:ANNU - TradingView</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>Annu Projects Ltd. Share Price Today - Annu Projects Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
-        </is>
-      </c>
+          <t>TCPL Packaging Ltd. (TCPLPACK) Share Price Today: Price Action Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 12:56:35 IST</t>
+          <t>2026-09-07 21:31:37 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2638,56 +2618,56 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>NIRAJISPAT.NS</t>
+          <t>COFFEEDAY.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Niraj Ispat Industries Limited</t>
+          <t>Coffee Day Enterprises Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>368.4500122070312</v>
+        <v>33.09999847412109</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>368.4500122070312</v>
+        <v>34.2599983215332</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>368.4500122070312</v>
+        <v>31</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>368.4500122070312</v>
+        <v>31.1299991607666</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>387.7999877929688</v>
+        <v>32.86000061035156</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>368.4500122070312</v>
+        <v>31.1299991607666</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>70</v>
+        <v>2059008</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-4.99</v>
+        <v>-5.26</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Niraj (NIRAJISPAT.NS) Price Update: Ends Down by 3.00% at ₹205.65 for the Current Session - siam.in</t>
+          <t>Coffee Day Enterprises Jumps Nearly 5% to ₹32.86; Faces Key Hurdle at ₹34.5 - Retail Driven Moves - siam.in</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Precision Wires and 11 Other Stocks That Hit the 20% Upper Circuit Today; Are You Holding Any? - Trade Brains</t>
+          <t>Coffee Day Enterprises Jumps Nearly 5% to ₹32.86; Faces Key Hurdle at ₹34.5 - Retail Driven Moves - siam.in</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Niraj (NIRAJISPAT.NS) Session: Finishes Nearly Flat at ₹216.00; Levels: the ₹205.20 to ₹226.80 Range Remains in Focus in the Available Record - PSAR Stop - siam.in</t>
+          <t>Coffee Day promoter Malavika Hegde releases 18,745 invoked shares - scanx.trade</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Precision Wires and 11 Other Stocks That Hit the 20% Upper Circuit Today; Are You Holding Any? - Trade Brains</t>
+          <t>Coffee Day Enterprises schedules 18th AGM for September 21, 2026 - scanx.trade</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr"/>
@@ -2695,7 +2675,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 12:56:35 IST</t>
+          <t>2026-09-07 21:31:37 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2703,56 +2683,64 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>BIRLACABLE.NS</t>
+          <t>LORDSCHLO.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Birla Cable Limited</t>
+          <t>Lords Chloro Alkali Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>395</v>
+        <v>149</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>395</v>
+        <v>149</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>357.75</v>
+        <v>138.0500030517578</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>357.75</v>
+        <v>138.9299926757812</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>376.5499877929688</v>
+        <v>146.6000061035156</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>357.75</v>
+        <v>138.9299926757812</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>763650</v>
+        <v>20253</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-4.99</v>
+        <v>-5.23</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Birla Cable Limited Files Quarterly Compliance Certificate for Q4 FY26 Under SEBI Regulations - scanx.trade</t>
+          <t>Lords (LORDSCHLO.NS) Earnings Reading: The Report Supplies Updated Headline Figures under the Current Snapshot; Investor Response: Shares Finish 0.40% Higher - EBITDA Estimate Trend - siam.in</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Birla Cable Limited Files Quarterly Compliance Certificate for Q4 FY26 Under SEBI Regulations - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr"/>
-      <c r="P12" s="2" t="inlineStr"/>
+          <t>Lords Chloro Alkali cancels physical investor meet scheduled for September 4 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>Lords (LORDSCHLO.NS) Earnings Reading: The Report Supplies Updated Headline Figures under the Current Snapshot; Investor Response: Shares Finish 0.40% Higher - Earnings Preview - siam.in</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>Lords Chloro Alkali cancels physical investor meet scheduled for September 4 - scanx.trade</t>
+        </is>
+      </c>
       <c r="Q12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 12:56:35 IST</t>
+          <t>2026-09-07 21:31:37 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2760,64 +2748,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>CALSOFT.NS</t>
+          <t>SHYAMTEL.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>California Software Company Limited</t>
+          <t>Shyam Telecom Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>38.93999862670898</v>
+        <v>11.6899995803833</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>38.93999862670898</v>
+        <v>11.6899995803833</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>38.93999862670898</v>
+        <v>10.51000022888184</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>38.93999862670898</v>
+        <v>11</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>40.97999954223633</v>
+        <v>11.60000038146973</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>38.93999862670898</v>
+        <v>11</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>62294</v>
+        <v>15284</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-4.98</v>
+        <v>-5.17</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>CALSOFT Stock Price and Chart — NSE:CALSOFT - TradingView</t>
+          <t>SHYAMTEL Q2 2025 Earnings: Sustained Losses Amid Negligible Revenue - Adjusted Earnings Analysis - vinanet.vn</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>California Software profit rises to ₹411.64 lakh in Q1FY27 - scanx.trade</t>
+          <t>SHYAMTEL Mar 2026 Earnings: Revenue Stays at Zero, EPS Remains Negative Amidst Operational Lull - Debt Analysis Report - vinanet.vn</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>California Software profit rises to ₹411.64 lakh in Q1FY27 - scanx.trade</t>
+          <t>Shyam Telecom (SHYAMTEL.NS) Slides 2% Amid Weak Volume – Key Support at ₹19.16 in Focus - Dynamic Hedging - vinanet.vn</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>GRMN Q2 2026 Earnings: EPS Blowout Beats Estimates by 22.72%, Yet Shares Slip 1.61% - Pre-Earnings Setup - vinanet.vn</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr"/>
+          <t>Shyam Telecom Limited Q4 FY26 Earnings: Zero Revenue and Negative EPS Highlight Persistent Operational Challenges - Financial Summary - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>Shyam Telecom Ltd Share Price Today,, SHYAMTEL Share Price NSE, BSE - Business Today</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 12:56:35 IST</t>
+          <t>2026-09-07 21:31:37 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2825,68 +2817,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>SUPTANERY.NS</t>
+          <t>ANNU.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Super Tannery Limited</t>
+          <t>Annu Projects Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>12.59000015258789</v>
+        <v>64.81999969482422</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>12.59000015258789</v>
+        <v>64.81999969482422</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>12.59000015258789</v>
+        <v>64.81999969482422</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>12.59000015258789</v>
+        <v>64.81999969482422</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>13.25</v>
+        <v>68.23000335693359</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>12.59000015258789</v>
+        <v>64.81999969482422</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>38042</v>
+        <v>124866</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-4.98</v>
+        <v>-5</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>SUPTANERY Stock Price and Chart — NSE:SUPTANERY - TradingView</t>
+          <t>Weak market debut: Annu Projects shares list at over 27% discount to its IPO price - Moneycontrol.com</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Super Tannery Ltd. (SUPTANERY) Profile, Company FAQs &amp; Facts, Industry, Sector, Employee Strength - Stocktwits</t>
+          <t>Annu Projects Ltd. Share Price Today - Annu Projects Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>SUPTANERY Historical Data - equitypandit.com</t>
+          <t>Annu Projects Shares List at 27% Discount on NSE - Groww</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Super Tannery Ltd. (SUPTANERY) Profile, Company FAQs &amp; Facts, Industry, Sector, Employee Strength - Stocktwits</t>
+          <t>Annu Projects shares list at 27% discount on NSE; here's how much investors lost per lot - Upstox</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>Super Tannery Ltd. (SUPTANERY) Fundamental and Financial Data - Stocktwits</t>
+          <t>Annu Projects Ltd. Share Price Today - Annu Projects Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 12:56:35 IST</t>
+          <t>2026-09-07 21:31:37 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2894,68 +2886,60 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>BURNPUR.NS</t>
+          <t>UEL.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Burnpur Cement Limited</t>
+          <t>Ujaas Energy Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>22.6299991607666</v>
+        <v>245.8000030517578</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>22.6299991607666</v>
+        <v>245.8000030517578</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>20.48999977111816</v>
+        <v>229.5200042724609</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>20.48999977111816</v>
+        <v>229.5200042724609</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>21.55999946594238</v>
+        <v>241.6000061035156</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>20.48999977111816</v>
+        <v>229.5200042724609</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>371470</v>
+        <v>34226</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-4.96</v>
+        <v>-5</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Burnpur Cement dispatches web links for 40th AGM and FY26 annual report - scanx.trade</t>
+          <t>Luxembourg's Social Partners Strike Wage Deal — Pay Indexation Pushed to Spring 2027 - AD HOC NEWS</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Price Band Hitters on September 7, 2026 at 12:00 PM - HDFC Sky</t>
+          <t>Luxembourg's Social Partners Strike Wage Deal — Pay Indexation Pushed to Spring 2027 - AD HOC NEWS</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Burnpur Cement Share Price - Upstox</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>Burnpur Cement Ltd Locks at Upper Circuit With 4.96% Gain — Buyers Queue, Sellers Absent - MarketsMojo</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>Burnpur Cement FY26 Results: Net loss widens 87% to ₹792 crore - scanx.trade</t>
-        </is>
-      </c>
+          <t>Ujaas Energy addresses share price movement clarification - Business Upturn</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 12:56:35 IST</t>
+          <t>2026-09-07 21:31:37 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2963,68 +2947,64 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>ELITECON.NS</t>
+          <t>NIRAJISPAT.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Elitecon International Limited</t>
+          <t>Niraj Ispat Industries Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>8.25</v>
+        <v>368.4500122070312</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>8.909999847412109</v>
+        <v>368.4500122070312</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>8.25</v>
+        <v>368.4500122070312</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>8.25</v>
+        <v>368.4500122070312</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>8.680000305175781</v>
+        <v>387.7999877929688</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>8.25</v>
+        <v>368.4500122070312</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>3864394</v>
+        <v>1523</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-4.95</v>
+        <v>-4.99</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Elitecon International Fined ₹1.12 Lakh by BSE for Late Financial Results Submission - scanx.trade</t>
+          <t>Niraj (NIRAJISPAT.NS) Price Update: Ends Down by 3.00% at ₹205.65 for the Current Session - siam.in</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Elitecon International Fined ₹1.12 Lakh by BSE for Late Financial Results Submission - scanx.trade</t>
+          <t>Precision Wires and 11 Other Stocks That Hit the 20% Upper Circuit Today; Are You Holding Any? - Trade Brains</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Elitecon International Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>Niraj (NIRAJISPAT.NS) Session: Finishes Nearly Flat at ₹216.00; Levels: the ₹205.20 to ₹226.80 Range Remains in Focus in the Available Record - PSAR Stop - siam.in</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Small-cap stock under Rs.50 hits 5% upper circuit following stock market rebound - TradingView</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>Elitecon International Declines 4.92% to ₹11.2: Support at ₹10.64 Holds Key - Jurik MA - siam.in</t>
-        </is>
-      </c>
+          <t>Precision Wires and 11 Other Stocks That Hit the 20% Upper Circuit Today; Are You Holding Any? - Trade Brains</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 12:56:35 IST</t>
+          <t>2026-09-07 21:31:37 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -3032,68 +3012,60 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>TIJARIA.NS</t>
+          <t>SETL.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Tijaria Polypipes Limited</t>
+          <t>Standard Engineering Technology Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>9.739999771118164</v>
+        <v>410</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>9.800000190734863</v>
+        <v>412.7999877929688</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>9.069999694824219</v>
+        <v>388.5499877929688</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>9.069999694824219</v>
+        <v>388.5499877929688</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>9.539999961853027</v>
+        <v>408.9500122070312</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>9.069999694824219</v>
+        <v>388.5499877929688</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>141636</v>
+        <v>1260676</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-4.93</v>
+        <v>-4.99</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Tijaria Polypipes (NSE: TIJARIA) Gains Momentum - Kalkine India</t>
+          <t>SETL Share Price News after yearly high and valuation check - Univest</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Tijaria Polypipes Ltd Locks at Upper Circuit With 4.95% Gain — Buyers Queue, Sellers Absent - MarketsMojo</t>
+          <t>SETL Share Price News after yearly high and valuation check - Univest</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Tijaria Polypipes Ltd Locks at Upper Circuit With 4.95% Gain — Buyers Queue, Sellers Absent - MarketsMojo</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>Tijaria Polypipes (NSE: TIJARIA) Sees Sharp Upmove - Kalkine India</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>Tijaria Polypipes posts ₹36.11 crore loss in Q1FY27 as revenue remains zero - scanx.trade</t>
-        </is>
-      </c>
+          <t>Standard (SETL.NS) Results Check: The Report Provides a New Financial Snapshot for the Current Session; Market Reaction: The Stock Ends Down 2.36% for the Current Session - EPS Revision Trend - siam.in</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 12:56:35 IST</t>
+          <t>2026-09-07 21:31:37 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -3101,68 +3073,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>EASTSILK.NS</t>
+          <t>SUPTANERY.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Eastern Silk Industries Limited</t>
+          <t>Super Tannery Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>60.79999923706055</v>
+        <v>12.59000015258789</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>60.79999923706055</v>
+        <v>12.59000015258789</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>58.02000045776367</v>
+        <v>12.59000015258789</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>58.04000091552734</v>
+        <v>12.59000015258789</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>61</v>
+        <v>13.25</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>58.04000091552734</v>
+        <v>12.59000015258789</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>330</v>
+        <v>37276</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-4.85</v>
+        <v>-4.98</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Eastern Silk Industries Limited Schedules Board Meeting on May 27, 2026 to Approve FY26 Audited Financial Results - scanx.trade</t>
+          <t>SUPTANERY Stock Price and Chart — NSE:SUPTANERY - TradingView</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>EASTSILK Q2 2026 Earnings: Revenue Grows 8.48% to ₹23.71 Crore, but EPS Loss of ₹27.2 Dents Sentiment - siam.in</t>
+          <t>Super Tannery Ltd. (SUPTANERY) Profile, Company FAQs &amp; Facts, Industry, Sector, Employee Strength - Stocktwits</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>EASTSILK Q2 2026 Earnings: Revenue Grows 8.48% to ₹23.71 Crore, but EPS Loss of ₹27.2 Dents Sentiment - siam.in</t>
+          <t>SUPTANERY Historical Data - Equitypandit</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Eastern Silk Industries Trades Flat Near ₹50.5; Key Support and Resistance Levels in Focus - Beta Neutral Pair - vinanet.vn</t>
+          <t>Super Tannery Ltd. (SUPTANERY) Profile, Company FAQs &amp; Facts, Industry, Sector, Employee Strength - Stocktwits</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>Eastern Silk Industries Limited Announces Q3 FY26 Financial Results - scanx.trade</t>
+          <t>Super Tannery Ltd. (SUPTANERY) Fundamental and Financial Data - Stocktwits</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 12:56:35 IST</t>
+          <t>2026-09-07 21:31:37 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -3170,68 +3142,64 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>PIONRINV.NS</t>
+          <t>RBZJEWEL.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Pioneer Investcorp Limited</t>
+          <t>RBZ Jewellers Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>79.75</v>
+        <v>198.9900054931641</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>79.84999847412109</v>
+        <v>199</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>79.75</v>
+        <v>186.1799926757812</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>79.84999847412109</v>
+        <v>190.7100067138672</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>83.88999938964844</v>
+        <v>200.6900024414062</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>79.84999847412109</v>
+        <v>190.7100067138672</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>1426</v>
+        <v>1088746</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-4.82</v>
+        <v>-4.97</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Pioneer Investcorp Limited (PIONRINV.NS) Mar 2026 Earnings: EPS of ₹2.18 Reported Amid Modest Revenue; Stock Declines 3.55% - Revenue Growth Report - vinanet.vn</t>
+          <t>With EPS Growth And More, RBZ Jewellers (NSE:RBZJEWEL) Makes An Interesting Case - simplywall.st</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Pioneer Investcorp Limited (PIONRINV.NS) Mar 2026 Earnings: EPS of ₹2.18 Reported Amid Modest Revenue; Stock Declines 3.55% - Revenue Growth Report - vinanet.vn</t>
+          <t>With EPS Growth And More, RBZ Jewellers (NSE:RBZJEWEL) Makes An Interesting Case - simplywall.st</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Technical Analysis of Pioneer Investcorp Limited (NSE:PIONRINV) - TradingView</t>
+          <t>RBZ (RBZJEWEL.NS) Move: Finishes 3.13% Higher at ₹139.70; Price Context: the Near-Term Reference Band Stretches From ₹132.71 to ₹146.69 in the Latest Session - Breakout Stock Alerts - siam.in</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Pioneer Investcorp (PIONRINV.NS) Slips 3.26%: Support at ₹85.5 in Focus - Momentum Surge Alerts - vinanet.vn</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>Pioneer Investcorp Limited (PIONRINV.NS) Mar 2026 Earnings: Net Profit Scales Higher – EPS of ₹2.18; Revenue at ₹1.9 Crore - Performance Review - vinanet.vn</t>
-        </is>
-      </c>
+          <t>RBZ Jewellers (RBZJEWEL.NS) Edges Higher: Stock Gains 1.44% Amid Steady Demand - Trend Reversal Picks - siam.in</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 12:56:35 IST</t>
+          <t>2026-09-07 21:31:37 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -3239,68 +3207,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>DIVGIITTS.NS</t>
+          <t>BURNPUR.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Divgi Torqtransfer Systems Limited</t>
+          <t>Burnpur Cement Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1242</v>
+        <v>22.6299991607666</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1285.199951171875</v>
+        <v>22.6299991607666</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>1155.199951171875</v>
+        <v>20.48999977111816</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>1176.5</v>
+        <v>20.48999977111816</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1235.800048828125</v>
+        <v>21.55999946594238</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1176.5</v>
+        <v>20.48999977111816</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>167874</v>
+        <v>377775</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-4.8</v>
+        <v>-4.96</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Divgi (DIVGIITTS.NS) Session: Finishes 2.96% Down at ₹1,226.05; Level Watch: the Supplied Trading Band Runs From ₹1,164.75 to ₹1,287.35 in Latest Trading - Momentum Trade - siam.in</t>
+          <t>Price Band Hitters on September 7, 2026 at 12:00 PM - HDFC Sky</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Divgi TorqTransfer Systems to Meet Investors in Non-Deal Roadshow - TipRanks</t>
+          <t>Price Band Hitters on September 7, 2026 at 4:00 PM - HDFC Sky</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Divgi Torqtransfer Slips 0.99% to ₹1219.75: Key Support and Resistance Levels in Focus - Sector Leader Stocks - siam.in</t>
+          <t>Burnpur Cement dispatches web links for 40th AGM and FY26 annual report - scanx.trade</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Divgi Torqtransfer Systems Share Price Hits One-Year High - Univest</t>
+          <t>Burnpur Cement Ltd. Peer Comparison – Compare with Others - Value Research</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Divgi TorqTransfer Stock Surges 13% As Q1 FY27 PAT Jumps 183% To ₹25.2 Cr - Trade Brains</t>
+          <t>Burnpur Cement Share Price - Upstox</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 12:56:35 IST</t>
+          <t>2026-09-07 21:31:37 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -3308,61 +3276,61 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>BETA.NS</t>
+          <t>ELITECON.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Beta Drugs Limited</t>
+          <t>Elitecon International Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>2204</v>
+        <v>8.25</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>2204</v>
+        <v>8.909999847412109</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>2087.89990234375</v>
+        <v>8.25</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>2114.60009765625</v>
+        <v>8.25</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>2218.5</v>
+        <v>8.680000305175781</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>2114.60009765625</v>
+        <v>8.25</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>34067</v>
+        <v>4027315</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-4.68</v>
+        <v>-4.95</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Beta bionics CEO Sean Saint sells $113,258 in company stock - Investing.com India</t>
+          <t>Elitecon International Fined ₹1.12 Lakh by BSE for Late Financial Results Submission - scanx.trade</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Beta Technologies terminates security control agreement with US Defense Department - scanx.trade</t>
+          <t>Elitecon International Fined ₹1.12 Lakh by BSE for Late Financial Results Submission - scanx.trade</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Beta Technologies terminates security control agreement with US Defense Department - scanx.trade</t>
+          <t>Elitecon International Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>What Is the Beta of a Stock? Meaning &amp; Formula - Britannica</t>
+          <t>Small-cap stock under Rs.50 hits 5% upper circuit following stock market rebound - TradingView</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>Independent Director of BETA Technologies Picks Up 1.5% More Stock - simplywall.st</t>
+          <t>Elitecon International Declines 4.92% to ₹11.2: Support at ₹10.64 Holds Key - Jurik MA - siam.in</t>
         </is>
       </c>
     </row>

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -439,12 +439,12 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="37" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:31:37 IST</t>
+          <t>2026-09-08 12:54:21 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -553,68 +553,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>UDAYJEW.NS</t>
+          <t>GENESYS.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Uday Jewellery Industries Limited</t>
+          <t>Genesys International Corporation Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>168.3999938964844</v>
+        <v>240.25</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>171.6000061035156</v>
+        <v>287.7999877929688</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>148</v>
+        <v>239.5</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>167.5800018310547</v>
+        <v>282.510009765625</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>143</v>
+        <v>240.1600036621094</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>167.5800018310547</v>
+        <v>282.510009765625</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>638450</v>
+        <v>7356997</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>17.19</v>
+        <v>17.63</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Uday Jewellery Industries Share Price Rises 8.82% Today - Univest</t>
+          <t>Genesys International Corp files FY26 business responsibility report - scanx.trade</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Uday Jewellery Industries Share Price Rises 8.82% Today - Univest</t>
+          <t>Genesys International Corp files FY26 business responsibility report - scanx.trade</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Uday Jewellery Industries Ltd. (UDAYJEW) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
+          <t>Genesys International Corporation Ltd (NSE: GENESYS) Gains 10.74% as Stock Movement Draws Market Attention - Kalkine India</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Technical Analysis of Uday Jewellery Industries Ltd. (NSE:UDAYJEW) - TradingView</t>
+          <t>Genesys International Corporation Ltd. - RE Share Price Live Today - CNBC TV18</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Uday Jewellery Promoters Acquire 73.34 Lakh Shares Through Merger Scheme - scanx.trade</t>
+          <t>Genesys International Corporation Share: Geospatial Buy? - Univest</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:31:37 IST</t>
+          <t>2026-09-08 12:54:21 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -622,68 +622,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>CENTUM.NS</t>
+          <t>ASTEC.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Centum Electronics Limited</t>
+          <t>Astec LifeSciences Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>3778.199951171875</v>
+        <v>551.2000122070312</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>4420</v>
+        <v>649</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>3778.199951171875</v>
+        <v>551.2000122070312</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>4376.89990234375</v>
+        <v>645</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>3767.300048828125</v>
+        <v>552.3499755859375</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>4376.89990234375</v>
+        <v>645</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>826784</v>
+        <v>1048331</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>16.18</v>
+        <v>16.77</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Centum Electronics Share Price Today Near One-Year High - Univest</t>
+          <t>Astec Lifesciences Share Price rises 9.49% on price action - Univest</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Centum Electronics Share Price Today Near One-Year High - Univest</t>
+          <t>Astec Lifesciences Share Price rises 9.49% on price action - Univest</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Centum Electronics Ltd. Stock News - Value Research</t>
+          <t>Astec (ASTE) Shares: Finishes 4.01% Up at $43.55 in the Latest Reading; Next Test: the Session Ends Within the Reported Technical Boundaries in the Current Update - Market Profile - siam.in</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Centum Electronics Ltd. Share Price Today: key stock move - Univest</t>
+          <t>Astec Life Consolidated June 2026 Net Sales at Rs 83.56 crore, down 8.25% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>CTUM stock gains on Nairobi exchange as investors watch Centum fundamentals - AD HOC NEWS</t>
+          <t>Implied Volatility Surging for Astec Industries Stock Options - Yahoo Finance</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:31:37 IST</t>
+          <t>2026-09-08 12:54:21 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -691,68 +691,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>MITTAL.NS</t>
+          <t>WHEELS.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Mittal Life Style Limited</t>
+          <t>Wheels India Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.8199999928474426</v>
+        <v>1760.900024414062</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9599999785423279</v>
+        <v>1990.900024414062</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.8100000023841858</v>
+        <v>1760.900024414062</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.9200000166893005</v>
+        <v>1987.300048828125</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.800000011920929</v>
+        <v>1755.400024414062</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.9200000166893005</v>
+        <v>1987.300048828125</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>11565075</v>
+        <v>1155610</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>15</v>
+        <v>13.21</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Mittal Life Style Limited (NSE: MITTAL) Gains 13.75% as Stock Movement Draws Market Attention - Kalkine India</t>
+          <t>Wheels India Ltd. Stock News - Value Research</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Mittal Life Style Limited (NSE: MITTAL) Gains 13.75% as Stock Movement Draws Market Attention - Kalkine India</t>
+          <t>Wheels India hosts investor conference call from Sep 7 to Sep 9 - scanx.trade</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>BCL Industries Promoter Rajinder Mittal Continues Share Acquisition Spree - scanx.trade</t>
+          <t>Wheels India hosts investor conference call from Sep 7 to Sep 9 - scanx.trade</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Divya Mittal’s digital diary: 'Don’t fight the Sirens. Tie yourself to the mast' - The Times of India</t>
+          <t>Ck Wheels LLC sells $43,163 of Wheels Up Experience stock - Investing.com India</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>"Hate This": Cancer Survivor Chhavi Mittal Shares Health Update After Fibroid Surgery - NDTV</t>
+          <t>Wheels India Share Price News: Price Rise and Valuation - Univest</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:31:37 IST</t>
+          <t>2026-09-08 12:54:21 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -760,68 +760,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>GNRL.NS</t>
+          <t>CORDSCABLE.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Gujarat Natural Resources Limited</t>
+          <t>Cords Cable Industries Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>100</v>
+        <v>314.8500061035156</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>116.3300018310547</v>
+        <v>365.2999877929688</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>100</v>
+        <v>303</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>113.9599990844727</v>
+        <v>353.8999938964844</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>99.26999664306641</v>
+        <v>313.3500061035156</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>113.9599990844727</v>
+        <v>353.8999938964844</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>3632884</v>
+        <v>906581</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>14.8</v>
+        <v>12.94</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>GNRL Jun 2026 Earnings: EPS of ₹0.69 Reported with Nil Revenue; Stock Falls 6.87% - Earnings Whisper Number - siam.in</t>
+          <t>Here's Why Cords Cable Industries (NSE:CORDSCABLE) Has Caught The Eye Of Investors - simplywall.st</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>GNRL Shares Surge 12% As Post-Monsoon Drilling Program Resumes - Trade Brains</t>
+          <t>Cords Cable Industries Share Price Gain With Valuation View - Univest</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>GNRL.NS Jun 2026 Earnings: EPS at ₹0.69 Despite Nil Revenue; Shares Slip 2.72% - Analyst Coverage Count - siam.in</t>
+          <t>Cords Cable Industries Share Price Gain With Valuation View - Univest</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Gujarat Natural Resources Share Price Rises 13.47% Today - Univest</t>
+          <t>Cords Cable Industries sets August 31 deadline for dividend TDS declarations - scanx.trade</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>Gujarat Natural Resources Share Price Rises 8.06% Today - Univest</t>
+          <t>Cords Cable Q1 Results: Net profit up 102% YoY to ₹7.8 crore - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:31:37 IST</t>
+          <t>2026-09-08 12:54:21 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -829,68 +829,64 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>RADHIKAJWE.NS</t>
+          <t>GVT&amp;D.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Radhika Jeweltech Limited</t>
+          <t>GE Vernova T&amp;D India Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>84.62000274658203</v>
+        <v>4636.10009765625</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>97.40000152587891</v>
+        <v>4785.89990234375</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>84.61000061035156</v>
+        <v>4610</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>94.27999877929688</v>
+        <v>4776</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>83.16000366210938</v>
+        <v>4367.2001953125</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>94.27999877929688</v>
+        <v>4776</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>31904994</v>
+        <v>3415263</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>13.37</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Here's Why Radhika Jeweltech (NSE:RADHIKAJWE) Has Caught The Eye Of Investors - simplywall.st</t>
+          <t>GE Vernova T&amp;D India (NSE:GVT&amp;D) Could Be A Buy For Its Upcoming Dividend - simplywall.st</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Radhika Jeweltech Surges 13%: Key Levels and Momentum Analysis - Channel Breakout - vinanet.vn</t>
+          <t>GE Vernova T&amp;D India to transfer shares to IEPF on August 27, 2026 - scanx.trade</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Radhika Jeweltech (RADHIKAJWE.NS) Eases Marginally: Key Support and Resistance Levels in Focus - Factor Timing - vinanet.vn</t>
+          <t>GE Vernova T&amp;D India Share Price Today and Stock Analysis - Univest</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>RADHIKAJWE Stock Price and Chart — NSE:RADHIKAJWE - TradingView</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>RADHIKAJWE Share Price Today - Radhika Jeweltech Ltd. Stock Price Live NSE/BSE - Univest</t>
-        </is>
-      </c>
+          <t>GE Vernova T&amp;D India to transfer shares to IEPF on August 27, 2026 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:31:37 IST</t>
+          <t>2026-09-08 12:54:21 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -898,68 +894,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>RIR.NS</t>
+          <t>DUCON.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>RIR Power Electronics Limited</t>
+          <t>Ducon Infratechnologies Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>175.0399932861328</v>
+        <v>1.789999961853027</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>203.8300018310547</v>
+        <v>1.980000019073486</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>175.0399932861328</v>
+        <v>1.779999971389771</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>191.9499969482422</v>
+        <v>1.950000047683716</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>169.8600006103516</v>
+        <v>1.789999961853027</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>191.9499969482422</v>
+        <v>1.950000047683716</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>11233563</v>
+        <v>1423816</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>13</v>
+        <v>8.94</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>RIR Power Electronics Limited (NSE: RIR) Gains 11.90% as Stock Movement Draws Market Attention - Kalkine India</t>
+          <t>EBITDA margin % of Ducon Infratechnologies Ltd. Rights 2026-10.09.26 On Shares – NSE:DUCON_RE1 - tradingview.com</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>RIR Power Electronics Limited (NSE: RIR) Gains 11.90% as Stock Movement Draws Market Attention - Kalkine India</t>
+          <t>EBITDA margin % of Ducon Infratechnologies Ltd. Rights 2026-10.09.26 On Shares – NSE:DUCON_RE1 - tradingview.com</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Volume shocker stocks today: Why Innovassynth, RIR Power, Pashupati Cotspin, Zydus Wellness are soaring - Details here - Livemint</t>
+          <t>Ducon Infratechnologies approves rights issue of up to ₹25 Crore - scanx.trade</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>RIR Share Price Rises 11.78%: Price and Valuation - Univest</t>
+          <t>Ducon Infratechnologies Ltd. Rights 2026-10.09.26 On Shares Income Statement – NSE:DUCON_RE1 - tradingview.com</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>RIR Power Electronics sets Sept 22 record date for final dividend - scanx.trade</t>
+          <t>Ducon Infratechnologies Ltd. Rights 2026-10.09.26 On Shares Balance Sheet – BSE:DUCON_RE1 - tradingview.com</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:31:37 IST</t>
+          <t>2026-09-08 12:54:21 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -967,68 +963,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>SYRMA.NS</t>
+          <t>BCG.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Syrma SGS Technology Limited</t>
+          <t>Brightcom Group Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1458.5</v>
+        <v>9.699999809265137</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1645</v>
+        <v>11.18000030517578</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1458.300048828125</v>
+        <v>9.670000076293945</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1634.800048828125</v>
+        <v>10.43000030517578</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1457.300048828125</v>
+        <v>9.619999885559082</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1634.800048828125</v>
+        <v>10.43000030517578</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>13076470</v>
+        <v>56429631</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>12.18</v>
+        <v>8.42</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Record High: Syrma SGS Technology shares extend gains for third-consecutive day, surge nearly 12% — Here's why - CNBC TV18</t>
+          <t>Binah Capital Group (BCG) Edges Higher: Stock Holds Above Support at $1.41 - Active ETF Flow - siam.in</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Smallcap 500 index hits 52-week high; Syrma, Strides, Avalon soar up to 12% - Business Standard</t>
+          <t>IBRX Stock’s Decline Makes Retail See ‘Incredible’ Buying Opportunity After Anktiva + BCG Therapy Delivered Favorable Results - Stocktwits</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Zydus Wellness, Syrma SGS, PVR Inox shares spurt amid heavy volumes; check full list - Upstox</t>
+          <t>Baltic Classifieds Group PLC (BCG.L) Stock Analysis: Exploring A 11.61% Potential Upside - DirectorsTalk Interviews</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Smallcap 500 index hits 52-week high; Syrma, Strides, Avalon soar up to 12% - Business Standard</t>
+          <t>IBRX Stock Jumps 6% Pre-Market On BCG Update In Saudi Arabia – Retail Says Share Price Is ‘Attractive’ - Stocktwits</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Syrma SGS Technology Stock Surges Over 3% After ECMS Application Gets Approved By Govt - NDTV Profit</t>
+          <t>IBRX Stock’s Decline Makes Retail See ‘Incredible’ Buying Opportunity After Anktiva + BCG Therapy Delivered Favorable Results - Stocktwits</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:31:37 IST</t>
+          <t>2026-09-08 12:54:21 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1036,56 +1032,60 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>ANUHPHR.NS</t>
+          <t>NOVARTIND.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Anuh Pharma Limited</t>
+          <t>Novartis India Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>82.69999694824219</v>
+        <v>1659</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>91.80000305175781</v>
+        <v>1856</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>82</v>
+        <v>1640.099975585938</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>90.29000091552734</v>
+        <v>1766.199951171875</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>81.09999847412109</v>
+        <v>1639.599975585938</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>90.29000091552734</v>
+        <v>1766.199951171875</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>1068438</v>
+        <v>319276</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>11.33</v>
+        <v>7.72</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Anuh (ANUHPHR.NS) Update: Falls 1.28% to ₹77.82 in the Latest Reading; Price Context: the Supplied Trading Band Runs From ₹73.93 to ₹81.71 in the Available Record - Volume Gap - siam.in</t>
+          <t>Novartis (NOVARTIND.NS) Financial Update: The Company Lists Its Latest Available Figures; Stock Move: Shares Close 1.06% Lower - Earnings Weakness Phase - siam.in</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Anuh (ANUHPHR.NS) Update: Falls 1.28% to ₹77.82 in the Latest Reading; Price Context: the Supplied Trading Band Runs From ₹73.93 to ₹81.71 in the Available Record - Volume Gap - siam.in</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr"/>
+          <t>Novartis India Share Price Update With Valuation Context - Univest</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>Novartis India Share Price Update With Valuation Context - Univest</t>
+        </is>
+      </c>
       <c r="P9" s="2" t="inlineStr"/>
       <c r="Q9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:31:37 IST</t>
+          <t>2026-09-08 12:54:21 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1093,68 +1093,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>STAR.NS</t>
+          <t>NKIND.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Strides Pharma Science Limited</t>
+          <t>NK Industries Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1058.699951171875</v>
+        <v>65.80000305175781</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1187.599975585938</v>
+        <v>65.80000305175781</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>1045</v>
+        <v>58.65000152587891</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>1178.800048828125</v>
+        <v>61.38999938964844</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1059.599975585938</v>
+        <v>57.20999908447266</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1178.800048828125</v>
+        <v>61.38999938964844</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>2617100</v>
+        <v>2426</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>11.25</v>
+        <v>7.31</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Asia tech shares rally, others hesitant as oil rises - The Star</t>
+          <t>NK Industries Stock Near Key Technical Levels - Kalkine India</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Barbara Eden, 95, shares health update after dropping out of festival at last minute - The Independent</t>
+          <t>NK Industries Stock Near Key Technical Levels - Kalkine India</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Northern Star Resources Director Jeffrey Quartermaine Acquires 10,000 Shares On-Market - kalkine.com.au</t>
+          <t>N.K. Industries Limited Auditor Raises 'Going Concern' Doubt - marketscreener.com</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Evan, formerly ENHYPEN’s Heeseung, reveals his cancer battle for the first time - t2ONLINE</t>
+          <t>Spire (SRJN) Q2 2026 Earnings: EPS Comes in Above Forecast in the Current Update; After Results - vinanet.vn</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>5-Star Analyst Resets Intel Stock Price Target on Weaker PC Demand - TradingView</t>
+          <t>Fennec (FENC) Technical Check: Adds 0.51% to Close at $11.89 at the Close; Current Setup: the Supplied Trading Band Runs From $11.30 to $12.48 - Throwback Trade - vinanet.vn</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:31:37 IST</t>
+          <t>2026-09-08 12:54:21 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1162,68 +1162,60 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>SUNSHIEL.NS</t>
+          <t>ANUHPHR.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Sunshield Chemicals Limited</t>
+          <t>Anuh Pharma Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1175</v>
+        <v>92</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1275</v>
+        <v>99.5</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>1155</v>
+        <v>91.79000091552734</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>1268.599975585938</v>
+        <v>96.41999816894531</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1144.900024414062</v>
+        <v>90.29000091552734</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1268.599975585938</v>
+        <v>96.41999816894531</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>13356</v>
+        <v>1431986</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>10.8</v>
+        <v>6.79</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>SUNSHIEL Stock Price and Chart — NSE:SUNSHIEL - TradingView</t>
+          <t>Anuh (ANUHPHR.NS) Update: Falls 1.28% to ₹77.82 in the Latest Reading; Price Context: the Supplied Trading Band Runs From ₹73.93 to ₹81.71 in the Available Record - Volume Gap - siam.in</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Sunshield Chemicals Share Price: valuation and sector view - Univest</t>
+          <t>Anuh Pharma Share Price Today up 11.12% on price action - Univest</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Sunshield Chemicals Share Price: valuation and sector view - Univest</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>Free float of Sunshield Chemicals Limited – NSE:SUNSHIEL - TradingView</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>Sunshield Chemicals Ltd. (SUNSHIEL) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
-        </is>
-      </c>
+          <t>Anuh Pharma Share Price Today up 11.12% on price action - Univest</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:31:37 IST</t>
+          <t>2026-09-08 12:54:21 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1231,56 +1223,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>VENUSPIPES.NS</t>
+          <t>FINCABLES.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Venus Pipes &amp; Tubes Limited</t>
+          <t>Finolex Cables Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1639.800048828125</v>
+        <v>1235.099975585938</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1821</v>
+        <v>1303.699951171875</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>1639.800048828125</v>
+        <v>1230.199951171875</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1805.400024414062</v>
+        <v>1301</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1631</v>
+        <v>1227</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1805.400024414062</v>
+        <v>1301</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>603232</v>
+        <v>852693</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>10.69</v>
+        <v>6.03</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Venus Pipes &amp; Tubes Gains 1.22% to ₹1596.5: Stock Approaches Key Resistance on NSE - Trading Ideas - siam.in</t>
+          <t>Finolex Cables shares hit 52-week high for the second straight session; here is what's driving the rally - Upstox</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Venus Pipes &amp; Tubes Gains 1.22% to ₹1596.5: Stock Approaches Key Resistance on NSE - Trading Ideas - siam.in</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr"/>
-      <c r="P12" s="2" t="inlineStr"/>
-      <c r="Q12" s="2" t="inlineStr"/>
+          <t>Finolex Cables Share Price today: valuation and sector view - Univest</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>Finolex Cables Share Price News: Mid Cap Top Gainer Today - Univest</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>Finolex Cables Share Price today: valuation and sector view - Univest</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>Finolex Cables Limited announces Annual dividend, payable on October 27, 2026 - marketscreener.com</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:31:37 IST</t>
+          <t>2026-09-08 12:54:21 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1288,68 +1292,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>THEMISMED.NS</t>
+          <t>PVRINOX.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Themis Medicare Limited</t>
+          <t>PVR INOX Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>121.379997253418</v>
+        <v>1161.5</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>140.6000061035156</v>
+        <v>1243</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>119.1699981689453</v>
+        <v>1153.599975585938</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>133.0700073242188</v>
+        <v>1222.699951171875</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>120.4199981689453</v>
+        <v>1156.5</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>133.0700073242188</v>
+        <v>1222.699951171875</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>4732288</v>
+        <v>1384338</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>10.5</v>
+        <v>5.72</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Themis Medicare Holds Gains at ₹104.51: Key Levels to Monitor for THEMISMED.NS - Jurik MA - siam.in</t>
+          <t>PVR INOX Limited (NSE: PVRINOX) Falls 6.79% as Stock Movement Draws Market Attention - Kalkine India</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Themis Medicare Says No Undisclosed News Behind Share Volume Surge - TipRanks</t>
+          <t>PVR Inox Share Price rise: key price action and valuation - Univest</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>THEMISMED Share Price News: Price Action and Fundamentals - Univest</t>
+          <t>PVR INOX Limited announces an Equity Buyback for 2,068,965 shares, representing 2.11% for INR 3,000 million. - marketscreener.com</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Themis Medicare Share Price Today: price rise and valuation - Univest</t>
+          <t>PVRINOX Outlook for the Week - Equitypandit</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>Themis Medicare Says No Undisclosed News Behind Share Volume Surge - TipRanks</t>
+          <t>PVR INOX shares tumble over 8%; why are shares falling today? - Upstox</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:31:37 IST</t>
+          <t>2026-09-08 12:54:21 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1357,68 +1361,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>MGEL.NS</t>
+          <t>KABRAEXTRU.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Mangalam Global Enterprise Limited</t>
+          <t>Kabra Extrusion Technik Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>14.85999965667725</v>
+        <v>639.5</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>17.07999992370605</v>
+        <v>677.75</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>13</v>
+        <v>639</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>15.72000026702881</v>
+        <v>669.6500244140625</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>14.23999977111816</v>
+        <v>634.5</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>15.72000026702881</v>
+        <v>669.6500244140625</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1420121</v>
+        <v>394706</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>10.39</v>
+        <v>5.54</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>MGEL appoints Darshak Mehta as CEO of NEAT Everyday - Business Standard</t>
+          <t>Kabra Extrusion Technik Gains 5.93% to ₹513, Approaches Key Resistance at ₹538.65 - Strangle Setup - siam.in</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Mangalam Global changes designation of director - scanx.trade</t>
+          <t>Kabra Extrusion Technik Surges 9% After Receiving Letter Of Nomination From Vietnamese Auto OEM - Trade Brains</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Mangalam (MGEL.NS) Quarterly Figures: Available Data Shows the Latest Reported Performance in the Latest Reading; Market Move: Shares Finish 0.88% Lower in the Latest Session - Pretax Income Report - siam.in</t>
+          <t>Kabra Extrusiontechnik KABRAEXTRU Preferential Issue Allottee Change - Kalkine India</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Mangalam Global Enterprise Limited Announces Appointment of Darshak Mehta to Chief Executive Officer for the Brand 'NEAT EVERYDAY', Effective September 01, 2026 - marketscreener.com</t>
+          <t>Kabra Extrusiontechnik Share Price rises 8.59%: analysis - Univest</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>Mangalam Global changes designation of director - scanx.trade</t>
+          <t>Kabra Extrusiontechnik Ltd. (KABRAEXTRU) Share Price Rises 8.33% Today - Univest</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:31:37 IST</t>
+          <t>2026-09-08 12:54:21 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1426,56 +1430,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>ORIENTPPR.NS</t>
+          <t>TDPOWERSYS.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Orient Paper &amp; Industries Limited</t>
+          <t>TD Power Systems Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>17.03000068664551</v>
+        <v>736</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>19.28000068664551</v>
+        <v>778.8499755859375</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>16.85000038146973</v>
+        <v>736</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>18.80999946594238</v>
+        <v>774.6500244140625</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>17.07999992370605</v>
+        <v>734.1500244140625</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>18.80999946594238</v>
+        <v>774.6500244140625</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>2023696</v>
+        <v>1566643</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>10.13</v>
+        <v>5.52</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>BioMarin (BMRN) Earnings Update: The EPS Result Is Above Expectation in the Current Update; Latest Reaction: The Stock Records a 1.45% Decrease in Latest Trading - EPS Consistency Score - vinanet.vn</t>
+          <t>Brokers Are Upgrading Their Views On TD Power Systems Limited (NSE:TDPOWERSYS) With These New Forecasts - simplywall.st</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>BioMarin (BMRN) Earnings Update: The EPS Result Is Above Expectation in the Current Update; Latest Reaction: The Stock Records a 1.45% Decrease in Latest Trading - EPS Consistency Score - vinanet.vn</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr"/>
-      <c r="P15" s="2" t="inlineStr"/>
-      <c r="Q15" s="2" t="inlineStr"/>
+          <t>TD Power Systems: Promoter Group Adjusts Ownership - InvestyWise</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>TD Power Systems Publishes EGM Notices in Line with MCA Compliance Norms - The Globe and Mail</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>TD Power System shares surge most in over a year, hit 52-week high; here’s why - Upstox</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>Up 27x in 5 yrs! Why this multibagger smallcap stock showing 50% fall in some trading apps today? - Business Today</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:31:37 IST</t>
+          <t>2026-09-08 12:54:21 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1483,68 +1499,64 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>BODALCHEM.NS</t>
+          <t>JUBLPHARMA.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Bodal Chemicals Limited</t>
+          <t>Jubilant Pharmova Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>168</v>
+        <v>956</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>171.1799926757812</v>
+        <v>1021.549987792969</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>162.8000030517578</v>
+        <v>953.2999877929688</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>171.1799926757812</v>
+        <v>999.7999877929688</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>155.6199951171875</v>
+        <v>950.2999877929688</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>171.1799926757812</v>
+        <v>999.7999877929688</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>4910182</v>
+        <v>989371</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>10</v>
+        <v>5.21</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>With EPS Growth And More, Bodal Chemicals (NSE:BODALCHEM) Makes An Interesting Case - simplywall.st</t>
+          <t>Jubilant Pharmova files Q1FY27 unaudited financial results for review - scanx.trade</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Bodal Chemicals Sets Virtual AGM to Approve FY26 Accounts and Board Changes - TipRanks</t>
+          <t>Jubilant Pharmova Opens Special Window for Physical Share Transfers and KYC Update - tipranks.com</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Bodal Chemicals Share Price news with valuation context - Univest</t>
+          <t>Buzzing Stocks: Meesho shares slip on block deal; Apollo Tyres gains 2% after UBS upgrade to ‘buy’ - tradingview.com</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Bodal Chemicals Ltd. (BODALCHEM) Share Price Rises 9.21% Today; Key Levels, Valuation and Peer View - Univest</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>Bodal Chemicals Sets Virtual AGM to Approve FY26 Accounts and Board Changes - TipRanks</t>
-        </is>
-      </c>
+          <t>Jubilant Pharmova Opens Special Window for Physical Share Transfers and KYC Update - tipranks.com</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:31:37 IST</t>
+          <t>2026-09-08 12:54:21 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1552,68 +1564,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>FCL.NS</t>
+          <t>TAKE.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Fineotex Chemical Limited</t>
+          <t>TAKE Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>52.25</v>
+        <v>15.22999954223633</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>56.65999984741211</v>
+        <v>15.22999954223633</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>52.18999862670898</v>
+        <v>14.78999996185303</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>56.65999984741211</v>
+        <v>15.22999954223633</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>51.5099983215332</v>
+        <v>14.51000022888184</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>56.65999984741211</v>
+        <v>15.22999954223633</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>41997933</v>
+        <v>697096</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>10</v>
+        <v>4.96</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Why FINEOS Corporation (ASX: FCL) Could Be a Stock to Watch Into the Final Months of 2026 - kalkine.com.au</t>
+          <t>GST Council may take stock of one-year rate rationalisation; broad-based cuts unlikely in October meeting - Business Today</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>FINEOS Corporation (ASX: FCL) — Is This Insurance Software Stock Worth a Place on Your Watchlist? - kalkine.com.au</t>
+          <t>GST Council may take stock of one-year rate rationalisation; broad-based cuts unlikely in October meeting - Business Today</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Average basic shares outstanding of FCL-X FIRE SAFETY INC – TSXV:FCLX - TradingView</t>
+          <t>Players and umpires pause to take stock after strong tremors were felt at the ground - Cricinfo</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>FINEOS Corporation (ASX: FCL) — Is This Insurance Software Stock Worth a Place on Your Watchlist? - kalkine.com.au</t>
+          <t>Market Quick Take - Shares and bonds rebound as oil prices steady - 03 September 2026 - Saxo</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>Full Circle Lithium Rebrands as FCL-X Fire &amp; Safety Inc. and Provides Corporate Update - Stock Titan</t>
+          <t>Roblox stock plunges 47% YTD, while peers Take-Two and GameStop fall less amid gaming sector struggles. - Pluang</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:31:37 IST</t>
+          <t>2026-09-08 12:54:21 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1621,68 +1633,60 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>TBZ.NS</t>
+          <t>JOCIL.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Tribhovandas Bhimji Zaveri Limited</t>
+          <t>Jocil Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>528.9000244140625</v>
+        <v>160</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>528.9000244140625</v>
+        <v>174</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>528.9000244140625</v>
+        <v>158.5</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>528.9000244140625</v>
+        <v>167.1000061035156</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>480.8500061035156</v>
+        <v>159.3200073242188</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>528.9000244140625</v>
+        <v>167.1000061035156</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>318752</v>
+        <v>75449</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>9.99</v>
+        <v>4.88</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>TBZ shares jump 72% in six sessions: What's driving the rally? - Business Today</t>
+          <t>Jocil Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>TBZ shares jump 72% in six sessions: What's driving the rally? - Business Today</t>
+          <t>Jocil Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Jewellery Stocks In Focus: PC Jeweller Surges 15%, TBZ Hits 10% Upper Circuit; Shankesh Gains 8% — Know Why - NDTV Profit</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>Multibagger stock: Why TBZ shares are locked at 20% upper circuit - Business Standard</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>Tribhovandas Bhimji Zaveri is now GRT's jewel - Finshots</t>
-        </is>
-      </c>
+          <t>Jocil Ltd. Peer Comparison – Compare with Others - Value Research</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:31:37 IST</t>
+          <t>2026-09-08 12:54:21 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1690,68 +1694,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>AKI.NS</t>
+          <t>AKSHAR.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>AKI India Limited</t>
+          <t>Akshar Spintex Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>7.940000057220459</v>
+        <v>0.4300000071525574</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>7.940000057220459</v>
+        <v>0.4399999976158142</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>7.940000057220459</v>
+        <v>0.4199999868869781</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>7.940000057220459</v>
+        <v>0.4399999976158142</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>7.21999979019165</v>
+        <v>0.4199999868869781</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>7.940000057220459</v>
+        <v>0.4399999976158142</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>701339</v>
+        <v>1335495</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>9.970000000000001</v>
+        <v>4.76</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Penny stock under 10 rupees: Upper circuit - Leather share jumps 74% in 4 sessions | Back-to-back surge for third day - TradingView</t>
+          <t>Akshar Spintex Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Penny stock under 10 rupees: Upper circuit - Leather share jumps 74% in 4 sessions | Back-to-back surge for third day - TradingView</t>
+          <t>Akshar Spintex sets Sept 28 AGM date, approves key governance changes - scanx.trade</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>AKI India Ltd leads gainers in 'B' group - Business Standard</t>
+          <t>Akshar Spintex: Parshotam L. Vasoya ceases as independent director - scanx.trade</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>AKI India Ltd Upgraded to Sell on Technical Improvements Despite Lingering Financial Challenges - MarketsMojo</t>
+          <t>Akshar Spintex Standalone June 2026 Net Sales at Rs 29.93 crore, up 14.3% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>Volume shocker stocks: Why share price of EMS, Expleo Solutions, Windlas Biotech, AKI India, Heritage Foods are up today - Livemint</t>
+          <t>Akshar Spintex sets Sept 28 AGM date, approves key governance changes - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:31:37 IST</t>
+          <t>2026-09-08 12:54:21 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1759,68 +1763,56 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>KABRAEXTRU.NS</t>
+          <t>AVANTIFEED.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Kabra Extrusion Technik Limited</t>
+          <t>Avanti Feeds Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>587</v>
+        <v>786.9500122070312</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>642</v>
+        <v>831</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>587</v>
+        <v>784.75</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>634.5</v>
+        <v>823.6500244140625</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>579.1500244140625</v>
+        <v>786.5499877929688</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>634.5</v>
+        <v>823.6500244140625</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>758781</v>
+        <v>328524</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>9.56</v>
+        <v>4.72</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Kabra Extrusion Technik Gains 5.93% to ₹513, Approaches Key Resistance at ₹538.65 - Strangle Setup - siam.in</t>
+          <t>AVANTIFEED Jun 2026 Earnings: EPS at ₹6.18 on ₹1,565 Cr Revenue; Stock Slips 2.1% - Earnings Call Q&amp;A - siam.in</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Kabra Extrusion Technik Surges 9% After Receiving Letter Of Nomination From Vietnamese Auto OEM - Trade Brains</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>Kabra Extrusiontechnik Share Price rises 8.59%: analysis - Univest</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>Kabra Extrusiontechnik Ltd. (KABRAEXTRU) Share Price Rises 8.33% Today - Univest</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>Kabra Extrusion Technik Slips 2.21% to ₹509: Support Zone in Focus as Resistance Caps Upside - Low Vol ETF - siam.in</t>
-        </is>
-      </c>
+          <t>AVANTIFEED Jun 2026 Earnings: EPS at ₹6.18 on ₹1,565 Cr Revenue; Stock Slips 2.1% - Earnings Call Q&amp;A - siam.in</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:31:37 IST</t>
+          <t>2026-09-08 12:54:21 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1828,61 +1820,61 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>SAKAR.NS</t>
+          <t>HATSUN.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Sakar Healthcare Limited</t>
+          <t>Hatsun Agro Product Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1021</v>
+        <v>1132.800048828125</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>1124</v>
+        <v>1199.900024414062</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>1018.950012207031</v>
+        <v>1132.800048828125</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>1109.199951171875</v>
+        <v>1186.099975585938</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1013.900024414062</v>
+        <v>1132.800048828125</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1109.199951171875</v>
+        <v>1186.099975585938</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>339493</v>
+        <v>109906</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>9.4</v>
+        <v>4.71</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Sakar Healthcare FY26 net profit rises 74% to ₹3048.46 lakh - scanx.trade</t>
+          <t>Hatsun Agro Product Share Price: Buy or Sell - Univest</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Sakar Healthcare FY26 net profit rises 74% to ₹3048.46 lakh - scanx.trade</t>
+          <t>Hatsun Agro Product Share Price: Buy or Sell - Univest</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>192.61% Stock Return, 82.3% Profit Growth: What’s Driving Sakar Healthcare Ltd’s Multibagger Rerating? - MarketsMojo</t>
+          <t>Hatsun Agro Product sets Sept 25 for 41st AGM; e-voting opens Sept 22 - scanx.trade</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Sakar Healthcare Ltd. Share Price Today: Valuation Check - Univest</t>
+          <t>Hatsun Agro Product Share Price: Price Action and Valuation - Univest</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>Sakar Healthcare Ltd Technical Momentum Shifts Signal Bullish Outlook - MarketsMojo</t>
+          <t>Hatsun Agro Product Share Price News: Rs 1,017.75 Update - Univest</t>
         </is>
       </c>
     </row>
@@ -1903,14 +1895,14 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
@@ -2009,7 +2001,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:31:37 IST</t>
+          <t>2026-09-08 12:54:21 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -2017,68 +2009,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>SAICAPI.NS</t>
+          <t>NIACL.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Sai Capital Limited</t>
+          <t>The New India Assurance Company Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>158.3399963378906</v>
+        <v>231.1999969482422</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>158.3399963378906</v>
+        <v>232</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>133.5</v>
+        <v>199.5200042724609</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>141.6000061035156</v>
+        <v>210.8200073242188</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>157.5599975585938</v>
+        <v>231.1999969482422</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>141.6000061035156</v>
+        <v>210.8200073242188</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>899</v>
+        <v>30506845</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-10.13</v>
+        <v>-8.81</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>SAICAPI Stock Price and Chart — NSE:SAICAPI - TradingView</t>
+          <t>NIACL, IFCI shares fall up to 12% amid profit booking as NSE IPO GMP declines - Moneycontrol.com</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>SAICAPI Stock Price and Chart — NSE:SAICAPI - TradingView</t>
+          <t>NIACL, IFCI shares tumble after recent gains amid NSE IPO buzz; check technical outlook - Business Today</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Sai Capital Ltd. (SAICAPI) News, Articles, Events &amp; Latest Updates - Stocktwits</t>
+          <t>NIACL, IFCI shares tumble after recent gains amid NSE IPO buzz; check technical outlook - Business Today</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Sai Capital Ltd. (SAICAPI) Share Price Today, Quote, Latest Discussions, Interactive Chart and News - Stocktwits</t>
+          <t>NSE targets listing on Sep 25, reports CNBC-TV18; IFCI, NIACL shares rise up to 11% - tradingview.com</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Sai Capital Q1 Results: Standalone and consolidated financials approved - scanx.trade</t>
+          <t>The New India Assurance Co Share Price - Live NSE: NIACL Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:31:37 IST</t>
+          <t>2026-09-08 12:54:21 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -2086,64 +2078,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>LANDSMILL.NS</t>
+          <t>IFCI.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Landsmill Green Limited</t>
+          <t>IFCI Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.6399999856948853</v>
+        <v>103.4000015258789</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.6399999856948853</v>
+        <v>103.5899963378906</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.5799999833106995</v>
+        <v>92.75</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.5799999833106995</v>
+        <v>94.13999938964844</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.6299999952316284</v>
+        <v>102.5100021362305</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.5799999833106995</v>
+        <v>94.13999938964844</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>6337105</v>
+        <v>155501234</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-7.94</v>
+        <v>-8.17</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Landsmill Green promoter declares no share encumbrance in FY26 - scanx.trade</t>
+          <t>IFCI shares slide 7% after stellar 30% monthly surge amid NSE IPO buzz - The Economic Times</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Landsmill Green promoter declares no share encumbrance in FY26 - scanx.trade</t>
+          <t>IFCI share price tumbles over 8% amid ongoing NSE IPO buzz - Livemint</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Landsmill Green Limited Falls to 52-Week Low of Rs 0.65 as Sell-Off Deepens - MarketsMojo</t>
+          <t>NIACL, IFCI shares fall up to 12% amid profit booking as NSE IPO GMP declines - Moneycontrol.com</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Landsmill Green - 14 penny stocks plunge up to 85% in 6 months. Are you holding any? - The Economic Times</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr"/>
+          <t>IFCI share price tumbles over 8% amid ongoing NSE IPO buzz - Livemint</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>NIACL, IFCI shares tumble after recent gains amid NSE IPO buzz; check technical outlook - Business Today</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:31:37 IST</t>
+          <t>2026-09-08 12:54:21 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -2151,68 +2147,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>SKYWAYS.NS</t>
+          <t>IDBI.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Skyways Air Services Limited</t>
+          <t>IDBI Bank Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>122.5</v>
+        <v>91.30000305175781</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>123.0899963378906</v>
+        <v>92</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>112</v>
+        <v>83.15000152587891</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>113.9100036621094</v>
+        <v>83.84999847412109</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>122.7200012207031</v>
+        <v>90.75</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>113.9100036621094</v>
+        <v>83.84999847412109</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>9717767</v>
+        <v>21453774</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-7.18</v>
+        <v>-7.6</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Skyways Air Services shares list at 9% discount to IPO price on NSE, BSE - Moneycontrol.com</t>
+          <t>IDBI Bank Share Price Jumps 10% In Trade: What's Driving The Rally? - NDTV Profit</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Skyways Air Services sets ₹0.65 per share dividend record date - scanx.trade</t>
+          <t>IDBI Bank Ltd. Downgraded to Sell Amid Mixed Financial and Technical Signals - MarketsMojo</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Skyways Air Services shares defy GMP expectations, list at 10% discount - Business Standard</t>
+          <t>Buzzing stock: IDBI Bank extends rally to 5th day, jumps 5% on huge volume - business-standard.com</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Skyways Air Services tumble over 10% on market debut - BusinessLine</t>
+          <t>IDBI Bank shares surge over 10%; check what's fuelling the stock price today - Upstox</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Skyways Air Services shares list at 10% discount to IPO price, miss Street expectations - Fortune India</t>
+          <t>LIC stake sale in IDBI Bank: Officers’ body seeks IRDAI intervention - BusinessLine</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:31:37 IST</t>
+          <t>2026-09-08 12:54:21 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -2220,64 +2216,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>PAVNAIND.NS</t>
+          <t>ELITECON.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Pavna Industries Limited</t>
+          <t>Elitecon International Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>17.60000038146973</v>
+        <v>7.840000152587891</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>17.60000038146973</v>
+        <v>7.840000152587891</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>15.35999965667725</v>
+        <v>7.840000152587891</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>16.09000015258789</v>
+        <v>7.840000152587891</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>17.21999931335449</v>
+        <v>8.25</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>16.09000015258789</v>
+        <v>7.840000152587891</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>304082</v>
+        <v>700045</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-6.56</v>
+        <v>-4.97</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Pavna Industries Limited agreed to acquire 52.38% stake in Pavna Electric Systems Private Limited for INR 1.7 million. - marketscreener.com</t>
+          <t>Elitecon International Fined ₹1.12 Lakh by BSE for Late Financial Results Submission - scanx.trade</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Pavna Industries Reshapes Subsidiary Portfolio With New Acquisition and Divestments - TipRanks</t>
+          <t>Elitecon International Fined ₹1.12 Lakh by BSE for Late Financial Results Submission - scanx.trade</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Pavna Industries Reshapes Portfolio With New Subsidiary, Divests Two Units - TipRanks</t>
+          <t>Elitecon International Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Pavna Industries Reshapes Subsidiary Portfolio With New Acquisition and Divestments - TipRanks</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr"/>
+          <t>Elitecon International Declines 4.92% to ₹11.2: Support at ₹10.64 Holds Key - Jurik MA - siam.in</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>Small-cap stock under Rs.50 hits 5% upper circuit following stock market rebound - tradingview.com</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:31:37 IST</t>
+          <t>2026-09-08 12:54:21 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2285,68 +2285,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>TIMEX.NS</t>
+          <t>HEG.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Timex Group India Limited</t>
+          <t>HEG Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>672.0999755859375</v>
+        <v>265.3999938964844</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>672.1500244140625</v>
+        <v>265.3999938964844</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>617.5999755859375</v>
+        <v>258.6000061035156</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>628.2999877929688</v>
+        <v>258.7000122070312</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>669.8499755859375</v>
+        <v>272.2000122070312</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>628.2999877929688</v>
+        <v>258.7000122070312</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>615682</v>
+        <v>1149250</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-6.2</v>
+        <v>-4.96</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Stock Market Today | Share Market News | Sensex Today | BSE/NSE Live - NDTV Profit</t>
+          <t>Here’s why you should ignore the 65% plunge in HEG share price today post demerger - Moneycontrol.com</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Stock Market Today | Share Market News | Sensex Today | BSE/NSE Live - NDTV Profit</t>
+          <t>GE Vernova T&amp;D, HFCL surge as New India Assurance, HEG fall on Nifty 500 market open - CNBC TV18</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Timex Group India Limited: Target Price Consensus and Analysts Recommendations | TIMEX | INE064A01026 - marketscreener.com</t>
+          <t>Why are HEG Ltd shares showing a fall of 63% in Monday's trade? - business-standard.com</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Timex Group India Share Price: 5.42% Fall Analysis - Univest</t>
+          <t>HEG Demerger Record Date Today. What It Means For Shareholders? All You Need To Know - NDTV Profit</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>Timex Group India Gains 5.12% to ₹656.0: Stock Approaches Key Resistance at ₹688.8 - Price Target - siam.in</t>
+          <t>Did HEG shares really crash 64% in one day? Here’s how the demerger math works - The Economic Times</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:31:37 IST</t>
+          <t>2026-09-08 12:54:21 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2354,68 +2354,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>LPDC.NS</t>
+          <t>GATECH.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Landmark Property Development Company Limited</t>
+          <t>GACM Technologies Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>6.570000171661377</v>
+        <v>0.8299999833106995</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>6.920000076293945</v>
+        <v>0.8299999833106995</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>6.050000190734863</v>
+        <v>0.8299999833106995</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>6.320000171661377</v>
+        <v>0.8299999833106995</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>6.730000019073486</v>
+        <v>0.8700000047683716</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>6.320000171661377</v>
+        <v>0.8299999833106995</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>188005</v>
+        <v>3263292</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-6.09</v>
+        <v>-4.6</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>LPDC Q4 FY2026 Earnings: Modest Profit Amid Sluggish Revenue; Stock Declines 1.94% - Earnings Call Transcript - vinanet.vn</t>
+          <t>GACM Technologies: FII holding jumps to 29%; penny stock in focus - Business Today</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Landmark Property Development (LPDC.NS) Edges Higher; Support and Resistance in Focus - Day Trade Opportunities - vinanet.vn</t>
+          <t>GACM Technologies EGM Approves Foreign Currency Bonds with 99.91% Voting Support - scanx.trade</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Landmark Property Development (LPDC) Retraces Slightly Amid Low Volume; Support at ₹6.46 in Focus - Statistical Arbitrage - vinanet.vn</t>
+          <t>₹0.75 MultiBagger Penny Stock, +56% in 1 Month -- Why Institutions Are Paying 25% Premium for GACM TECHNOLOGIES Shares? - business-standard.com</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>LPDC Stock Price and Chart — NSE:LPDC - TradingView</t>
+          <t>GACM Technologies Hits Fresh 52-Week High as GATECH Surges 110% in One Month; 31% FII Holding and 250 Million AI Mandate Add to Investor Focus - indiagazette.com</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>Landmark Property Development (LPDC.NS) Edges Lower; Support and Resistance Levels in Focus - Buyback Factor - vinanet.vn</t>
+          <t>GACM Technologies EGM Approves Foreign Currency Bonds with 99.91% Voting Support - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:31:37 IST</t>
+          <t>2026-09-08 12:54:21 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2423,68 +2423,60 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>ICDSLTD.NS</t>
+          <t>TEXMOPIPES.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>ICDS Limited</t>
+          <t>Texmo Pipes and Products Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>71.55999755859375</v>
+        <v>54.95000076293945</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>77.69000244140625</v>
+        <v>54.95000076293945</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>64.30999755859375</v>
+        <v>52.04999923706055</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>67.31999969482422</v>
+        <v>52.33000183105469</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>71.44999694824219</v>
+        <v>54.18000030517578</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>67.31999969482422</v>
+        <v>52.33000183105469</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>120496</v>
+        <v>341655</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-5.78</v>
+        <v>-3.41</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>ICDS Limited (ICDSLTD.NS) Surges Over 7.8%: Strong Momentum or Resistance Ahead? - Bear Pennant - vinanet.vn</t>
+          <t>Texmo (TEXMOPIPES.NS) Results Versus Estimates: The Company Reports Its Latest Available Figures in the Reported Period; Share Response: Shares Move Lower 0.91% in the Latest Session - Fiscal Year Earnings - siam.in</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>ICDS Limited (ICDSLTD.NS): Mild Decline Amid Consolidation, Key Levels Hold - Value ETF - vinanet.vn</t>
+          <t>Texmo (TEXMOPIPES.NS) Results Versus Estimates: The Company Reports Its Latest Available Figures in the Reported Period; Share Response: Shares Move Lower 0.91% in the Latest Session - Fiscal Year Earnings - siam.in</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ICDS Ltd Sees Decline: Stock Slips 3.85% Amidst Key Support Test - Day Trade Opportunities - vinanet.vn</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>ICDS Share Price - Live NSE: ICDSLTD Stock Price &amp; Chart - Upstox</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>ICDSLTD Stock Price and Chart — NSE:ICDSLTD - TradingView</t>
-        </is>
-      </c>
+          <t>Texmo (TEXMOPIPES.NS) Move: Finishes 0.48% Higher at ₹44.29; Next Session: Price Remains Between ₹42.08 Support and ₹46.50 Resistance on the Day - Double Bottom - siam.in</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:31:37 IST</t>
+          <t>2026-09-08 12:54:21 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2492,68 +2484,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>PVRINOX.NS</t>
+          <t>UNITECH.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>PVR INOX Limited</t>
+          <t>Unitech Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1199.099975585938</v>
+        <v>4.25</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1199.099975585938</v>
+        <v>4.25</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>1125.699951171875</v>
+        <v>4.079999923706055</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1156.5</v>
+        <v>4.090000152587891</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1227.199951171875</v>
+        <v>4.21999979019165</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1156.5</v>
+        <v>4.090000152587891</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>3208260</v>
+        <v>5159169</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-5.76</v>
+        <v>-3.08</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>PVR INOX Limited (NSE: PVRINOX) Falls 6.79% as Stock Movement Draws Market Attention - Kalkine India</t>
+          <t>Unitech Ltd CMD Yudhvir Singh Malik ceases to be Chairman - scanx.trade</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>PVR Inox Denies Rs 200-Crore Kickback Allegations in Stock Exchange Filing - Whalesbook</t>
+          <t>Unitech Ltd CMD Yudhvir Singh Malik ceases to be Chairman - scanx.trade</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>PVR Inox Share Price - Live NSE: PVRINOX Stock Price &amp; Chart - Upstox</t>
+          <t>Unitech Ltd Share Price Today: price action and valuation - Univest</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>PVRINOX Outlook for the Week - Equitypandit</t>
+          <t>InvestingPro’s Fair Value warned of 54% drop in Unitech shares By Investing.com - Investing.com India</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>PVR INOX Limited announces an Equity Buyback for 2,068,965 shares, representing 2.11% for INR 3,000 million. - marketscreener.com</t>
+          <t>Unitech Group files FY26 BRSR; awards 10 Lot-5 tenders - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:31:37 IST</t>
+          <t>2026-09-08 12:54:21 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2561,46 +2553,46 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>TCPLPACK.NS</t>
+          <t>WELSPLSOL.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>TCPL Packaging Limited</t>
+          <t>Welspun Specialty Solutions Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>4140</v>
+        <v>59</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>4140</v>
+        <v>59.27999877929688</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>3800</v>
+        <v>56.72000122070312</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>3862.39990234375</v>
+        <v>57.22000122070312</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>4091.89990234375</v>
+        <v>58.9900016784668</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>3862.39990234375</v>
+        <v>57.22000122070312</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>34745</v>
+        <v>563267</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-5.61</v>
+        <v>-3</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>TCPL Packaging Ltd. (TCPLPACK) Share Price Today: Price Action Analysis - Univest</t>
+          <t>Welspun Specialty Solutions Slips 0.79% to ₹52.87, Holds Above Key ₹50 Support - Fundamental Weighted - siam.in</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>TCPL Packaging Ltd. (TCPLPACK) Share Price Today: Price Action Analysis - Univest</t>
+          <t>Welspun Specialty Solutions Slips 0.79% to ₹52.87, Holds Above Key ₹50 Support - Fundamental Weighted - siam.in</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr"/>
@@ -2610,7 +2602,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:31:37 IST</t>
+          <t>2026-09-08 12:54:21 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2618,64 +2610,60 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COFFEEDAY.NS</t>
+          <t>TVSHLTD.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Coffee Day Enterprises Limited</t>
+          <t>TVS Holdings Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>33.09999847412109</v>
+        <v>13743</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>34.2599983215332</v>
+        <v>13743</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>31</v>
+        <v>13302</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>31.1299991607666</v>
+        <v>13340</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>32.86000061035156</v>
+        <v>13748</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>31.1299991607666</v>
+        <v>13340</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>2059008</v>
+        <v>4503</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-5.26</v>
+        <v>-2.97</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Coffee Day Enterprises Jumps Nearly 5% to ₹32.86; Faces Key Hurdle at ₹34.5 - Retail Driven Moves - siam.in</t>
+          <t>TVS Holdings Share Price rise: stock analysis and context - Univest</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Coffee Day Enterprises Jumps Nearly 5% to ₹32.86; Faces Key Hurdle at ₹34.5 - Retail Driven Moves - siam.in</t>
+          <t>TVS Holdings Share Price rise: stock analysis and context - Univest</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Coffee Day promoter Malavika Hegde releases 18,745 invoked shares - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>Coffee Day Enterprises schedules 18th AGM for September 21, 2026 - scanx.trade</t>
-        </is>
-      </c>
+          <t>TVS Holdings Share Price today: decline, valuation and peers - Univest</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
       <c r="Q11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:31:37 IST</t>
+          <t>2026-09-08 12:54:21 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2683,56 +2671,56 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>LORDSCHLO.NS</t>
+          <t>SOTL.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Lords Chloro Alkali Limited</t>
+          <t>Savita Oil Technologies Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>149</v>
+        <v>713.5</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>149</v>
+        <v>713.5499877929688</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>138.0500030517578</v>
+        <v>678.5</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>138.9299926757812</v>
+        <v>685.2999877929688</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>146.6000061035156</v>
+        <v>705.75</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>138.9299926757812</v>
+        <v>685.2999877929688</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>20253</v>
+        <v>383687</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-5.23</v>
+        <v>-2.9</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Lords (LORDSCHLO.NS) Earnings Reading: The Report Supplies Updated Headline Figures under the Current Snapshot; Investor Response: Shares Finish 0.40% Higher - EBITDA Estimate Trend - siam.in</t>
+          <t>Oil stock with over 71% 1-year returns announces 250% final dividend; record date in 2 days - Zee Business</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Lords Chloro Alkali cancels physical investor meet scheduled for September 4 - scanx.trade</t>
+          <t>5 Debt Free Smallcap Stocks With a Beta Less Than 1; Do You Hold Any? - Trade Brains</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Lords (LORDSCHLO.NS) Earnings Reading: The Report Supplies Updated Headline Figures under the Current Snapshot; Investor Response: Shares Finish 0.40% Higher - Earnings Preview - siam.in</t>
+          <t>5 Debt Free Smallcap Stocks With a Beta Less Than 1; Do You Hold Any? - Trade Brains</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Lords Chloro Alkali cancels physical investor meet scheduled for September 4 - scanx.trade</t>
+          <t>Savita Oil Technologies Concludes 65th AGM with Remote E-Voting - tipranks.com</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr"/>
@@ -2740,7 +2728,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:31:37 IST</t>
+          <t>2026-09-08 12:54:21 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2748,68 +2736,56 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>SHYAMTEL.NS</t>
+          <t>WELSPUNLIV.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Shyam Telecom Limited</t>
+          <t>Welspun Living Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>11.6899995803833</v>
+        <v>212</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>11.6899995803833</v>
+        <v>212.8000030517578</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>10.51000022888184</v>
+        <v>204.5200042724609</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>11</v>
+        <v>205.9600067138672</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>11.60000038146973</v>
+        <v>211.9499969482422</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>11</v>
+        <v>205.9600067138672</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>15284</v>
+        <v>2171370</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-5.17</v>
+        <v>-2.83</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>SHYAMTEL Q2 2025 Earnings: Sustained Losses Amid Negligible Revenue - Adjusted Earnings Analysis - vinanet.vn</t>
+          <t>Welspun Living Sets 41st AGM via Video Conferencing on September 24 - tipranks.com</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>SHYAMTEL Mar 2026 Earnings: Revenue Stays at Zero, EPS Remains Negative Amidst Operational Lull - Debt Analysis Report - vinanet.vn</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>Shyam Telecom (SHYAMTEL.NS) Slides 2% Amid Weak Volume – Key Support at ₹19.16 in Focus - Dynamic Hedging - vinanet.vn</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>Shyam Telecom Limited Q4 FY26 Earnings: Zero Revenue and Negative EPS Highlight Persistent Operational Challenges - Financial Summary - vinanet.vn</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>Shyam Telecom Ltd Share Price Today,, SHYAMTEL Share Price NSE, BSE - Business Today</t>
-        </is>
-      </c>
+          <t>Welspun Living Sets 41st AGM via Video Conferencing on September 24 - tipranks.com</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr"/>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:31:37 IST</t>
+          <t>2026-09-08 12:54:21 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2817,68 +2793,60 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>ANNU.NS</t>
+          <t>MAITHANALL.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Annu Projects Limited</t>
+          <t>Maithan Alloys Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>64.81999969482422</v>
+        <v>1119.400024414062</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>64.81999969482422</v>
+        <v>1119.400024414062</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>64.81999969482422</v>
+        <v>1062.599975585938</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>64.81999969482422</v>
+        <v>1073.849975585938</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>68.23000335693359</v>
+        <v>1103.849975585938</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>64.81999969482422</v>
+        <v>1073.849975585938</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>124866</v>
+        <v>109780</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-5</v>
+        <v>-2.72</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Weak market debut: Annu Projects shares list at over 27% discount to its IPO price - Moneycontrol.com</t>
+          <t>Maithan (MAITHANALL.NS) Latest: Finishes 0.63% Down at ₹983.00 in the Latest Reading; Technical View - siam.in</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Annu Projects Ltd. Share Price Today - Annu Projects Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
+          <t>Maithan Alloys MAITHANALL NSE Volume Surge Clarification - Kalkine India</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Annu Projects Shares List at 27% Discount on NSE - Groww</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>Annu Projects shares list at 27% discount on NSE; here's how much investors lost per lot - Upstox</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>Annu Projects Ltd. Share Price Today - Annu Projects Ltd. Stock Price Live NSE/BSE - CNBC TV18</t>
-        </is>
-      </c>
+          <t>Maithan Alloys MAITHANALL NSE Volume Surge Clarification - Kalkine India</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:31:37 IST</t>
+          <t>2026-09-08 12:54:21 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2886,60 +2854,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>UEL.NS</t>
+          <t>RIR.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Ujaas Energy Limited</t>
+          <t>RIR Power Electronics Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>245.8000030517578</v>
+        <v>191.1600036621094</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>245.8000030517578</v>
+        <v>193.0099945068359</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>229.5200042724609</v>
+        <v>183.1000061035156</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>229.5200042724609</v>
+        <v>187</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>241.6000061035156</v>
+        <v>191.9499969482422</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>229.5200042724609</v>
+        <v>187</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>34226</v>
+        <v>632127</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-5</v>
+        <v>-2.58</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Luxembourg's Social Partners Strike Wage Deal — Pay Indexation Pushed to Spring 2027 - AD HOC NEWS</t>
+          <t>RIR Power Electronics Limited (NSE: RIR) Gains 11.90% as Stock Movement Draws Market Attention - Kalkine India</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Luxembourg's Social Partners Strike Wage Deal — Pay Indexation Pushed to Spring 2027 - AD HOC NEWS</t>
+          <t>RIR Power Electronics Limited (NSE: RIR) Gains 11.90% as Stock Movement Draws Market Attention - Kalkine India</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Ujaas Energy addresses share price movement clarification - Business Upturn</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr"/>
-      <c r="Q15" s="2" t="inlineStr"/>
+          <t>RIR Share Price Rises 11.78%: Price and Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>Volume shocker stocks today: Why Innovassynth, RIR Power, Pashupati Cotspin, Zydus Wellness are soaring - Details here - Livemint</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>RIR Power Electronics sets Sept 22 record date for final dividend - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:31:37 IST</t>
+          <t>2026-09-08 12:54:21 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2947,64 +2923,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>NIRAJISPAT.NS</t>
+          <t>KSL.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Niraj Ispat Industries Limited</t>
+          <t>Kalyani Steels Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>368.4500122070312</v>
+        <v>951.0499877929688</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>368.4500122070312</v>
+        <v>959</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>368.4500122070312</v>
+        <v>916.2999877929688</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>368.4500122070312</v>
+        <v>917.2000122070312</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>387.7999877929688</v>
+        <v>941.4500122070312</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>368.4500122070312</v>
+        <v>917.2000122070312</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1523</v>
+        <v>72042</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-4.99</v>
+        <v>-2.58</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Niraj (NIRAJISPAT.NS) Price Update: Ends Down by 3.00% at ₹205.65 for the Current Session - siam.in</t>
+          <t>KSL Shareholders Receive SC Exemption From Undertaking Mandatory Offer - BusinessToday Malaysia</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Precision Wires and 11 Other Stocks That Hit the 20% Upper Circuit Today; Are You Holding Any? - Trade Brains</t>
+          <t>KSL Holdings shareholders get SC exemption - thestar.com.my</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Niraj (NIRAJISPAT.NS) Session: Finishes Nearly Flat at ₹216.00; Levels: the ₹205.20 to ₹226.80 Range Remains in Focus in the Available Record - PSAR Stop - siam.in</t>
+          <t>KSL Holdings shareholders get SC exemption - thestar.com.my</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Precision Wires and 11 Other Stocks That Hit the 20% Upper Circuit Today; Are You Holding Any? - Trade Brains</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr"/>
+          <t>Ku family exempted from KSL mandatory offer after consolidating stakes in family setup - KLSE Screener</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>SLSB, eight individuals exempted from mandatory offer for KSL shares - EdgeProp</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:31:37 IST</t>
+          <t>2026-09-08 12:54:21 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -3012,51 +2992,51 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>SETL.NS</t>
+          <t>UNICHEMLAB.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Standard Engineering Technology Limited</t>
+          <t>Unichem Laboratories Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>410</v>
+        <v>567</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>412.7999877929688</v>
+        <v>575.2000122070312</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>388.5499877929688</v>
+        <v>552.4000244140625</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>388.5499877929688</v>
+        <v>555.2999877929688</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>408.9500122070312</v>
+        <v>569.75</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>388.5499877929688</v>
+        <v>555.2999877929688</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>1260676</v>
+        <v>48746</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-4.99</v>
+        <v>-2.54</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>SETL Share Price News after yearly high and valuation check - Univest</t>
+          <t>Unichem Laboratories UNICHEMLAB Volume Spurt Clarification - Kalkine India</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>SETL Share Price News after yearly high and valuation check - Univest</t>
+          <t>Unichem Laboratories UNICHEMLAB Volume Spurt Clarification - Kalkine India</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Standard (SETL.NS) Results Check: The Report Provides a New Financial Snapshot for the Current Session; Market Reaction: The Stock Ends Down 2.36% for the Current Session - EPS Revision Trend - siam.in</t>
+          <t>Exchange Seeks Clarification as Unichem Labs Shares See Volume Surge - tipranks.com</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr"/>
@@ -3065,7 +3045,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:31:37 IST</t>
+          <t>2026-09-08 12:54:21 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -3073,68 +3053,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>SUPTANERY.NS</t>
+          <t>MTNL.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Super Tannery Limited</t>
+          <t>Mahanagar Telephone Nigam Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>12.59000015258789</v>
+        <v>26.13999938964844</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>12.59000015258789</v>
+        <v>26.13999938964844</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>12.59000015258789</v>
+        <v>25.29999923706055</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>12.59000015258789</v>
+        <v>25.38999938964844</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>13.25</v>
+        <v>26.04999923706055</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>12.59000015258789</v>
+        <v>25.38999938964844</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>37276</v>
+        <v>709320</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-4.98</v>
+        <v>-2.53</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>SUPTANERY Stock Price and Chart — NSE:SUPTANERY - TradingView</t>
+          <t>MTNL FY26 Results: Standalone net loss narrows to ₹3,101.50 crore - scanx.trade</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Super Tannery Ltd. (SUPTANERY) Profile, Company FAQs &amp; Facts, Industry, Sector, Employee Strength - Stocktwits</t>
+          <t>MTNL FY26 Results: Standalone net loss narrows to ₹3,101.50 crore - scanx.trade</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>SUPTANERY Historical Data - Equitypandit</t>
+          <t>Teleco stocks: Bharti Airtel, Vi, MTNL shares in focus as telecom subscriber base grows to 135.3 crore in July; check TRAI data - Upstox</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Super Tannery Ltd. (SUPTANERY) Profile, Company FAQs &amp; Facts, Industry, Sector, Employee Strength - Stocktwits</t>
+          <t>MTNL files FY26 BRSR report; logs ₹1468.81 crore turnover - scanx.trade</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>Super Tannery Ltd. (SUPTANERY) Fundamental and Financial Data - Stocktwits</t>
+          <t>MTNL Slips 0.5% to ₹27.37; Stock Holds Above ₹26 Support Amid Revival Watch - MAMA Signal - siam.in</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:31:37 IST</t>
+          <t>2026-09-08 12:54:21 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -3142,64 +3122,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>RBZJEWEL.NS</t>
+          <t>BEARDSELL.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>RBZ Jewellers Limited</t>
+          <t>Beardsell Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>198.9900054931641</v>
+        <v>25.20000076293945</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>199</v>
+        <v>25.20000076293945</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>186.1799926757812</v>
+        <v>24.05999946594238</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>190.7100067138672</v>
+        <v>24.3700008392334</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>200.6900024414062</v>
+        <v>24.98999977111816</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>190.7100067138672</v>
+        <v>24.3700008392334</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>1088746</v>
+        <v>23695</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-4.97</v>
+        <v>-2.48</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>With EPS Growth And More, RBZ Jewellers (NSE:RBZJEWEL) Makes An Interesting Case - simplywall.st</t>
+          <t>Beardsell Ltd. Peer Comparison – Compare with Others - Value Research</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>With EPS Growth And More, RBZ Jewellers (NSE:RBZJEWEL) Makes An Interesting Case - simplywall.st</t>
+          <t>Beardsell sets date and process for 89th AGM with newspaper notice - tipranks.com</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>RBZ (RBZJEWEL.NS) Move: Finishes 3.13% Higher at ₹139.70; Price Context: the Near-Term Reference Band Stretches From ₹132.71 to ₹146.69 in the Latest Session - Breakout Stock Alerts - siam.in</t>
+          <t>Beardsell Consolidated June 2026 Net Sales at Rs 72.20 crore, up 9.96% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>RBZ Jewellers (RBZJEWEL.NS) Edges Higher: Stock Gains 1.44% Amid Steady Demand - Trend Reversal Picks - siam.in</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr"/>
+          <t>Beardsell Standalone June 2026 Net Sales at Rs 69.57 crore, up 10.55% Y-o-Y - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>Beardsell Ltd. Key Financial Ratios – Valuation, Profitability &amp; More - Value Research</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:31:37 IST</t>
+          <t>2026-09-08 12:54:21 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -3207,68 +3191,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>BURNPUR.NS</t>
+          <t>RICOAUTO.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Burnpur Cement Limited</t>
+          <t>Rico Auto Industries Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>22.6299991607666</v>
+        <v>135.6000061035156</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>22.6299991607666</v>
+        <v>136.25</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>20.48999977111816</v>
+        <v>131.2799987792969</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>20.48999977111816</v>
+        <v>132.1100006103516</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>21.55999946594238</v>
+        <v>135.4700012207031</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>20.48999977111816</v>
+        <v>132.1100006103516</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>377775</v>
+        <v>477050</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-4.96</v>
+        <v>-2.48</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Price Band Hitters on September 7, 2026 at 12:00 PM - HDFC Sky</t>
+          <t>Rico Auto Industries Limited (NSE:RICOAUTO) Looks Like A Good Stock, And It's Going Ex-Dividend Soon - simplywall.st</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Price Band Hitters on September 7, 2026 at 4:00 PM - HDFC Sky</t>
+          <t>Rico Auto Industries Limited (NSE:RICOAUTO) Looks Like A Good Stock, And It's Going Ex-Dividend Soon - simplywall.st</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Burnpur Cement dispatches web links for 40th AGM and FY26 annual report - scanx.trade</t>
+          <t>Rico (RICOAUTO.NS) Results Breakdown: The Report Provides a New Financial Snapshot in the Latest Session; Market Response: Shares Close 1.21% Lower in the Current Update - Earnings Surprise Stocks - siam.in</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Burnpur Cement Ltd. Peer Comparison – Compare with Others - Value Research</t>
+          <t>Rico Auto Industries Ltd. Share Price Falls 8.47% Today - Univest</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Burnpur Cement Share Price - Upstox</t>
+          <t>Rico Auto Industries Q1 Results: Earnings call scheduled for Aug 14 - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:31:37 IST</t>
+          <t>2026-09-08 12:54:21 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -3276,61 +3260,61 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>ELITECON.NS</t>
+          <t>CEMPRO.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Elitecon International Limited</t>
+          <t>Cemindia Projects Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>8.25</v>
+        <v>1319</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>8.909999847412109</v>
+        <v>1323.800048828125</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>8.25</v>
+        <v>1265.5</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>8.25</v>
+        <v>1286.599975585938</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>8.680000305175781</v>
+        <v>1316.900024414062</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>8.25</v>
+        <v>1286.599975585938</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>4027315</v>
+        <v>157290</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-4.95</v>
+        <v>-2.3</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Elitecon International Fined ₹1.12 Lakh by BSE for Late Financial Results Submission - scanx.trade</t>
+          <t>CEMPRO Forecast — Price Target — Prediction for 2027 - tradingview.com</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Elitecon International Fined ₹1.12 Lakh by BSE for Late Financial Results Submission - scanx.trade</t>
+          <t>Cemindia Projects Limited Just Missed Earnings - But Analysts Have Updated Their Models - simplywall.st</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Elitecon International Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>Cemindia Projects Limited Just Missed Earnings - But Analysts Have Updated Their Models - simplywall.st</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Small-cap stock under Rs.50 hits 5% upper circuit following stock market rebound - TradingView</t>
+          <t>ITD Cementation India Share Price - Live NSE: CEMPRO Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>Elitecon International Declines 4.92% to ₹11.2: Support at ₹10.64 Holds Key - Jurik MA - siam.in</t>
+          <t>CEMPRO Q2 2026 Earnings: Revenue Grows 8.81% YoY but Stock Dips 5% - Segment Revenue Breakdown - siam.in</t>
         </is>
       </c>
     </row>

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -439,12 +439,12 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 12:54:21 IST</t>
+          <t>2026-09-09 12:59:33 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -553,68 +553,60 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>GENESYS.NS</t>
+          <t>NOVARTIND.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Genesys International Corporation Limited</t>
+          <t>Novartis India Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>240.25</v>
+        <v>1873.699951171875</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>287.7999877929688</v>
+        <v>2186.39990234375</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>239.5</v>
+        <v>1851</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>282.510009765625</v>
+        <v>2186.39990234375</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>240.1600036621094</v>
+        <v>1822</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>282.510009765625</v>
+        <v>2186.39990234375</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>7356997</v>
+        <v>765240</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>17.63</v>
+        <v>20</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Genesys International Corp files FY26 business responsibility report - scanx.trade</t>
+          <t>Novartis (NOVARTIND.NS) Financial Update: The Company Lists Its Latest Available Figures; Stock Move: Shares Close 1.06% Lower - Earnings Weakness Phase - siam.in</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Genesys International Corp files FY26 business responsibility report - scanx.trade</t>
+          <t>Novartis India Share Price Update With Valuation Context - univest.in</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Genesys International Corporation Ltd (NSE: GENESYS) Gains 10.74% as Stock Movement Draws Market Attention - Kalkine India</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>Genesys International Corporation Ltd. - RE Share Price Live Today - CNBC TV18</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>Genesys International Corporation Share: Geospatial Buy? - Univest</t>
-        </is>
-      </c>
+          <t>Novartis India Share Price Update With Valuation Context - univest.in</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 12:54:21 IST</t>
+          <t>2026-09-09 12:59:33 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -622,68 +614,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>ASTEC.NS</t>
+          <t>ANMOL.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Astec LifeSciences Limited</t>
+          <t>Anmol India Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>551.2000122070312</v>
+        <v>11.47999954223633</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>649</v>
+        <v>13.64999961853027</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>551.2000122070312</v>
+        <v>11.05000019073486</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>645</v>
+        <v>13.64999961853027</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>552.3499755859375</v>
+        <v>11.38000011444092</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>645</v>
+        <v>13.64999961853027</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>1048331</v>
+        <v>1799037</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>16.77</v>
+        <v>19.95</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Astec Lifesciences Share Price rises 9.49% on price action - Univest</t>
+          <t>Anmol India schedules 28th AGM for September 26, 2026 - scanx.trade</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Astec Lifesciences Share Price rises 9.49% on price action - Univest</t>
+          <t>Anmol India schedules 28th AGM for September 26, 2026 - scanx.trade</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Astec (ASTE) Shares: Finishes 4.01% Up at $43.55 in the Latest Reading; Next Test: the Session Ends Within the Reported Technical Boundaries in the Current Update - Market Profile - siam.in</t>
+          <t>Anmol India Ltd is Rated Sell - MarketsMojo</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Astec Life Consolidated June 2026 Net Sales at Rs 83.56 crore, down 8.25% Y-o-Y - Moneycontrol.com</t>
+          <t>Anmol India Standalone June 2026 Net Sales at Rs 455.72 crore, down 21.07% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Implied Volatility Surging for Astec Industries Stock Options - Yahoo Finance</t>
+          <t>Anmol India promoter pledges 3.3M shares to SBI for ₹155 crore loan - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 12:54:21 IST</t>
+          <t>2026-09-09 12:59:33 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -691,68 +683,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>WHEELS.NS</t>
+          <t>GRAPHITE.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Wheels India Limited</t>
+          <t>Graphite India Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1760.900024414062</v>
+        <v>812.9000244140625</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1990.900024414062</v>
+        <v>870</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1760.900024414062</v>
+        <v>775</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1987.300048828125</v>
+        <v>858.4000244140625</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1755.400024414062</v>
+        <v>734.25</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1987.300048828125</v>
+        <v>858.4000244140625</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1155610</v>
+        <v>27411916</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>13.21</v>
+        <v>16.91</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Wheels India Ltd. Stock News - Value Research</t>
+          <t>Graphite India shares skyrocket 16% to fresh 52-week high; here's why - Business Standard</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Wheels India hosts investor conference call from Sep 7 to Sep 9 - scanx.trade</t>
+          <t>Graphite India, Reliance Power, DLF shares spurt amid heavy volumes; check full list - Upstox</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Wheels India hosts investor conference call from Sep 7 to Sep 9 - scanx.trade</t>
+          <t>Here's why Graphite India shares surged over 16% on Wednesday - CNBC TV18</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Ck Wheels LLC sells $43,163 of Wheels Up Experience stock - Investing.com India</t>
+          <t>Graphite India shares jump 18%, hit 52-wk high after GrafTech’s 30% price hike; why currently listed HEG stock may not benefit - Upstox</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Wheels India Share Price News: Price Rise and Valuation - Univest</t>
+          <t>Graphite India stock soars 18%, HEG hits upper circuit; GrafTech’s 30% price hike sparks electrode rally - Moneycontrol.com</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 12:54:21 IST</t>
+          <t>2026-09-09 12:59:33 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -760,68 +752,64 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>CORDSCABLE.NS</t>
+          <t>TEXMOPIPES.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Cords Cable Industries Limited</t>
+          <t>Texmo Pipes and Products Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>314.8500061035156</v>
+        <v>52.29999923706055</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>365.2999877929688</v>
+        <v>59.20000076293945</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>303</v>
+        <v>51.31000137329102</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>353.8999938964844</v>
+        <v>57.31000137329102</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>313.3500061035156</v>
+        <v>52.52000045776367</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>353.8999938964844</v>
+        <v>57.31000137329102</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>906581</v>
+        <v>711761</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>12.94</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Here's Why Cords Cable Industries (NSE:CORDSCABLE) Has Caught The Eye Of Investors - simplywall.st</t>
+          <t>Texmo (TEXMOPIPES.NS) Results Versus Estimates: The Company Reports Its Latest Available Figures in the Reported Period; Share Response: Shares Move Lower 0.91% in the Latest Session - Fiscal Year Earnings - siam.in</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Cords Cable Industries Share Price Gain With Valuation View - Univest</t>
+          <t>Texmo (TEXMOPIPES.NS) Results Versus Estimates: The Company Reports Its Latest Available Figures in the Reported Period; Share Response: Shares Move Lower 0.91% in the Latest Session - Fiscal Year Earnings - siam.in</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Cords Cable Industries Share Price Gain With Valuation View - Univest</t>
+          <t>Texmo (TEXMOPIPES.NS) Move: Finishes 0.48% Higher at ₹44.29; Next Session: Price Remains Between ₹42.08 Support and ₹46.50 Resistance on the Day - Double Bottom - siam.in</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Cords Cable Industries sets August 31 deadline for dividend TDS declarations - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>Cords Cable Q1 Results: Net profit up 102% YoY to ₹7.8 crore - scanx.trade</t>
-        </is>
-      </c>
+          <t>Texmo Pipes And Products Ltd. Share Price Today Up 8.45% - univest.in</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 12:54:21 IST</t>
+          <t>2026-09-09 12:59:33 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -829,64 +817,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>GVT&amp;D.NS</t>
+          <t>CHENNPETRO.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>GE Vernova T&amp;D India Limited</t>
+          <t>Chennai Petroleum Corporation Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>4636.10009765625</v>
+        <v>1466.5</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>4785.89990234375</v>
+        <v>1604</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>4610</v>
+        <v>1466</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>4776</v>
+        <v>1587.099975585938</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>4367.2001953125</v>
+        <v>1457.800048828125</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>4776</v>
+        <v>1587.099975585938</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>3415263</v>
+        <v>5723433</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>9.359999999999999</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>GE Vernova T&amp;D India (NSE:GVT&amp;D) Could Be A Buy For Its Upcoming Dividend - simplywall.st</t>
+          <t>CHENNPETRO Share Price today: price rise and sector view - univest.in</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>GE Vernova T&amp;D India to transfer shares to IEPF on August 27, 2026 - scanx.trade</t>
+          <t>CHENNPETRO Share Price today: price rise and sector view - univest.in</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>GE Vernova T&amp;D India Share Price Today and Stock Analysis - Univest</t>
+          <t>Chennai Petroleum Corporation Ltd. Share Price at 52-Week - univest.in</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>GE Vernova T&amp;D India to transfer shares to IEPF on August 27, 2026 - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr"/>
+          <t>Chennai Petroleum Corporation Ltd. (CHENNPETRO) Share Price Hits Fresh 52-Week High - univest.in</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>Chennai Petroleum Corporation Ltd. (CHENNPETRO) Share Price Within 2% of 52-Week High - univest.in</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 12:54:21 IST</t>
+          <t>2026-09-09 12:59:33 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -894,68 +886,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>DUCON.NS</t>
+          <t>TCC.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Ducon Infratechnologies Limited</t>
+          <t>TCC Concept Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1.789999961853027</v>
+        <v>49.09999847412109</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1.980000019073486</v>
+        <v>58.88000106811523</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>1.779999971389771</v>
+        <v>45.59999847412109</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1.950000047683716</v>
+        <v>52.70999908447266</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1.789999961853027</v>
+        <v>49.06999969482422</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.950000047683716</v>
+        <v>52.70999908447266</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>1423816</v>
+        <v>27995420</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>8.94</v>
+        <v>7.42</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>EBITDA margin % of Ducon Infratechnologies Ltd. Rights 2026-10.09.26 On Shares – NSE:DUCON_RE1 - tradingview.com</t>
+          <t>TCC Concept confirms credit of 1:5 split shares to depositories - scanx.trade</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>EBITDA margin % of Ducon Infratechnologies Ltd. Rights 2026-10.09.26 On Shares – NSE:DUCON_RE1 - tradingview.com</t>
+          <t>TCC Concept files FY26 sustainability report with ₹179.4 crore revenue - scanx.trade</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Ducon Infratechnologies approves rights issue of up to ₹25 Crore - scanx.trade</t>
+          <t>TCC Share Price Update: Trading Metrics and Peer Analysis - univest.in</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Ducon Infratechnologies Ltd. Rights 2026-10.09.26 On Shares Income Statement – NSE:DUCON_RE1 - tradingview.com</t>
+          <t>TCC Concept Limited (NSE: TCC) Falls 5.53% as Stock Movement Draws Market Attention - Kalkine India</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>Ducon Infratechnologies Ltd. Rights 2026-10.09.26 On Shares Balance Sheet – BSE:DUCON_RE1 - tradingview.com</t>
+          <t>TCC Concept files FY26 sustainability report with ₹179.4 crore revenue - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 12:54:21 IST</t>
+          <t>2026-09-09 12:59:33 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -963,68 +955,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>BCG.NS</t>
+          <t>WABAG.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Brightcom Group Limited</t>
+          <t>VA Tech Wabag Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>9.699999809265137</v>
+        <v>2011.300048828125</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>11.18000030517578</v>
+        <v>2188</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>9.670000076293945</v>
+        <v>2011.300048828125</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>10.43000030517578</v>
+        <v>2151</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>9.619999885559082</v>
+        <v>2008.400024414062</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>10.43000030517578</v>
+        <v>2151</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>56429631</v>
+        <v>2037541</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>8.42</v>
+        <v>7.1</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Binah Capital Group (BCG) Edges Higher: Stock Holds Above Support at $1.41 - Active ETF Flow - siam.in</t>
+          <t>VA Tech Wabag Shares Rise After Repeat RIL Order - Equitypandit</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>IBRX Stock’s Decline Makes Retail See ‘Incredible’ Buying Opportunity After Anktiva + BCG Therapy Delivered Favorable Results - Stocktwits</t>
+          <t>VA Tech Wabag secured ₹100-250 crore order from Reliance Industries; shares rise 3% - Upstox</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Baltic Classifieds Group PLC (BCG.L) Stock Analysis: Exploring A 11.61% Potential Upside - DirectorsTalk Interviews</t>
+          <t>VA Tech Wabag (NSEI:WABAG) Stock Sees Modest Fair Value Lift On Backlog Confidence - Yahoo Finance</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>IBRX Stock Jumps 6% Pre-Market On BCG Update In Saudi Arabia – Retail Says Share Price Is ‘Attractive’ - Stocktwits</t>
+          <t>VA Tech Wabag shares gain after repeat order win from Reliance Industries for effluent treatment plant - CNBC TV18</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>IBRX Stock’s Decline Makes Retail See ‘Incredible’ Buying Opportunity After Anktiva + BCG Therapy Delivered Favorable Results - Stocktwits</t>
+          <t>VA Tech Wabag shares jump 3% after securing repeat order from RIL for ETP project - The Economic Times</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 12:54:21 IST</t>
+          <t>2026-09-09 12:59:33 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1032,60 +1024,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>NOVARTIND.NS</t>
+          <t>BLUSPRING.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Novartis India Limited</t>
+          <t>Bluspring Enterprises Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1659</v>
+        <v>123</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1856</v>
+        <v>134.8999938964844</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>1640.099975585938</v>
+        <v>120.75</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1766.199951171875</v>
+        <v>132.3399963378906</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1639.599975585938</v>
+        <v>123.6100006103516</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1766.199951171875</v>
+        <v>132.3399963378906</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>319276</v>
+        <v>474466</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>7.72</v>
+        <v>7.06</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Novartis (NOVARTIND.NS) Financial Update: The Company Lists Its Latest Available Figures; Stock Move: Shares Close 1.06% Lower - Earnings Weakness Phase - siam.in</t>
+          <t>BLUSPRING Share Price update after 8.92% rise in early trade - univest.in</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Novartis India Share Price Update With Valuation Context - Univest</t>
+          <t>BLUSPRING Share Price update after 8.92% rise in early trade - univest.in</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Novartis India Share Price Update With Valuation Context - Univest</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr"/>
+          <t>Bluspring (BLUSPRING.NS) Trading: Moves 4.65% Lower to ₹126.83 on the Day; Immediate View: the Session Ends Within the Reported Technical Boundaries under the Current Snapshot - Retracement Entry - siam.in</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>Bluspring Enterprises publishes 2nd AGM notice in newspapers ahead of August 31 meeting - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>BLUSPRING ENTERPRISES LTD Share Price: Price Rise Analysis - univest.in</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 12:54:21 IST</t>
+          <t>2026-09-09 12:59:33 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1093,68 +1093,64 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>NKIND.NS</t>
+          <t>EIEL.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>NK Industries Limited</t>
+          <t>Enviro Infra Engineers Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>65.80000305175781</v>
+        <v>204.75</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>65.80000305175781</v>
+        <v>215</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>58.65000152587891</v>
+        <v>204.5</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>61.38999938964844</v>
+        <v>208.6100006103516</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>57.20999908447266</v>
+        <v>196.1999969482422</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>61.38999938964844</v>
+        <v>208.6100006103516</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>2426</v>
+        <v>10901806</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>7.31</v>
+        <v>6.33</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>NK Industries Stock Near Key Technical Levels - Kalkine India</t>
+          <t>Enviro (EIEL.NS) Outlook: Gains 0.30% to Reach ₹195.31 for the Current Session; Price Remains Between ₹185.54 Support and ₹205.08 Resistance in Latest Trading - Block Trade Flow - siam.in</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>NK Industries Stock Near Key Technical Levels - Kalkine India</t>
+          <t>Stocks To Buy or Sell Today, September 9, 2026: Bank of Baroda, TCS and Biocon Among Shares That May Remain - LatestLY</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>N.K. Industries Limited Auditor Raises 'Going Concern' Doubt - marketscreener.com</t>
+          <t>Enviro Infra Engineers Limited Beat Revenue Forecasts By 12%: Here's What Analysts Are Forecasting Next - simplywall.st</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Spire (SRJN) Q2 2026 Earnings: EPS Comes in Above Forecast in the Current Update; After Results - vinanet.vn</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>Fennec (FENC) Technical Check: Adds 0.51% to Close at $11.89 at the Close; Current Setup: the Supplied Trading Band Runs From $11.30 to $12.48 - Throwback Trade - vinanet.vn</t>
-        </is>
-      </c>
+          <t>Stocks To Buy or Sell Today, September 9, 2026: Bank of Baroda, TCS and Biocon Among Shares That May Remain - LatestLY</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 12:54:21 IST</t>
+          <t>2026-09-09 12:59:33 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1162,51 +1158,51 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>ANUHPHR.NS</t>
+          <t>STEELXIND.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Anuh Pharma Limited</t>
+          <t>STEEL EXCHANGE INDIA LIMITED</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>92</v>
+        <v>11.60999965667725</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>99.5</v>
+        <v>12.89000034332275</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>91.79000091552734</v>
+        <v>11.47000026702881</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>96.41999816894531</v>
+        <v>12.22999954223633</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>90.29000091552734</v>
+        <v>11.52999973297119</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>96.41999816894531</v>
+        <v>12.22999954223633</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1431986</v>
+        <v>47166153</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>6.79</v>
+        <v>6.07</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Anuh (ANUHPHR.NS) Update: Falls 1.28% to ₹77.82 in the Latest Reading; Price Context: the Supplied Trading Band Runs From ₹73.93 to ₹81.71 in the Available Record - Volume Gap - siam.in</t>
+          <t>Steel Exchange India Ltd (STEELXIND.NS) Inches Up 0.47% to ₹10.61: Consolidation Within a Defined Trading Range - Fundamentals - siam.in</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Anuh Pharma Share Price Today up 11.12% on price action - Univest</t>
+          <t>Steel Exchange India Ltd (STEELXIND.NS) Inches Up 0.47% to ₹10.61: Consolidation Within a Defined Trading Range - Fundamentals - siam.in</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Anuh Pharma Share Price Today up 11.12% on price action - Univest</t>
+          <t>Steel Exchange India Limited Shareholders Approve Rs 341.58 Crore Convertible Equity Warrants Issue - scanx.trade</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr"/>
@@ -1215,7 +1211,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 12:54:21 IST</t>
+          <t>2026-09-09 12:59:33 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1223,68 +1219,56 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>FINCABLES.NS</t>
+          <t>EPACKPEB.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Finolex Cables Limited</t>
+          <t>EPack Prefab Technologies Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1235.099975585938</v>
+        <v>234</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1303.699951171875</v>
+        <v>247.8999938964844</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>1230.199951171875</v>
+        <v>231.2100067138672</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1301</v>
+        <v>245.8800048828125</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1227</v>
+        <v>234</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1301</v>
+        <v>245.8800048828125</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>852693</v>
+        <v>915912</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>6.03</v>
+        <v>5.08</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Finolex Cables shares hit 52-week high for the second straight session; here is what's driving the rally - Upstox</t>
+          <t>EPack (EPACKPEB.NS) Latest Quarter: The Company Publishes Its Latest Results in Latest Trading; Shares Close 2.09% Lower for the Current Session - EBITDA Estimate Trend - siam.in</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Finolex Cables Share Price today: valuation and sector view - Univest</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>Finolex Cables Share Price News: Mid Cap Top Gainer Today - Univest</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>Finolex Cables Share Price today: valuation and sector view - Univest</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>Finolex Cables Limited announces Annual dividend, payable on October 27, 2026 - marketscreener.com</t>
-        </is>
-      </c>
+          <t>EPack (EPACKPEB.NS) Latest Quarter: The Company Publishes Its Latest Results in Latest Trading; Shares Close 2.09% Lower for the Current Session - EBITDA Estimate Trend - siam.in</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 12:54:21 IST</t>
+          <t>2026-09-09 12:59:33 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1292,68 +1276,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>PVRINOX.NS</t>
+          <t>CHEMCON.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>PVR INOX Limited</t>
+          <t>Chemcon Speciality Chemicals Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1161.5</v>
+        <v>212.5299987792969</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1243</v>
+        <v>220</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>1153.599975585938</v>
+        <v>212</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>1222.699951171875</v>
+        <v>220</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1156.5</v>
+        <v>209.5299987792969</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1222.699951171875</v>
+        <v>220</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>1384338</v>
+        <v>123510</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>5.72</v>
+        <v>5</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>PVR INOX Limited (NSE: PVRINOX) Falls 6.79% as Stock Movement Draws Market Attention - Kalkine India</t>
+          <t>Chemcon Speciality Chemicals sets September 17 AGM, opts for virtual-only format - ET Chemicals</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>PVR Inox Share Price rise: key price action and valuation - Univest</t>
+          <t>Chemcon Speciality Chemicals Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>PVR INOX Limited announces an Equity Buyback for 2,068,965 shares, representing 2.11% for INR 3,000 million. - marketscreener.com</t>
+          <t>Chemcon Speciality Chemicals files FY26 BRSR with stock exchanges - scanx.trade</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>PVRINOX Outlook for the Week - Equitypandit</t>
+          <t>Chemcon Speciality Chemicals schedules 37th AGM for September 17, 2026 - scanx.trade</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>PVR INOX shares tumble over 8%; why are shares falling today? - Upstox</t>
+          <t>Chemcon Speciality Chemicals Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 12:54:21 IST</t>
+          <t>2026-09-09 12:59:33 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1361,68 +1345,60 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>KABRAEXTRU.NS</t>
+          <t>SETL.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Kabra Extrusion Technik Limited</t>
+          <t>Standard Engineering Technology Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>639.5</v>
+        <v>402</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>677.75</v>
+        <v>424.7000122070312</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>639</v>
+        <v>401.3999938964844</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>669.6500244140625</v>
+        <v>424.7000122070312</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>634.5</v>
+        <v>404.5</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>669.6500244140625</v>
+        <v>424.7000122070312</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>394706</v>
+        <v>1718263</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>5.54</v>
+        <v>4.99</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Kabra Extrusion Technik Gains 5.93% to ₹513, Approaches Key Resistance at ₹538.65 - Strangle Setup - siam.in</t>
+          <t>SETL Share Price News after yearly high and valuation check - univest.in</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Kabra Extrusion Technik Surges 9% After Receiving Letter Of Nomination From Vietnamese Auto OEM - Trade Brains</t>
+          <t>SETL Share Price News after yearly high and valuation check - univest.in</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Kabra Extrusiontechnik KABRAEXTRU Preferential Issue Allottee Change - Kalkine India</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>Kabra Extrusiontechnik Share Price rises 8.59%: analysis - Univest</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>Kabra Extrusiontechnik Ltd. (KABRAEXTRU) Share Price Rises 8.33% Today - Univest</t>
-        </is>
-      </c>
+          <t>Standard (SETL.NS) Results Check: The Report Provides a New Financial Snapshot for the Current Session; Market Reaction: The Stock Ends Down 2.36% for the Current Session - EPS Revision Trend - siam.in</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 12:54:21 IST</t>
+          <t>2026-09-09 12:59:33 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1430,68 +1406,60 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>TDPOWERSYS.NS</t>
+          <t>STLTECH.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>TD Power Systems Limited</t>
+          <t>Sterlite Technologies Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>736</v>
+        <v>815</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>778.8499755859375</v>
+        <v>865.9000244140625</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>736</v>
+        <v>796.0499877929688</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>774.6500244140625</v>
+        <v>865.7999877929688</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>734.1500244140625</v>
+        <v>824.7000122070312</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>774.6500244140625</v>
+        <v>865.7999877929688</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>1566643</v>
+        <v>4052530</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>5.52</v>
+        <v>4.98</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Brokers Are Upgrading Their Views On TD Power Systems Limited (NSE:TDPOWERSYS) With These New Forecasts - simplywall.st</t>
+          <t>Sterlite (STLTECH.NS) Move: Adds 1.75% to Close at ₹662.75 in the Latest Session; Range View: Price Remains Between ₹629.61 Support and ₹695.89 Resistance for the Current Session - Impulse Wave - siam.in</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>TD Power Systems: Promoter Group Adjusts Ownership - InvestyWise</t>
+          <t>Sterlite (STLTECH.NS) Move: Adds 1.75% to Close at ₹662.75 in the Latest Session; Range View: Price Remains Between ₹629.61 Support and ₹695.89 Resistance for the Current Session - Impulse Wave - siam.in</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>TD Power Systems Publishes EGM Notices in Line with MCA Compliance Norms - The Globe and Mail</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>TD Power System shares surge most in over a year, hit 52-week high; here’s why - Upstox</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>Up 27x in 5 yrs! Why this multibagger smallcap stock showing 50% fall in some trading apps today? - Business Today</t>
-        </is>
-      </c>
+          <t>Sterlite (STLTECH.NS) Q2 2026 Results: The Latest Report Adds New Financial Reference Points in the Latest Reading; Post-Earnings: Shares Move Higher 0.93% in the Latest Reading - Estimate Accuracy - siam.in</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 12:54:21 IST</t>
+          <t>2026-09-09 12:59:33 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1499,64 +1467,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>JUBLPHARMA.NS</t>
+          <t>FINCABLES.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Jubilant Pharmova Limited</t>
+          <t>Finolex Cables Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>956</v>
+        <v>1320</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>1021.549987792969</v>
+        <v>1376</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>953.2999877929688</v>
+        <v>1295.400024414062</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>999.7999877929688</v>
+        <v>1367</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>950.2999877929688</v>
+        <v>1302.300048828125</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>999.7999877929688</v>
+        <v>1367</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>989371</v>
+        <v>2368176</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>5.21</v>
+        <v>4.97</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Jubilant Pharmova files Q1FY27 unaudited financial results for review - scanx.trade</t>
+          <t>Finolex Cables Share Price News: Mid Cap Top Gainer Today - univest.in</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Jubilant Pharmova Opens Special Window for Physical Share Transfers and KYC Update - tipranks.com</t>
+          <t>Shriram Pistons and 4 Other Financially Strong Smallcap Stocks With Beta Less Than 1; Do You Own Any? - Trade Brains</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Buzzing Stocks: Meesho shares slip on block deal; Apollo Tyres gains 2% after UBS upgrade to ‘buy’ - tradingview.com</t>
+          <t>Finolex Cables shares hit 52-week high for the second straight session; here is what's driving the rally - Upstox</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Jubilant Pharmova Opens Special Window for Physical Share Transfers and KYC Update - tipranks.com</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr"/>
+          <t>Finolex Cables Limited announces Annual dividend, payable on October 27, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>Finolex Cables net profit rises 59% in Q1FY27; accelerates fiber capex - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 12:54:21 IST</t>
+          <t>2026-09-09 12:59:33 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1564,68 +1536,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>TAKE.NS</t>
+          <t>MVELECTRO.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>TAKE Limited</t>
+          <t>MV Electrosystems Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>15.22999954223633</v>
+        <v>887.8499755859375</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>15.22999954223633</v>
+        <v>948</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>14.78999996185303</v>
+        <v>880</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>15.22999954223633</v>
+        <v>925</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>14.51000022888184</v>
+        <v>883.25</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>15.22999954223633</v>
+        <v>925</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>697096</v>
+        <v>11813764</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>4.96</v>
+        <v>4.73</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>GST Council may take stock of one-year rate rationalisation; broad-based cuts unlikely in October meeting - Business Today</t>
+          <t>Newly-listed stock MV Electrosystems jumps 15% to hit record high - What's fuelling the rally? - TradingView</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>GST Council may take stock of one-year rate rationalisation; broad-based cuts unlikely in October meeting - Business Today</t>
+          <t>Newly-listed stock MV Electrosystems jumps 15% to hit record high - What's fuelling the rally? - TradingView</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Players and umpires pause to take stock after strong tremors were felt at the ground - Cricinfo</t>
+          <t>MV Electrosystems Share Price: price rise and valuation - univest.in</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Market Quick Take - Shares and bonds rebound as oil prices steady - 03 September 2026 - Saxo</t>
+          <t>MV Electrosystems Share Price Falls 8.25%: Full Analysis - univest.in</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>Roblox stock plunges 47% YTD, while peers Take-Two and GameStop fall less amid gaming sector struggles. - Pluang</t>
+          <t>MV Electrosystems shares jump 19% to touch record high after Q1 earnings call; here’s what’s in focus next - Upstox</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 12:54:21 IST</t>
+          <t>2026-09-09 12:59:33 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1633,60 +1605,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>JOCIL.NS</t>
+          <t>TRIGYN.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Jocil Limited</t>
+          <t>Trigyn Technologies Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>160</v>
+        <v>56.95000076293945</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>174</v>
+        <v>61.5</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>158.5</v>
+        <v>56.5099983215332</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>167.1000061035156</v>
+        <v>59.56000137329102</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>159.3200073242188</v>
+        <v>56.91999816894531</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>167.1000061035156</v>
+        <v>59.56000137329102</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>75449</v>
+        <v>46733</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>4.88</v>
+        <v>4.64</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Jocil Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>Trigyn Technologies Slips 3.4% to ₹59.36: Stock Nears Key Support After Downward Move - Conversion Trade - siam.in</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Jocil Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>Trigyn Technologies schedules 40th AGM for September 30 - scanx.trade</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Jocil Ltd. Peer Comparison – Compare with Others - Value Research</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr"/>
-      <c r="Q18" s="2" t="inlineStr"/>
+          <t>Trigyn Technologies schedules 40th AGM for September 30 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>Trigyn Technologies posts ₹3.49 crore consolidated profit in Q1FY27 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>Trigyn Technologies Sets September 30 Virtual AGM With Remote E-Voting - TipRanks</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 12:54:21 IST</t>
+          <t>2026-09-09 12:59:33 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1694,68 +1674,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>AKSHAR.NS</t>
+          <t>STLNETWORK.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Akshar Spintex Limited</t>
+          <t>STL Networks Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.4300000071525574</v>
+        <v>31.95000076293945</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>0.4399999976158142</v>
+        <v>33.20000076293945</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.4199999868869781</v>
+        <v>30.70999908447266</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>0.4399999976158142</v>
+        <v>33.08000183105469</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0.4199999868869781</v>
+        <v>31.6200008392334</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.4399999976158142</v>
+        <v>33.08000183105469</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>1335495</v>
+        <v>11590423</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>4.76</v>
+        <v>4.62</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Akshar Spintex Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>We Think STL Networks (NSE:STLNETWORK) Can Stay On Top Of Its Debt - simplywall.st</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Akshar Spintex sets Sept 28 AGM date, approves key governance changes - scanx.trade</t>
+          <t>STL Networks Ltd (STLNETWORK) Rises 2.30% as Stock Tests Key Resistance Levels - NHNL Divergence - vinanet.vn</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Akshar Spintex: Parshotam L. Vasoya ceases as independent director - scanx.trade</t>
+          <t>STL Networks Limited Board Meeting Scheduled to Consider Audited Financial Results for FY2026 - scanx.trade</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Akshar Spintex Standalone June 2026 Net Sales at Rs 29.93 crore, up 14.3% Y-o-Y - Moneycontrol.com</t>
+          <t>STL Networks Ltd (STLNETWORK) Rises 2.30% as Stock Tests Key Resistance Levels - NHNL Divergence - vinanet.vn</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>Akshar Spintex sets Sept 28 AGM date, approves key governance changes - scanx.trade</t>
+          <t>STL Networks Q4 FY26: Revenue Rises to ₹2.03B but Net Loss Widens to ₹469M YoY - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 12:54:21 IST</t>
+          <t>2026-09-09 12:59:33 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1763,56 +1743,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>AVANTIFEED.NS</t>
+          <t>PAYTM.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Avanti Feeds Limited</t>
+          <t>One 97 Communications Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>786.9500122070312</v>
+        <v>1677</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>831</v>
+        <v>1753</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>784.75</v>
+        <v>1676.099975585938</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>823.6500244140625</v>
+        <v>1747</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>786.5499877929688</v>
+        <v>1670</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>823.6500244140625</v>
+        <v>1747</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>328524</v>
+        <v>5450704</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>4.72</v>
+        <v>4.61</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>AVANTIFEED Jun 2026 Earnings: EPS at ₹6.18 on ₹1,565 Cr Revenue; Stock Slips 2.1% - Earnings Call Q&amp;A - siam.in</t>
+          <t>Paytm shares jump 5% as workplace AI push gains traction - The Economic Times</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>AVANTIFEED Jun 2026 Earnings: EPS at ₹6.18 on ₹1,565 Cr Revenue; Stock Slips 2.1% - Earnings Call Q&amp;A - siam.in</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr"/>
-      <c r="P20" s="2" t="inlineStr"/>
-      <c r="Q20" s="2" t="inlineStr"/>
+          <t>Paytm shares jump 5% as workplace AI push gains traction - The Economic Times</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>Paytm shares rise over 4% on report of AI expansion - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>Paytm Share Price Jumps Over 5% To Hit 52-Week High Amid Reports Of Block Deal, AI Expansion - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>Paytm share price surges to 52-week high on report of new agentic AI business launch plans - CNBC TV18</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 12:54:21 IST</t>
+          <t>2026-09-09 12:59:33 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1820,63 +1812,59 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>HATSUN.NS</t>
+          <t>SUVIDHAA.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Hatsun Agro Product Limited</t>
+          <t>Suvidhaa Infoserve Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1132.800048828125</v>
+        <v>2.289999961853027</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>1199.900024414062</v>
+        <v>2.490000009536743</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>1132.800048828125</v>
+        <v>2.200000047683716</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>1186.099975585938</v>
+        <v>2.410000085830688</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1132.800048828125</v>
+        <v>2.309999942779541</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1186.099975585938</v>
+        <v>2.410000085830688</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>109906</v>
+        <v>269129</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>4.71</v>
+        <v>4.33</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Hatsun Agro Product Share Price: Buy or Sell - Univest</t>
+          <t>Suvidhaa Infoserve closes books Sep 24-30 for 19th AGM - scanx.trade</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Hatsun Agro Product Share Price: Buy or Sell - Univest</t>
+          <t>Suvidhaa Infoserve closes books Sep 24-30 for 19th AGM - scanx.trade</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Hatsun Agro Product sets Sept 25 for 41st AGM; e-voting opens Sept 22 - scanx.trade</t>
+          <t>Suvidhaa Infoserve Q1 Results: Standalone financials approved by board - scanx.trade</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Hatsun Agro Product Share Price: Price Action and Valuation - Univest</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>Hatsun Agro Product Share Price News: Rs 1,017.75 Update - Univest</t>
-        </is>
-      </c>
+          <t>Suvidhaa Infoserve Sets September 30 Virtual AGM, Closes Books for FY 2025-26 Decisions - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1895,7 +1883,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="59" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -2001,7 +1989,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 12:54:21 IST</t>
+          <t>2026-09-09 12:59:33 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -2009,68 +1997,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>NIACL.NS</t>
+          <t>DCI.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>The New India Assurance Company Limited</t>
+          <t>Dc Infotech And Communication Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>231.1999969482422</v>
+        <v>301.9500122070312</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>232</v>
+        <v>302.0499877929688</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>199.5200042724609</v>
+        <v>271.1499938964844</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>210.8200073242188</v>
+        <v>272</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>231.1999969482422</v>
+        <v>300.75</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>210.8200073242188</v>
+        <v>272</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>30506845</v>
+        <v>1178610</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-8.81</v>
+        <v>-9.56</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>NIACL, IFCI shares fall up to 12% amid profit booking as NSE IPO GMP declines - Moneycontrol.com</t>
+          <t>(DCI) Price Dynamics and Execution-Aware Positioning - Stock Traders Daily</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>NIACL, IFCI shares tumble after recent gains amid NSE IPO buzz; check technical outlook - Business Today</t>
+          <t>(DCI) Price Dynamics and Execution-Aware Positioning - Stock Traders Daily</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>NIACL, IFCI shares tumble after recent gains amid NSE IPO buzz; check technical outlook - Business Today</t>
+          <t>DCI Share Price Rise: Fundamentals, Peers and Market Cap - univest.in</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>NSE targets listing on Sep 25, reports CNBC-TV18; IFCI, NIACL shares rise up to 11% - tradingview.com</t>
+          <t>Donaldson (DCI) Stock Slips After Record Margins Set A Higher Bar - simplywall.st</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>The New India Assurance Co Share Price - Live NSE: NIACL Stock Price &amp; Chart - Upstox</t>
+          <t>Donaldson (DCI) Stock Looks Reasonable On Earnings But Rich On Cash Flow - Yahoo Finance</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 12:54:21 IST</t>
+          <t>2026-09-09 12:59:33 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -2078,68 +2066,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>IFCI.NS</t>
+          <t>MEDICO.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>IFCI Limited</t>
+          <t>Medico Remedies Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>103.4000015258789</v>
+        <v>39.22999954223633</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>103.5899963378906</v>
+        <v>39.2400016784668</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>92.75</v>
+        <v>34.11000061035156</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>94.13999938964844</v>
+        <v>36.70000076293945</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>102.5100021362305</v>
+        <v>39.27999877929688</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>94.13999938964844</v>
+        <v>36.70000076293945</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>155501234</v>
+        <v>1557138</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-8.17</v>
+        <v>-6.57</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>IFCI shares slide 7% after stellar 30% monthly surge amid NSE IPO buzz - The Economic Times</t>
+          <t>Medico Intercontinental schedules AGM for September 30, 2026 - scanx.trade</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>IFCI share price tumbles over 8% amid ongoing NSE IPO buzz - Livemint</t>
+          <t>Medico Intercontinental schedules AGM for September 30, 2026 - scanx.trade</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>NIACL, IFCI shares fall up to 12% amid profit booking as NSE IPO GMP declines - Moneycontrol.com</t>
+          <t>Medico Intercontinental Q1 Results: Standalone profit rises 9% YoY to ₹60.8 lakh - scanx.trade</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>IFCI share price tumbles over 8% amid ongoing NSE IPO buzz - Livemint</t>
+          <t>Medico Remedies Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>NIACL, IFCI shares tumble after recent gains amid NSE IPO buzz; check technical outlook - Business Today</t>
+          <t>Medico Remedies Q1 Results FY27: PAT Rs 2 Cr, Revenue Rs 69 crore - univest.in</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 12:54:21 IST</t>
+          <t>2026-09-09 12:59:33 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -2147,68 +2135,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>IDBI.NS</t>
+          <t>BODALCHEM.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>IDBI Bank Limited</t>
+          <t>Bodal Chemicals Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>91.30000305175781</v>
+        <v>186.3999938964844</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>92</v>
+        <v>189.6799926757812</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>83.15000152587891</v>
+        <v>174.8500061035156</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>83.84999847412109</v>
+        <v>174.8500061035156</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>90.75</v>
+        <v>184.0500030517578</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>83.84999847412109</v>
+        <v>174.8500061035156</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>21453774</v>
+        <v>3456475</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-7.6</v>
+        <v>-5</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>IDBI Bank Share Price Jumps 10% In Trade: What's Driving The Rally? - NDTV Profit</t>
+          <t>Bodal Chemicals Share Price news with valuation context - univest.in</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>IDBI Bank Ltd. Downgraded to Sell Amid Mixed Financial and Technical Signals - MarketsMojo</t>
+          <t>Bodal Chemicals Ltd. Lower Circuit Today: Price, Data and Peers - univest.in</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Buzzing stock: IDBI Bank extends rally to 5th day, jumps 5% on huge volume - business-standard.com</t>
+          <t>With EPS Growth And More, Bodal Chemicals (NSE:BODALCHEM) Makes An Interesting Case - simplywall.st</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>IDBI Bank shares surge over 10%; check what's fuelling the stock price today - Upstox</t>
+          <t>Bodal Chemicals Ltd. (BODALCHEM) Share Price Rises 9.21% Today; Key Levels, Valuation and Peer View - univest.in</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>LIC stake sale in IDBI Bank: Officers’ body seeks IRDAI intervention - BusinessLine</t>
+          <t>Bodal Chemicals Ltd. Lower Circuit Today: Price, Data and Peers - univest.in</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 12:54:21 IST</t>
+          <t>2026-09-09 12:59:33 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -2216,68 +2204,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>ELITECON.NS</t>
+          <t>RAJTV.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Elitecon International Limited</t>
+          <t>Raj Television Network Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>7.840000152587891</v>
+        <v>8.600000381469727</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>7.840000152587891</v>
+        <v>8.789999961853027</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>7.840000152587891</v>
+        <v>8.210000038146973</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>7.840000152587891</v>
+        <v>8.210000038146973</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>8.25</v>
+        <v>8.640000343322754</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>7.840000152587891</v>
+        <v>8.210000038146973</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>700045</v>
+        <v>95765</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-4.97</v>
+        <v>-4.98</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Elitecon International Fined ₹1.12 Lakh by BSE for Late Financial Results Submission - scanx.trade</t>
+          <t>Raj TV Network Q1 Results: Unaudited financials for June quarter filed - scanx.trade</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Elitecon International Fined ₹1.12 Lakh by BSE for Late Financial Results Submission - scanx.trade</t>
+          <t>Kiran Kumar Jain M. sells 0.9% stake in Raj TV Network - scanx.trade</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Elitecon International Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>Kiran Kumar Jain M. sells 0.9% stake in Raj TV Network - scanx.trade</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Elitecon International Declines 4.92% to ₹11.2: Support at ₹10.64 Holds Key - Jurik MA - siam.in</t>
+          <t>Raj TV Network Q1 Results: Net Loss Widens To ₹10.08 Million - scanx.trade</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>Small-cap stock under Rs.50 hits 5% upper circuit following stock market rebound - tradingview.com</t>
+          <t>Raj Television moves AGM online and digitizes access to 2025–26 annual report - TipRanks</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 12:54:21 IST</t>
+          <t>2026-09-09 12:59:33 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2285,68 +2273,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>HEG.NS</t>
+          <t>AKI.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>HEG Limited</t>
+          <t>AKI India Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>265.3999938964844</v>
+        <v>7.150000095367432</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>265.3999938964844</v>
+        <v>7.349999904632568</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>258.6000061035156</v>
+        <v>6.800000190734863</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>258.7000122070312</v>
+        <v>6.800000190734863</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>272.2000122070312</v>
+        <v>7.150000095367432</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>258.7000122070312</v>
+        <v>6.800000190734863</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>1149250</v>
+        <v>90144</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-4.96</v>
+        <v>-4.9</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Here’s why you should ignore the 65% plunge in HEG share price today post demerger - Moneycontrol.com</t>
+          <t>Penny stock under 10 rupees: Upper circuit - Leather share jumps 74% in 4 sessions | Back-to-back surge for third day - TradingView</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>GE Vernova T&amp;D, HFCL surge as New India Assurance, HEG fall on Nifty 500 market open - CNBC TV18</t>
+          <t>AKI India Share Price: Is It a Good Buy After Q1 FY27 Results? - univest.in</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Why are HEG Ltd shares showing a fall of 63% in Monday's trade? - business-standard.com</t>
+          <t>AKI India Share Price: Is It a Good Buy After Q1 FY27 Results? - univest.in</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>HEG Demerger Record Date Today. What It Means For Shareholders? All You Need To Know - NDTV Profit</t>
+          <t>AKI India Ltd leads gainers in 'B' group - Business Standard</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>Did HEG shares really crash 64% in one day? Here’s how the demerger math works - The Economic Times</t>
+          <t>AKI India Ltd Upgraded to Sell on Technical Improvements Despite Lingering Financial Challenges - MarketsMojo</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 12:54:21 IST</t>
+          <t>2026-09-09 12:59:33 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2354,68 +2342,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>GATECH.NS</t>
+          <t>COFORGE.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>GACM Technologies Limited</t>
+          <t>Coforge Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.8299999833106995</v>
+        <v>1815.5</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.8299999833106995</v>
+        <v>1877.599975585938</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.8299999833106995</v>
+        <v>1780.699951171875</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.8299999833106995</v>
+        <v>1856.099975585938</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.8700000047683716</v>
+        <v>1950</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.8299999833106995</v>
+        <v>1856.099975585938</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>3263292</v>
+        <v>8015372</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-4.6</v>
+        <v>-4.82</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>GACM Technologies: FII holding jumps to 29%; penny stock in focus - Business Today</t>
+          <t>Coforge stock plunges 7% as chairman OP Bhatt quits after internal audit flags board evaluation lapses - Moneycontrol.com</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>GACM Technologies EGM Approves Foreign Currency Bonds with 99.91% Voting Support - scanx.trade</t>
+          <t>O P Bhatt resigns from Coforge board over evaluation concerns; stock falls 8.7% - Fortune India</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>₹0.75 MultiBagger Penny Stock, +56% in 1 Month -- Why Institutions Are Paying 25% Premium for GACM TECHNOLOGIES Shares? - business-standard.com</t>
+          <t>Coforge shares plunge nearly 9% after Chairman OP Bhatt’s sudden exit; key details - Upstox</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>GACM Technologies Hits Fresh 52-Week High as GATECH Surges 110% in One Month; 31% FII Holding and 250 Million AI Mandate Add to Investor Focus - indiagazette.com</t>
+          <t>Coforge Shares Slide 8% as Chairman OP Bhatt Quits Abruptly - Equitypandit</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>GACM Technologies EGM Approves Foreign Currency Bonds with 99.91% Voting Support - scanx.trade</t>
+          <t>Infosys, TCS, Coforge, Mphasis shares: Targets as Amazon, Google, Microsoft ramp up capex - Business Today</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 12:54:21 IST</t>
+          <t>2026-09-09 12:59:33 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2423,60 +2411,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>TEXMOPIPES.NS</t>
+          <t>PNGSREVA.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Texmo Pipes and Products Limited</t>
+          <t>PNGS Reva Diamond Jewellery Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>54.95000076293945</v>
+        <v>548.6500244140625</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>54.95000076293945</v>
+        <v>550.4500122070312</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>52.04999923706055</v>
+        <v>513.25</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>52.33000183105469</v>
+        <v>522</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>54.18000030517578</v>
+        <v>546.5499877929688</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>52.33000183105469</v>
+        <v>522</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>341655</v>
+        <v>175115</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-3.41</v>
+        <v>-4.49</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Texmo (TEXMOPIPES.NS) Results Versus Estimates: The Company Reports Its Latest Available Figures in the Reported Period; Share Response: Shares Move Lower 0.91% in the Latest Session - Fiscal Year Earnings - siam.in</t>
+          <t>PNGSREVA Stock Price and Chart — NSE:PNGSREVA - TradingView</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Texmo (TEXMOPIPES.NS) Results Versus Estimates: The Company Reports Its Latest Available Figures in the Reported Period; Share Response: Shares Move Lower 0.91% in the Latest Session - Fiscal Year Earnings - siam.in</t>
+          <t>Mohit Industries Ltd leads gainers in 'B' group - Business Standard</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Texmo (TEXMOPIPES.NS) Move: Finishes 0.48% Higher at ₹44.29; Next Session: Price Remains Between ₹42.08 Support and ₹46.50 Resistance on the Day - Double Bottom - siam.in</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr"/>
+          <t>PNGS Reva Diamond Jewellery (PNGSREVA) Declines 1.35% as Stock Hovers Near Support; Key Levels in Focus - WMA Signal - siam.in</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>PNGS REVA DIAMOND JEWEL L Share Price - Live NSE: PNGSREVA Stock Price &amp; Chart - Upstox</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>PNGS Reva Diamond Jewellery's (NSE:PNGSREVA) Promising Earnings May Rest On Soft Foundations - simplywall.st</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 12:54:21 IST</t>
+          <t>2026-09-09 12:59:33 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2484,68 +2480,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>UNITECH.NS</t>
+          <t>ANDHRAPAP.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Unitech Limited</t>
+          <t>ANDHRA PAPER LIMITED</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>4.25</v>
+        <v>69.16000366210938</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>4.25</v>
+        <v>71.55999755859375</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>4.079999923706055</v>
+        <v>67.70999908447266</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>4.090000152587891</v>
+        <v>68.91000366210938</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>4.21999979019165</v>
+        <v>72.08999633789062</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>4.090000152587891</v>
+        <v>68.91000366210938</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>5159169</v>
+        <v>2208049</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-3.08</v>
+        <v>-4.41</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Unitech Ltd CMD Yudhvir Singh Malik ceases to be Chairman - scanx.trade</t>
+          <t>Andhra Paper Limited Re-appoints Saurabh Bangur as Managing Director for Five-Year Term - scanx.trade</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Unitech Ltd CMD Yudhvir Singh Malik ceases to be Chairman - scanx.trade</t>
+          <t>Andhra Paper Faces ₹21 Crore Environmental Levy from AP Pollution Board - TipRanks</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Unitech Ltd Share Price Today: price action and valuation - Univest</t>
+          <t>Andhra Paper Limited (ANDHRAPAP.NS) Edges Higher: Stock Gains 1.72% Amid Defensive Buying - Investment Factor - siam.in</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>InvestingPro’s Fair Value warned of 54% drop in Unitech shares By Investing.com - Investing.com India</t>
+          <t>Andhra Paper Rises 3.3% to ₹61.93: Key Levels to Watch - Short Setup Alerts - siam.in</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>Unitech Group files FY26 BRSR; awards 10 Lot-5 tenders - scanx.trade</t>
+          <t>Andhra Paper reappoints Saurabh Bangur as MD for five years - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 12:54:21 IST</t>
+          <t>2026-09-09 12:59:33 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2553,56 +2549,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>WELSPLSOL.NS</t>
+          <t>GNFC.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Welspun Specialty Solutions Limited</t>
+          <t>Gujarat Narmada Valley Fertilizers and Chemicals Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>59</v>
+        <v>564</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>59.27999877929688</v>
+        <v>566.0499877929688</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>56.72000122070312</v>
+        <v>556.5</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>57.22000122070312</v>
+        <v>565.5999755859375</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>58.9900016784668</v>
+        <v>589.0999755859375</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>57.22000122070312</v>
+        <v>565.5999755859375</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>563267</v>
+        <v>533392</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-3</v>
+        <v>-3.99</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Welspun Specialty Solutions Slips 0.79% to ₹52.87, Holds Above Key ₹50 Support - Fundamental Weighted - siam.in</t>
+          <t>GNFC Outlook for the Week - Equitypandit</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Welspun Specialty Solutions Slips 0.79% to ₹52.87, Holds Above Key ₹50 Support - Fundamental Weighted - siam.in</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr"/>
-      <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="2" t="inlineStr"/>
+          <t>GNFC accepts Rajkumar Beniwal resignation, appoints Sanjeev Kumar as MD - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>GNFC accepts Rajkumar Beniwal resignation, appoints Sanjeev Kumar as MD - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>Gujarat Narmada Valley Fertilizers (GNFC.NS) Holds Near ₹577; Support at ₹548.1 Becomes Key Watchpoint - Float Adjusted Cap - siam.in</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>MRPL vs GNFC: Which PSU Stock Offers Value - univest.in</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 12:54:21 IST</t>
+          <t>2026-09-09 12:59:33 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2610,60 +2618,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>TVSHLTD.NS</t>
+          <t>MOLDTECH.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>TVS Holdings Limited</t>
+          <t>Mold-Tek Technologies Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>13743</v>
+        <v>218.2700042724609</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>13743</v>
+        <v>224.3999938964844</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>13302</v>
+        <v>210</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>13340</v>
+        <v>210.1999969482422</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>13748</v>
+        <v>218.2700042724609</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>13340</v>
+        <v>210.1999969482422</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>4503</v>
+        <v>23478</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-2.97</v>
+        <v>-3.7</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>TVS Holdings Share Price rise: stock analysis and context - Univest</t>
+          <t>Mold-Tek Technologies (MOLDTECH.NS) Gains 2.44% to ₹207.31, Moves Toward Key Resistance - Double Top - siam.in</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>TVS Holdings Share Price rise: stock analysis and context - Univest</t>
+          <t>Be Sure To Check Out Mold-Tek Technologies Limited (NSE:MOLDTECH) Before It Goes Ex-Dividend - simplywall.st</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>TVS Holdings Share Price today: decline, valuation and peers - Univest</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr"/>
-      <c r="Q11" s="2" t="inlineStr"/>
+          <t>Mold-Tek (MOLDTECH.NS) Session: Loses 0.32% to Close at ₹193.00 in the Latest Session; Technical View: the Price Remains Bounded by the Supplied Support and Resistance in the Available Record - Wyckoff Accumulation - siam.in</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>Be Sure To Check Out Mold-Tek Technologies Limited (NSE:MOLDTECH) Before It Goes Ex-Dividend - simplywall.st</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>Mold-Tek Technologies Limited Recommends Final Dividend for the Financial Year Ended 31 March 2026 - marketscreener.com</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 12:54:21 IST</t>
+          <t>2026-09-09 12:59:33 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2671,56 +2687,56 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>SOTL.NS</t>
+          <t>AEROENTER.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Savita Oil Technologies Limited</t>
+          <t>Aeroflex Enterprises Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>713.5</v>
+        <v>151.8099975585938</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>713.5499877929688</v>
+        <v>152.5500030517578</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>678.5</v>
+        <v>144.9100036621094</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>685.2999877929688</v>
+        <v>147.0399932861328</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>705.75</v>
+        <v>152.6499938964844</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>685.2999877929688</v>
+        <v>147.0399932861328</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>383687</v>
+        <v>749940</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-2.9</v>
+        <v>-3.68</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Oil stock with over 71% 1-year returns announces 250% final dividend; record date in 2 days - Zee Business</t>
+          <t>Sat Industries Ltd. Share Price News and Price Action Today - univest.in</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5 Debt Free Smallcap Stocks With a Beta Less Than 1; Do You Hold Any? - Trade Brains</t>
+          <t>Sat Industries Share Price Rises 8.5%: Market Cap, Valuation - univest.in</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5 Debt Free Smallcap Stocks With a Beta Less Than 1; Do You Hold Any? - Trade Brains</t>
+          <t>Sat Industries Share Price Rises 8.5%: Market Cap, Valuation - univest.in</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Savita Oil Technologies Concludes 65th AGM with Remote E-Voting - tipranks.com</t>
+          <t>Aeroflex Enterprises Q1 Results: Net profit jumps 616% YoY - scanx.trade</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr"/>
@@ -2728,7 +2744,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 12:54:21 IST</t>
+          <t>2026-09-09 12:59:33 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2736,56 +2752,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>WELSPUNLIV.NS</t>
+          <t>NETWEB.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Welspun Living Limited</t>
+          <t>Netweb Technologies India Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>212</v>
+        <v>5100</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>212.8000030517578</v>
+        <v>5127.5</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>204.5200042724609</v>
+        <v>4895</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>205.9600067138672</v>
+        <v>4901</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>211.9499969482422</v>
+        <v>5087.5</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>205.9600067138672</v>
+        <v>4901</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>2171370</v>
+        <v>1132712</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-2.83</v>
+        <v>-3.67</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Welspun Living Sets 41st AGM via Video Conferencing on September 24 - tipranks.com</t>
+          <t>Netweb Technologies seeks nod to raise ₹1,200 crore via postal ballot - scanx.trade</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Welspun Living Sets 41st AGM via Video Conferencing on September 24 - tipranks.com</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr"/>
-      <c r="P13" s="2" t="inlineStr"/>
-      <c r="Q13" s="2" t="inlineStr"/>
+          <t>Netweb Technologies seeks nod to raise ₹1,200 crore via postal ballot - scanx.trade</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>Netweb Technologies shares fall 4% after raising Rs 1,200 crore through QIP - The Economic Times</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>3 Indian AI Stocks To Own In September 2026 - simplywall.st</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>Netweb Technologies Shares Jump 5% On Strong FY26 Show - Equitypandit</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 12:54:21 IST</t>
+          <t>2026-09-09 12:59:33 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2793,60 +2821,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>MAITHANALL.NS</t>
+          <t>IFCI.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Maithan Alloys Limited</t>
+          <t>IFCI Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1119.400024414062</v>
+        <v>92.5</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1119.400024414062</v>
+        <v>93.55999755859375</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>1062.599975585938</v>
+        <v>87.76000213623047</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>1073.849975585938</v>
+        <v>89.23000335693359</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1103.849975585938</v>
+        <v>92.61000061035156</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1073.849975585938</v>
+        <v>89.23000335693359</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>109780</v>
+        <v>124038219</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-2.72</v>
+        <v>-3.65</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Maithan (MAITHANALL.NS) Latest: Finishes 0.63% Down at ₹983.00 in the Latest Reading; Technical View - siam.in</t>
+          <t>IFCI Share Price Today: Stock Falls 8% as NSE IPO-Linked Rally Faces Profit Booking; What Investors Should Know - India Infoline</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Maithan Alloys MAITHANALL NSE Volume Surge Clarification - Kalkine India</t>
+          <t>NSE IPO Speculation Lifts IFCI, NIACL; Profit Booking Cuts Gains - HDFC Sky</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Maithan Alloys MAITHANALL NSE Volume Surge Clarification - Kalkine India</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr"/>
-      <c r="Q14" s="2" t="inlineStr"/>
+          <t>IFCI shares fall 4% on reports of lower price band for NSE IPO - The Economic Times</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>IFCI share price down today- drops 14% in 2 days- Why is the stock falling? - Livemint</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>NSE IPO: Stake-Selling Shareholders Under Pressure As SBI, GIC Re, IFCI, BoB Stocks Decline - HDFC Sky</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 12:54:21 IST</t>
+          <t>2026-09-09 12:59:33 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2854,68 +2890,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>RIR.NS</t>
+          <t>ATLASCYCLE.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>RIR Power Electronics Limited</t>
+          <t>Atlas Cycles (Haryana) Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>191.1600036621094</v>
+        <v>116</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>193.0099945068359</v>
+        <v>116</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>183.1000061035156</v>
+        <v>107.3000030517578</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>187</v>
+        <v>109</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>191.9499969482422</v>
+        <v>113.0299987792969</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>187</v>
+        <v>109</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>632127</v>
+        <v>136614</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-2.58</v>
+        <v>-3.57</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>RIR Power Electronics Limited (NSE: RIR) Gains 11.90% as Stock Movement Draws Market Attention - Kalkine India</t>
+          <t>Atlas Cycles (Haryana) shareholders approve FY26 financials despite promoter dissent - scanx.trade</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>RIR Power Electronics Limited (NSE: RIR) Gains 11.90% as Stock Movement Draws Market Attention - Kalkine India</t>
+          <t>20% Upper Circuit: Wheels India and 9 Other Stocks That Hit the Upper Circuit Today; Are You Holding Any? - Trade Brains</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>RIR Share Price Rises 11.78%: Price and Valuation - Univest</t>
+          <t>Penny Stock Below Rs 100 Posts Wider Loss in Q1 FY27 Even as Land Sale Deal Gets Extended - Dalal Street Investment Journal</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Volume shocker stocks today: Why Innovassynth, RIR Power, Pashupati Cotspin, Zydus Wellness are soaring - Details here - Livemint</t>
+          <t>Atlas Cycles (Haryana) grants sale deed extension for Sonepat land - scanx.trade</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>RIR Power Electronics sets Sept 22 record date for final dividend - scanx.trade</t>
+          <t>20% Upper Circuit: Wheels India and 9 Other Stocks That Hit the Upper Circuit Today; Are You Holding Any? - Trade Brains</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 12:54:21 IST</t>
+          <t>2026-09-09 12:59:33 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2923,68 +2959,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>KSL.NS</t>
+          <t>PVRINOX.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Kalyani Steels Limited</t>
+          <t>PVR INOX Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>951.0499877929688</v>
+        <v>1231.300048828125</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>959</v>
+        <v>1232</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>916.2999877929688</v>
+        <v>1185.599975585938</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>917.2000122070312</v>
+        <v>1188</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>941.4500122070312</v>
+        <v>1231.300048828125</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>917.2000122070312</v>
+        <v>1188</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>72042</v>
+        <v>316858</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-2.58</v>
+        <v>-3.52</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>KSL Shareholders Receive SC Exemption From Undertaking Mandatory Offer - BusinessToday Malaysia</t>
+          <t>PVR Inox Share Price - Live NSE: PVRINOX Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>KSL Holdings shareholders get SC exemption - thestar.com.my</t>
+          <t>PVR INOX shares gain over 7% after firm announces updated buyback date; check key details - Upstox</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>KSL Holdings shareholders get SC exemption - thestar.com.my</t>
+          <t>PVR INOX Limited (NSE: PVRINOX) Falls 6.79% as Stock Movement Draws Market Attention - Kalkine India</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Ku family exempted from KSL mandatory offer after consolidating stakes in family setup - KLSE Screener</t>
+          <t>PVR INOX Limited announces an Equity Buyback for 2,068,965 shares, representing 2.11% for INR 3,000 million. - marketscreener.com</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>SLSB, eight individuals exempted from mandatory offer for KSL shares - EdgeProp</t>
+          <t>PVRINOX Outlook for the Week - Equitypandit</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 12:54:21 IST</t>
+          <t>2026-09-09 12:59:33 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -2992,60 +3028,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>UNICHEMLAB.NS</t>
+          <t>HCLTECH.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Unichem Laboratories Limited</t>
+          <t>HCL Technologies Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>567</v>
+        <v>1248.800048828125</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>575.2000122070312</v>
+        <v>1264.800048828125</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>552.4000244140625</v>
+        <v>1228</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>555.2999877929688</v>
+        <v>1234.400024414062</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>569.75</v>
+        <v>1277</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>555.2999877929688</v>
+        <v>1234.400024414062</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>48746</v>
+        <v>1357443</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-2.54</v>
+        <v>-3.34</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Unichem Laboratories UNICHEMLAB Volume Spurt Clarification - Kalkine India</t>
+          <t>HCLTech invests ₹185 crore to set up advanced semiconductor lab in Bengaluru; shares down 22% YTD - Upstox</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Unichem Laboratories UNICHEMLAB Volume Spurt Clarification - Kalkine India</t>
+          <t>HCLTech Launches Rs 185 Crore Semiconductor Lab in Bengaluru - Equitypandit</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Exchange Seeks Clarification as Unichem Labs Shares See Volume Surge - tipranks.com</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr"/>
-      <c r="Q17" s="2" t="inlineStr"/>
+          <t>HCLTech Launches ₹185 Crore Semiconductor Lab; Shares Fall 0.25% - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>HCLTech Launches Rs 185 Crore Semiconductor Lab in Bengaluru - Equitypandit</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>HCLTech launches Advanced Semiconductor Lab in Bengaluru: How the stock market reacted - theweek.in</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 12:54:21 IST</t>
+          <t>2026-09-09 12:59:33 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -3053,68 +3097,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>MTNL.NS</t>
+          <t>UNIMECH.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Mahanagar Telephone Nigam Limited</t>
+          <t>Unimech Aerospace and Manufacturing Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>26.13999938964844</v>
+        <v>1649</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>26.13999938964844</v>
+        <v>1652.800048828125</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>25.29999923706055</v>
+        <v>1542</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>25.38999938964844</v>
+        <v>1575.5</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>26.04999923706055</v>
+        <v>1629.599975585938</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>25.38999938964844</v>
+        <v>1575.5</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>709320</v>
+        <v>294495</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-2.53</v>
+        <v>-3.32</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>MTNL FY26 Results: Standalone net loss narrows to ₹3,101.50 crore - scanx.trade</t>
+          <t>Unimech Aerospace And Manufacturing Buys 850 Shares Of Dheya Engineering For 30 Million Rupees - TradingView</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>MTNL FY26 Results: Standalone net loss narrows to ₹3,101.50 crore - scanx.trade</t>
+          <t>UNIMECH Share Price update: price action and sector view - univest.in</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Teleco stocks: Bharti Airtel, Vi, MTNL shares in focus as telecom subscriber base grows to 135.3 crore in July; check TRAI data - Upstox</t>
+          <t>UNIMECH Share Price update: price action and sector view - univest.in</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>MTNL files FY26 BRSR report; logs ₹1468.81 crore turnover - scanx.trade</t>
+          <t>Unimech Aerospace reshuffles senior management amid restructuring - scanx.trade</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>MTNL Slips 0.5% to ₹27.37; Stock Holds Above ₹26 Support Amid Revival Watch - MAMA Signal - siam.in</t>
+          <t>Unimech (UNIMECH.NS) Range: Records a Muted Move to ₹1,508.50 in the Available Record; Price Setup: the Current Price Sits Inside the Supplied Technical Range in the Available Record - Time Weighted Price - siam.in</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 12:54:21 IST</t>
+          <t>2026-09-09 12:59:33 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -3122,68 +3166,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>BEARDSELL.NS</t>
+          <t>PFIZER.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Beardsell Limited</t>
+          <t>Pfizer Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>25.20000076293945</v>
+        <v>4310.7001953125</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>25.20000076293945</v>
+        <v>4318</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>24.05999946594238</v>
+        <v>4165</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>24.3700008392334</v>
+        <v>4171.39990234375</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>24.98999977111816</v>
+        <v>4310.7001953125</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>24.3700008392334</v>
+        <v>4171.39990234375</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>23695</v>
+        <v>84968</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-2.48</v>
+        <v>-3.23</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Beardsell Ltd. Peer Comparison – Compare with Others - Value Research</t>
+          <t>Pfizer Ltd. Share Price Falls to One-Year Low: Key View - univest.in</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Beardsell sets date and process for 89th AGM with newspaper notice - tipranks.com</t>
+          <t>Novartis India shares zoom 20% to hit record high; Minipress deal fuels rally - Business Today</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Beardsell Consolidated June 2026 Net Sales at Rs 72.20 crore, up 9.96% Y-o-Y - Moneycontrol.com</t>
+          <t>This Is What I'd Do With Pfizer Stock Right Now - Yahoo Finance</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Beardsell Standalone June 2026 Net Sales at Rs 69.57 crore, up 10.55% Y-o-Y - Moneycontrol.com</t>
+          <t>Pfizer, PCBL, Data Patterns shares spurt amid surge in volumes; check full list - Upstox</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>Beardsell Ltd. Key Financial Ratios – Valuation, Profitability &amp; More - Value Research</t>
+          <t>Pfizer stock offers 13.8% upside plus a 5.91% d... - Pluang</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 12:54:21 IST</t>
+          <t>2026-09-09 12:59:33 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -3191,68 +3235,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>RICOAUTO.NS</t>
+          <t>MTARTECH.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Rico Auto Industries Limited</t>
+          <t>Mtar Technologies Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>135.6000061035156</v>
+        <v>7900</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>136.25</v>
+        <v>7945</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>131.2799987792969</v>
+        <v>7453.5</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>132.1100006103516</v>
+        <v>7550.5</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>135.4700012207031</v>
+        <v>7799.5</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>132.1100006103516</v>
+        <v>7550.5</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>477050</v>
+        <v>104203</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-2.48</v>
+        <v>-3.19</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Rico Auto Industries Limited (NSE:RICOAUTO) Looks Like A Good Stock, And It's Going Ex-Dividend Soon - simplywall.st</t>
+          <t>MTAR Technologies Share Price - Live NSE: MTARTECH Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Rico Auto Industries Limited (NSE:RICOAUTO) Looks Like A Good Stock, And It's Going Ex-Dividend Soon - simplywall.st</t>
+          <t>MTAR Technologies: Promoter Sells 18,000 Shares - InvestyWise</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Rico (RICOAUTO.NS) Results Breakdown: The Report Provides a New Financial Snapshot in the Latest Session; Market Response: Shares Close 1.21% Lower in the Current Update - Earnings Surprise Stocks - siam.in</t>
+          <t>Mtar Technologies (MTARTECH.NS) Drops 2.55% to ₹7,049.5: Key Support and Resistance Levels - Volume Climax - siam.in</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Rico Auto Industries Ltd. Share Price Falls 8.47% Today - Univest</t>
+          <t>Mtar (MTARTECH.NS) Earnings Reading: The Latest Report Adds New Financial Reference Points in the Latest Reading; Latest Reaction: Shares Finish 3.09% Lower - Revenue Breakdown Analysis - siam.in</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Rico Auto Industries Q1 Results: Earnings call scheduled for Aug 14 - scanx.trade</t>
+          <t>Mtar (MTARTECH.NS) Earnings Reading: The Latest Report Adds New Financial Reference Points in the Latest Reading; Latest Reaction: Shares Finish 3.09% Lower - EPS Surprise History - siam.in</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 12:54:21 IST</t>
+          <t>2026-09-09 12:59:33 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -3260,61 +3304,61 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>CEMPRO.NS</t>
+          <t>HARSHA.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Cemindia Projects Limited</t>
+          <t>Harsha Engineers International Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1319</v>
+        <v>466.7999877929688</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>1323.800048828125</v>
+        <v>470.9500122070312</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>1265.5</v>
+        <v>449.0499877929688</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>1286.599975585938</v>
+        <v>452.2000122070312</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1316.900024414062</v>
+        <v>466.7999877929688</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1286.599975585938</v>
+        <v>452.2000122070312</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>157290</v>
+        <v>119630</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-2.3</v>
+        <v>-3.13</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>CEMPRO Forecast — Price Target — Prediction for 2027 - tradingview.com</t>
+          <t>Harsha Engineers International Ltd. Stock News - Value Research</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Cemindia Projects Limited Just Missed Earnings - But Analysts Have Updated Their Models - simplywall.st</t>
+          <t>Harsha Engineers International Ltd. Stock News - Value Research</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Cemindia Projects Limited Just Missed Earnings - But Analysts Have Updated Their Models - simplywall.st</t>
+          <t>Earnings call transcript: Harsha Engineers posts strong Q1 2026 growth, shares fall - Investing.com India</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>ITD Cementation India Share Price - Live NSE: CEMPRO Stock Price &amp; Chart - Upstox</t>
+          <t>Harsha Engineers International Limited Just Recorded A 7.4% Revenue Beat: Here's What Analysts Think - simplywall.st</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>CEMPRO Q2 2026 Earnings: Revenue Grows 8.81% YoY but Stock Dips 5% - Segment Revenue Breakdown - siam.in</t>
+          <t>Harsha Engineer Consolidated June 2026 Net Sales at Rs 457.43 crore, up 25.22% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
     </row>

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -438,8 +438,8 @@
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 12:59:33 IST</t>
+          <t>2026-09-09 20:33:13 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -553,60 +553,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>NOVARTIND.NS</t>
+          <t>GOACARBON.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Novartis India Limited</t>
+          <t>Goa Carbon Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1873.699951171875</v>
+        <v>400</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2186.39990234375</v>
+        <v>463.5</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1851</v>
+        <v>400</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>2186.39990234375</v>
+        <v>463.5</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1822</v>
+        <v>386.25</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>2186.39990234375</v>
+        <v>463.5</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>765240</v>
+        <v>1188144</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>20</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Novartis (NOVARTIND.NS) Financial Update: The Company Lists Its Latest Available Figures; Stock Move: Shares Close 1.06% Lower - Earnings Weakness Phase - siam.in</t>
+          <t>Goa (GOACARBON.NS) Financial Results: The Company Publishes Its Latest Results under the Current Snapshot; Market Response: The Stock Gains 1.63% in the Latest Reading - Earnings Recovery Stocks - siam.in</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Novartis India Share Price Update With Valuation Context - univest.in</t>
+          <t>Goa Carbon concludes 58th AGM, reappoints Shrinivas Dempo - scanx.trade</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Novartis India Share Price Update With Valuation Context - univest.in</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
+          <t>Goa (GOACARBON.NS) Price: Finishes 0.67% Up at ₹359.85 at the Close; the Supplied Trading Band Runs From ₹341.86 to ₹377.84 - Range Breakout - siam.in</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Goa Carbon Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>Goa Carbon concludes 58th AGM, reappoints Shrinivas Dempo - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 12:59:33 IST</t>
+          <t>2026-09-09 20:33:13 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -614,68 +622,64 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>ANMOL.NS</t>
+          <t>NOVARTIND.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Anmol India Limited</t>
+          <t>Novartis India Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>11.47999954223633</v>
+        <v>1873.699951171875</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>13.64999961853027</v>
+        <v>2186.39990234375</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>11.05000019073486</v>
+        <v>1851</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>13.64999961853027</v>
+        <v>2186.39990234375</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>11.38000011444092</v>
+        <v>1822</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>13.64999961853027</v>
+        <v>2186.39990234375</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>1799037</v>
+        <v>785776</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>19.95</v>
+        <v>20</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Anmol India schedules 28th AGM for September 26, 2026 - scanx.trade</t>
+          <t>Novartis (NOVARTIND.NS) Financial Update: The Company Lists Its Latest Available Figures; Stock Move: Shares Close 1.06% Lower - Earnings Weakness Phase - siam.in</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Anmol India schedules 28th AGM for September 26, 2026 - scanx.trade</t>
+          <t>Novartis India FY26 Net Profit Declines; Dividend Nil - scanx.trade</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Anmol India Ltd is Rated Sell - MarketsMojo</t>
+          <t>Novartis India Share Price Update With Valuation Context - Univest</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Anmol India Standalone June 2026 Net Sales at Rs 455.72 crore, down 21.07% Y-o-Y - Moneycontrol.com</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>Anmol India promoter pledges 3.3M shares to SBI for ₹155 crore loan - scanx.trade</t>
-        </is>
-      </c>
+          <t>Novartis India FY26 Net Profit Declines; Dividend Nil - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 12:59:33 IST</t>
+          <t>2026-09-09 20:33:13 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -683,68 +687,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>GRAPHITE.NS</t>
+          <t>SREEL.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Graphite India Limited</t>
+          <t>Sreeleathers Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>812.9000244140625</v>
+        <v>288</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>870</v>
+        <v>345.010009765625</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>775</v>
+        <v>287.5</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>858.4000244140625</v>
+        <v>345.010009765625</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>734.25</v>
+        <v>287.510009765625</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>858.4000244140625</v>
+        <v>345.010009765625</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>27411916</v>
+        <v>635223</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>16.91</v>
+        <v>20</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Graphite India shares skyrocket 16% to fresh 52-week high; here's why - Business Standard</t>
+          <t>Sreeleathers Ltd. Share Price Gain: Technicals &amp; Valuation - Univest</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Graphite India, Reliance Power, DLF shares spurt amid heavy volumes; check full list - Upstox</t>
+          <t>Sreeleathers Share Price rises 20%: price, fundamentals - Univest</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Here's why Graphite India shares surged over 16% on Wednesday - CNBC TV18</t>
+          <t>Sreeleathers Limited Declares Interim Dividend of ₹1 Per Share for FY 2025-26 - scanx.trade</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Graphite India shares jump 18%, hit 52-wk high after GrafTech’s 30% price hike; why currently listed HEG stock may not benefit - Upstox</t>
+          <t>Sreeleathers Share Price rises 20%: price, fundamentals - Univest</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Graphite India stock soars 18%, HEG hits upper circuit; GrafTech’s 30% price hike sparks electrode rally - Moneycontrol.com</t>
+          <t>Sreeleathers Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 12:59:33 IST</t>
+          <t>2026-09-09 20:33:13 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -752,64 +756,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>TEXMOPIPES.NS</t>
+          <t>SHIVALIK.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Texmo Pipes and Products Limited</t>
+          <t>Shivalik Rasayan Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>52.29999923706055</v>
+        <v>322</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>59.20000076293945</v>
+        <v>384.8999938964844</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>51.31000137329102</v>
+        <v>318.2999877929688</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>57.31000137329102</v>
+        <v>384.8999938964844</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>52.52000045776367</v>
+        <v>320.75</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>57.31000137329102</v>
+        <v>384.8999938964844</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>711761</v>
+        <v>471777</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>9.119999999999999</v>
+        <v>20</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Texmo (TEXMOPIPES.NS) Results Versus Estimates: The Company Reports Its Latest Available Figures in the Reported Period; Share Response: Shares Move Lower 0.91% in the Latest Session - Fiscal Year Earnings - siam.in</t>
+          <t>Sirmaur Hospitality Acquires 67,500 Shares in Shivalik Bimetal Controls Through Open Market - scanx.trade</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Texmo (TEXMOPIPES.NS) Results Versus Estimates: The Company Reports Its Latest Available Figures in the Reported Period; Share Response: Shares Move Lower 0.91% in the Latest Session - Fiscal Year Earnings - siam.in</t>
+          <t>Shivalik Rasayan Share Price: Today’s Rise and Valuation - Univest</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Texmo (TEXMOPIPES.NS) Move: Finishes 0.48% Higher at ₹44.29; Next Session: Price Remains Between ₹42.08 Support and ₹46.50 Resistance on the Day - Double Bottom - siam.in</t>
+          <t>Shivalik Rasayan Share Price: Today’s Rise and Valuation - Univest</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Texmo Pipes And Products Ltd. Share Price Today Up 8.45% - univest.in</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr"/>
+          <t>Mount Shivalik Industries Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>Read This Before Considering Shivalik Bimetal Controls Limited (NSE:SBCL) For Its Upcoming ₹2.00 Dividend - simplywall.st</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 12:59:33 IST</t>
+          <t>2026-09-09 20:33:13 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -817,68 +825,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>CHENNPETRO.NS</t>
+          <t>CFEL.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Chennai Petroleum Corporation Limited</t>
+          <t>Confidence Futuristic Energetech Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1466.5</v>
+        <v>32.5</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1604</v>
+        <v>38.65000152587891</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>1466</v>
+        <v>32.04999923706055</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>1587.099975585938</v>
+        <v>38.65000152587891</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1457.800048828125</v>
+        <v>32.20999908447266</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1587.099975585938</v>
+        <v>38.65000152587891</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>5723433</v>
+        <v>147540</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>8.869999999999999</v>
+        <v>19.99</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>CHENNPETRO Share Price today: price rise and sector view - univest.in</t>
+          <t>Confidence Futuristic Energetech Ltd. Upper Circuit: Price and Key Data - Univest</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>CHENNPETRO Share Price today: price rise and sector view - univest.in</t>
+          <t>Confidence Futuristic Energetech Ltd. Upper Circuit: Price and Key Data - Univest</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Chennai Petroleum Corporation Ltd. Share Price at 52-Week - univest.in</t>
+          <t>Confidence Futuristic Energetech Ltd. Financial Statements – NSE:CFEL - TradingView</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Chennai Petroleum Corporation Ltd. (CHENNPETRO) Share Price Hits Fresh 52-Week High - univest.in</t>
+          <t>Confidence Futuristic Energetech Ltd. (CFEL) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>Chennai Petroleum Corporation Ltd. (CHENNPETRO) Share Price Within 2% of 52-Week High - univest.in</t>
+          <t>Confidence Futuristic Energetech Ltd. (CFEL) Share Price Today, Quote, Latest Discussions, Interactive Chart and News - Stocktwits</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 12:59:33 IST</t>
+          <t>2026-09-09 20:33:13 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -886,68 +894,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>TCC.NS</t>
+          <t>BALPHARMA.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>TCC Concept Limited</t>
+          <t>Bal Pharma Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>49.09999847412109</v>
+        <v>95.09999847412109</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>58.88000106811523</v>
+        <v>114.4499969482422</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>45.59999847412109</v>
+        <v>95.09999847412109</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>52.70999908447266</v>
+        <v>114.4499969482422</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>49.06999969482422</v>
+        <v>95.37999725341797</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>52.70999908447266</v>
+        <v>114.4499969482422</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>27995420</v>
+        <v>782802</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>7.42</v>
+        <v>19.99</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>TCC Concept confirms credit of 1:5 split shares to depositories - scanx.trade</t>
+          <t>Bal Pharma Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>TCC Concept files FY26 sustainability report with ₹179.4 crore revenue - scanx.trade</t>
+          <t>Bal Pharma Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>TCC Share Price Update: Trading Metrics and Peer Analysis - univest.in</t>
+          <t>Bal Pharma Limited announced that it has received INR 21 million in funding - marketscreener.com</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>TCC Concept Limited (NSE: TCC) Falls 5.53% as Stock Movement Draws Market Attention - Kalkine India</t>
+          <t>PARNAXLAB Stock Price and Chart — NSE:PARNAXLAB - TradingView</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>TCC Concept files FY26 sustainability report with ₹179.4 crore revenue - scanx.trade</t>
+          <t>Bal Pharma Q1 Results: IEPF share transfer notice issued - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 12:59:33 IST</t>
+          <t>2026-09-09 20:33:13 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -955,68 +963,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>WABAG.NS</t>
+          <t>MEDICAPQ.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>VA Tech Wabag Limited</t>
+          <t>Medi Caps Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2011.300048828125</v>
+        <v>27.71999931335449</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>2188</v>
+        <v>30.73999977111816</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>2011.300048828125</v>
+        <v>26.98999977111816</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>2151</v>
+        <v>30.73999977111816</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2008.400024414062</v>
+        <v>25.6200008392334</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>2151</v>
+        <v>30.73999977111816</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>2037541</v>
+        <v>101209</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>7.1</v>
+        <v>19.98</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>VA Tech Wabag Shares Rise After Repeat RIL Order - Equitypandit</t>
+          <t>MEDICAPQ Stock Price and Chart — NSE:MEDICAPQ - TradingView</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>VA Tech Wabag secured ₹100-250 crore order from Reliance Industries; shares rise 3% - Upstox</t>
+          <t>MEDI-CAPS LIMITED: Discloses Process for Shareholder Annual Report Distribution - InvestyWise</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>VA Tech Wabag (NSEI:WABAG) Stock Sees Modest Fair Value Lift On Backlog Confidence - Yahoo Finance</t>
+          <t>Medi-Caps Ltd. (MEDICAPQ) Profile, Company FAQs &amp; Facts, Industry, Sector, Employee Strength - Stocktwits</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>VA Tech Wabag shares gain after repeat order win from Reliance Industries for effluent treatment plant - CNBC TV18</t>
+          <t>Medi-Caps Ltd. (MEDICAPQ) Share Price Today, Quote, Latest Discussions, Interactive Chart and News - Stocktwits</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>VA Tech Wabag shares jump 3% after securing repeat order from RIL for ETP project - The Economic Times</t>
+          <t>Medi-Caps Ltd. (MEDICAPQ) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 12:59:33 IST</t>
+          <t>2026-09-09 20:33:13 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1024,68 +1032,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>BLUSPRING.NS</t>
+          <t>ANMOL.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Bluspring Enterprises Limited</t>
+          <t>Anmol India Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>123</v>
+        <v>11.47999954223633</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>134.8999938964844</v>
+        <v>13.64999961853027</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>120.75</v>
+        <v>11.05000019073486</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>132.3399963378906</v>
+        <v>13.63000011444092</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>123.6100006103516</v>
+        <v>11.38000011444092</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>132.3399963378906</v>
+        <v>13.63000011444092</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>474466</v>
+        <v>2032124</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>7.06</v>
+        <v>19.77</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>BLUSPRING Share Price update after 8.92% rise in early trade - univest.in</t>
+          <t>Anmol India schedules 28th AGM for September 26, 2026 - scanx.trade</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>BLUSPRING Share Price update after 8.92% rise in early trade - univest.in</t>
+          <t>Anmol India schedules 28th AGM for September 26, 2026 - scanx.trade</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Bluspring (BLUSPRING.NS) Trading: Moves 4.65% Lower to ₹126.83 on the Day; Immediate View: the Session Ends Within the Reported Technical Boundaries under the Current Snapshot - Retracement Entry - siam.in</t>
+          <t>Anmol India Ltd is Rated Sell - MarketsMojo</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Bluspring Enterprises publishes 2nd AGM notice in newspapers ahead of August 31 meeting - scanx.trade</t>
+          <t>Anmol India Standalone June 2026 Net Sales at Rs 455.72 crore, down 21.07% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>BLUSPRING ENTERPRISES LTD Share Price: Price Rise Analysis - univest.in</t>
+          <t>Anmol India promoter pledges 3.3M shares to SBI for ₹155 crore loan - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 12:59:33 IST</t>
+          <t>2026-09-09 20:33:13 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1093,64 +1101,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EIEL.NS</t>
+          <t>BIL.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Enviro Infra Engineers Limited</t>
+          <t>Bhartiya International Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>204.75</v>
+        <v>938.4000244140625</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>215</v>
+        <v>1124.199951171875</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>204.5</v>
+        <v>915.0999755859375</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>208.6100006103516</v>
+        <v>1108.199951171875</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>196.1999969482422</v>
+        <v>936.8499755859375</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>208.6100006103516</v>
+        <v>1108.199951171875</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>10901806</v>
+        <v>191445</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>6.33</v>
+        <v>18.29</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Enviro (EIEL.NS) Outlook: Gains 0.30% to Reach ₹195.31 for the Current Session; Price Remains Between ₹185.54 Support and ₹205.08 Resistance in Latest Trading - Block Trade Flow - siam.in</t>
+          <t>The BIL Vyapar Bull Case - Univest</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Stocks To Buy or Sell Today, September 9, 2026: Bank of Baroda, TCS and Biocon Among Shares That May Remain - LatestLY</t>
+          <t>The BIL Vyapar Bull Case - Univest</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Enviro Infra Engineers Limited Beat Revenue Forecasts By 12%: Here's What Analysts Are Forecasting Next - simplywall.st</t>
+          <t>BIL Vyapar auditor TLB &amp; Co resigns citing professional pre-occupation - scanx.trade</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Stocks To Buy or Sell Today, September 9, 2026: Bank of Baroda, TCS and Biocon Among Shares That May Remain - LatestLY</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr"/>
+          <t>BIL Vyapar vs Nifty 50: Share Price Performance Compared - Univest</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>Qualcomm strikes AI chip deal with Amazon, offers right to buy about US$4 bil in stock - The Edge Malaysia</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 12:59:33 IST</t>
+          <t>2026-09-09 20:33:13 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1158,51 +1170,51 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>STEELXIND.NS</t>
+          <t>INDNIPPON.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>STEEL EXCHANGE INDIA LIMITED</t>
+          <t>India Nippon Electricals Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>11.60999965667725</v>
+        <v>1120.099975585938</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>12.89000034332275</v>
+        <v>1346.699951171875</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>11.47000026702881</v>
+        <v>1111.199951171875</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>12.22999954223633</v>
+        <v>1313.300048828125</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>11.52999973297119</v>
+        <v>1122.300048828125</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>12.22999954223633</v>
+        <v>1313.300048828125</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>47166153</v>
+        <v>1613145</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>6.07</v>
+        <v>17.02</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Steel Exchange India Ltd (STEELXIND.NS) Inches Up 0.47% to ₹10.61: Consolidation Within a Defined Trading Range - Fundamentals - siam.in</t>
+          <t>India (INDNIPPON.NS) Quarterly Figures: The Report Supplies Updated Headline Figures in the Latest Session; Price Move: The Market Price Declines 0.18% in the Available Record - Dividend Earnings Report - siam.in</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Steel Exchange India Ltd (STEELXIND.NS) Inches Up 0.47% to ₹10.61: Consolidation Within a Defined Trading Range - Fundamentals - siam.in</t>
+          <t>India Nippon Electricals Ltd. Upper Circuit: Price and Key Data - Univest</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Steel Exchange India Limited Shareholders Approve Rs 341.58 Crore Convertible Equity Warrants Issue - scanx.trade</t>
+          <t>India Nippon Electricals Ltd. Upper Circuit: Price and Key Data - Univest</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr"/>
@@ -1211,7 +1223,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 12:59:33 IST</t>
+          <t>2026-09-09 20:33:13 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1219,56 +1231,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>EPACKPEB.NS</t>
+          <t>PKTEA.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>EPack Prefab Technologies Limited</t>
+          <t>The Peria Karamalai Tea &amp; Produce Company Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>234</v>
+        <v>976.8499755859375</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>247.8999938964844</v>
+        <v>1160</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>231.2100067138672</v>
+        <v>880</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>245.8800048828125</v>
+        <v>1136.300048828125</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>234</v>
+        <v>972.75</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>245.8800048828125</v>
+        <v>1136.300048828125</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>915912</v>
+        <v>59194</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>5.08</v>
+        <v>16.81</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>EPack (EPACKPEB.NS) Latest Quarter: The Company Publishes Its Latest Results in Latest Trading; Shares Close 2.09% Lower for the Current Session - EBITDA Estimate Trend - siam.in</t>
+          <t>Peria Karamalai Tea &amp; Produce (PKTEA) Slips 2.83% – Support Levels Come into Focus - Relative Volume - vinanet.vn</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>EPack (EPACKPEB.NS) Latest Quarter: The Company Publishes Its Latest Results in Latest Trading; Shares Close 2.09% Lower for the Current Session - EBITDA Estimate Trend - siam.in</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr"/>
-      <c r="P12" s="2" t="inlineStr"/>
-      <c r="Q12" s="2" t="inlineStr"/>
+          <t>SS&amp;C Technologies (SSNC) Climbs 3% as Fintech Momentum Drives Shares Higher - Last Point Support - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>Peria Karamalai Tea &amp; Produce (PKTEA.NS) Moves Higher: Price Nears Mid‑Range Resistance - Rounding Top - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>THE P K TEA PROD CO LTD Share Price - upstox.com</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>PKTEA Mar 2026 Earnings: Tea Plantation Faces Steep Loss Amid Operational Challenges - Gross Profit Margin - vinanet.vn</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 12:59:33 IST</t>
+          <t>2026-09-09 20:33:13 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1276,68 +1300,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>CHEMCON.NS</t>
+          <t>RPPINFRA.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Chemcon Speciality Chemicals Limited</t>
+          <t>R.P.P. Infra Projects Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>212.5299987792969</v>
+        <v>54</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>220</v>
+        <v>63.61999893188477</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>212</v>
+        <v>53</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>220</v>
+        <v>62</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>209.5299987792969</v>
+        <v>53.68000030517578</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>220</v>
+        <v>62</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>123510</v>
+        <v>1012661</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>5</v>
+        <v>15.5</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Chemcon Speciality Chemicals sets September 17 AGM, opts for virtual-only format - ET Chemicals</t>
+          <t>R.P.P. Infra Projects Share Price Today After Strong Gain - Univest</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Chemcon Speciality Chemicals Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>R.P.P. Infra Projects Share Price Today After Strong Gain - Univest</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Chemcon Speciality Chemicals files FY26 BRSR with stock exchanges - scanx.trade</t>
+          <t>R.P.P (RPPINFRA.NS) Session: Records a 1.86% Increase to ₹57.50 in the Latest Reading; Price Levels - siam.in</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Chemcon Speciality Chemicals schedules 37th AGM for September 17, 2026 - scanx.trade</t>
+          <t>R.P.P. Infra Projects Limited Does Not Proposes Dividend for the Year Ended March 31, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>Chemcon Speciality Chemicals Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>R.P.P. Infra Projects Holds Near ₹58.78: Key Levels to Watch for RPPINFRA - Factor Momentum - siam.in</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 12:59:33 IST</t>
+          <t>2026-09-09 20:33:13 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1345,60 +1369,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>SETL.NS</t>
+          <t>GRAPHITE.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Standard Engineering Technology Limited</t>
+          <t>Graphite India Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>402</v>
+        <v>812.9000244140625</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>424.7000122070312</v>
+        <v>874.3499755859375</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>401.3999938964844</v>
+        <v>775</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>424.7000122070312</v>
+        <v>844.6500244140625</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>404.5</v>
+        <v>734.25</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>424.7000122070312</v>
+        <v>844.6500244140625</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1718263</v>
+        <v>36288867</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>4.99</v>
+        <v>15.04</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>SETL Share Price News after yearly high and valuation check - univest.in</t>
+          <t>Graphite India shares skyrocket 16% to fresh 52-week high; here's why - Business Standard</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>SETL Share Price News after yearly high and valuation check - univest.in</t>
+          <t>Graphite India Shares Surge 18% Following GrafTech Price Hikes - Sahi</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Standard (SETL.NS) Results Check: The Report Provides a New Financial Snapshot for the Current Session; Market Reaction: The Stock Ends Down 2.36% for the Current Session - EPS Revision Trend - siam.in</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr"/>
-      <c r="Q14" s="2" t="inlineStr"/>
+          <t>Graphite India stock soars 18%, HEG hits upper circuit; GrafTech’s 30% price hike sparks electrode rally - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>Here's why Graphite India shares surged over 16% on Wednesday - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>Graphite India Shares Surge 18% Following GrafTech Price Hikes - Sahi</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 12:59:33 IST</t>
+          <t>2026-09-09 20:33:13 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1406,60 +1438,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>STLTECH.NS</t>
+          <t>INDORAMA.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Sterlite Technologies Limited</t>
+          <t>Indo Rama Synthetics (India) Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>815</v>
+        <v>75.30000305175781</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>865.9000244140625</v>
+        <v>88.19999694824219</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>796.0499877929688</v>
+        <v>72.76000213623047</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>865.7999877929688</v>
+        <v>86.12999725341797</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>824.7000122070312</v>
+        <v>74.98000335693359</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>865.7999877929688</v>
+        <v>86.12999725341797</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>4052530</v>
+        <v>7583783</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>4.98</v>
+        <v>14.87</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Sterlite (STLTECH.NS) Move: Adds 1.75% to Close at ₹662.75 in the Latest Session; Range View: Price Remains Between ₹629.61 Support and ₹695.89 Resistance for the Current Session - Impulse Wave - siam.in</t>
+          <t>Should You Be Adding Indo Rama Synthetics (India) (NSE:INDORAMA) To Your Watchlist Today? - simplywall.st</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Sterlite (STLTECH.NS) Move: Adds 1.75% to Close at ₹662.75 in the Latest Session; Range View: Price Remains Between ₹629.61 Support and ₹695.89 Resistance for the Current Session - Impulse Wave - siam.in</t>
+          <t>Indorama Ventures Number of Employees 2026 | Employee Count &amp; Headcount Data - Revelio Labs</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Sterlite (STLTECH.NS) Q2 2026 Results: The Latest Report Adds New Financial Reference Points in the Latest Reading; Post-Earnings: Shares Move Higher 0.93% in the Latest Reading - Estimate Accuracy - siam.in</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr"/>
-      <c r="Q15" s="2" t="inlineStr"/>
+          <t>Indorama Ventures Number of Employees 2026 | Employee Count &amp; Headcount Data - Revelio Labs</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>Indo Rama Synthetics (India) Limited Schedules Board Meeting on May 25, 2026 to Approve FY26 Financial Results - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>Indo Rama Synthetics Q2 2026 Earnings: Profitability Gains as Revenue Surges 15% - Earnings Risk Report - vinanet.vn</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 12:59:33 IST</t>
+          <t>2026-09-09 20:33:13 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1467,68 +1507,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>FINCABLES.NS</t>
+          <t>ASTEC.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Finolex Cables Limited</t>
+          <t>Astec LifeSciences Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1320</v>
+        <v>691</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>1376</v>
+        <v>779.3499755859375</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>1295.400024414062</v>
+        <v>690</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>1367</v>
+        <v>761</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1302.300048828125</v>
+        <v>662.7999877929688</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1367</v>
+        <v>761</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>2368176</v>
+        <v>5355488</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>4.97</v>
+        <v>14.82</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Finolex Cables Share Price News: Mid Cap Top Gainer Today - univest.in</t>
+          <t>Astec Lifesciences share price skyrockets 17% despite weak sentiments on D-Street. Do you own? - Livemint</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Shriram Pistons and 4 Other Financially Strong Smallcap Stocks With Beta Less Than 1; Do You Own Any? - Trade Brains</t>
+          <t>Astec Lifesciences share price skyrockets 17% despite weak sentiments on D-Street. Do you own? - Livemint</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Finolex Cables shares hit 52-week high for the second straight session; here is what's driving the rally - Upstox</t>
+          <t>Astec Lifesciences Share Price rises 9.49% on price action - Univest</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Finolex Cables Limited announces Annual dividend, payable on October 27, 2026 - marketscreener.com</t>
+          <t>Implied Volatility Surging for Astec Industries Stock Options - finance.yahoo.com</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>Finolex Cables net profit rises 59% in Q1FY27; accelerates fiber capex - scanx.trade</t>
+          <t>2 Reasons to Like ASTE (and 1 Not So Much) - TradingView</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 12:59:33 IST</t>
+          <t>2026-09-09 20:33:13 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1536,68 +1576,60 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>MVELECTRO.NS</t>
+          <t>RESPONIND.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>MV Electrosystems Limited</t>
+          <t>Responsive Industries Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>887.8499755859375</v>
+        <v>147.1499938964844</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>948</v>
+        <v>175.1999969482422</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>880</v>
+        <v>144.8800048828125</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>925</v>
+        <v>169.5899963378906</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>883.25</v>
+        <v>148.2299957275391</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>925</v>
+        <v>169.5899963378906</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>11813764</v>
+        <v>12729156</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>4.73</v>
+        <v>14.41</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Newly-listed stock MV Electrosystems jumps 15% to hit record high - What's fuelling the rally? - TradingView</t>
+          <t>Fairpoint Tradecom pledges shares with Timelink Agencies - scanx.trade</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Newly-listed stock MV Electrosystems jumps 15% to hit record high - What's fuelling the rally? - TradingView</t>
+          <t>Responsive Industries Share Price today after 10.91% gain - Univest</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>MV Electrosystems Share Price: price rise and valuation - univest.in</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>MV Electrosystems Share Price Falls 8.25%: Full Analysis - univest.in</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>MV Electrosystems shares jump 19% to touch record high after Q1 earnings call; here’s what’s in focus next - Upstox</t>
-        </is>
-      </c>
+          <t>Responsive Industries Share Price today after 10.91% gain - Univest</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 12:59:33 IST</t>
+          <t>2026-09-09 20:33:13 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1605,68 +1637,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>TRIGYN.NS</t>
+          <t>LADDERUP.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Trigyn Technologies Limited</t>
+          <t>Ladderup Finance Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>56.95000076293945</v>
+        <v>45.84999847412109</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>61.5</v>
+        <v>54.22000122070312</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>56.5099983215332</v>
+        <v>45.84999847412109</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>59.56000137329102</v>
+        <v>51.61000061035156</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>56.91999816894531</v>
+        <v>45.18999862670898</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>59.56000137329102</v>
+        <v>51.61000061035156</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>46733</v>
+        <v>11637</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>4.64</v>
+        <v>14.21</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Trigyn Technologies Slips 3.4% to ₹59.36: Stock Nears Key Support After Downward Move - Conversion Trade - siam.in</t>
+          <t>Ladderup Finance Ltd. Peer Comparison – Compare with Others - Value Research</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Trigyn Technologies schedules 40th AGM for September 30 - scanx.trade</t>
+          <t>Ladderup Finance Ltd. Peer Comparison – Compare with Others - Value Research</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Trigyn Technologies schedules 40th AGM for September 30 - scanx.trade</t>
+          <t>Ladderup Fin Consolidated June 2026 Net Sales at Rs 9.32 crore, up 61.22% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Trigyn Technologies posts ₹3.49 crore consolidated profit in Q1FY27 - scanx.trade</t>
+          <t>Ladderup Finance secures ₹20 crore secured loan from Tata Capital - scanx.trade</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>Trigyn Technologies Sets September 30 Virtual AGM With Remote E-Voting - TipRanks</t>
+          <t>Ladderup Finance Q1 FY27 Results: Revenue Rs 9 Cr, PAT Rs 3 Cr and Key Highlights - Univest</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 12:59:33 IST</t>
+          <t>2026-09-09 20:33:13 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1674,68 +1706,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>STLNETWORK.NS</t>
+          <t>WHEELS.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>STL Networks Limited</t>
+          <t>Wheels India Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>31.95000076293945</v>
+        <v>2110</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>33.20000076293945</v>
+        <v>2450</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>30.70999908447266</v>
+        <v>2110</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>33.08000183105469</v>
+        <v>2400.60009765625</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>31.6200008392334</v>
+        <v>2106.39990234375</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>33.08000183105469</v>
+        <v>2400.60009765625</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>11590423</v>
+        <v>6608643</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>4.62</v>
+        <v>13.97</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>We Think STL Networks (NSE:STLNETWORK) Can Stay On Top Of Its Debt - simplywall.st</t>
+          <t>Wheels India share price hits a 52-week high, jumps over 55% in just 6 sessions- Should you buy? - Livemint</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>STL Networks Ltd (STLNETWORK) Rises 2.30% as Stock Tests Key Resistance Levels - NHNL Divergence - vinanet.vn</t>
+          <t>Wheels India share price hits a 52-week high, jumps over 55% in just 6 sessions- Should you buy? - Livemint</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>STL Networks Limited Board Meeting Scheduled to Consider Audited Financial Results for FY2026 - scanx.trade</t>
+          <t>Steel Strips Wheels promoter Sunena Garg acquires 48,000 shares - scanx.trade</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>STL Networks Ltd (STLNETWORK) Rises 2.30% as Stock Tests Key Resistance Levels - NHNL Divergence - vinanet.vn</t>
+          <t>Wheels India Share Price news: 52-week peak and valuation - Univest</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>STL Networks Q4 FY26: Revenue Rises to ₹2.03B but Net Loss Widens to ₹469M YoY - scanx.trade</t>
+          <t>Wheels India Approves Issuing 1,269,391 Equity Shares At ₹1,418 To Raise ₹180 Crores - Sahi</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 12:59:33 IST</t>
+          <t>2026-09-09 20:33:13 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1743,68 +1775,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>PAYTM.NS</t>
+          <t>MOLBIO.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>One 97 Communications Limited</t>
+          <t>Molbio Diagnostics Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1677</v>
+        <v>1119</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1753</v>
+        <v>1293.5</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>1676.099975585938</v>
+        <v>1111.5</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>1747</v>
+        <v>1257.900024414062</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1670</v>
+        <v>1117.5</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1747</v>
+        <v>1257.900024414062</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>5450704</v>
+        <v>9413749</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>4.61</v>
+        <v>12.56</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Paytm shares jump 5% as workplace AI push gains traction - The Economic Times</t>
+          <t>Stocks to Watch Today: Rail Vikas Nigam, Cohance Lifesciences, Molbio Diagnostics, Purple Style Labs,... - Moneycontrol.com</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Paytm shares jump 5% as workplace AI push gains traction - The Economic Times</t>
+          <t>Stock Market Live | IFCI, RVNL, Molbio Diagnostics, Swiggy, Lupin Share में क्या करें? - x.com</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Paytm shares rise over 4% on report of AI expansion - Moneycontrol.com</t>
+          <t>Molbio Diagnostics Q1FY27 Results: Net profit up 523% YoY to ₹527.44 million - scanx.trade</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Paytm Share Price Jumps Over 5% To Hit 52-Week High Amid Reports Of Block Deal, AI Expansion - NDTV Profit</t>
+          <t>Solid debut! Molbio Diagnostics shares list at 21% premium over IPO price - Business Standard</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Paytm share price surges to 52-week high on report of new agentic AI business launch plans - CNBC TV18</t>
+          <t>Molbio Diagnostics shares rally 6% after strong debut. What should investors do? - The Economic Times</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 12:59:33 IST</t>
+          <t>2026-09-09 20:33:13 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1812,59 +1844,63 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>SUVIDHAA.NS</t>
+          <t>CHEMBOND.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Suvidhaa Infoserve Limited</t>
+          <t>Chembond Material Technologies Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>2.289999961853027</v>
+        <v>204.6000061035156</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>2.490000009536743</v>
+        <v>236.8000030517578</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>2.200000047683716</v>
+        <v>200.5</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>2.410000085830688</v>
+        <v>220.3600006103516</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>2.309999942779541</v>
+        <v>197.7200012207031</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>2.410000085830688</v>
+        <v>220.3600006103516</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>269129</v>
+        <v>328623</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>4.33</v>
+        <v>11.45</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Suvidhaa Infoserve closes books Sep 24-30 for 19th AGM - scanx.trade</t>
+          <t>Chembond promoter group buys 15,020 equity shares on open market - scanx.trade</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Suvidhaa Infoserve closes books Sep 24-30 for 19th AGM - scanx.trade</t>
+          <t>Chembond Chemicals Ltd Locks at Upper Circuit With 5% Gain — Buyers Queue, Sellers Absent - MarketsMojo</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Suvidhaa Infoserve Q1 Results: Standalone financials approved by board - scanx.trade</t>
+          <t>Chembond Chemicals Ltd Locks at Upper Circuit With 5% Gain — Buyers Queue, Sellers Absent - MarketsMojo</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Suvidhaa Infoserve Sets September 30 Virtual AGM, Closes Books for FY 2025-26 Decisions - TipRanks</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr"/>
+          <t>Chembond Chemicals Share Price and Fundamental Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>Chembond (CHEMBOND.NS) Earnings Data Review: The Report Supplies Updated Headline Figures in the Latest Reading; Reaction Snapshot: Shares Move 0.16% Higher in the Current Update - Margin Improvement Report - siam.in</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1883,7 +1919,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="59" customWidth="1" min="4" max="4"/>
+    <col width="43" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -1989,7 +2025,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 12:59:33 IST</t>
+          <t>2026-09-09 20:33:13 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -1997,68 +2033,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>DCI.NS</t>
+          <t>MONEYBOXX.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Dc Infotech And Communication Limited</t>
+          <t>Moneyboxx Finance Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>301.9500122070312</v>
+        <v>57</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>302.0499877929688</v>
+        <v>57</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>271.1499938964844</v>
+        <v>44.81000137329102</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>272</v>
+        <v>44.81000137329102</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>300.75</v>
+        <v>56.0099983215332</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>272</v>
+        <v>44.81000137329102</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>1178610</v>
+        <v>349419</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-9.56</v>
+        <v>-20</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>(DCI) Price Dynamics and Execution-Aware Positioning - Stock Traders Daily</t>
+          <t>Moneyboxx Finance Ltd leads losers in 'B' group - Business Standard</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>(DCI) Price Dynamics and Execution-Aware Positioning - Stock Traders Daily</t>
+          <t>Moneyboxx Finance Ltd leads losers in 'B' group - Business Standard</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>DCI Share Price Rise: Fundamentals, Peers and Market Cap - univest.in</t>
+          <t>Moneyboxx Finance Share Price Update After Sharp Day Gain - Univest</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Donaldson (DCI) Stock Slips After Record Margins Set A Higher Bar - simplywall.st</t>
+          <t>Moneyboxx Finance Promoters Boost Stake To 46.79% Through ₹33.4 Crore Allotment - scanx.trade</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Donaldson (DCI) Stock Looks Reasonable On Earnings But Rich On Cash Flow - Yahoo Finance</t>
+          <t>Moneyboxx Finance NRC approves grant of 9,09,200 stock options - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 12:59:33 IST</t>
+          <t>2026-09-09 20:33:13 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -2066,68 +2102,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>MEDICO.NS</t>
+          <t>ATALREAL.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Medico Remedies Limited</t>
+          <t>Atal Realtech Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>39.22999954223633</v>
+        <v>16.95999908447266</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>39.2400016784668</v>
+        <v>16.95999908447266</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>34.11000061035156</v>
+        <v>16.95999908447266</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>36.70000076293945</v>
+        <v>16.95999908447266</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>39.27999877929688</v>
+        <v>21.20000076293945</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>36.70000076293945</v>
+        <v>16.95999908447266</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>1557138</v>
+        <v>701191</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-6.57</v>
+        <v>-20</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Medico Intercontinental schedules AGM for September 30, 2026 - scanx.trade</t>
+          <t>Here's Why We Think Atal Realtech (NSE:ATALREAL) Might Deserve Your Attention Today - simplywall.st</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Medico Intercontinental schedules AGM for September 30, 2026 - scanx.trade</t>
+          <t>ATALREAL Q2 2026 Earnings: Revenue Surges 25.4% YoY, EPS Delivers at ₹0.99 - Profit Inflection Point - vinanet.vn</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Medico Intercontinental Q1 Results: Standalone profit rises 9% YoY to ₹60.8 lakh - scanx.trade</t>
+          <t>Atal Realtech Limited (ATALREAL.NS) Trades Higher with Modest Gains; Support and Resistance Levels in Focus - Box Spread - vinanet.vn</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Medico Remedies Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>Is Atal Realtech (NSE:ATALREAL) A Risky Investment? - simplywall.st</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Medico Remedies Q1 Results FY27: PAT Rs 2 Cr, Revenue Rs 69 crore - univest.in</t>
+          <t>Atal Realtech (ATALREAL.NS) Holds Ground Near Support After Slight Decline - Bearish Pattern Stocks - vinanet.vn</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 12:59:33 IST</t>
+          <t>2026-09-09 20:33:13 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -2135,68 +2171,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>BODALCHEM.NS</t>
+          <t>DCI.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Bodal Chemicals Limited</t>
+          <t>Dc Infotech And Communication Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>186.3999938964844</v>
+        <v>301.9500122070312</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>189.6799926757812</v>
+        <v>302.0499877929688</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>174.8500061035156</v>
+        <v>270.2000122070312</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>174.8500061035156</v>
+        <v>270.7999877929688</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>184.0500030517578</v>
+        <v>300.75</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>174.8500061035156</v>
+        <v>270.7999877929688</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>3456475</v>
+        <v>1464455</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-5</v>
+        <v>-9.960000000000001</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Bodal Chemicals Share Price news with valuation context - univest.in</t>
+          <t>HighTower Advisors LLC Sells 151,767 Shares of Donaldson Company, Inc. $DCI - MarketBeat</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Bodal Chemicals Ltd. Lower Circuit Today: Price, Data and Peers - univest.in</t>
+          <t>HighTower Advisors LLC Sells 151,767 Shares of Donaldson Company, Inc. $DCI - MarketBeat</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>With EPS Growth And More, Bodal Chemicals (NSE:BODALCHEM) Makes An Interesting Case - simplywall.st</t>
+          <t>(DCI) Price Dynamics and Execution-Aware Positioning - Stock Traders Daily</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Bodal Chemicals Ltd. (BODALCHEM) Share Price Rises 9.21% Today; Key Levels, Valuation and Peer View - univest.in</t>
+          <t>DCI Share Price Rise: Fundamentals, Peers and Market Cap - Univest</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Bodal Chemicals Ltd. Lower Circuit Today: Price, Data and Peers - univest.in</t>
+          <t>Donaldson (DCI) Stock Looks Reasonable On Earnings But Rich On Cash Flow - finance.yahoo.com</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 12:59:33 IST</t>
+          <t>2026-09-09 20:33:13 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -2204,68 +2240,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>RAJTV.NS</t>
+          <t>MEDICO.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Raj Television Network Limited</t>
+          <t>Medico Remedies Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>8.600000381469727</v>
+        <v>39.22999954223633</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>8.789999961853027</v>
+        <v>39.2400016784668</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>8.210000038146973</v>
+        <v>34.11000061035156</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>8.210000038146973</v>
+        <v>35.43999862670898</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>8.640000343322754</v>
+        <v>39.27999877929688</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>8.210000038146973</v>
+        <v>35.43999862670898</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>95765</v>
+        <v>2382325</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-4.98</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Raj TV Network Q1 Results: Unaudited financials for June quarter filed - scanx.trade</t>
+          <t>Medico Intercontinental schedules AGM for September 30, 2026 - scanx.trade</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Kiran Kumar Jain M. sells 0.9% stake in Raj TV Network - scanx.trade</t>
+          <t>Medico Intercontinental schedules AGM for September 30, 2026 - scanx.trade</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Kiran Kumar Jain M. sells 0.9% stake in Raj TV Network - scanx.trade</t>
+          <t>Medico Intercontinental Q1 Results: Standalone profit rises 9% YoY to ₹60.8 lakh - scanx.trade</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Raj TV Network Q1 Results: Net Loss Widens To ₹10.08 Million - scanx.trade</t>
+          <t>Medico Remedies Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>Raj Television moves AGM online and digitizes access to 2025–26 annual report - TipRanks</t>
+          <t>Prism Medico and Pharmacy Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 12:59:33 IST</t>
+          <t>2026-09-09 20:33:13 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2273,68 +2309,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>AKI.NS</t>
+          <t>DAVANGERE.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>AKI India Limited</t>
+          <t>Davangere Sugar Company Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>7.150000095367432</v>
+        <v>1.960000038146973</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>7.349999904632568</v>
+        <v>2.019999980926514</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>6.800000190734863</v>
+        <v>1.740000009536743</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>6.800000190734863</v>
+        <v>1.75</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>7.150000095367432</v>
+        <v>1.929999947547913</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>6.800000190734863</v>
+        <v>1.75</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>90144</v>
+        <v>161990871</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-4.9</v>
+        <v>-9.33</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Penny stock under 10 rupees: Upper circuit - Leather share jumps 74% in 4 sessions | Back-to-back surge for third day - TradingView</t>
+          <t>Trending Stocks Today, September 9, 2026: PC Jeweller, Vodafone Idea, IFCI, Davangere Sugar In Focus - HDFC Sky</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>AKI India Share Price: Is It a Good Buy After Q1 FY27 Results? - univest.in</t>
+          <t>Trending Stocks Today, September 9, 2026: PC Jeweller, Vodafone Idea, IFCI, Davangere Sugar In Focus - HDFC Sky</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>AKI India Share Price: Is It a Good Buy After Q1 FY27 Results? - univest.in</t>
+          <t>Davangere Sugar Company Share Price Update and Analysis - Univest</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>AKI India Ltd leads gainers in 'B' group - Business Standard</t>
+          <t>Davangere Sugar to convert Rs 40.12 crore promoter loan into equity warrants, doubles authorised capital - ChiniMandi</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>AKI India Ltd Upgraded to Sell on Technical Improvements Despite Lingering Financial Challenges - MarketsMojo</t>
+          <t>Davangere Sugar Company allots 26.59 cr equity shares on conversion of FCCBs - Business Standard</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 12:59:33 IST</t>
+          <t>2026-09-09 20:33:13 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2342,68 +2378,64 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COFORGE.NS</t>
+          <t>EMPIND.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Coforge Limited</t>
+          <t>Empire Industries Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1815.5</v>
+        <v>1107.199951171875</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1877.599975585938</v>
+        <v>1120</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>1780.699951171875</v>
+        <v>1068.099975585938</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1856.099975585938</v>
+        <v>1076.599975585938</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1950</v>
+        <v>1176.800048828125</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1856.099975585938</v>
+        <v>1076.599975585938</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>8015372</v>
+        <v>13226</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-4.82</v>
+        <v>-8.51</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Coforge stock plunges 7% as chairman OP Bhatt quits after internal audit flags board evaluation lapses - Moneycontrol.com</t>
+          <t>Empire Industries Ltd. (India) Financial Statements – NSE:EMPIND - TradingView</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>O P Bhatt resigns from Coforge board over evaluation concerns; stock falls 8.7% - Fortune India</t>
+          <t>Empire Industries Ltd. (EMPIND) Fundamental and Financial Data - Stocktwits</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Coforge shares plunge nearly 9% after Chairman OP Bhatt’s sudden exit; key details - Upstox</t>
+          <t>Empire Industries Ltd. (EMPIND) Fundamental and Financial Data - Stocktwits</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Coforge Shares Slide 8% as Chairman OP Bhatt Quits Abruptly - Equitypandit</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>Infosys, TCS, Coforge, Mphasis shares: Targets as Amazon, Google, Microsoft ramp up capex - Business Today</t>
-        </is>
-      </c>
+          <t>Empire Industries Ltd. (EMPIND) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 12:59:33 IST</t>
+          <t>2026-09-09 20:33:13 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2411,68 +2443,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>PNGSREVA.NS</t>
+          <t>GSPCROP.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>PNGS Reva Diamond Jewellery Limited</t>
+          <t>GSP Crop Science Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>548.6500244140625</v>
+        <v>524.8499755859375</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>550.4500122070312</v>
+        <v>531.4000244140625</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>513.25</v>
+        <v>479.9500122070312</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>522</v>
+        <v>491.3500061035156</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>546.5499877929688</v>
+        <v>531</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>522</v>
+        <v>491.3500061035156</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>175115</v>
+        <v>1797741</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-4.49</v>
+        <v>-7.47</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>PNGSREVA Stock Price and Chart — NSE:PNGSREVA - TradingView</t>
+          <t>GSP CROP SCIENCE LIMITED (GSPCROP) Share Price Hits Fresh 52-Week High - Univest</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Mohit Industries Ltd leads gainers in 'B' group - Business Standard</t>
+          <t>GSP CROP SCIENCE LIMITED (GSPCROP) Share Price Hits Fresh 52-Week High - Univest</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>PNGS Reva Diamond Jewellery (PNGSREVA) Declines 1.35% as Stock Hovers Near Support; Key Levels in Focus - WMA Signal - siam.in</t>
+          <t>GSP (GSPCROP.NS) Results Review: The Company Reports Its Latest Available Figures in the Latest Session; Stock Move: Shares Close 4.75% Higher in the Current Update - Earnings Call Q&amp;A - siam.in</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>PNGS REVA DIAMOND JEWEL L Share Price - Live NSE: PNGSREVA Stock Price &amp; Chart - Upstox</t>
+          <t>GSP (GSPCROP.NS) Quarterly Results: The Company Lists Its Latest Available Figures in Latest Trading; Share Response: Shares Rise 0.29% in the Current Update - Preliminary Results - siam.in</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>PNGS Reva Diamond Jewellery's (NSE:PNGSREVA) Promising Earnings May Rest On Soft Foundations - simplywall.st</t>
+          <t>GSP (GSPCROP.NS) Earnings Reading: The Latest Report Adds New Financial Reference Points in the Available Record; After Earnings: The Stock Records a 0.59% Increase at the Close - Estimate Uncertainty - siam.in</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 12:59:33 IST</t>
+          <t>2026-09-09 20:33:13 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2480,68 +2512,56 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>ANDHRAPAP.NS</t>
+          <t>AGROPHOS.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>ANDHRA PAPER LIMITED</t>
+          <t>Agro Phos India Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>69.16000366210938</v>
+        <v>23.45000076293945</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>71.55999755859375</v>
+        <v>23.88999938964844</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>67.70999908447266</v>
+        <v>21</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>68.91000366210938</v>
+        <v>21.71999931335449</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>72.08999633789062</v>
+        <v>23.44000053405762</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>68.91000366210938</v>
+        <v>21.71999931335449</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>2208049</v>
+        <v>143020</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-4.41</v>
+        <v>-7.34</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Andhra Paper Limited Re-appoints Saurabh Bangur as Managing Director for Five-Year Term - scanx.trade</t>
+          <t>Agro Phos India Board Clears FY26 Reports, Sets September 30 AGM and E‑Voting Timeline - tipranks.com</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Andhra Paper Faces ₹21 Crore Environmental Levy from AP Pollution Board - TipRanks</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>Andhra Paper Limited (ANDHRAPAP.NS) Edges Higher: Stock Gains 1.72% Amid Defensive Buying - Investment Factor - siam.in</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>Andhra Paper Rises 3.3% to ₹61.93: Key Levels to Watch - Short Setup Alerts - siam.in</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>Andhra Paper reappoints Saurabh Bangur as MD for five years - scanx.trade</t>
-        </is>
-      </c>
+          <t>Agro Phos India Board Clears FY26 Reports, Sets September 30 AGM and E‑Voting Timeline - tipranks.com</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 12:59:33 IST</t>
+          <t>2026-09-09 20:33:13 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2549,68 +2569,64 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>GNFC.NS</t>
+          <t>JOCIL.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Gujarat Narmada Valley Fertilizers and Chemicals Limited</t>
+          <t>Jocil Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>564</v>
+        <v>163.9900054931641</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>566.0499877929688</v>
+        <v>164</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>556.5</v>
+        <v>145.2599945068359</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>565.5999755859375</v>
+        <v>152.2899932861328</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>589.0999755859375</v>
+        <v>164.2899932861328</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>565.5999755859375</v>
+        <v>152.2899932861328</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>533392</v>
+        <v>30735</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-3.99</v>
+        <v>-7.3</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>GNFC Outlook for the Week - Equitypandit</t>
+          <t>Jocil Share Price Falls 9.15%: Valuation and Peer View - Univest</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>GNFC accepts Rajkumar Beniwal resignation, appoints Sanjeev Kumar as MD - scanx.trade</t>
+          <t>Jocil Share Price Falls 9.15%: Valuation and Peer View - Univest</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>GNFC accepts Rajkumar Beniwal resignation, appoints Sanjeev Kumar as MD - scanx.trade</t>
+          <t>Jocil Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Gujarat Narmada Valley Fertilizers (GNFC.NS) Holds Near ₹577; Support at ₹548.1 Becomes Key Watchpoint - Float Adjusted Cap - siam.in</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>MRPL vs GNFC: Which PSU Stock Offers Value - univest.in</t>
-        </is>
-      </c>
+          <t>Jocil Ltd. Peer Comparison – Compare with Others - Value Research</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 12:59:33 IST</t>
+          <t>2026-09-09 20:33:13 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2618,68 +2634,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>MOLDTECH.NS</t>
+          <t>NGIL.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Mold-Tek Technologies Limited</t>
+          <t>Nakoda Group of Industries Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>218.2700042724609</v>
+        <v>37.36000061035156</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>224.3999938964844</v>
+        <v>39.75</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>210</v>
+        <v>34.75</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>210.1999969482422</v>
+        <v>35.04000091552734</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>218.2700042724609</v>
+        <v>37.72999954223633</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>210.1999969482422</v>
+        <v>35.04000091552734</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>23478</v>
+        <v>43179</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-3.7</v>
+        <v>-7.13</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Mold-Tek Technologies (MOLDTECH.NS) Gains 2.44% to ₹207.31, Moves Toward Key Resistance - Double Top - siam.in</t>
+          <t>Nakoda Group of Industries (NGIL) Hovers Near Resistance as Stock Gains Marginally - Put Flow Alert - vinanet.vn</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Be Sure To Check Out Mold-Tek Technologies Limited (NSE:MOLDTECH) Before It Goes Ex-Dividend - simplywall.st</t>
+          <t>Nakoda Group Faces Selling Pressure; Key Support Levels in Focus (NGIL.NS) - Break of Structure - vinanet.vn</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Mold-Tek (MOLDTECH.NS) Session: Loses 0.32% to Close at ₹193.00 in the Latest Session; Technical View: the Price Remains Bounded by the Supplied Support and Resistance in the Available Record - Wyckoff Accumulation - siam.in</t>
+          <t>Nakoda Group of Industries (NGIL.NS) Rises Over 3%: Key Levels Hold as Momentum Builds - Unusual Call Volume - vinanet.vn</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Be Sure To Check Out Mold-Tek Technologies Limited (NSE:MOLDTECH) Before It Goes Ex-Dividend - simplywall.st</t>
+          <t>Nakoda Group Industries (NGIL) Edges Higher, Consolidating Near Resistance - ETF Outflow Streak - vinanet.vn</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>Mold-Tek Technologies Limited Recommends Final Dividend for the Financial Year Ended 31 March 2026 - marketscreener.com</t>
+          <t>NAKODA GROUP OF IND. LTD Share Price - upstox.com</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 12:59:33 IST</t>
+          <t>2026-09-09 20:33:13 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2687,64 +2703,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>AEROENTER.NS</t>
+          <t>GKB.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Aeroflex Enterprises Limited</t>
+          <t>GKB Ophthalmics Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>151.8099975585938</v>
+        <v>72</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>152.5500030517578</v>
+        <v>74</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>144.9100036621094</v>
+        <v>65</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>147.0399932861328</v>
+        <v>66.43000030517578</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>152.6499938964844</v>
+        <v>71.51999664306641</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>147.0399932861328</v>
+        <v>66.43000030517578</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>749940</v>
+        <v>17482</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-3.68</v>
+        <v>-7.12</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Sat Industries Ltd. Share Price News and Price Action Today - univest.in</t>
+          <t>GKB Stock Price and Chart — NSE:GKB - TradingView</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Sat Industries Share Price Rises 8.5%: Market Cap, Valuation - univest.in</t>
+          <t>GKB Ophthalmics Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Sat Industries Share Price Rises 8.5%: Market Cap, Valuation - univest.in</t>
+          <t>GKB Ophthalmics Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Aeroflex Enterprises Q1 Results: Net profit jumps 616% YoY - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr"/>
+          <t>GKB Ophthalmics shareholders unanimously approve all seven AGM resolutions - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>Gkb Ophthalmics Limited Statistics – NSE:GKB - TradingView</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 12:59:33 IST</t>
+          <t>2026-09-09 20:33:13 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2752,68 +2772,60 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>NETWEB.NS</t>
+          <t>ANSALBU.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Netweb Technologies India Limited</t>
+          <t>Ansal Buildwell Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>5100</v>
+        <v>82.5</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>5127.5</v>
+        <v>82.5</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>4895</v>
+        <v>75</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>4901</v>
+        <v>77.15000152587891</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>5087.5</v>
+        <v>82.5</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>4901</v>
+        <v>77.15000152587891</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>1132712</v>
+        <v>567</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-3.67</v>
+        <v>-6.48</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Netweb Technologies seeks nod to raise ₹1,200 crore via postal ballot - scanx.trade</t>
+          <t>ANSALBU Stock Price and Chart — NSE:ANSALBU - TradingView</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Netweb Technologies seeks nod to raise ₹1,200 crore via postal ballot - scanx.trade</t>
+          <t>Ansal Buildwell Ltd - Equitypandit</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Netweb Technologies shares fall 4% after raising Rs 1,200 crore through QIP - The Economic Times</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>3 Indian AI Stocks To Own In September 2026 - simplywall.st</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>Netweb Technologies Shares Jump 5% On Strong FY26 Show - Equitypandit</t>
-        </is>
-      </c>
+          <t>Ansal Buildwell Ltd - Equitypandit</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 12:59:33 IST</t>
+          <t>2026-09-09 20:33:13 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2821,68 +2833,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>IFCI.NS</t>
+          <t>THAKDEV.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>IFCI Limited</t>
+          <t>Thakkers Developers Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>92.5</v>
+        <v>148</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>93.55999755859375</v>
+        <v>148</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>87.76000213623047</v>
+        <v>137</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>89.23000335693359</v>
+        <v>138.5</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>92.61000061035156</v>
+        <v>148</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>89.23000335693359</v>
+        <v>138.5</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>124038219</v>
+        <v>17</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-3.65</v>
+        <v>-6.42</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>IFCI Share Price Today: Stock Falls 8% as NSE IPO-Linked Rally Faces Profit Booking; What Investors Should Know - India Infoline</t>
+          <t>THAKDEV Stock Price and Chart — NSE:THAKDEV - TradingView</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>NSE IPO Speculation Lifts IFCI, NIACL; Profit Booking Cuts Gains - HDFC Sky</t>
+          <t>Thakkers Developers Holds Steady at ₹128.9 – Key Levels in Focus for THAKDEV.NS - Initial Balance - vinanet.vn</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>IFCI shares fall 4% on reports of lower price band for NSE IPO - The Economic Times</t>
+          <t>THAKDEV Mar 2026 Earnings: Revenue Decline and Net Loss Drag Stock Lower - EPS Revision Trend - vinanet.vn</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>IFCI share price down today- drops 14% in 2 days- Why is the stock falling? - Livemint</t>
+          <t>Thakkers Developers Limited: Sideways Consolidation Near Key Resistance at ₹127 - Wave Equality - vinanet.vn</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>NSE IPO: Stake-Selling Shareholders Under Pressure As SBI, GIC Re, IFCI, BoB Stocks Decline - HDFC Sky</t>
+          <t>Thakkers Developers (THAKDEV.NS) Holds Steady at ₹123 – Consolidation Phase Ahead? - Unusual Put Volume - vinanet.vn</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 12:59:33 IST</t>
+          <t>2026-09-09 20:33:13 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2890,68 +2902,64 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>ATLASCYCLE.NS</t>
+          <t>AEROENTER.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Atlas Cycles (Haryana) Limited</t>
+          <t>Aeroflex Enterprises Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>116</v>
+        <v>151.8099975585938</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>116</v>
+        <v>152.5500030517578</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>107.3000030517578</v>
+        <v>140.6999969482422</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>109</v>
+        <v>142.9499969482422</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>113.0299987792969</v>
+        <v>152.6499938964844</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>109</v>
+        <v>142.9499969482422</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>136614</v>
+        <v>1381005</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-3.57</v>
+        <v>-6.35</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Atlas Cycles (Haryana) shareholders approve FY26 financials despite promoter dissent - scanx.trade</t>
+          <t>Sat Industries Ltd. Share Price News and Price Action Today - Univest</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>20% Upper Circuit: Wheels India and 9 Other Stocks That Hit the Upper Circuit Today; Are You Holding Any? - Trade Brains</t>
+          <t>Sat Industries Share Price Rises 8.5%: Market Cap, Valuation - Univest</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Penny Stock Below Rs 100 Posts Wider Loss in Q1 FY27 Even as Land Sale Deal Gets Extended - Dalal Street Investment Journal</t>
+          <t>Sat Industries Share Price Rises 8.5%: Market Cap, Valuation - Univest</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Atlas Cycles (Haryana) grants sale deed extension for Sonepat land - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>20% Upper Circuit: Wheels India and 9 Other Stocks That Hit the Upper Circuit Today; Are You Holding Any? - Trade Brains</t>
-        </is>
-      </c>
+          <t>Aeroflex Enterprises Q1 Results: Net profit jumps 616% YoY - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 12:59:33 IST</t>
+          <t>2026-09-09 20:33:13 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2959,68 +2967,60 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>PVRINOX.NS</t>
+          <t>KIRIINDUS.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>PVR INOX Limited</t>
+          <t>Kiri Industries Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1231.300048828125</v>
+        <v>596.0499877929688</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>1232</v>
+        <v>600.5</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>1185.599975585938</v>
+        <v>546.5999755859375</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>1188</v>
+        <v>550.75</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1231.300048828125</v>
+        <v>588.0999755859375</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1188</v>
+        <v>550.75</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>316858</v>
+        <v>2371065</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-3.52</v>
+        <v>-6.35</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>PVR Inox Share Price - Live NSE: PVRINOX Stock Price &amp; Chart - Upstox</t>
+          <t>Kiri Industries Share Price today: valuation and sector view - Univest</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>PVR INOX shares gain over 7% after firm announces updated buyback date; check key details - Upstox</t>
+          <t>Kiri Industries Share Price today: valuation and sector view - Univest</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>PVR INOX Limited (NSE: PVRINOX) Falls 6.79% as Stock Movement Draws Market Attention - Kalkine India</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>PVR INOX Limited announces an Equity Buyback for 2,068,965 shares, representing 2.11% for INR 3,000 million. - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>PVRINOX Outlook for the Week - Equitypandit</t>
-        </is>
-      </c>
+          <t>Kiri Industries Ltd. Share Price Today Up 8.18%: Stock News - Univest</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 12:59:33 IST</t>
+          <t>2026-09-09 20:33:13 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -3028,68 +3028,56 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>HCLTECH.NS</t>
+          <t>XPROINDIA.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>HCL Technologies Limited</t>
+          <t>Xpro India Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1248.800048828125</v>
+        <v>1393.800048828125</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>1264.800048828125</v>
+        <v>1393.800048828125</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>1228</v>
+        <v>1291.800048828125</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>1234.400024414062</v>
+        <v>1301.400024414062</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1277</v>
+        <v>1389.699951171875</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1234.400024414062</v>
+        <v>1301.400024414062</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>1357443</v>
+        <v>85026</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-3.34</v>
+        <v>-6.35</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>HCLTech invests ₹185 crore to set up advanced semiconductor lab in Bengaluru; shares down 22% YTD - Upstox</t>
+          <t>Xpro (XPROINDIA.NS) Session: Ends Higher by 1.94% at ₹1,164.10 in Latest Trading; Current Setup: Price Remains Between ₹1,105.89 Support and ₹1,222.31 Resistance in the Current Update - Max Pain Level - siam.in</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>HCLTech Launches Rs 185 Crore Semiconductor Lab in Bengaluru - Equitypandit</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>HCLTech Launches ₹185 Crore Semiconductor Lab; Shares Fall 0.25% - HDFC Sky</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>HCLTech Launches Rs 185 Crore Semiconductor Lab in Bengaluru - Equitypandit</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>HCLTech launches Advanced Semiconductor Lab in Bengaluru: How the stock market reacted - theweek.in</t>
-        </is>
-      </c>
+          <t>Xpro (XPROINDIA.NS) Session: Ends Higher by 1.94% at ₹1,164.10 in Latest Trading; Current Setup: Price Remains Between ₹1,105.89 Support and ₹1,222.31 Resistance in the Current Update - Max Pain Level - siam.in</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr"/>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 12:59:33 IST</t>
+          <t>2026-09-09 20:33:13 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -3097,68 +3085,60 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>UNIMECH.NS</t>
+          <t>PAVNAIND.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Unimech Aerospace and Manufacturing Limited</t>
+          <t>Pavna Industries Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1649</v>
+        <v>16.18000030517578</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>1652.800048828125</v>
+        <v>16.48999977111816</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>1542</v>
+        <v>14.65999984741211</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>1575.5</v>
+        <v>15.17000007629395</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1629.599975585938</v>
+        <v>16.18000030517578</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1575.5</v>
+        <v>15.17000007629395</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>294495</v>
+        <v>297899</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-3.32</v>
+        <v>-6.24</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Unimech Aerospace And Manufacturing Buys 850 Shares Of Dheya Engineering For 30 Million Rupees - TradingView</t>
+          <t>Pavna Industries Limited agreed to acquire 52.38% stake in Pavna Electric Systems Private Limited for INR 1.7 million. - marketscreener.com</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>UNIMECH Share Price update: price action and sector view - univest.in</t>
+          <t>Pavna Industries Reshapes Portfolio With New Subsidiary, Divests Two Units - tipranks.com</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>UNIMECH Share Price update: price action and sector view - univest.in</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>Unimech Aerospace reshuffles senior management amid restructuring - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>Unimech (UNIMECH.NS) Range: Records a Muted Move to ₹1,508.50 in the Available Record; Price Setup: the Current Price Sits Inside the Supplied Technical Range in the Available Record - Time Weighted Price - siam.in</t>
-        </is>
-      </c>
+          <t>Pavna Industries Reshapes Portfolio With New Subsidiary, Divests Two Units - tipranks.com</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 12:59:33 IST</t>
+          <t>2026-09-09 20:33:13 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -3166,68 +3146,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>PFIZER.NS</t>
+          <t>TERASOFT.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Pfizer Limited</t>
+          <t>Tera Software Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>4310.7001953125</v>
+        <v>272.3500061035156</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>4318</v>
+        <v>272.3500061035156</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>4165</v>
+        <v>251.5</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>4171.39990234375</v>
+        <v>255.3999938964844</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>4310.7001953125</v>
+        <v>272.3500061035156</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>4171.39990234375</v>
+        <v>255.3999938964844</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>84968</v>
+        <v>40575</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-3.23</v>
+        <v>-6.22</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Pfizer Ltd. Share Price Falls to One-Year Low: Key View - univest.in</t>
+          <t>Tera Software Limited Announces Appointment of G. Anil Kumar as Key Managerial Personnel, Effective September 7, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Novartis India shares zoom 20% to hit record high; Minipress deal fuels rally - Business Today</t>
+          <t>Tera Software Sets AGM Date, Opens Remote E-Voting for Shareholders - tipranks.com</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>This Is What I'd Do With Pfizer Stock Right Now - Yahoo Finance</t>
+          <t>Tera Software makes TS Innovations a wholly owned subsidiary - scanx.trade</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Pfizer, PCBL, Data Patterns shares spurt amid surge in volumes; check full list - Upstox</t>
+          <t>Tera Software Sets AGM Date, Opens Remote E-Voting for Shareholders - tipranks.com</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>Pfizer stock offers 13.8% upside plus a 5.91% d... - Pluang</t>
+          <t>Tera Software Sets Record Date and AGM Schedule for 2026 Dividend - tipranks.com</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 12:59:33 IST</t>
+          <t>2026-09-09 20:33:13 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -3235,68 +3215,64 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>MTARTECH.NS</t>
+          <t>SARVESHWAR.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Mtar Technologies Limited</t>
+          <t>Sarveshwar Foods Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>7900</v>
+        <v>4.159999847412109</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>7945</v>
+        <v>4.170000076293945</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>7453.5</v>
+        <v>3.740000009536743</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>7550.5</v>
+        <v>3.779999971389771</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>7799.5</v>
+        <v>4.03000020980835</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>7550.5</v>
+        <v>3.779999971389771</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>104203</v>
+        <v>7127812</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-3.19</v>
+        <v>-6.2</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>MTAR Technologies Share Price - Live NSE: MTARTECH Stock Price &amp; Chart - Upstox</t>
+          <t>Sarveshwar Foods Share Price Today: Price Rise Analysis - Univest</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>MTAR Technologies: Promoter Sells 18,000 Shares - InvestyWise</t>
+          <t>Sarveshwar Foods sets September 30 AGM for warrant issue, ESOP approval - scanx.trade</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Mtar Technologies (MTARTECH.NS) Drops 2.55% to ₹7,049.5: Key Support and Resistance Levels - Volume Climax - siam.in</t>
+          <t>Sarveshwar Foods sets September 30 AGM for warrant issue, ESOP approval - scanx.trade</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Mtar (MTARTECH.NS) Earnings Reading: The Latest Report Adds New Financial Reference Points in the Latest Reading; Latest Reaction: Shares Finish 3.09% Lower - Revenue Breakdown Analysis - siam.in</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>Mtar (MTARTECH.NS) Earnings Reading: The Latest Report Adds New Financial Reference Points in the Latest Reading; Latest Reaction: Shares Finish 3.09% Lower - EPS Surprise History - siam.in</t>
-        </is>
-      </c>
+          <t>Sarveshwar (SARVESHWAR.NS) Results Review: The Company Publishes Its Latest Results in the Current Update; Post-Report: Shares Move Higher 0.29% at the Close - SaaS Earnings Trends - siam.in</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 12:59:33 IST</t>
+          <t>2026-09-09 20:33:13 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -3304,61 +3280,61 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>HARSHA.NS</t>
+          <t>AEPL.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Harsha Engineers International Limited</t>
+          <t>Artemis Electricals and Projects Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>466.7999877929688</v>
+        <v>18.5</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>470.9500122070312</v>
+        <v>18.5</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>449.0499877929688</v>
+        <v>16.1200008392334</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>452.2000122070312</v>
+        <v>16.98999977111816</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>466.7999877929688</v>
+        <v>18.11000061035156</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>452.2000122070312</v>
+        <v>16.98999977111816</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>119630</v>
+        <v>122988</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-3.13</v>
+        <v>-6.18</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Harsha Engineers International Ltd. Stock News - Value Research</t>
+          <t>AEPL Stock Price and Chart — NSE:AEPL - TradingView</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Harsha Engineers International Ltd. Stock News - Value Research</t>
+          <t>Artemis Electricals and Projects (AEPL.NS) Mar 2026 Earnings: Modest Profit Amid Flat Revenue - Financial Health Score - vinanet.vn</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Earnings call transcript: Harsha Engineers posts strong Q1 2026 growth, shares fall - Investing.com India</t>
+          <t>Artemis Electricals Gets NSE Approval To List 25.10 Cr Equity Shares On Main Board - scanx.trade</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Harsha Engineers International Limited Just Recorded A 7.4% Revenue Beat: Here's What Analysts Think - simplywall.st</t>
+          <t>Artemis Electricals Tests Support Zone: AEPL Declines 2.12% to ₹16.17 - Catalyst Driven Stocks - vinanet.vn</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>Harsha Engineer Consolidated June 2026 Net Sales at Rs 457.43 crore, up 25.22% Y-o-Y - Moneycontrol.com</t>
+          <t>Nectar Lifesciences Completes ₹24.96 Lakh AEPL Acquisition, Forms Wholly-Owned Subsidiary - scanx.trade</t>
         </is>
       </c>
     </row>

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -439,14 +439,14 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 12:56:51 IST</t>
+          <t>2026-09-10 20:07:15 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -553,68 +553,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>MOLBIO.NS</t>
+          <t>LADDERUP.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics Limited</t>
+          <t>Ladderup Finance Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1271</v>
+        <v>54.90000152587891</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1509.400024414062</v>
+        <v>61.93000030517578</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1271</v>
+        <v>53</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>1509.400024414062</v>
+        <v>61.93000030517578</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1257.900024414062</v>
+        <v>51.61000061035156</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>1509.400024414062</v>
+        <v>61.93000030517578</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>11284539</v>
+        <v>9326</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>19.99</v>
+        <v>20</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics share price hits 20% upper circuit, jumps 87% from IPO price - Livemint</t>
+          <t>Ladderup Finance Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics share price hits 20% upper circuit, jumps 87% from IPO price - Livemint</t>
+          <t>Saraswati Saree Depot Ltd leads gainers in 'B' group - Business Standard</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics shares rally 30% in 2 days, jump 80% since debut. What lies ahead? - The Economic Times</t>
+          <t>Saraswati Saree Depot Ltd leads gainers in 'B' group - Business Standard</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Stocks to Watch Today: Rail Vikas Nigam, Cohance Lifesciences, Molbio Diagnostics, Purple Style Labs,... - Moneycontrol.com</t>
+          <t>Ladderup Finance Ltd. Peer Comparison – Compare with Others - Value Research</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics Ltd Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>Ladderup Finance releases FY26 annual report, sets Sep 24 AGM date - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 12:56:51 IST</t>
+          <t>2026-09-10 20:07:15 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -622,68 +622,60 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>MEDICAPQ.NS</t>
+          <t>SSDL.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Medi Caps Limited</t>
+          <t>Saraswati Saree Depot Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>32.79000091552734</v>
+        <v>58.65000152587891</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>36.79999923706055</v>
+        <v>67.83999633789062</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>29.95999908447266</v>
+        <v>58.5</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>35.06999969482422</v>
+        <v>67.83999633789062</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>30.73999977111816</v>
+        <v>56.54000091552734</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>35.06999969482422</v>
+        <v>67.83999633789062</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>399022</v>
+        <v>296352</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>14.09</v>
+        <v>19.99</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>MEDICAPQ Stock Price and Chart — NSE:MEDICAPQ - TradingView</t>
+          <t>Saraswati Saree Depot SSDL Fresh High Analysis - Kalkine India</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>MEDI-CAPS LIMITED: Discloses Process for Shareholder Annual Report Distribution - InvestyWise</t>
+          <t>Saraswati Saree Depot SSDL Fresh High Analysis - Kalkine India</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Medi-Caps Ltd. (MEDICAPQ) Profile, Company FAQs &amp; Facts, Industry, Sector, Employee Strength - Stocktwits</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>Medi-Caps Ltd. (MEDICAPQ) Share Price Today, Quote, Latest Discussions, Interactive Chart and News - Stocktwits</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>Medi-Caps Ltd. (MEDICAPQ) Fundamental and Financial Data - Stocktwits</t>
-        </is>
-      </c>
+          <t>Saraswati Saree Depot Ltd. Share Price Gain: Key Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 12:56:51 IST</t>
+          <t>2026-09-10 20:07:15 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -691,68 +683,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>GENESYS.NS</t>
+          <t>VEDAVAAG.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Genesys International Corporation Limited</t>
+          <t>VEDAVAAG Systems Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>274.3099975585938</v>
+        <v>18.70000076293945</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>323.2300109863281</v>
+        <v>22.20999908447266</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>265.6300048828125</v>
+        <v>18.51000022888184</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>311.6499938964844</v>
+        <v>22.20999908447266</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>274.3099975585938</v>
+        <v>18.51000022888184</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>311.6499938964844</v>
+        <v>22.20999908447266</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>7147620</v>
+        <v>526243</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>13.61</v>
+        <v>19.99</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Genesys International Share Price gains 8.93% in stock news - Univest</t>
+          <t>Vedavaag Systems schedules 28th AGM for September 30 - scanx.trade</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Genesys International Share Price gains 8.93% in stock news - Univest</t>
+          <t>Vedavaag Systems schedules 28th AGM for September 30 - scanx.trade</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Genesys Intnl Share Price Today, Genesys Intnl Stock Price Live NSE/BSE Updates - The Economic Times</t>
+          <t>VEDAVAAG Stock Price and Chart — NSE:VEDAVAAG - TradingView</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Genesys International seeks approval to use ₹4,000 lakh QIP proceeds for loan repayment - scanx.trade</t>
+          <t>Vedavaag Systems Ltd. Financials – Balance Sheet, Profit &amp; Loss, Cash Flow - Value Research</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Genesys International Corporation Ltd (NSE: GENESYS) Gains 10.74% as Stock Movement Draws Market Attention - Kalkine India</t>
+          <t>Vedavaag Systems Ltd Share Price, Stock Price - NSE/BSE Live - NDTV Profit</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 12:56:51 IST</t>
+          <t>2026-09-10 20:07:15 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -760,56 +752,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>OSWALSEEDS.NS</t>
+          <t>MOLBIO.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>ShreeOswal Seeds And Chemicals Limited</t>
+          <t>Molbio Diagnostics Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>13.69999980926514</v>
+        <v>1271</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>15.60000038146973</v>
+        <v>1509.400024414062</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>13.19999980926514</v>
+        <v>1271</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>14.85999965667725</v>
+        <v>1509.400024414062</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>13.07999992370605</v>
+        <v>1257.900024414062</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>14.85999965667725</v>
+        <v>1509.400024414062</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>1218895</v>
+        <v>11329688</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>13.61</v>
+        <v>19.99</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>ShreeOswal (OSWALSEEDS.NS) Jun 2026 Earnings: The Latest Report Adds New Financial Reference Points in Latest Trading; Market Move: The Share Price Sheds 2.35% in the Current Update - Financial Summary - siam.in</t>
+          <t>Molbio Diagnostics shares surge 35% in two sessions; here’s why the healthcare stock hit record high on Sept 10 - Upstox</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>ShreeOswal (OSWALSEEDS.NS) Jun 2026 Earnings: The Latest Report Adds New Financial Reference Points in Latest Trading; Market Move: The Share Price Sheds 2.35% in the Current Update - Financial Summary - siam.in</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
+          <t>Molbio Diagnostics share price hits 20% upper circuit, jumps 87% from IPO price - TradingView</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>Molbio Diagnostics share price hits 20% upper circuit, jumps 87% from IPO price - TradingView</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>Molbio Diagnostics shares rally 30% in 2 days, jump 80% since debut. What lies ahead? - The Economic Times</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>Molbio Diagnostics hits 20% upper circuit on heavy volume; up 35% in 2 days - Business Standard</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 12:56:51 IST</t>
+          <t>2026-09-10 20:07:15 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -817,68 +821,56 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>ANMOL.NS</t>
+          <t>GRAVISSHO.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Anmol India Limited</t>
+          <t>Graviss Hospitality Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>13.69999980926514</v>
+        <v>29.15999984741211</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>15.55000019073486</v>
+        <v>35.59000015258789</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>12.5600004196167</v>
+        <v>28.64999961853027</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>15.11999988555908</v>
+        <v>35.59000015258789</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>13.63000011444092</v>
+        <v>29.65999984741211</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>15.11999988555908</v>
+        <v>35.59000015258789</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>1288756</v>
+        <v>491934</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>10.93</v>
+        <v>19.99</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Anmol India schedules 28th AGM for September 26, 2026 - scanx.trade</t>
+          <t>Graviss Hospitality (GRAVISSHO.NS) Falls 3.99% to ₹29.6, Approaches Key Support at ₹28.12 - High Low Breadth - siam.in</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Anmol India schedules 28th AGM for September 26, 2026 - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>Anmol India promoter pledges 3.3M shares to SBI for ₹155 crore loan - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>Anmol India schedules Aug 29 board meeting to finalize AGM and annual report - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>Anmol India Promoter Pledges 5.79% Stake to State Bank of India - Whalesbook</t>
-        </is>
-      </c>
+          <t>Graviss Hospitality (GRAVISSHO.NS) Falls 3.99% to ₹29.6, Approaches Key Support at ₹28.12 - High Low Breadth - siam.in</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 12:56:51 IST</t>
+          <t>2026-09-10 20:07:15 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -886,68 +878,64 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>SAMHI.NS</t>
+          <t>DIGJAMLMTD.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Samhi Hotels Limited</t>
+          <t>Digjam Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>151.1000061035156</v>
+        <v>52.97999954223633</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>169</v>
+        <v>61.84000015258789</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>151.1000061035156</v>
+        <v>52.97000122070312</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>168.1000061035156</v>
+        <v>61.84000015258789</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>152.4299926757812</v>
+        <v>51.54000091552734</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>168.1000061035156</v>
+        <v>61.84000015258789</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>1822324</v>
+        <v>732310</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>10.28</v>
+        <v>19.98</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Samhi Hotels shareholders approve ₹750 crore raise despite institutional dissent - scanx.trade</t>
+          <t>Digjam (DIGJAMLMTD.NS) Stock: Retreats 0.27% to ₹51.50; the Supplied Trading Band Runs From ₹48.92 to ₹54.08 - Sector ETF Flow - siam.in</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Samhi Hotels shareholders approve ₹750 crore raise despite institutional dissent - scanx.trade</t>
+          <t>Digjam (DIGJAMLMTD.NS) Stock: Retreats 0.27% to ₹51.50; the Supplied Trading Band Runs From ₹48.92 to ₹54.08 - Sector ETF Flow - siam.in</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>FMR LLC raises stake in Samhi Hotels to 5.06% via open market buys - scanx.trade</t>
+          <t>Digjam Shareholders Weigh NCLT-Directed Scheme of Arrangement with Reid &amp; Taylor - The Globe and Mail</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Fidelity: Acquires 4.53% Stake in Samhi Hotels - InvestyWise</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>SAMHI HOTELS LIMITED: Regulatory Filing on Share Acquisition - InvestyWise</t>
-        </is>
-      </c>
+          <t>Digjam Shareholders Clear Scheme of Arrangement with Reid &amp; Taylor - The Globe and Mail</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 12:56:51 IST</t>
+          <t>2026-09-10 20:07:15 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -955,64 +943,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>SHAREINDIA.NS</t>
+          <t>KAVDEFENCE.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Share India Securities Limited</t>
+          <t>Kavveri Defence &amp; Wireless Technologies Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>191.4799957275391</v>
+        <v>63</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>212.3300018310547</v>
+        <v>75.81999969482422</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>191.0099945068359</v>
+        <v>61</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>207.75</v>
+        <v>74.76999664306641</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>189.4600067138672</v>
+        <v>63.18999862670898</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>207.75</v>
+        <v>74.76999664306641</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>44662342</v>
+        <v>2358786</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>9.65</v>
+        <v>18.33</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Share India Securities Announces NCLT Hearing Date for Silverleaf Capital Amalgamation Scheme - scanx.trade</t>
+          <t>KAVDEFENCE Share Price Rise: Price Action and Valuation - Univest</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Share India Securities Share Price Today: Key Price Rise - Univest</t>
+          <t>Kavveri Defence Board Clears Amalgamation of Samoro Telecoms Unit - TipRanks</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Share India Securities Share Price Today: Key Price Rise - Univest</t>
+          <t>2 Data Centre Stocks and 7 Others Hit the 20% Upper Circuit Today; Do You Own Any? - Trade Brains</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Share India Securities Limited Announces Appointment of Rajesh Arora as Additional Director, Designated as A Non-Executive Independent Director - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr"/>
+          <t>Kavveri Defence Board Clears Amalgamation of Samoro Telecoms Unit - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>Kavveri Defence &amp; Wireless Technologies Clears Amalgamation with Samoro Telecoms - TipRanks</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 12:56:51 IST</t>
+          <t>2026-09-10 20:07:15 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1020,68 +1012,64 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>SREEL.NS</t>
+          <t>BIOFILCHEM.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Sreeleathers Limited</t>
+          <t>Biofil Chemicals &amp; Pharmaceuticals Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>350.5</v>
+        <v>31.45999908447266</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>400</v>
+        <v>37.75</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>350.5</v>
+        <v>31.45999908447266</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>373.6400146484375</v>
+        <v>36.79000091552734</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>345.010009765625</v>
+        <v>31.45999908447266</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>373.6400146484375</v>
+        <v>36.79000091552734</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>407850</v>
+        <v>681883</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>16.94</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Sreeleathers Ltd. Share Price Gain: Technicals &amp; Valuation - Univest</t>
+          <t>Biofil Chemicals &amp; Pharmaceuticals (BIOFILCHEM): Small Pharma Maker Explained - Kalkine India</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Sreeleathers Share Price rises 20%: price, fundamentals - Univest</t>
+          <t>Biofil Chemicals &amp; Pharmaceuticals (BIOFILCHEM): Small Pharma Maker Explained - Kalkine India</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Sreeleathers Limited Declares Interim Dividend of ₹1 Per Share for FY 2025-26 - scanx.trade</t>
+          <t>Biofil (BIOFILCHEM.NS) Technicals: Moves 0.87% Lower to ₹32.06 at the Close; Next Test: the ₹30.46 to ₹33.66 Range Remains in Focus in Latest Trading - Fibonacci Time Zone - siam.in</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Sreeleathers Share Price rises 20%: price, fundamentals - Univest</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>Sreeleathers Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
-        </is>
-      </c>
+          <t>Biofil Chemicals NSE:BIOFILCHEM Q1 FY27 Newspaper Publication - Kalkine India</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 12:56:51 IST</t>
+          <t>2026-09-10 20:07:15 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1089,68 +1077,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>SIGACHI.NS</t>
+          <t>CFEL.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Sigachi Industries Limited</t>
+          <t>Confidence Futuristic Energetech Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>35.59999847412109</v>
+        <v>43</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>38.77000045776367</v>
+        <v>46.38000106811523</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>35.36000061035156</v>
+        <v>40.31999969482422</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>38.13999938964844</v>
+        <v>44.91999816894531</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>35.27000045776367</v>
+        <v>38.65000152587891</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>38.13999938964844</v>
+        <v>44.91999816894531</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>11311934</v>
+        <v>1071863</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>8.140000000000001</v>
+        <v>16.22</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Sigachi Industries Share Price Today Up 8.33%: Stock View - Univest</t>
+          <t>Confidence Futuristic Energetech Ltd. Upper Circuit: Price and Key Data - Univest</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>how Fair Value models spotted Sigachi Industries’ 67% rally - Investing.com India</t>
+          <t>20% Upper Circuit: Molbio Diagnostics and 8 Other Stocks That Hit the Upper Circuit Today; Do You Own Any? - Trade Brains</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>how Fair Value models spotted Sigachi Industries’ 67% rally - Investing.com India</t>
+          <t>Confidence Futuristic Energetech Ltd. (CFEL) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Sigachi Industries sets Sept 15 EGM for ₹290.4 crore warrant issue - scanx.trade</t>
+          <t>Confidence Futuristic Energetech Ltd. (CFEL) Share Price Today, Quote, Latest Discussions, Interactive Chart and News - Stocktwits</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>Sigachi Industries Share Price Today: Price Rise Analysis - Univest</t>
+          <t>20% Upper Circuit: Molbio Diagnostics and 8 Other Stocks That Hit the Upper Circuit Today; Do You Own Any? - Trade Brains</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 12:56:51 IST</t>
+          <t>2026-09-10 20:07:15 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1158,68 +1146,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>KROSS.NS</t>
+          <t>MEDICAPQ.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Kross Limited</t>
+          <t>Medi Caps Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>220.75</v>
+        <v>32.79000091552734</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>240.8000030517578</v>
+        <v>36.79999923706055</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>220</v>
+        <v>29.95999908447266</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>237.5</v>
+        <v>35.22000122070312</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>219.6699981689453</v>
+        <v>30.73999977111816</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>237.5</v>
+        <v>35.22000122070312</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>6872404</v>
+        <v>493535</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>8.119999999999999</v>
+        <v>14.57</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Kross Ltd seeks shareholder approval for ₹63.6 crore preferential fundraise - scanx.trade</t>
+          <t>MEDICAPQ Stock Price and Chart — NSE:MEDICAPQ - TradingView</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Kross Ltd seeks shareholder approval for ₹63.6 crore preferential fundraise - scanx.trade</t>
+          <t>MEDI-CAPS LIMITED: Discloses Process for Shareholder Annual Report Distribution - InvestyWise</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Kross Ltd Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>Medi-Caps Ltd. (MEDICAPQ) Profile, Company FAQs &amp; Facts, Industry, Sector, Employee Strength - Stocktwits</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Kross Ltd files FY26 annual report with BSE and NSE - scanx.trade</t>
+          <t>Medi-Caps Ltd. (MEDICAPQ) Share Price Today, Quote, Latest Discussions, Interactive Chart and News - Stocktwits</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>Kross schedules 35th AGM for September 16; board changes on agenda - scanx.trade</t>
+          <t>Medi-Caps Ltd. (MEDICAPQ) Fundamental and Financial Data - Stocktwits</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 12:56:51 IST</t>
+          <t>2026-09-10 20:07:15 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1227,68 +1215,56 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>KABRAEXTRU.NS</t>
+          <t>OSWALSEEDS.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Kabra Extrusion Technik Limited</t>
+          <t>ShreeOswal Seeds And Chemicals Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>659.9000244140625</v>
+        <v>13.69999980926514</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>717</v>
+        <v>15.60000038146973</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>655</v>
+        <v>13.19999980926514</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>712.4000244140625</v>
+        <v>14.75</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>662.9500122070312</v>
+        <v>13.07999992370605</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>712.4000244140625</v>
+        <v>14.75</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>632606</v>
+        <v>1571288</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>7.46</v>
+        <v>12.77</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Kabra Extrusion Technik Gains 5.93% to ₹513, Approaches Key Resistance at ₹538.65 - Strangle Setup - siam.in</t>
+          <t>ShreeOswal (OSWALSEEDS.NS) Jun 2026 Earnings: The Latest Report Adds New Financial Reference Points in Latest Trading; Market Move: The Share Price Sheds 2.35% in the Current Update - Financial Summary - siam.in</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Kabra Extrusion Technik Surges 9% After Receiving Letter Of Nomination From Vietnamese Auto OEM - Trade Brains</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>Kabra Extrusiontechnik Ltd. (KABRAEXTRU) Share Price Rises 8.33% Today - Univest</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>Kabra Extrusiontechnik Share Price rises 8.59%: analysis - Univest</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>Kabra Extrusiontechnik KABRAEXTRU Preferential Issue Allottee Change - Kalkine India</t>
-        </is>
-      </c>
+          <t>ShreeOswal (OSWALSEEDS.NS) Jun 2026 Earnings: The Latest Report Adds New Financial Reference Points in Latest Trading; Market Move: The Share Price Sheds 2.35% in the Current Update - Financial Summary - siam.in</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 12:56:51 IST</t>
+          <t>2026-09-10 20:07:15 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1296,64 +1272,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>SARVESHWAR.NS</t>
+          <t>ANMOL.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Sarveshwar Foods Limited</t>
+          <t>Anmol India Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>3.769999980926514</v>
+        <v>13.69999980926514</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>4.090000152587891</v>
+        <v>15.55000019073486</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>3.710000038146973</v>
+        <v>12.5600004196167</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>4.03000020980835</v>
+        <v>15.34000015258789</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>3.779999971389771</v>
+        <v>13.63000011444092</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>4.03000020980835</v>
+        <v>15.34000015258789</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>5603427</v>
+        <v>1843869</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>6.61</v>
+        <v>12.55</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Sarveshwar Foods Share Price Today: Price Rise Analysis - Univest</t>
+          <t>Anmol India schedules 28th AGM for September 26, 2026 - scanx.trade</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Sarveshwar Foods sets September 30 AGM for warrant issue, ESOP approval - scanx.trade</t>
+          <t>Anmol India schedules 28th AGM for September 26, 2026 - scanx.trade</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Sarveshwar Foods sets September 30 AGM for warrant issue, ESOP approval - scanx.trade</t>
+          <t>Anmol India (ANMOL.NS) Holds Steady at ₹10.28; Consolidation Phase in Focus - Early Entry Signals - siam.in</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Sarveshwar (SARVESHWAR.NS) Results Review: The Company Publishes Its Latest Results in the Current Update; Post-Report: Shares Move Higher 0.29% at the Close - SaaS Earnings Trends - siam.in</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr"/>
+          <t>Anmol India promoter pledges 3.3M shares to SBI for ₹155 crore loan - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>Anmol India schedules Aug 29 board meeting to finalize AGM and annual report - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 12:56:51 IST</t>
+          <t>2026-09-10 20:07:15 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1361,56 +1341,56 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>OLAELEC.NS</t>
+          <t>KOTIC.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Ola Electric Mobility Limited</t>
+          <t>Kothari Industrial Corporation Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>37.31000137329102</v>
+        <v>136.8999938964844</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>40.5099983215332</v>
+        <v>159.9700012207031</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>37.31000137329102</v>
+        <v>136.1000061035156</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>39.65000152587891</v>
+        <v>151.2100067138672</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>37.31000137329102</v>
+        <v>135.5399932861328</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>39.65000152587891</v>
+        <v>151.2100067138672</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>145149193</v>
+        <v>804024</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>6.27</v>
+        <v>11.56</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>OLA Electric Mobility Share Price rises 5.82%: analysis - Univest</t>
+          <t>Kothari Industrial share price zooms 11%! Stock down 74% in one year | What’s fuelling the rally? - Livemint</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Stocks To Buy or Sell Today, August 31, 2026: Ola Electric and HDFC Bank Among Shares That May Remain in - latestly.com</t>
+          <t>Kothari Industrial share price zooms 11%! Stock down 74% in one year | What’s fuelling the rally? - Livemint</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Ola Electric Launches New Battery Energy Storage Portfolio in India - The Globe and Mail</t>
+          <t>Kothari Industrial Corporation Share Price rises 10.14% - Univest</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Stocks To Buy or Sell Today, August 31, 2026: Ola Electric and HDFC Bank Among Shares That May Remain in - latestly.com</t>
+          <t>Kothari Industrial Stock Falls 6% Despite Securing ₹14.56 Cr Government Orders - Trade Brains</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr"/>
@@ -1418,7 +1398,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 12:56:51 IST</t>
+          <t>2026-09-10 20:07:15 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1426,60 +1406,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>PGIL.NS</t>
+          <t>PANORAMA.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Pearl Global Industries Limited</t>
+          <t>Panorama Studios International Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>2295.10009765625</v>
+        <v>48</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>2424.89990234375</v>
+        <v>56.20000076293945</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>2286.39990234375</v>
+        <v>48</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>2412.699951171875</v>
+        <v>52.91999816894531</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>2277.89990234375</v>
+        <v>47.56000137329102</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>2412.699951171875</v>
+        <v>52.91999816894531</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>215393</v>
+        <v>1538580</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>5.92</v>
+        <v>11.27</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Pearl Global Industries: Promoter Sells 1.19% Stake in Market Transaction - InvestyWise</t>
+          <t>Panorama Studios Share Price rises 13.84% with valuation - Univest</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Pearl Global Industries: Promoter Sells 1.19% Stake in Market Transaction - InvestyWise</t>
+          <t>Panorama Studios Share Price rises 13.84% with valuation - Univest</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Pearl Global: Approves Grant of 2,500 Employee Stock Options - InvestyWise</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr"/>
-      <c r="Q15" s="2" t="inlineStr"/>
+          <t>Panorama Studios acquires 10% stake in Rhea &amp; Dia Enterprises - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>Panorama Studio Share Price, Stock Price - NSE/BSE Live - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>Panorama Studios International Ltd. Stock News - Value Research</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 12:56:51 IST</t>
+          <t>2026-09-10 20:07:15 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1487,60 +1475,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>INDBANK.NS</t>
+          <t>DEEP.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Indbank Merchant Banking Services Limited</t>
+          <t>Deep Polymers Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>26.61000061035156</v>
+        <v>37</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>28.5</v>
+        <v>42.90000152587891</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>26.45000076293945</v>
+        <v>36.95999908447266</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>28.14999961853027</v>
+        <v>40.97999954223633</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>26.61000061035156</v>
+        <v>36.88999938964844</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>28.14999961853027</v>
+        <v>40.97999954223633</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>151151</v>
+        <v>209619</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>5.79</v>
+        <v>11.09</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Indbank (INDBANK.NS) Earnings Snapshot: The Report Supplies Updated Headline Figures for This Review; Share Response: The Stock Loses 0.06% in the Latest Reading - Revenue Recognition Risk - siam.in</t>
+          <t>How Deep Can RKLB Stock Fall? - Forbes</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Indbank Merchant Banking sets Sep 17 as AGM record date - scanx.trade</t>
+          <t>SKYQ Stock Coils As Traders Weigh Deep Losses And Cash Boost - timothysykes.com</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Indbank Merchant Banking sets Sep 17 as AGM record date - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr"/>
-      <c r="Q16" s="2" t="inlineStr"/>
+          <t>SKYQ Stock Coils As Traders Weigh Deep Losses And Cash Boost - timothysykes.com</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>Happiest Minds Tech share price in deep red - What's behind the stock plunge? - Livemint</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>Deep Energy Resources Ltd. Stock News - Value Research</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 12:56:51 IST</t>
+          <t>2026-09-10 20:07:15 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1548,68 +1544,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>VPRPL.NS</t>
+          <t>SHILGRAVQ.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Vishnu Prakash R Punglia Limited</t>
+          <t>Shilp Gravures Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>35</v>
+        <v>153.8000030517578</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>39</v>
+        <v>177.3800048828125</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>34.70000076293945</v>
+        <v>153.8000030517578</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>37.11000061035156</v>
+        <v>168.3999938964844</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>35.11000061035156</v>
+        <v>151.6100006103516</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>37.11000061035156</v>
+        <v>168.3999938964844</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>1950528</v>
+        <v>93780</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>5.7</v>
+        <v>11.07</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>VPRPL Forecast — Price Target — Prediction for 2027 - TradingView</t>
+          <t>SHILGRAVQ Stock Price and Chart — NSE:SHILGRAVQ - TradingView</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Vishnu Prakash R Punglia (VPRPL) Faces Modest Decline, Support Near ₹25 Holds Key - Fundamental Weighted - siam.in</t>
+          <t>Technical Analysis of Shilp Gravures Limited (NSE:SHILGRAVQ) - TradingView</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>VPRPL Reports ₹130 Cr Q4 Net Loss as Revenue Slumps 75% YoY - Sahi</t>
+          <t>Technical Analysis of Shilp Gravures Limited (NSE:SHILGRAVQ) - TradingView</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Should Weakness in Vishnu Prakash R Punglia Limited's (NSE:VPRPL) Stock Be Seen As A Sign That Market Will Correct The Share Price Given Decent Financials? - simplywall.st</t>
+          <t>Shilp Gravures Ltd. (SHILGRAVQ) Share Price Today, Quote, Latest Discussions, Interactive Chart and News - Stocktwits</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>VPRPL posts ₹151.77 cr Q4 loss; stock hits lower circuit - BusinessLine</t>
+          <t>Shilp Gravures Ltd. (SHILGRAVQ) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 12:56:51 IST</t>
+          <t>2026-09-10 20:07:15 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1617,68 +1613,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>CORDELIA.NS</t>
+          <t>NOVARTIND.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Waterways Leisure Tourism Limited</t>
+          <t>Novartis India Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>105.6500015258789</v>
+        <v>2260</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>109.4599990844727</v>
+        <v>2588.800048828125</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>104.1800003051758</v>
+        <v>2232.10009765625</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>109.4599990844727</v>
+        <v>2428.199951171875</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>104.25</v>
+        <v>2186.39990234375</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>109.4599990844727</v>
+        <v>2428.199951171875</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>1890754</v>
+        <v>2292765</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>5</v>
+        <v>11.06</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Cordelia Cruises Announces October Sailings From Mumbai; Shares Rise 0.37% - HDFC Sky</t>
+          <t>Novartis (NOVARTIND.NS) Quarter in Focus: The Company Publishes Its Latest Results for This Review; Share Move: The Stock Records a 3.23% Decrease in the Latest Reading - Post-Earnings Reaction - siam.in</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Shares of recently listed Waterways Leisure to be in focus as company unveils Cordelia Sky - India TV News</t>
+          <t>Novartis India Share Price: fresh 52-week high, valuation - Univest</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Waterways Leisure Tourism Limited Share Price Today,, CORDELIA Share Price NSE, BSE - Business Today</t>
+          <t>Novartis India Share Price: fresh 52-week high, valuation - Univest</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Waterways Leisure Tourism shares adjust to 1:10 stock split ahead of record date - Check details - Moneycontrol.com</t>
+          <t>Novartis India Fresh High: Chart Analysis - Kalkine India</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>Stock split alert! Last day to buy this recently-listed travel firm's shares after over 50% rally in 2 mon - The Economic Times</t>
+          <t>Novartis India Share Price Update With Valuation Context - Univest</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 12:56:51 IST</t>
+          <t>2026-09-10 20:07:15 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1686,56 +1682,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>SETL.NS</t>
+          <t>MANINDS.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Standard Engineering Technology Limited</t>
+          <t>Man Industries (India) Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>445.2000122070312</v>
+        <v>781</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>445.8999938964844</v>
+        <v>944</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>440.0499877929688</v>
+        <v>772.6500244140625</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>445.8999938964844</v>
+        <v>876.4500122070312</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>424.7000122070312</v>
+        <v>792.5499877929688</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>445.8999938964844</v>
+        <v>876.4500122070312</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>305331</v>
+        <v>8837154</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>4.99</v>
+        <v>10.59</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>SETL Share Price News after yearly high and valuation check - Univest</t>
+          <t>MANINDS Jun 2026 Earnings: EPS of ₹10.39 on ₹1,010 Crore Revenue; Stock Climbs 7.07% on NSE - Earnings Acceleration Picks - siam.in</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>SETL Share Price News after yearly high and valuation check - Univest</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr"/>
-      <c r="P19" s="2" t="inlineStr"/>
-      <c r="Q19" s="2" t="inlineStr"/>
+          <t>Man Industries Share Price: fresh 52-week high, valuation - Univest</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>Man Industries Share Price: Fundamentals at 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>Man Industries (India) Ltd. Share Price Near 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>Man Industries Share Price: fresh 52-week high, valuation - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 12:56:51 IST</t>
+          <t>2026-09-10 20:07:15 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1743,68 +1751,68 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>DIACABS.NS</t>
+          <t>LGHL.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Diamond Power Infrastructure Limited</t>
+          <t>Laxmi Goldorna House Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>336.3999938964844</v>
+        <v>170</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>351.5</v>
+        <v>198.0099945068359</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>332.2000122070312</v>
+        <v>168.6600036621094</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>351.5</v>
+        <v>189.4900054931641</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>334.7999877929688</v>
+        <v>172.2299957275391</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>351.5</v>
+        <v>189.4900054931641</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>956691</v>
+        <v>52139</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>4.99</v>
+        <v>10.02</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>DICABS Board to consider FY26 audited results on May 26 - scanx.trade</t>
+          <t>Lion Group Holding Ltd (NASDAQ: LGHL) Share Price, LGHL Stock News, LGHL Share Price &amp; Updates - Kalkine</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Diamond Power Infrastructure Ltd. (DIACABS-BE): Diamond Power Infrastructure Share Price Rises 2.26% Today - Univest</t>
+          <t>LGHL Announces Strategic Investment in Indonesian Stablecoin and Digital Financial Infrastructure Provider via Stock-for-Participation Arrangement - Eastern Progress</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Diamond (DIACABS.NS) Results Review: The Company Releases Its Current Earnings Data under the Current Snapshot; Trading Move: Shares Move 0.31% Up - Retail Earnings Report - siam.in</t>
+          <t>$LGHL stock is up 19% today. Here's what we see in our data. - Quiver Quantitative</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Diamond Power Infrastructure Share Price Near 52-Week High - Univest</t>
+          <t>Lion Group Reaffirms $15.8 Million Hyperliquid Token Holdings in Treasury Strategy - The Globe and Mail</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Diamond Power Infrastructure Ltd. (DIACABS-BE): Diamond Power Infrastructure Share Price Rises 2.26% Today - Univest</t>
+          <t>LGHL Announces Strategic Investment in Indonesian Stablecoin and Digital Financial Infrastructure Provider via Stock-for-Participation Arrangement - Eastern Progress</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 12:56:51 IST</t>
+          <t>2026-09-10 20:07:15 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1812,61 +1820,61 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>BIRLACABLE.NS</t>
+          <t>MANGALAM.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Birla Cable Limited</t>
+          <t>Mangalam Drugs And Organics Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>369.4500122070312</v>
+        <v>31.98999977111816</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>374.6499938964844</v>
+        <v>34.88000106811523</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>360.3999938964844</v>
+        <v>31.70999908447266</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>374.6499938964844</v>
+        <v>34.88000106811523</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>356.8500061035156</v>
+        <v>31.70999908447266</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>374.6499938964844</v>
+        <v>34.88000106811523</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>739927</v>
+        <v>284789</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>4.99</v>
+        <v>10</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Birla Cable fixes record date for FY26 dividend - scanx.trade</t>
+          <t>With EPS Growth And More, Mangalam Global Enterprise (NSE:MGEL) Makes An Interesting Case - simplywall.st</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Birla Cable appoints Somesh Laddha as Manager for three-year term - scanx.trade</t>
+          <t>Kumar Mangalam Birla Appointed Vodafone Idea's Non-Executive Chairman, Shares Up 5% - News18</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Birla Cable Soars 5% to ₹213.78: Bulls Test Key Hurdle (BIRLACABLE.NS) - Mutual Fund Flow - vinanet.vn</t>
+          <t>Kumar Mangalam Birla Appointed Vodafone Idea's Non-Executive Chairman, Shares Up 5% - News18</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>BIRLACABLE Q2 2026 Earnings: Robust Revenue Growth of 16.5% Driven by Telecom Infrastructure Demand - Debt Analysis Report - vinanet.vn</t>
+          <t>Mangalam Global changes designation of director - scanx.trade</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>Vindhya Telelinks confirms no fresh encumbrance on Birla Cable shares in FY26 - scanx.trade</t>
+          <t>Mangalam Drugs &amp; Organics Gains 1.57%: Stock Climbs to ₹30.33 as Pharma Momentum Builds - Bull Flag - siam.in</t>
         </is>
       </c>
     </row>
@@ -1887,7 +1895,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="43" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -1993,7 +2001,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 12:56:51 IST</t>
+          <t>2026-09-10 20:07:15 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -2001,68 +2009,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>ASTEC.NS</t>
+          <t>SRGHFL.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Astec LifeSciences Limited</t>
+          <t>SRG Housing Finance Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>751</v>
+        <v>195</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>751</v>
+        <v>224.8500061035156</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>702.0499877929688</v>
+        <v>195</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>704.0999755859375</v>
+        <v>195</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>761</v>
+        <v>243.75</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>704.0999755859375</v>
+        <v>195</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>340585</v>
+        <v>126912</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-7.48</v>
+        <v>-20</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Astec Lifesciences share price skyrockets 17% despite weak sentiments on D-Street. Do you own? - TradingView</t>
+          <t>Improved Earnings Required Before SRG Housing Finance Limited (NSE:SRGHFL) Shares Find Their Feet - simplywall.st</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Astec Lifesciences share price skyrockets 17% despite weak sentiments on D-Street. Do you own? - TradingView</t>
+          <t>SRG Housing Finance Holds Near ₹308 Support Zone Amid Modest Decline - IV Crush Alert - vinanet.vn</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Astec Lifesciences share price skyrockets 17% despite weak sentiments on D-Street. Do you own? - Livemint</t>
+          <t>SRG Housing Finance Mar 2026 Earnings: EPS of ₹5.89 Reported; Stock Declines 2.7% - Earnings Surprise Score - vinanet.vn</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Astec Lifesciences Share Price rises 9.49% on price action - Univest</t>
+          <t>SRG Housing Finance (SRGHFL.NS) Holds Steady Near Resistance; Consolidation Phase Continues - Covered Call Trade - vinanet.vn</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Implied Volatility Surging for Astec Industries Stock Options - Yahoo Finance</t>
+          <t>SRGHFL Stock Price and Chart — NSE:SRGHFL - TradingView</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 12:56:51 IST</t>
+          <t>2026-09-10 20:07:15 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -2070,60 +2078,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>RADIANTCMS.NS</t>
+          <t>MONEYBOXX.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Radiant Cash Management Services Limited</t>
+          <t>Moneyboxx Finance Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>38.20000076293945</v>
+        <v>40.75</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>38.20000076293945</v>
+        <v>40.75</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>36.40000152587891</v>
+        <v>35.84999847412109</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>37.40000152587891</v>
+        <v>37.15000152587891</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>40.25</v>
+        <v>44.81000137329102</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>37.40000152587891</v>
+        <v>37.15000152587891</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>417305</v>
+        <v>1459080</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-7.08</v>
+        <v>-17.09</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>We Wouldn't Be Too Quick To Buy Radiant Cash Management Services Limited (NSE:RADIANTCMS) Before It Goes Ex-Dividend - simplywall.st</t>
+          <t>Moneyboxx Finance Ltd leads losers in 'B' group - Business Standard</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>We Wouldn't Be Too Quick To Buy Radiant Cash Management Services Limited (NSE:RADIANTCMS) Before It Goes Ex-Dividend - simplywall.st</t>
+          <t>Moneyboxx Finance Daily Chart and Financial View - Kalkine India</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ONEGLOBAL Stock Price and Chart — NSE:ONEGLOBAL - TradingView</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
+          <t>Moneyboxx Finance Share Price Update After Sharp Day Gain - Univest</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>Markets Rally, But Moneyboxx Finance Ltd Sinks to 52-Week Low in Stock-Specific Sell-Off - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>Moneyboxx Finance Promoters Boost Stake To 46.79% Through ₹33.4 Crore Allotment - scanx.trade</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 12:56:51 IST</t>
+          <t>2026-09-10 20:07:15 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -2131,68 +2147,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>UTKARSHBNK.NS</t>
+          <t>ATALREAL.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Utkarsh Small Finance Bank Limited</t>
+          <t>Atal Realtech Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>15.75</v>
+        <v>15.27000045776367</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>15.89999961853027</v>
+        <v>15.27000045776367</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>14.01000022888184</v>
+        <v>15.27000045776367</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>14.85999965667725</v>
+        <v>15.27000045776367</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>15.89999961853027</v>
+        <v>16.95999908447266</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>14.85999965667725</v>
+        <v>15.27000045776367</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>46236087</v>
+        <v>503950</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-6.54</v>
+        <v>-9.960000000000001</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>UTKARSHBNK Forecast — Price Target — Prediction for 2027 - TradingView</t>
+          <t>Atal Realtech Share Price Near ATH With Fundamental View - Univest</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Utkarsh Small Finance Bank Limited Approves Call Option Exercise for Redemption of 1,950 Rated, Listed, Unsecured, Redeemable, Lower Tier II Bonds - marketscreener.com</t>
+          <t>Atal Realtech Share Price and Daily Chart View - Kalkine India</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Utkarsh CoreInvest confirms no encumbrance on Utkarsh Small Finance Bank shares in FY 2025-26 - scanx.trade</t>
+          <t>Atal Realtech Lower Circuit: Chart Analysis - Kalkine India</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Utkarsh Small Finance Bank (UTKARSHBNK) Gains 2.98% – Analysis of Key Levels and Support - Throwback Trade - vinanet.vn</t>
+          <t>Atal Realtech Share Price update: price action and valuation - Univest</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Utkarsh Small Finance Bank (UTKARSHBNK.NS): Consolidating Near Resistance – A Measured Uptrend - ETF Inflow Streak - vinanet.vn</t>
+          <t>Atal Realtech 20.00% Fall: Chart Analysis - Kalkine India</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 12:56:51 IST</t>
+          <t>2026-09-10 20:07:15 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -2200,68 +2216,64 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>ARVEE.NS</t>
+          <t>LCCINFOTEC.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Arvee Laboratories (India) Limited</t>
+          <t>LCC Infotech Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>210.2899932861328</v>
+        <v>3.640000104904175</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>210.2899932861328</v>
+        <v>3.680000066757202</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>194.2100067138672</v>
+        <v>3.190000057220459</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>198.7899932861328</v>
+        <v>3.190000057220459</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>210.2899932861328</v>
+        <v>3.539999961853027</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>198.7899932861328</v>
+        <v>3.190000057220459</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>14194</v>
+        <v>328095</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-5.47</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Arvee Laboratories India Share: Bull Case vs Bear Case for 2026 - Univest</t>
+          <t>LCC Infotech AGM Notice FY2025-26 | NSE:LCCINFOTEC - Kalkine India</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Arvee Laboratories India Share: Bull Case vs Bear Case for 2026 - Univest</t>
+          <t>LCC Infotech AGM Notice FY2025-26 | NSE:LCCINFOTEC - Kalkine India</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Arvee Laboratories (India) Share Price rises 11.69%: - Univest</t>
+          <t>LCC Infotech Q1 Results: Net loss widens 16% YoY to ₹12.18 lakh - scanx.trade</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Arvee (ARVEE.NS) Outlook: Ends Lower by 1.98% at ₹165.00; Technical View: ₹156.75 and ₹173.25 Define the Nearby Reference Levels in Latest Trading - OBV Divergence - siam.in</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>Arvee Lab Standalone June 2026 Net Sales at Rs 17.23 crore, up 130.28% Y-o-Y - Moneycontrol.com</t>
-        </is>
-      </c>
+          <t>LCC Infotech issues corrigendum to AGM notice and annual report disclosures - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 12:56:51 IST</t>
+          <t>2026-09-10 20:07:15 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2269,68 +2281,64 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>BHAGERIA.NS</t>
+          <t>MVELECTRO.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Bhageria Industries Limited</t>
+          <t>MV Electrosystems Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>303.1000061035156</v>
+        <v>911.4500122070312</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>303.1000061035156</v>
+        <v>911.4500122070312</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>303.1000061035156</v>
+        <v>826.0999755859375</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>303.1000061035156</v>
+        <v>835.4500122070312</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>319.0499877929688</v>
+        <v>917.5</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>303.1000061035156</v>
+        <v>835.4500122070312</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>33819</v>
+        <v>5082680</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-5</v>
+        <v>-8.94</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Bhageria Industries Share: Bull Case vs Bear Case for 2026 - Univest</t>
+          <t>Newly-listed stock MV Electrosystems jumps 15% to hit record high - What's fuelling the rally? - TradingView</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Bhageria Industries Share: Bull Case vs Bear Case for 2026 - Univest</t>
+          <t>Newly-listed stock MV Electrosystems jumps 15% to hit record high - What's fuelling the rally? - TradingView</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Bhageria Industries Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
+          <t>MV Electrosystems Share Price: price rise and valuation - Univest</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Bhageria Industries Share Price: Buy or Sell - Univest</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>DJS Stock appoints Shukla as independent director for five years - scanx.trade</t>
-        </is>
-      </c>
+          <t>MV Electrosystems Share Price Falls 8.25%: Full Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 12:56:51 IST</t>
+          <t>2026-09-10 20:07:15 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2338,68 +2346,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>HEG.NS</t>
+          <t>VIVOBIOT.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>HEG Limited</t>
+          <t>Vivo Bio Tech Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>253.8999938964844</v>
+        <v>18.81999969482422</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>256.1000061035156</v>
+        <v>18.81999969482422</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>249.6499938964844</v>
+        <v>16.75</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>249.6499938964844</v>
+        <v>16.98999977111816</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>262.75</v>
+        <v>18.63999938964844</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>249.6499938964844</v>
+        <v>16.98999977111816</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>1700393</v>
+        <v>112181</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-4.99</v>
+        <v>-8.85</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Here’s why you should ignore the 65% plunge in HEG share price today post demerger - Moneycontrol.com</t>
+          <t>Dwight Technologies acquires 5.41% stake in Vivo Bio Tech - scanx.trade</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>IRB Infra, Ola Electric lead Nifty 500 gainers; HEG, Craftsman Automation fall at market open - CNBC TV18</t>
+          <t>Virinchi Limited Allots 8.5 Lakh Equity Shares on Warrant Conversion Worth Rs.1.79 Crore - scanx.trade</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Why are HEG Ltd shares showing a fall of 63% in Monday's trade? - Business Standard</t>
+          <t>An undisclosed buyer acquired 5.41% stake in Vivo Bio Tech Limited from Max Cell Phone Communications Pvt. Ltd. - marketscreener.com</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Did HEG shares really crash 64% in one day? Here’s how the demerger math works - The Economic Times</t>
+          <t>Vivo Bio Tech Ltd. (VIVOBIOT) Share Price Today, Quote, Latest Discussions, Interactive Chart and News - Stocktwits</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>HEG share price falls over 64% to ₹260: Don’t panic! Here’s what actually happened - Livemint</t>
+          <t>Virinchi Limited Allots 8.5 Lakh Equity Shares on Warrant Conversion Worth Rs.1.79 Crore - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 12:56:51 IST</t>
+          <t>2026-09-10 20:07:15 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2407,68 +2415,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>TBZ.NS</t>
+          <t>ATLASCYCLE.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Tribhovandas Bhimji Zaveri Limited</t>
+          <t>Atlas Cycles (Haryana) Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>511</v>
+        <v>108</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>542.9000244140625</v>
+        <v>109.9899978637695</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>501.25</v>
+        <v>97.19999694824219</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>501.25</v>
+        <v>98.06999969482422</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>527.5999755859375</v>
+        <v>106.4700012207031</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>501.25</v>
+        <v>98.06999969482422</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>1564495</v>
+        <v>85015</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-4.99</v>
+        <v>-7.89</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>GRT Jewellers to acquire 74.12% stake in TBZ for up to ₹1,034 crore - smallcapspotlight.in</t>
+          <t>Atlas Cycles (Haryana) shareholders approve FY26 financials despite promoter dissent - scanx.trade</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>GRT Jewellers publishes TBZ open offer DPS, sets Oct 26 tender start - scanx.trade</t>
+          <t>20% Upper Circuit: Wheels India and 9 Other Stocks That Hit the Upper Circuit Today; Are You Holding Any? - Trade Brains</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>GRT Jewellers publishes TBZ open offer DPS, sets Oct 26 tender start - scanx.trade</t>
+          <t>Penny Stock Below Rs 100 Posts Wider Loss in Q1 FY27 Even as Land Sale Deal Gets Extended - Dalal Street Investment Journal</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>TBZ Hits 52-week High as GRT’s ₹1,034 Crore Takeover Deal Triggers Open Offer - Moneylife</t>
+          <t>Atlas Cycles (Haryana) grants sale deed extension for Sonepat land - scanx.trade</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Multibagger stock: Why TBZ shares are locked at 20% upper circuit - Business Standard</t>
+          <t>20% Upper Circuit: Wheels India and 9 Other Stocks That Hit the Upper Circuit Today; Are You Holding Any? - Trade Brains</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 12:56:51 IST</t>
+          <t>2026-09-10 20:07:15 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2476,68 +2484,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>SUDEEPPHRM.NS</t>
+          <t>TANAA.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Sudeep Pharma Limited</t>
+          <t>Taneja Aerospace &amp; Aviation Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1226</v>
+        <v>277.7000122070312</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1259.800048828125</v>
+        <v>279</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>1213.5</v>
+        <v>243.25</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1213.5</v>
+        <v>251.5</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1277.300048828125</v>
+        <v>272.75</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1213.5</v>
+        <v>251.5</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>269843</v>
+        <v>64780</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-4.99</v>
+        <v>-7.79</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>SUDEEPPHRM Stock Price and Chart — NSE:SUDEEPPHRM - TradingView</t>
+          <t>TANAA Stock Price and Chart — NSE:TANAA - TradingView</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>SUDEEPPHRM Stock Price and Chart — NSE:SUDEEPPHRM - TradingView</t>
+          <t>Taneja Aerospace &amp; Aviation Ltd. (TANAA) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>SUDEEP PHARMA LIMITED Share Price - Upstox</t>
+          <t>Taneja Aerospace &amp; Aviation Ltd. (TANAA) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>SUDEEPPHRM Forecast — Price Target — Prediction for 2027 - TradingView</t>
+          <t>Technical Analysis of Taneja Aerospace &amp; Aviation Ltd. (NSE:TANAA) - TradingView</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>Sudeep Pharma Limited Submits Q4FY26 Compliance Certificate Under SEBI Depositories Regulations - scanx.trade</t>
+          <t>Taneja Aerospace &amp; Aviation Ltd. Income Statement – NSE:TANAA - TradingView</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 12:56:51 IST</t>
+          <t>2026-09-10 20:07:15 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2545,56 +2553,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>KSHITIJPOL.NS</t>
+          <t>BALPHARMA.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Kshitij Polyline Limited</t>
+          <t>Bal Pharma Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>3.269999980926514</v>
+        <v>120</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>3.490000009536743</v>
+        <v>124.5999984741211</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>3.269999980926514</v>
+        <v>105.0500030517578</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>3.269999980926514</v>
+        <v>106.2099990844727</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>3.440000057220459</v>
+        <v>114.4499969482422</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>3.269999980926514</v>
+        <v>106.2099990844727</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>2450939</v>
+        <v>687435</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-4.94</v>
+        <v>-7.2</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Kshitij Polyline KSHITIJPOL Rights Issue Corrigendum August 2026 - Kalkine India</t>
+          <t>Bal Pharma Gains 2.9% to ₹95.38; Resistance at ₹100.15 in Focus - Volatility Term Structure - siam.in</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Kshitij Polyline KSHITIJPOL Rights Issue Corrigendum August 2026 - Kalkine India</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr"/>
-      <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="2" t="inlineStr"/>
+          <t>Bal Pharma 19.99% Surge: Key Chart Levels - Kalkine India</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>Bal Pharma 19.99% Surge: Key Chart Levels - Kalkine India</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>Bal Pharma Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>Bal Pharma Limited announced that it has received INR 21 million in funding - marketscreener.com</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 12:56:51 IST</t>
+          <t>2026-09-10 20:07:15 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2602,60 +2622,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>ANUHPHR.NS</t>
+          <t>MARSONS.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Anuh Pharma Limited</t>
+          <t>Marsons Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>97.90000152587891</v>
+        <v>135.1900024414062</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>98.87999725341797</v>
+        <v>141.7599945068359</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>91.41000366210938</v>
+        <v>125.0100021362305</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>92.19000244140625</v>
+        <v>125.379997253418</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>96.73999786376953</v>
+        <v>135.0800018310547</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>92.19000244140625</v>
+        <v>125.379997253418</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>247009</v>
+        <v>6401332</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-4.7</v>
+        <v>-7.18</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Anuh (ANUHPHR.NS) Update: Falls 1.28% to ₹77.82 in the Latest Reading; Price Context: the Supplied Trading Band Runs From ₹73.93 to ₹81.71 in the Available Record - Volume Gap - siam.in</t>
+          <t>Marsons Ltd Hits Intraday Low Amid Price Pressure on 10 Sep 2026 - MarketsMojo</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Anuh Pharma Share Price Today up 11.12% on price action - Univest</t>
+          <t>Marsons Ltd Hits Intraday Low Amid Price Pressure on 10 Sep 2026 - MarketsMojo</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Anuh Pharma Share Price Today up 11.12% on price action - Univest</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr"/>
-      <c r="Q11" s="2" t="inlineStr"/>
+          <t>Marsons Ltd. Share Price rises 8.51% | MARSONS analysis - Univest</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>Marsons (MARSONS.NS) Latest Quarter: The Report Supplies Updated Headline Figures in the Available Record; Post-Report: Shares Move Higher 6.61% in the Latest Reading - Earnings Revision Report - siam.in</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>Marsons Q1 Results FY27: PAT Rs 5 Cr, Revenue Rs 49 crore - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 12:56:51 IST</t>
+          <t>2026-09-10 20:07:15 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2663,60 +2691,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>LXCHEM.NS</t>
+          <t>DHATRE.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Laxmi Organic Industries Limited</t>
+          <t>Dhatre Udyog Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>177.5</v>
+        <v>4.28000020980835</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>179</v>
+        <v>4.699999809265137</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>170.6300048828125</v>
+        <v>3.799999952316284</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>171</v>
+        <v>4.139999866485596</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>178.5599975585938</v>
+        <v>4.460000038146973</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>171</v>
+        <v>4.139999866485596</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>1202194</v>
+        <v>101237</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-4.23</v>
+        <v>-7.17</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Laxmi (LXCHEM.NS) Earnings Numbers in Focus: The Company Reports Its Latest Available Figures; Market Read: Shares Finish 0.07% Lower - ROA Comparison - siam.in</t>
+          <t>Dhatre Udyog corrects 31st AGM time to 11 am on Sept 26 - scanx.trade</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Laxmi (LXCHEM.NS) Earnings Numbers in Focus: The Company Reports Its Latest Available Figures; Market Read: Shares Finish 0.07% Lower - ROA Comparison - siam.in</t>
+          <t>Dhatre Udyog corrects 31st AGM time to 11 am on Sept 26 - scanx.trade</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Laxmi Organic Industries: Allots 703,126 Shares Under ESOP-2020 - InvestyWise</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr"/>
-      <c r="Q12" s="2" t="inlineStr"/>
+          <t>DHATRE Stock Price and Chart — NSE:DHATRE - TradingView</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>Dhatre Udyog Ltd. (DHATRE) Profile, Company FAQs &amp; Facts, Industry, Sector, Employee Strength - Stocktwits</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>Dhatre Udyog Q1 FY27 Results: Revenue and PAT Highlights - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 12:56:51 IST</t>
+          <t>2026-09-10 20:07:15 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2724,68 +2760,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>HFCL.NS</t>
+          <t>ARVEE.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>HFCL Limited</t>
+          <t>Arvee Laboratories (India) Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>243.6900024414062</v>
+        <v>210.2899932861328</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>243.9600067138672</v>
+        <v>210.2899932861328</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>233.1600036621094</v>
+        <v>194</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>235.0800018310547</v>
+        <v>195.25</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>245.4299926757812</v>
+        <v>210.2899932861328</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>235.0800018310547</v>
+        <v>195.25</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>5962358</v>
+        <v>18221</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-4.22</v>
+        <v>-7.15</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>HFCL shares surge 16% in three sessions; here is why the stock is soaring - Upstox</t>
+          <t>Arvee Laboratories India Share: Bull Case vs Bear Case for 2026 - Univest</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>HFCL shares hit lower circuit after 240% rally in 2026. What technical charts now indicate - The Economic Times</t>
+          <t>Arvee Laboratories India Share: Bull Case vs Bear Case for 2026 - Univest</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>HFCL Share Price: Over 260% jump in 6 months - what's the reason and what investors should do? - TradingView</t>
+          <t>Arvee Laboratories (India) Share Price rises 11.69%: - Univest</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>HFCL shares hit lower circuit after 240% rally in 2026. What technical charts now indicate - The Economic Times</t>
+          <t>Arvee (ARVEE.NS) Outlook: Ends Lower by 1.98% at ₹165.00; Technical View: ₹156.75 and ₹173.25 Define the Nearby Reference Levels in Latest Trading - OBV Divergence - siam.in</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>HFCL snaps 4-day losing streak, hits 5% upper circuit; stock up 252% YTD - Business Standard</t>
+          <t>Arvee Lab Standalone June 2026 Net Sales at Rs 17.23 crore, up 130.28% Y-o-Y - Moneycontrol.com</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 12:56:51 IST</t>
+          <t>2026-09-10 20:07:15 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2793,68 +2829,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>PKTEA.NS</t>
+          <t>ALKALI.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>The Peria Karamalai Tea &amp; Produce Company Limited</t>
+          <t>Alkali Metals Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1169</v>
+        <v>83.75</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1169</v>
+        <v>84</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>1072.400024414062</v>
+        <v>78.11000061035156</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>1090.150024414062</v>
+        <v>79.19000244140625</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1136.300048828125</v>
+        <v>85.20999908447266</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1090.150024414062</v>
+        <v>79.19000244140625</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>9212</v>
+        <v>36476</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-4.06</v>
+        <v>-7.06</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>The Peria Karamalai Tea &amp; Produce (PKTEA.NS) Declines Nearly 2%: Key Levels to Monitor - Late Stage Breakouts - vinanet.vn</t>
+          <t>Momentum Stocks: Alkali Metals, Deepak Builders jump up to 15% on sheer momentum - Moneycontrol.com</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>SS&amp;C Technologies (SSNC) Climbs 3% as Fintech Momentum Drives Shares Higher - Last Point Support - vinanet.vn</t>
+          <t>Tuticorin Alkali unveils new brand identity to signal sustainable growth - scanx.trade</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Peria Karamalai Tea &amp; Produce (PKTEA) Slips 2.83% – Support Levels Come into Focus - Relative Volume - vinanet.vn</t>
+          <t>The Alkali Metals Bull Case - Univest</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>THE P K TEA PROD CO LTD Share Price - Upstox</t>
+          <t>Tuticorin Alkali Chemicals schedules 53rd AGM for September 25, 2026 - scanx.trade</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>Peria Karamalai Tea &amp; Produce (PKTEA.NS) Moves Higher: Price Nears Mid‑Range Resistance - Rounding Top - vinanet.vn</t>
+          <t>Lords Chloro Alkali Commissions 14.5 MW Solar Plant; Shares Rise 1.33% - HDFC Sky</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 12:56:51 IST</t>
+          <t>2026-09-10 20:07:15 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2862,68 +2898,64 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>BCONCEPTS.NS</t>
+          <t>UTKARSHBNK.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Brand Concepts Limited</t>
+          <t>Utkarsh Small Finance Bank Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>163</v>
+        <v>15.75</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>163</v>
+        <v>15.89999961853027</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>153.9199981689453</v>
+        <v>14.01000022888184</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>154.8099975585938</v>
+        <v>14.80000019073486</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>161.3600006103516</v>
+        <v>15.89999961853027</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>154.8099975585938</v>
+        <v>14.80000019073486</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>11353</v>
+        <v>53894190</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-4.06</v>
+        <v>-6.92</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Brand (BCONCEPTS.NS) Market: Moves 0.58% Down to ₹158.78 in Latest Trading; Level Watch: Support at ₹150.84 and Resistance at ₹166.72 Frame the Range in the Available Record - Strong Buy Stocks - siam.in</t>
+          <t>Utkarsh SFB Daily Chart and Financial Analysis - Kalkine India</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Brand (BCONCEPTS.NS) Market: Moves 0.58% Down to ₹158.78 in Latest Trading; Level Watch: Support at ₹150.84 and Resistance at ₹166.72 Frame the Range in the Available Record - Strong Buy Stocks - siam.in</t>
+          <t>Utkarsh SFB Daily Chart and Financial Analysis - Kalkine India</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Brand Concepts Ltd. Share Price Up 13.46%: Stock Analysis - Univest</t>
+          <t>Utkarsh Small Finance Bank Share Price Drops to Rs 14.43 - Univest</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Brand Concepts Q1 FY27 EBITDA up 50%; net loss widens to ₹31.6 crore - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>GameSquare Holdings (GAME) Rallies 9.47% to $0.41, Nears Key Resistance at $0.43 - Reversal Setup Alerts - vinanet.vn</t>
-        </is>
-      </c>
+          <t>Utkarsh Small Finance Bank Ltd. Lower Circuit: Price and Key Data - Univest</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 12:56:51 IST</t>
+          <t>2026-09-10 20:07:15 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2931,68 +2963,56 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>MARSONS.NS</t>
+          <t>ARENTERP.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Marsons Limited</t>
+          <t>Rajdarshan Industries Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>135.1900024414062</v>
+        <v>34.9900016784668</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>141.7599945068359</v>
+        <v>34.9900016784668</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>129.3999938964844</v>
+        <v>32.13000106811523</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>129.7400054931641</v>
+        <v>32.59999847412109</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>135.0800018310547</v>
+        <v>34.9900016784668</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>129.7400054931641</v>
+        <v>32.59999847412109</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>5473219</v>
+        <v>5299</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-3.95</v>
+        <v>-6.83</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Marsons Ltd. Share Price rises 8.51% | MARSONS analysis - Univest</t>
+          <t>Pennant Group (PNTG) Climbs 1.76% to $39.32, Holding Ground Above Key Support - Dynamic Hedging - vinanet.vn</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Marsons wins ₹31.27 cr order from Assam Electricity Grid - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>Marsons (MARSONS.NS) Latest Quarter: The Report Supplies Updated Headline Figures in the Available Record; Post-Report: Shares Move Higher 6.61% in the Latest Reading - Earnings Revision Report - siam.in</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>Marsons Q1 Results FY27: PAT Rs 5 Cr, Revenue Rs 49 crore - Univest</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>Marsons wins ₹31.27 cr order from Assam Electricity Grid - scanx.trade</t>
-        </is>
-      </c>
+          <t>Pennant Group (PNTG) Climbs 1.76% to $39.32, Holding Ground Above Key Support - Dynamic Hedging - vinanet.vn</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 12:56:51 IST</t>
+          <t>2026-09-10 20:07:15 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -3000,56 +3020,60 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>TICL.NS</t>
+          <t>RADIANTCMS.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Twamev Construction and Infrastructure Limited</t>
+          <t>Radiant Cash Management Services Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>7.510000228881836</v>
+        <v>38.20000076293945</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>7.699999809265137</v>
+        <v>38.20000076293945</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>7.320000171661377</v>
+        <v>36.40000152587891</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>7.400000095367432</v>
+        <v>37.52999877929688</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>7.699999809265137</v>
+        <v>40.25</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>7.400000095367432</v>
+        <v>37.52999877929688</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>132910</v>
+        <v>577436</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-3.9</v>
+        <v>-6.76</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Twamev (TICL.NS) Earnings Snapshot: The Latest Report Adds New Financial Reference Points in the Latest Reading; Market Reaction: The Stock Loses 3.35% in the Available Record - Free Cash Flow Trends - siam.in</t>
+          <t>We Wouldn't Be Too Quick To Buy Radiant Cash Management Services Limited (NSE:RADIANTCMS) Before It Goes Ex-Dividend - simplywall.st</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Twamev (TICL.NS) Earnings Snapshot: The Latest Report Adds New Financial Reference Points in the Latest Reading; Market Reaction: The Stock Loses 3.35% in the Available Record - Free Cash Flow Trends - siam.in</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr"/>
+          <t>We Wouldn't Be Too Quick To Buy Radiant Cash Management Services Limited (NSE:RADIANTCMS) Before It Goes Ex-Dividend - simplywall.st</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>ONEGLOBAL Stock Price and Chart — NSE:ONEGLOBAL - TradingView</t>
+        </is>
+      </c>
       <c r="P17" s="2" t="inlineStr"/>
       <c r="Q17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 12:56:51 IST</t>
+          <t>2026-09-10 20:07:15 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -3057,68 +3081,64 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>GATECH.NS</t>
+          <t>KANCOTEA.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>GACM Technologies Limited</t>
+          <t>Kanco Tea &amp; Industries Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.7599999904632568</v>
+        <v>55.88999938964844</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0.7599999904632568</v>
+        <v>55.93999862670898</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.7599999904632568</v>
+        <v>52.29000091552734</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>0.7599999904632568</v>
+        <v>52.29000091552734</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0.7900000214576721</v>
+        <v>55.95000076293945</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.7599999904632568</v>
+        <v>52.29000091552734</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>3393531</v>
+        <v>860</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-3.8</v>
+        <v>-6.54</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>GACM Technologies: FII holding jumps to 29%; penny stock in focus - Business Today</t>
+          <t>KANCOTEA Stock Price and Chart — NSE:KANCOTEA - TradingView</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>​GACM Technologies (GATECH) hits new 52-week high, up over 110% in 1 month - Zee Business</t>
+          <t>Kanco Tea &amp; Industries Ltd (KANCOTEA) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>GACM Technologies Hits Fresh 52-Week High as GATECH Surges 110% in One Month; 31% FII Holding and 250 Million AI Mandate Add to Investor Focus - indiagazette.com</t>
+          <t>Kanco Tea &amp; Industries Ltd (KANCOTEA) Fundamental and Financial Data - Stocktwits</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>₹0.75 MultiBagger Penny Stock, +56% in 1 Month -- Why Institutions Are Paying 25% Premium for GACM TECHNOLOGIES Shares? - Business Standard</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>​GACM Technologies (GATECH) hits new 52-week high, up over 110% in 1 month - Zee Business</t>
-        </is>
-      </c>
+          <t>Kanco Tea &amp; Industries Ltd (KANCOTEA) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 12:56:51 IST</t>
+          <t>2026-09-10 20:07:15 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -3126,68 +3146,56 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>AFCONS.NS</t>
+          <t>SBGLP.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Afcons Infrastructure Limited</t>
+          <t>Suratwwala Business Group Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>273</v>
+        <v>24.04999923706055</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>275.4500122070312</v>
+        <v>24.28000068664551</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>263.75</v>
+        <v>19.20000076293945</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>264.6000061035156</v>
+        <v>22.44000053405762</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>274.1499938964844</v>
+        <v>23.98999977111816</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>264.6000061035156</v>
+        <v>22.44000053405762</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>1136857</v>
+        <v>485619</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-3.48</v>
+        <v>-6.46</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Afcons Infrastructure sees release of encumbrance on 9.2 crore shares - scanx.trade</t>
+          <t>Suratwwala Business Group Slips 1.91% to ₹24.16: Stock Tests Key Support Zone - Equal Weight ETF - siam.in</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Afcons Infrastructure sees release of encumbrance on 9.2 crore shares - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>Afcons Infrastructure Ltd. Stock News - Value Research</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>Afcons Infrastructure shares in focus on receiving arbitral award of ₹335 crore; all you need to know - Upstox</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>Afcons Infrastructure shares rally 4% after receiving Rs 335.5 crore arbitration award - The Economic Times</t>
-        </is>
-      </c>
+          <t>Suratwwala Business Group Slips 1.91% to ₹24.16: Stock Tests Key Support Zone - Equal Weight ETF - siam.in</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr"/>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 12:56:51 IST</t>
+          <t>2026-09-10 20:07:15 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -3195,68 +3203,64 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>AARNAV.NS</t>
+          <t>RUBYMILLS.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Aarnav Fashions Limited</t>
+          <t>The Ruby Mills Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>31</v>
+        <v>485</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>31.70999908447266</v>
+        <v>485</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>30.60000038146973</v>
+        <v>441.2000122070312</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>30.79999923706055</v>
+        <v>445.8999938964844</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>31.89999961853027</v>
+        <v>474.8500061035156</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>30.79999923706055</v>
+        <v>445.8999938964844</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>3281</v>
+        <v>31491</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-3.45</v>
+        <v>-6.1</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Aarnav Fashions Share Price News: Technicals, Valuation - Univest</t>
+          <t>The Ruby Mills Share Price Rises 11.94% on Price Action - Univest</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Aarnav Fashions AGM set for Sep 30, 2026 to adopt FY26 accounts - scanx.trade</t>
+          <t>The Ruby Mills Share Price Rises 11.94% on Price Action - Univest</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Aarnav Fashions Ltd. Peer Comparison – Compare with Others - Value Research</t>
+          <t>Ad-hoc Addition Towards Undervaluation of Closing Stock After Sec.145 Rejection Unsustainable under Income Tax Act: ITAT [Read Order] - Taxscan</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Aarnav Fashions Ltd. Shareholding Pattern – Promoters, FIIs &amp; DIIs - Value Research</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>Aarnav Fashions Ltd. Financials – Balance Sheet, Profit &amp; Loss, Cash Flow - Value Research</t>
-        </is>
-      </c>
+          <t>Ruby Mills Q1 EBITDA jumps 134% to ₹255M; profit dips 2% - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 12:56:51 IST</t>
+          <t>2026-09-10 20:07:15 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -3264,61 +3268,61 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>ELGIRUBCO.NS</t>
+          <t>ASTEC.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Elgi Rubber Company Limited</t>
+          <t>Astec LifeSciences Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>62.81999969482422</v>
+        <v>751</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>63.54000091552734</v>
+        <v>751</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>60.59999847412109</v>
+        <v>693.4000244140625</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>60.70999908447266</v>
+        <v>715.7999877929688</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>62.81999969482422</v>
+        <v>761</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>60.70999908447266</v>
+        <v>715.7999877929688</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>41030</v>
+        <v>523902</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-3.36</v>
+        <v>-5.94</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Elgi Rubber (ELGIRUBCO) Dips 0.66% to ₹58.69 on NSE, Holds Between Key Support and Resistance - Gamma Flip Level - siam.in</t>
+          <t>Astec Lifesciences share price skyrockets 17% despite weak sentiments on D-Street. Do you own? - Livemint</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Elgi Rubber Sells Hyderabad Non-Core Land Asset for Rs 12 Crore - TipRanks</t>
+          <t>Astec Lifesciences share price skyrockets 17% despite weak sentiments on D-Street. Do you own? - TradingView</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Elgi (ELGIRUBCO.NS) Q2 2026 Scorecard: The Report Supplies Updated Headline Figures in Latest Trading; Shares Move Higher 1.47% - Return On Capital - siam.in</t>
+          <t>Astec Lifesciences share price skyrockets 17% despite weak sentiments on D-Street. Do you own? - TradingView</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Elgi (ELGIRUBCO.NS) Technicals: Finishes 3.04% Up at ₹61.00 in Latest Trading; Price Setup: Traders Can Monitor the ₹57.95-₹64.05 Range under the Current Snapshot - Overvalued Signals - siam.in</t>
+          <t>Astec Lifesciences Share Price rises 9.49% on price action - Univest</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>Elgi Rubber Company Share Price analysis after 8.66% rise - Univest</t>
+          <t>Astec (ASTE) Price: Advances 0.14% to $41.77; Range Check: the Near-Term Reference Band Stretches From $39.68 to $43.86 - Social Sentiment - siam.in</t>
         </is>
       </c>
     </row>

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -439,14 +439,14 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 20:07:15 IST</t>
+          <t>2026-09-11 12:54:16 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -553,68 +553,64 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>LADDERUP.NS</t>
+          <t>NIBL.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Ladderup Finance Limited</t>
+          <t>NRB Industrial Bearings Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>54.90000152587891</v>
+        <v>31</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>61.93000030517578</v>
+        <v>36.68999862670898</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>53</v>
+        <v>29.96999931335449</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>61.93000030517578</v>
+        <v>36</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>51.61000061035156</v>
+        <v>30.57999992370605</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>61.93000030517578</v>
+        <v>36</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>9326</v>
+        <v>207036</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>20</v>
+        <v>17.72</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Ladderup Finance Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
+          <t>NRB (NIBL.NS) Session Brief: Posts a 3.94% Loss to ₹31.43 at the Close; Reference Levels - siam.in</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Saraswati Saree Depot Ltd leads gainers in 'B' group - Business Standard</t>
+          <t>NRB Industrial Bearings accepts VP Manufacturing resignation - scanx.trade</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Saraswati Saree Depot Ltd leads gainers in 'B' group - Business Standard</t>
+          <t>NRB Industrial Bearings accepts VP Manufacturing resignation - scanx.trade</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Ladderup Finance Ltd. Peer Comparison – Compare with Others - Value Research</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>Ladderup Finance releases FY26 annual report, sets Sep 24 AGM date - scanx.trade</t>
-        </is>
-      </c>
+          <t>NSE returns NRB Industrial Bearings promoter reclassification application - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 20:07:15 IST</t>
+          <t>2026-09-11 12:54:16 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -622,60 +618,68 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>SSDL.NS</t>
+          <t>RAYMOND.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Saraswati Saree Depot Limited</t>
+          <t>Raymond Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>58.65000152587891</v>
+        <v>853.8499755859375</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>67.83999633789062</v>
+        <v>1024.5</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>58.5</v>
+        <v>835.0499877929688</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>67.83999633789062</v>
+        <v>986.9500122070312</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>56.54000091552734</v>
+        <v>853.8499755859375</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>67.83999633789062</v>
+        <v>986.9500122070312</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>296352</v>
+        <v>13306913</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>19.99</v>
+        <v>15.59</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Saraswati Saree Depot SSDL Fresh High Analysis - Kalkine India</t>
+          <t>Raymond surges 20% on huge volume; here's why stock rose 66% in 11 days - Business Standard</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Saraswati Saree Depot SSDL Fresh High Analysis - Kalkine India</t>
+          <t>Raymond shares rally over 57% in two weeks; what's fuelling the surge? - Business Today</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Saraswati Saree Depot Ltd. Share Price Gain: Key Analysis - Univest</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
+          <t>Raymond shares rally over 57% in two weeks; what's fuelling the surge? - Business Today</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>Stock to buy today: Raymond (₹853.50) - BusinessLine</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>Ceribell CTO Raymond Woo sells $118,900 of company stock - Investing.com India</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 20:07:15 IST</t>
+          <t>2026-09-11 12:54:16 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -683,68 +687,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>VEDAVAAG.NS</t>
+          <t>UGARSUGAR.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>VEDAVAAG Systems Limited</t>
+          <t>The Ugar Sugar Works Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>18.70000076293945</v>
+        <v>49.9900016784668</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>22.20999908447266</v>
+        <v>57.9900016784668</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>18.51000022888184</v>
+        <v>48.4900016784668</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>22.20999908447266</v>
+        <v>56.31999969482422</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>18.51000022888184</v>
+        <v>49.91999816894531</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>22.20999908447266</v>
+        <v>56.31999969482422</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>526243</v>
+        <v>4668049</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>19.99</v>
+        <v>12.82</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Vedavaag Systems schedules 28th AGM for September 30 - scanx.trade</t>
+          <t>UGARSUGAR Share Price Rise: Fundamentals and Sector View - Univest</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Vedavaag Systems schedules 28th AGM for September 30 - scanx.trade</t>
+          <t>Ugar Sugar Works (NSE: UGARSUGAR) Analysis - Kalkine India</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>VEDAVAAG Stock Price and Chart — NSE:VEDAVAAG - TradingView</t>
+          <t>Ugar (UGARSUGAR.NS) Earnings Update: The Report Provides a New Financial Snapshot in the Reported Period; Trading Response: Shares Finish 4.05% Down in the Latest Reading - Financial Data - siam.in</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Vedavaag Systems Ltd. Financials – Balance Sheet, Profit &amp; Loss, Cash Flow - Value Research</t>
+          <t>Ugar (UGARSUGAR.NS) Results Versus Estimates: The Company Releases Its Current Earnings Data in the Available Record; Price Move: The Stock Ends Down 0.14% - Guidance Downgrade Alert - siam.in</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Vedavaag Systems Ltd Share Price, Stock Price - NSE/BSE Live - NDTV Profit</t>
+          <t>Ugar Sugar Works (NSE: UGARSUGAR) Analysis - Kalkine India</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 20:07:15 IST</t>
+          <t>2026-09-11 12:54:16 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -752,68 +756,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>MOLBIO.NS</t>
+          <t>PINELABS.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics Limited</t>
+          <t>Pine Labs Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1271</v>
+        <v>171</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1509.400024414062</v>
+        <v>192.8999938964844</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>1271</v>
+        <v>170.9600067138672</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>1509.400024414062</v>
+        <v>192.8399963378906</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1257.900024414062</v>
+        <v>173.1699981689453</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1509.400024414062</v>
+        <v>192.8399963378906</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>11329688</v>
+        <v>143835794</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>19.99</v>
+        <v>11.36</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics shares surge 35% in two sessions; here’s why the healthcare stock hit record high on Sept 10 - Upstox</t>
+          <t>Pine (PINELABS.NS) Chart: Loses 1.77% to Close at ₹156.91 for the Current Session; Market Levels: ₹149.06 and ₹164.76 Define the Nearby Reference Levels in Latest Trading - Sign of Strength - siam.in</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics share price hits 20% upper circuit, jumps 87% from IPO price - TradingView</t>
+          <t>PINE LABS LIMITED (PINELABS) Share Price Rises 5.43% Today - Univest</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics share price hits 20% upper circuit, jumps 87% from IPO price - TradingView</t>
+          <t>Pine (PINELABS.NS) Results at a Glance: The Company Publishes Its Latest Results for the Current Session - siam.in</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics shares rally 30% in 2 days, jump 80% since debut. What lies ahead? - The Economic Times</t>
+          <t>PINE LABS LIMITED (PINELABS) Share Price Rises 5.43% Today - Univest</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>Molbio Diagnostics hits 20% upper circuit on heavy volume; up 35% in 2 days - Business Standard</t>
+          <t>Chandan Pinelabs.mp4 - What Our Speaker Says - The Economic Times</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 20:07:15 IST</t>
+          <t>2026-09-11 12:54:16 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -821,56 +825,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>GRAVISSHO.NS</t>
+          <t>ORIENTTECH.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Graviss Hospitality Limited</t>
+          <t>Orient Technologies Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>29.15999984741211</v>
+        <v>237.1799926757812</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>35.59000015258789</v>
+        <v>274.5</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>28.64999961853027</v>
+        <v>233.6999969482422</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>35.59000015258789</v>
+        <v>258.8399963378906</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>29.65999984741211</v>
+        <v>235.3600006103516</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>35.59000015258789</v>
+        <v>258.8399963378906</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>491934</v>
+        <v>7339204</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>19.99</v>
+        <v>9.98</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Graviss Hospitality (GRAVISSHO.NS) Falls 3.99% to ₹29.6, Approaches Key Support at ₹28.12 - High Low Breadth - siam.in</t>
+          <t>ORIENT TECHNOLOGIES LTD Share Price - Live NSE: ORIENTTECH Stock Price &amp; Chart - Upstox</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Graviss Hospitality (GRAVISSHO.NS) Falls 3.99% to ₹29.6, Approaches Key Support at ₹28.12 - High Low Breadth - siam.in</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
+          <t>Orient Technologies Share Price Today: market cap, valuation - Univest</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>Orient (ORIENTTECH.NS) Quarterly Results: The Latest Report Adds New Financial Reference Points in Latest Trading; Market Reaction: Shares Move Lower 0.35% in Latest Trading - Next Quarter Guidance - siam.in</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Orient Technologies Share Price Today: market cap, valuation - Univest</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>Orient (ORIENTTECH.NS) Today: Climbs 0.27% to ₹244.30 in the Latest Session; Level Watch: Support at ₹232.09 and Resistance at ₹256.52 Frame the Range in the Current Update - Delta Hedging - siam.in</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 20:07:15 IST</t>
+          <t>2026-09-11 12:54:16 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -878,64 +894,60 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>DIGJAMLMTD.NS</t>
+          <t>QUADFUTURE.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Digjam Limited</t>
+          <t>Quadrant Future Tek Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>52.97999954223633</v>
+        <v>431</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>61.84000015258789</v>
+        <v>511.7999877929688</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>52.97000122070312</v>
+        <v>428.2000122070312</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>61.84000015258789</v>
+        <v>478.1000061035156</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>51.54000091552734</v>
+        <v>435.7999877929688</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>61.84000015258789</v>
+        <v>478.1000061035156</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>732310</v>
+        <v>8566368</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>19.98</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Digjam (DIGJAMLMTD.NS) Stock: Retreats 0.27% to ₹51.50; the Supplied Trading Band Runs From ₹48.92 to ₹54.08 - Sector ETF Flow - siam.in</t>
+          <t>Quadrant Future Tek Holds Firm Near ₹362 Amid Positive Momentum - PCR Moving Average - siam.in</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Digjam (DIGJAMLMTD.NS) Stock: Retreats 0.27% to ₹51.50; the Supplied Trading Band Runs From ₹48.92 to ₹54.08 - Sector ETF Flow - siam.in</t>
+          <t>QUADRANT FUTURE TEK LTD Share Price, Valuation, Sector View - Univest</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Digjam Shareholders Weigh NCLT-Directed Scheme of Arrangement with Reid &amp; Taylor - The Globe and Mail</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>Digjam Shareholders Clear Scheme of Arrangement with Reid &amp; Taylor - The Globe and Mail</t>
-        </is>
-      </c>
+          <t>QUADRANT FUTURE TEK LTD Share Price, Valuation, Sector View - Univest</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
       <c r="Q7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 20:07:15 IST</t>
+          <t>2026-09-11 12:54:16 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -943,68 +955,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>KAVDEFENCE.NS</t>
+          <t>AWFIS.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Kavveri Defence &amp; Wireless Technologies Limited</t>
+          <t>Awfis Space Solutions Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>63</v>
+        <v>248.5</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>75.81999969482422</v>
+        <v>285</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>61</v>
+        <v>244.1000061035156</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>74.76999664306641</v>
+        <v>273.6000061035156</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>63.18999862670898</v>
+        <v>249.6000061035156</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>74.76999664306641</v>
+        <v>273.6000061035156</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>2358786</v>
+        <v>10681874</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>18.33</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>KAVDEFENCE Share Price Rise: Price Action and Valuation - Univest</t>
+          <t>Awfis Space Solutions Share Price: Buy or Sell - Univest</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Kavveri Defence Board Clears Amalgamation of Samoro Telecoms Unit - TipRanks</t>
+          <t>Awfis Space Solutions Share Price: Buy or Sell - Univest</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2 Data Centre Stocks and 7 Others Hit the 20% Upper Circuit Today; Do You Own Any? - Trade Brains</t>
+          <t>Awfis Closes GST Litigation; Pays Interest - scanx.trade</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Kavveri Defence Board Clears Amalgamation of Samoro Telecoms Unit - TipRanks</t>
+          <t>₹524: That's What Analysts Think Awfis Space Solutions Limited (NSE:AWFIS) Is Worth After Its Latest Results - simplywall.st</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Kavveri Defence &amp; Wireless Technologies Clears Amalgamation with Samoro Telecoms - TipRanks</t>
+          <t>Awfis Space Solutions Declines 1.54% to ₹268.35, Holds Above Key Support at ₹254.93 - News Sentiment - siam.in</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 20:07:15 IST</t>
+          <t>2026-09-11 12:54:16 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1012,64 +1024,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>BIOFILCHEM.NS</t>
+          <t>DAVANGERE.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Biofil Chemicals &amp; Pharmaceuticals Limited</t>
+          <t>Davangere Sugar Company Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>31.45999908447266</v>
+        <v>1.950000047683716</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>37.75</v>
+        <v>2.099999904632568</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>31.45999908447266</v>
+        <v>1.899999976158142</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>36.79000091552734</v>
+        <v>2.089999914169312</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>31.45999908447266</v>
+        <v>1.909999966621399</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>36.79000091552734</v>
+        <v>2.089999914169312</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>681883</v>
+        <v>31096409</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>16.94</v>
+        <v>9.42</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Biofil Chemicals &amp; Pharmaceuticals (BIOFILCHEM): Small Pharma Maker Explained - Kalkine India</t>
+          <t>Sugar stock under ₹10 jumps 6% despite sideways trend in Indian stock market | Here's why - Livemint</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Biofil Chemicals &amp; Pharmaceuticals (BIOFILCHEM): Small Pharma Maker Explained - Kalkine India</t>
+          <t>Davangere Sugar Company Ltd Locks at Upper Circuit With 9.95% Gain — Buyers Queue, Sellers Absent - MarketsMojo</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Biofil (BIOFILCHEM.NS) Technicals: Moves 0.87% Lower to ₹32.06 at the Close; Next Test: the ₹30.46 to ₹33.66 Range Remains in Focus in Latest Trading - Fibonacci Time Zone - siam.in</t>
+          <t>Davangere Sugar Company Ltd Locks at Upper Circuit With 9.95% Gain — Buyers Queue, Sellers Absent - MarketsMojo</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Biofil Chemicals NSE:BIOFILCHEM Q1 FY27 Newspaper Publication - Kalkine India</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr"/>
+          <t>Davangere Sugar Company Share: Bull Case vs Bear Case for 2026 - Univest</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>Trending Stocks Today, September 9, 2026: PC Jeweller, Vodafone Idea, IFCI, Davangere Sugar In Focus - HDFC Sky</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 20:07:15 IST</t>
+          <t>2026-09-11 12:54:16 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1077,68 +1093,56 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>CFEL.NS</t>
+          <t>PWL.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Confidence Futuristic Energetech Limited</t>
+          <t>Physicswallah Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>43</v>
+        <v>125.5</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>46.38000106811523</v>
+        <v>137.1199951171875</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>40.31999969482422</v>
+        <v>125.370002746582</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>44.91999816894531</v>
+        <v>135.8200073242188</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>38.65000152587891</v>
+        <v>126.7300033569336</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>44.91999816894531</v>
+        <v>135.8200073242188</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>1071863</v>
+        <v>25825059</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>16.22</v>
+        <v>7.17</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Confidence Futuristic Energetech Ltd. Upper Circuit: Price and Key Data - Univest</t>
+          <t>Earnings Update: Physicswallah Limited (NSE:PWL) Just Reported Its First-Quarter Results And Analysts Are Updating Their Forecasts - simplywall.st</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20% Upper Circuit: Molbio Diagnostics and 8 Other Stocks That Hit the Upper Circuit Today; Do You Own Any? - Trade Brains</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>Confidence Futuristic Energetech Ltd. (CFEL) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>Confidence Futuristic Energetech Ltd. (CFEL) Share Price Today, Quote, Latest Discussions, Interactive Chart and News - Stocktwits</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>20% Upper Circuit: Molbio Diagnostics and 8 Other Stocks That Hit the Upper Circuit Today; Do You Own Any? - Trade Brains</t>
-        </is>
-      </c>
+          <t>Earnings Update: Physicswallah Limited (NSE:PWL) Just Reported Its First-Quarter Results And Analysts Are Updating Their Forecasts - simplywall.st</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 20:07:15 IST</t>
+          <t>2026-09-11 12:54:16 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1146,68 +1150,68 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>MEDICAPQ.NS</t>
+          <t>SHANKESH.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Medi Caps Limited</t>
+          <t>Shankesh Jewellers Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>32.79000091552734</v>
+        <v>104.4000015258789</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>36.79999923706055</v>
+        <v>115.9000015258789</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>29.95999908447266</v>
+        <v>101.5100021362305</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>35.22000122070312</v>
+        <v>103.8199996948242</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>30.73999977111816</v>
+        <v>98.41000366210938</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>35.22000122070312</v>
+        <v>103.8199996948242</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>493535</v>
+        <v>45170362</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>14.57</v>
+        <v>5.5</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>MEDICAPQ Stock Price and Chart — NSE:MEDICAPQ - TradingView</t>
+          <t>Newly-listed stock Shankesh Jewellers surges 18% to hit a record high- What is fuelling the rally? - Livemint</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>MEDI-CAPS LIMITED: Discloses Process for Shareholder Annual Report Distribution - InvestyWise</t>
+          <t>Neogen Chemicals Slides, Shankesh Jewellers Jumps 12% on Earnings - Whalesbook</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Medi-Caps Ltd. (MEDICAPQ) Profile, Company FAQs &amp; Facts, Industry, Sector, Employee Strength - Stocktwits</t>
+          <t>Shankesh Jewellers bucks market sell-off to zoom 18% as Q1 PAT doubles - Business Standard</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Medi-Caps Ltd. (MEDICAPQ) Share Price Today, Quote, Latest Discussions, Interactive Chart and News - Stocktwits</t>
+          <t>Shankesh Jewellers Share Price Jumps 9% As Q1 Net Profit Doubles - NDTV Profit</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>Medi-Caps Ltd. (MEDICAPQ) Fundamental and Financial Data - Stocktwits</t>
+          <t>Buzzing Stocks: Neogen Chemicals shares fall 4% on QIP launch; Shankesh Jewellers surges 12% after Q1... - Moneycontrol.com</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 20:07:15 IST</t>
+          <t>2026-09-11 12:54:16 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1215,46 +1219,46 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>OSWALSEEDS.NS</t>
+          <t>KWIL.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>ShreeOswal Seeds And Chemicals Limited</t>
+          <t>Kwality Wall's (India) Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>13.69999980926514</v>
+        <v>41.09999847412109</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>15.60000038146973</v>
+        <v>43.90000152587891</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>13.19999980926514</v>
+        <v>40.70000076293945</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>14.75</v>
+        <v>43.72000122070312</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>13.07999992370605</v>
+        <v>41.52999877929688</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>14.75</v>
+        <v>43.72000122070312</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>1571288</v>
+        <v>28782901</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>12.77</v>
+        <v>5.27</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>ShreeOswal (OSWALSEEDS.NS) Jun 2026 Earnings: The Latest Report Adds New Financial Reference Points in Latest Trading; Market Move: The Share Price Sheds 2.35% in the Current Update - Financial Summary - siam.in</t>
+          <t>Kwality (KWIL.NS) Results Review: The Report Supplies Updated Headline Figures in Latest Trading; Share Response: The Stock Ends Down 2.96% in the Available Record - Revenue Per Share - siam.in</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>ShreeOswal (OSWALSEEDS.NS) Jun 2026 Earnings: The Latest Report Adds New Financial Reference Points in Latest Trading; Market Move: The Share Price Sheds 2.35% in the Current Update - Financial Summary - siam.in</t>
+          <t>Kwality (KWIL.NS) Results Review: The Report Supplies Updated Headline Figures in Latest Trading; Share Response: The Stock Ends Down 2.96% in the Available Record - Revenue Per Share - siam.in</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr"/>
@@ -1264,7 +1268,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 20:07:15 IST</t>
+          <t>2026-09-11 12:54:16 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1272,68 +1276,68 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>ANMOL.NS</t>
+          <t>SAKHTISUG.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Anmol India Limited</t>
+          <t>Sakthi Sugars Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>13.69999980926514</v>
+        <v>19.19000053405762</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>15.55000019073486</v>
+        <v>20.39999961853027</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>12.5600004196167</v>
+        <v>19.04999923706055</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>15.34000015258789</v>
+        <v>20.17000007629395</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>13.63000011444092</v>
+        <v>19.19000053405762</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>15.34000015258789</v>
+        <v>20.17000007629395</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>1843869</v>
+        <v>137952</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>12.55</v>
+        <v>5.11</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Anmol India schedules 28th AGM for September 26, 2026 - scanx.trade</t>
+          <t>Sakthi Sugars Ltd. Share Price Rises 10.69%: Full Analysis - Univest</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Anmol India schedules 28th AGM for September 26, 2026 - scanx.trade</t>
+          <t>Sakthi Sugars (NSE:SAKHTISUG): Cane, Ethanol and Power - Kalkine India</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Anmol India (ANMOL.NS) Holds Steady at ₹10.28; Consolidation Phase in Focus - Early Entry Signals - siam.in</t>
+          <t>Sakthi Sugars Ltd. Share Price Up 10.82%: Stock Analysis - Univest</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Anmol India promoter pledges 3.3M shares to SBI for ₹155 crore loan - scanx.trade</t>
+          <t>Sakthi Sugars Share Price news with sector and peer view - Univest</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>Anmol India schedules Aug 29 board meeting to finalize AGM and annual report - scanx.trade</t>
+          <t>Sakthi Sugars (NSE:SAKHTISUG): Cane, Ethanol and Power - Kalkine India</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 20:07:15 IST</t>
+          <t>2026-09-11 12:54:16 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1341,64 +1345,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>KOTIC.NS</t>
+          <t>MILKYMIST.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Kothari Industrial Corporation Limited</t>
+          <t>Milky Mist Dairy Food Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>136.8999938964844</v>
+        <v>279</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>159.9700012207031</v>
+        <v>292.7699890136719</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>136.1000061035156</v>
+        <v>276.8299865722656</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>151.2100067138672</v>
+        <v>292.7699890136719</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>135.5399932861328</v>
+        <v>278.8299865722656</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>151.2100067138672</v>
+        <v>292.7699890136719</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>804024</v>
+        <v>8589450</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>11.56</v>
+        <v>5</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Kothari Industrial share price zooms 11%! Stock down 74% in one year | What’s fuelling the rally? - Livemint</t>
+          <t>Milky Mist Dairy Food Limited Share Price - Upstox</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Kothari Industrial share price zooms 11%! Stock down 74% in one year | What’s fuelling the rally? - Livemint</t>
+          <t>MILKY MIST DAIRY FOOD L 52 Week High Streak and Valuation - Univest</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Kothari Industrial Corporation Share Price rises 10.14% - Univest</t>
+          <t>Diluted shares outstanding of Milky Mist Dairy Food Ltd. – NSE:MILKYMIST - TradingView</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Kothari Industrial Stock Falls 6% Despite Securing ₹14.56 Cr Government Orders - Trade Brains</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr"/>
+          <t>MILKYMIST Share Price Today - MILKY MIST DAIRY FOOD L Stock Price Live NSE/BSE - Univest</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>Share Price Today - Milky Mist Dairy Food Ltd. Stock Price Live NSE/BSE - HDFC Sky</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 20:07:15 IST</t>
+          <t>2026-09-11 12:54:16 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1406,68 +1414,56 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>PANORAMA.NS</t>
+          <t>STLNETWORK.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Panorama Studios International Limited</t>
+          <t>STL Networks Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>56.20000076293945</v>
+        <v>36.59999847412109</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>48</v>
+        <v>35.56999969482422</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>52.91999816894531</v>
+        <v>36.59999847412109</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>47.56000137329102</v>
+        <v>34.86000061035156</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>52.91999816894531</v>
+        <v>36.59999847412109</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>1538580</v>
+        <v>5409543</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>11.27</v>
+        <v>4.99</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Panorama Studios Share Price rises 13.84% with valuation - Univest</t>
+          <t>STLNETWORK Stock Price and Chart — NSE:STLNETWORK - TradingView</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Panorama Studios Share Price rises 13.84% with valuation - Univest</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>Panorama Studios acquires 10% stake in Rhea &amp; Dia Enterprises - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>Panorama Studio Share Price, Stock Price - NSE/BSE Live - NDTV Profit</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>Panorama Studios International Ltd. Stock News - Value Research</t>
-        </is>
-      </c>
+          <t>STLNETWORK Stock Price and Chart — NSE:STLNETWORK - TradingView</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr"/>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 20:07:15 IST</t>
+          <t>2026-09-11 12:54:16 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1475,68 +1471,64 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>DEEP.NS</t>
+          <t>TRACXN.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Deep Polymers Limited</t>
+          <t>Tracxn Technologies Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>37</v>
+        <v>28.59000015258789</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>42.90000152587891</v>
+        <v>30.29999923706055</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>36.95999908447266</v>
+        <v>28.43000030517578</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>40.97999954223633</v>
+        <v>30.01000022888184</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>36.88999938964844</v>
+        <v>28.61000061035156</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>40.97999954223633</v>
+        <v>30.01000022888184</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>209619</v>
+        <v>164614</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>11.09</v>
+        <v>4.89</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>How Deep Can RKLB Stock Fall? - Forbes</t>
+          <t>Tracxn Technologies (TRACXN.NS) Slips 1.16% to ₹29.71 — Key Support at ₹28.22 Comes into Focus - Breakout Stock Alerts - siam.in</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>SKYQ Stock Coils As Traders Weigh Deep Losses And Cash Boost - timothysykes.com</t>
+          <t>Tracxn Technologies (TRACXN.NS) Slips 1.16% to ₹29.71 — Key Support at ₹28.22 Comes into Focus - Breakout Stock Alerts - siam.in</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>SKYQ Stock Coils As Traders Weigh Deep Losses And Cash Boost - timothysykes.com</t>
+          <t>Tracxn (TRACXN.NS) Watch: Rises 0.64% to ₹29.76 for the Current Session; Technical Setup: Traders Can Monitor the ₹28.27-₹31.25 Range in the Available Record - Growth ETF - siam.in</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Happiest Minds Tech share price in deep red - What's behind the stock plunge? - Livemint</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>Deep Energy Resources Ltd. Stock News - Value Research</t>
-        </is>
-      </c>
+          <t>Tracxn (TRACXN.NS) Snapshot: Climbs 1.49% to ₹30.01 at the Close; Range View: Price Remains Between ₹28.51 Support and ₹31.51 Resistance in the Current Update - Bull Flag - siam.in</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 20:07:15 IST</t>
+          <t>2026-09-11 12:54:16 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1544,68 +1536,64 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>SHILGRAVQ.NS</t>
+          <t>TOYAMSL.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Shilp Gravures Limited</t>
+          <t>Toyam Sports Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>153.8000030517578</v>
+        <v>0.6399999856948853</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>177.3800048828125</v>
+        <v>0.6600000262260437</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>153.8000030517578</v>
+        <v>0.6299999952316284</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>168.3999938964844</v>
+        <v>0.6600000262260437</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>151.6100006103516</v>
+        <v>0.6299999952316284</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>168.3999938964844</v>
+        <v>0.6600000262260437</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>93780</v>
+        <v>1594795</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>11.07</v>
+        <v>4.76</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>SHILGRAVQ Stock Price and Chart — NSE:SHILGRAVQ - TradingView</t>
+          <t>Toyam Sports Reports Q3 FY27 Results with Qualified Audit Opinion - scanx.trade</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Technical Analysis of Shilp Gravures Limited (NSE:SHILGRAVQ) - TradingView</t>
+          <t>Can Toyam Sports (BSE: TOYAMSL) Surprise the Market in 2026? The Numbers and Catalysts to Watch - Kalkine India</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Technical Analysis of Shilp Gravures Limited (NSE:SHILGRAVQ) - TradingView</t>
+          <t>Can Toyam Sports (BSE: TOYAMSL) Surprise the Market in 2026? The Numbers and Catalysts to Watch - Kalkine India</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Shilp Gravures Ltd. (SHILGRAVQ) Share Price Today, Quote, Latest Discussions, Interactive Chart and News - Stocktwits</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>Shilp Gravures Ltd. (SHILGRAVQ) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
-        </is>
-      </c>
+          <t>Toyam Sports Ltd. (TOYAMSL) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 20:07:15 IST</t>
+          <t>2026-09-11 12:54:16 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1613,68 +1601,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>NOVARTIND.NS</t>
+          <t>DISHTV.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Novartis India Limited</t>
+          <t>Dish TV India Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>2260</v>
+        <v>2.380000114440918</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>2588.800048828125</v>
+        <v>2.5</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>2232.10009765625</v>
+        <v>2.329999923706055</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>2428.199951171875</v>
+        <v>2.5</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>2186.39990234375</v>
+        <v>2.390000104904175</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>2428.199951171875</v>
+        <v>2.5</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>2292765</v>
+        <v>1186572</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>11.06</v>
+        <v>4.6</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Novartis (NOVARTIND.NS) Quarter in Focus: The Company Publishes Its Latest Results for This Review; Share Move: The Stock Records a 3.23% Decrease in the Latest Reading - Post-Earnings Reaction - siam.in</t>
+          <t>Dish TV India Limited Dispatches Postal Ballot Notice for Independent Directors - scanx.trade</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Novartis India Share Price: fresh 52-week high, valuation - Univest</t>
+          <t>Dish TV schedules 38th AGM for September 29, 2026 via video conferencing - scanx.trade</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Novartis India Share Price: fresh 52-week high, valuation - Univest</t>
+          <t>Dish (DISHTV.NS) Q2 2026 Results: The Report Provides a New Financial Snapshot for the Current Session; Investor Response: Shares Fall 0.72% in the Latest Session - Energy Earnings Report - siam.in</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Novartis India Fresh High: Chart Analysis - Kalkine India</t>
+          <t>Dish (DISHTV.NS) Move: Advances 0.36% to ₹2.80 in Latest Trading; Support at ₹2.66 and Resistance at ₹2.94 Frame the Range for the Current Session - Continuation Pattern Picks - siam.in</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>Novartis India Share Price Update With Valuation Context - Univest</t>
+          <t>Dish TV India Limited Announces Resignation of Abhishek Gupta from Corporate Head ? Information Technology, Effective August 31, 2026 - marketscreener.com</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 20:07:15 IST</t>
+          <t>2026-09-11 12:54:16 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1682,68 +1670,60 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>MANINDS.NS</t>
+          <t>INDUSTOWER.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Man Industries (India) Limited</t>
+          <t>Indus Towers Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>781</v>
+        <v>372</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>944</v>
+        <v>389.7999877929688</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>772.6500244140625</v>
+        <v>372</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>876.4500122070312</v>
+        <v>389.1000061035156</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>792.5499877929688</v>
+        <v>372</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>876.4500122070312</v>
+        <v>389.1000061035156</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>8837154</v>
+        <v>13465319</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>10.59</v>
+        <v>4.6</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>MANINDS Jun 2026 Earnings: EPS of ₹10.39 on ₹1,010 Crore Revenue; Stock Climbs 7.07% on NSE - Earnings Acceleration Picks - siam.in</t>
+          <t>INDUSTOWER Outlook for the Week - Equitypandit</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Man Industries Share Price: fresh 52-week high, valuation - Univest</t>
+          <t>INDUSTOWER Outlook for the Week - Equitypandit</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Man Industries Share Price: Fundamentals at 52-Week High - Univest</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>Man Industries (India) Ltd. Share Price Near 52-Week High - Univest</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>Man Industries Share Price: fresh 52-week high, valuation - Univest</t>
-        </is>
-      </c>
+          <t>Indus (INDUSTOWER.NS) Financial Results: The Company Reports Its Latest Available Figures in the Current Update; Investor Response: Shares Fall 0.70% at the Close - Dividend Increase Stocks - siam.in</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 20:07:15 IST</t>
+          <t>2026-09-11 12:54:16 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1751,68 +1731,64 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>LGHL.NS</t>
+          <t>EMPOWER.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Laxmi Goldorna House Limited</t>
+          <t>Empower India Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>170</v>
+        <v>2.230000019073486</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>198.0099945068359</v>
+        <v>2.289999961853027</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>168.6600036621094</v>
+        <v>2.230000019073486</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>189.4900054931641</v>
+        <v>2.289999961853027</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>172.2299957275391</v>
+        <v>2.190000057220459</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>189.4900054931641</v>
+        <v>2.289999961853027</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>52139</v>
+        <v>16023696</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>10.02</v>
+        <v>4.57</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Lion Group Holding Ltd (NASDAQ: LGHL) Share Price, LGHL Stock News, LGHL Share Price &amp; Updates - Kalkine</t>
+          <t>AI penny stock under ₹10 hits 5% upper circuit as IndiaAI Mission boosts infrastructure demand - Livemint</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>LGHL Announces Strategic Investment in Indonesian Stablecoin and Digital Financial Infrastructure Provider via Stock-for-Participation Arrangement - Eastern Progress</t>
+          <t>AI penny stock under ₹10 hits 5% upper circuit as IndiaAI Mission boosts infrastructure demand - Livemint</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>$LGHL stock is up 19% today. Here's what we see in our data. - Quiver Quantitative</t>
+          <t>NET Power Closes Acquisition of 123 MW Power Generation Rights From EMPower; Shares Rise - marketscreener.com</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Lion Group Reaffirms $15.8 Million Hyperliquid Token Holdings in Treasury Strategy - The Globe and Mail</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>LGHL Announces Strategic Investment in Indonesian Stablecoin and Digital Financial Infrastructure Provider via Stock-for-Participation Arrangement - Eastern Progress</t>
-        </is>
-      </c>
+          <t>A West Texas project plans 10 gas engines totaling 123 megawatts - Stock Titan</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 20:07:15 IST</t>
+          <t>2026-09-11 12:54:16 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1820,61 +1796,61 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>MANGALAM.NS</t>
+          <t>BALPHARMA.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Mangalam Drugs And Organics Limited</t>
+          <t>Bal Pharma Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>31.98999977111816</v>
+        <v>105.5999984741211</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>34.88000106811523</v>
+        <v>114.9499969482422</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>31.70999908447266</v>
+        <v>104.129997253418</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>34.88000106811523</v>
+        <v>111</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>31.70999908447266</v>
+        <v>106.2099990844727</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>34.88000106811523</v>
+        <v>111</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>284789</v>
+        <v>245004</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>10</v>
+        <v>4.51</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>With EPS Growth And More, Mangalam Global Enterprise (NSE:MGEL) Makes An Interesting Case - simplywall.st</t>
+          <t>Bal Pharma Gains 2.9% to ₹95.38; Resistance at ₹100.15 in Focus - Volatility Term Structure - siam.in</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Kumar Mangalam Birla Appointed Vodafone Idea's Non-Executive Chairman, Shares Up 5% - News18</t>
+          <t>Bal Pharma 19.99% Surge: Key Chart Levels - Kalkine India</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Kumar Mangalam Birla Appointed Vodafone Idea's Non-Executive Chairman, Shares Up 5% - News18</t>
+          <t>Bal Pharma 19.99% Surge: Key Chart Levels - Kalkine India</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Mangalam Global changes designation of director - scanx.trade</t>
+          <t>Bal Pharma Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>Mangalam Drugs &amp; Organics Gains 1.57%: Stock Climbs to ₹30.33 as Pharma Momentum Builds - Bull Flag - siam.in</t>
+          <t>Bal Pharma Limited announced that it has received INR 21 million in funding - marketscreener.com</t>
         </is>
       </c>
     </row>
@@ -1895,14 +1871,14 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="43" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
@@ -2001,7 +1977,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 20:07:15 IST</t>
+          <t>2026-09-11 12:54:16 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -2009,68 +1985,68 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>SRGHFL.NS</t>
+          <t>SUNSHINE.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>SRG Housing Finance Limited</t>
+          <t>Sunshine Pictures Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>195</v>
+        <v>512.4000244140625</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>224.8500061035156</v>
+        <v>524.9500122070312</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>195</v>
+        <v>407.7999877929688</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>195</v>
+        <v>407.7999877929688</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>243.75</v>
+        <v>509.7000122070312</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>195</v>
+        <v>407.7999877929688</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>126912</v>
+        <v>3886396</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-20</v>
+        <v>-19.99</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Improved Earnings Required Before SRG Housing Finance Limited (NSE:SRGHFL) Shares Find Their Feet - simplywall.st</t>
+          <t>SUNSHINE Share Price Today - SUNSHINE PICTURES LIMITED Stock Price Live NSE/BSE - Univest</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>SRG Housing Finance Holds Near ₹308 Support Zone Amid Modest Decline - IV Crush Alert - vinanet.vn</t>
+          <t>Sunshine Capital corrects CFO name in board meeting disclosure - scanx.trade</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>SRG Housing Finance Mar 2026 Earnings: EPS of ₹5.89 Reported; Stock Declines 2.7% - Earnings Surprise Score - vinanet.vn</t>
+          <t>Sunshine Capital corrects CFO name in board meeting disclosure - scanx.trade</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>SRG Housing Finance (SRGHFL.NS) Holds Steady Near Resistance; Consolidation Phase Continues - Covered Call Trade - vinanet.vn</t>
+          <t>Sunshine Pictures IPO Listing: Shares List at 9.97% Premium on NSE, Fall Short of Grey-Market Hopes - India Infoline</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>SRGHFL Stock Price and Chart — NSE:SRGHFL - TradingView</t>
+          <t>Sunshine Pictures shares list at 10% premium over IPO price - The Economic Times</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 20:07:15 IST</t>
+          <t>2026-09-11 12:54:16 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -2078,68 +2054,64 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>MONEYBOXX.NS</t>
+          <t>COCHINSHIP.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Moneyboxx Finance Limited</t>
+          <t>Cochin Shipyard Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>40.75</v>
+        <v>1510</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>40.75</v>
+        <v>1510</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>35.84999847412109</v>
+        <v>1386</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>37.15000152587891</v>
+        <v>1390</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>44.81000137329102</v>
+        <v>1520.400024414062</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>37.15000152587891</v>
+        <v>1390</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>1459080</v>
+        <v>4247868</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-17.09</v>
+        <v>-8.58</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Moneyboxx Finance Ltd leads losers in 'B' group - Business Standard</t>
+          <t>Cochin Shipyard Share Price Today, August 24, 2026: COCHINSHIP Closes at ₹1,514 on NSE - The Eastern Herald</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Moneyboxx Finance Daily Chart and Financial View - Kalkine India</t>
+          <t>Cochin Shipyard Ltd. Share Price News After Higher Closes - Univest</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Moneyboxx Finance Share Price Update After Sharp Day Gain - Univest</t>
+          <t>Cochin Shipyard Ltd. Share Price News After Higher Closes - Univest</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Markets Rally, But Moneyboxx Finance Ltd Sinks to 52-Week Low in Stock-Specific Sell-Off - MarketsMojo</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>Moneyboxx Finance Promoters Boost Stake To 46.79% Through ₹33.4 Crore Allotment - scanx.trade</t>
-        </is>
-      </c>
+          <t>Cochin Shipyard Ltd receives Notice from stock exchange for non-compliance - PSU Connect</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 20:07:15 IST</t>
+          <t>2026-09-11 12:54:16 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -2147,68 +2119,68 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>ATALREAL.NS</t>
+          <t>KOTIC.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Atal Realtech Limited</t>
+          <t>Kothari Industrial Corporation Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>15.27000045776367</v>
+        <v>148.7599945068359</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>15.27000045776367</v>
+        <v>148.7599945068359</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>15.27000045776367</v>
+        <v>137.3000030517578</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>15.27000045776367</v>
+        <v>139.0899963378906</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>16.95999908447266</v>
+        <v>151.2100067138672</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>15.27000045776367</v>
+        <v>139.0899963378906</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>503950</v>
+        <v>67618</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-9.960000000000001</v>
+        <v>-8.02</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Atal Realtech Share Price Near ATH With Fundamental View - Univest</t>
+          <t>Kothari Industrial share price zooms 11%! Stock down 74% in one year | What’s fuelling the rally? - Livemint</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Atal Realtech Share Price and Daily Chart View - Kalkine India</t>
+          <t>Kothari Industrial Share Price Today: Fundamental Check - Univest</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Atal Realtech Lower Circuit: Chart Analysis - Kalkine India</t>
+          <t>Kothari Industrial Corporation (KOTIC.NS) Slips 1.23% to ₹134.79; Support at ₹128.05 in Focus - Bullish Sentiment - siam.in</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Atal Realtech Share Price update: price action and valuation - Univest</t>
+          <t>Kothari Industrial Declines 2.23%: KOTIC.NS Navigates Key Support Zone - Volume Dry Up - siam.in</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Atal Realtech 20.00% Fall: Chart Analysis - Kalkine India</t>
+          <t>Kothari Industrial Corporation Share Price rises 10.14% - Univest</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 20:07:15 IST</t>
+          <t>2026-09-11 12:54:16 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -2216,64 +2188,68 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>LCCINFOTEC.NS</t>
+          <t>KAVDEFENCE.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>LCC Infotech Limited</t>
+          <t>Kavveri Defence &amp; Wireless Technologies Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>3.640000104904175</v>
+        <v>72.41000366210938</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>3.680000066757202</v>
+        <v>73.80000305175781</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>3.190000057220459</v>
+        <v>68.19999694824219</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>3.190000057220459</v>
+        <v>69.56999969482422</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>3.539999961853027</v>
+        <v>74.76999664306641</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>3.190000057220459</v>
+        <v>69.56999969482422</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>328095</v>
+        <v>999558</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-9.890000000000001</v>
+        <v>-6.95</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>LCC Infotech AGM Notice FY2025-26 | NSE:LCCINFOTEC - Kalkine India</t>
+          <t>Kavveri Defence &amp; Wireless Technologies (KAVDEFENCE.NS): Defence Stock Moves Up 1.52% as Rangebound Trading Continues - Intraday Trade Ideas - siam.in</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>LCC Infotech AGM Notice FY2025-26 | NSE:LCCINFOTEC - Kalkine India</t>
+          <t>Kavveri Defence Board Clears Amalgamation of Samoro Telecoms Unit - TipRanks</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>LCC Infotech Q1 Results: Net loss widens 16% YoY to ₹12.18 lakh - scanx.trade</t>
+          <t>KAVDEFENCE Share Price Rise: Price Action and Valuation - Univest</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>LCC Infotech issues corrigendum to AGM notice and annual report disclosures - TipRanks</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr"/>
+          <t>Kavveri Defence Board Clears Amalgamation of Samoro Telecoms Unit - TipRanks</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>Kavveri Defence &amp; Wireless Technologies Clears Amalgamation with Samoro Telecoms - TipRanks</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 20:07:15 IST</t>
+          <t>2026-09-11 12:54:16 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2281,64 +2257,68 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>MVELECTRO.NS</t>
+          <t>HEIDELBERG.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>MV Electrosystems Limited</t>
+          <t>HeidelbergCement India Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>911.4500122070312</v>
+        <v>150.9499969482422</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>911.4500122070312</v>
+        <v>150.9499969482422</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>826.0999755859375</v>
+        <v>147.8000030517578</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>835.4500122070312</v>
+        <v>149.6199951171875</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>917.5</v>
+        <v>158.7899932861328</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>835.4500122070312</v>
+        <v>149.6199951171875</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>5082680</v>
+        <v>231222</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-8.94</v>
+        <v>-5.77</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Newly-listed stock MV Electrosystems jumps 15% to hit record high - What's fuelling the rally? - TradingView</t>
+          <t>Heidelberg Materials stock heads into the open after a steady Xetra close - AD HOC NEWS</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Newly-listed stock MV Electrosystems jumps 15% to hit record high - What's fuelling the rally? - TradingView</t>
+          <t>Heidelberg Materials stock heads into the open after a steady Xetra close - AD HOC NEWS</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>MV Electrosystems Share Price: price rise and valuation - Univest</t>
+          <t>Heidelberg Cement India Ltd. Stock News - Value Research</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>MV Electrosystems Share Price Falls 8.25%: Full Analysis - Univest</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr"/>
+          <t>Heidelberg Materials Tokenized Stock (xStock) price today, HEI.DEx to USD live price, marketcap and chart - CoinMarketCap</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>BlackRock lifts Heidelberg Materials voting stake to 5.22% as shares holding rises - Bitget</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 20:07:15 IST</t>
+          <t>2026-09-11 12:54:16 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2346,68 +2326,68 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>VIVOBIOT.NS</t>
+          <t>GUJENERGY.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Vivo Bio Tech Limited</t>
+          <t>GUJARAT ENERGY LIMITED</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>18.81999969482422</v>
+        <v>247.9400024414062</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>18.81999969482422</v>
+        <v>249.2100067138672</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>16.75</v>
+        <v>240.3600006103516</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>16.98999977111816</v>
+        <v>240.9400024414062</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>18.63999938964844</v>
+        <v>254.8000030517578</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>16.98999977111816</v>
+        <v>240.9400024414062</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>112181</v>
+        <v>1143830</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-8.85</v>
+        <v>-5.44</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Dwight Technologies acquires 5.41% stake in Vivo Bio Tech - scanx.trade</t>
+          <t>Gujarat Energy (NSE:GUJENERGY) Could Be A Buy For Its Upcoming Dividend - simplywall.st</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Virinchi Limited Allots 8.5 Lakh Equity Shares on Warrant Conversion Worth Rs.1.79 Crore - scanx.trade</t>
+          <t>Gujarat Energy Limited Appoints Dhirubhai Shah &amp; Co. LLP as Statutory Auditors - PSU Connect</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>An undisclosed buyer acquired 5.41% stake in Vivo Bio Tech Limited from Max Cell Phone Communications Pvt. Ltd. - marketscreener.com</t>
+          <t>Gujarat Gas Share Price Up 2.36%: Price, Valuation View - Univest</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Vivo Bio Tech Ltd. (VIVOBIOT) Share Price Today, Quote, Latest Discussions, Interactive Chart and News - Stocktwits</t>
+          <t>Gujarat Energy Limited announces Annual dividend, payable on October 28, 2026 - marketscreener.com</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>Virinchi Limited Allots 8.5 Lakh Equity Shares on Warrant Conversion Worth Rs.1.79 Crore - scanx.trade</t>
+          <t>Gujarat Energy schedules 14th AGM for September 29, 2026 - scanx.trade</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 20:07:15 IST</t>
+          <t>2026-09-11 12:54:16 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2415,68 +2395,68 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>ATLASCYCLE.NS</t>
+          <t>HEG.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Atlas Cycles (Haryana) Limited</t>
+          <t>HEG Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>108</v>
+        <v>238.1000061035156</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>109.9899978637695</v>
+        <v>243</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>97.19999694824219</v>
+        <v>237.1999969482422</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>98.06999969482422</v>
+        <v>237.1999969482422</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>106.4700012207031</v>
+        <v>249.6499938964844</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>98.06999969482422</v>
+        <v>237.1999969482422</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>85015</v>
+        <v>857020</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-7.89</v>
+        <v>-4.99</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Atlas Cycles (Haryana) shareholders approve FY26 financials despite promoter dissent - scanx.trade</t>
+          <t>Here’s why you should ignore the 65% plunge in HEG share price today post demerger - Moneycontrol.com</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>20% Upper Circuit: Wheels India and 9 Other Stocks That Hit the Upper Circuit Today; Are You Holding Any? - Trade Brains</t>
+          <t>HEG Advanced Materials Debuts At Rs 260 As Demerger Creates Separate Graphite Play - BW Businessworld</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Penny Stock Below Rs 100 Posts Wider Loss in Q1 FY27 Even as Land Sale Deal Gets Extended - Dalal Street Investment Journal</t>
+          <t>Why are HEG Ltd shares showing a fall of 63% in Monday's trade? - Business Standard</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Atlas Cycles (Haryana) grants sale deed extension for Sonepat land - scanx.trade</t>
+          <t>Did HEG shares really crash 64% in one day? Here’s how the demerger math works - The Economic Times</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>20% Upper Circuit: Wheels India and 9 Other Stocks That Hit the Upper Circuit Today; Are You Holding Any? - Trade Brains</t>
+          <t>HEG share price falls over 64% to ₹260: Don’t panic! Here’s what actually happened - Livemint</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 20:07:15 IST</t>
+          <t>2026-09-11 12:54:16 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2484,68 +2464,68 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>TANAA.NS</t>
+          <t>SUPTANERY.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Taneja Aerospace &amp; Aviation Limited</t>
+          <t>Super Tannery Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>277.7000122070312</v>
+        <v>10.27999973297119</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>279</v>
+        <v>10.27999973297119</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>243.25</v>
+        <v>10.27999973297119</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>251.5</v>
+        <v>10.27999973297119</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>272.75</v>
+        <v>10.81999969482422</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>251.5</v>
+        <v>10.27999973297119</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>64780</v>
+        <v>10890</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-7.79</v>
+        <v>-4.99</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>TANAA Stock Price and Chart — NSE:TANAA - TradingView</t>
+          <t>Super Tannery Ltd. (SUPTANERY) Profile, Company FAQs &amp; Facts, Industry, Sector, Employee Strength - Stocktwits</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Taneja Aerospace &amp; Aviation Ltd. (TANAA) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
+          <t>Super Tannery Ltd. (SUPTANERY) Profile, Company FAQs &amp; Facts, Industry, Sector, Employee Strength - Stocktwits</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Taneja Aerospace &amp; Aviation Ltd. (TANAA) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
+          <t>Super Tannery Ltd. (SUPTANERY) Share Price Today, Quote, Latest Discussions, Interactive Chart and News - Stocktwits</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Technical Analysis of Taneja Aerospace &amp; Aviation Ltd. (NSE:TANAA) - TradingView</t>
+          <t>Super Tannery Ltd. (SUPTANERY) Fundamental and Financial Data - Stocktwits</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>Taneja Aerospace &amp; Aviation Ltd. Income Statement – NSE:TANAA - TradingView</t>
+          <t>Super Tannery Ltd. (SUPTANERY) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 20:07:15 IST</t>
+          <t>2026-09-11 12:54:16 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2553,68 +2533,68 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>BALPHARMA.NS</t>
+          <t>AKI.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Bal Pharma Limited</t>
+          <t>AKI India Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>120</v>
+        <v>6.150000095367432</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>124.5999984741211</v>
+        <v>6.150000095367432</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>105.0500030517578</v>
+        <v>6.139999866485596</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>106.2099990844727</v>
+        <v>6.139999866485596</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>114.4499969482422</v>
+        <v>6.460000038146973</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>106.2099990844727</v>
+        <v>6.139999866485596</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>687435</v>
+        <v>84658</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-7.2</v>
+        <v>-4.95</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Bal Pharma Gains 2.9% to ₹95.38; Resistance at ₹100.15 in Focus - Volatility Term Structure - siam.in</t>
+          <t>AKI India Share: Bull Case vs Bear Case for 2026 - Univest</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Bal Pharma 19.99% Surge: Key Chart Levels - Kalkine India</t>
+          <t>AKI India Share: Bull Case vs Bear Case for 2026 - Univest</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Bal Pharma 19.99% Surge: Key Chart Levels - Kalkine India</t>
+          <t>Penny stock under 10 rupees: Upper circuit - Leather share jumps 74% in 4 sessions | Back-to-back surge for third day - TradingView</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Bal Pharma Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
+          <t>AKI India Limited (AKI.NS) Jumps 10.12% to ₹4.57: Key Levels to Watch - On Balance Volume - siam.in</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>Bal Pharma Limited announced that it has received INR 21 million in funding - marketscreener.com</t>
+          <t>Penny stock under 10 rupees: Upper circuit — Leather share jumps 74% in 4 sessions | Back-to-back surge for third day - Livemint</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 20:07:15 IST</t>
+          <t>2026-09-11 12:54:16 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2622,68 +2602,64 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>MARSONS.NS</t>
+          <t>RADIANTCMS.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Marsons Limited</t>
+          <t>Radiant Cash Management Services Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>135.1900024414062</v>
+        <v>37.20999908447266</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>141.7599945068359</v>
+        <v>37.68999862670898</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>125.0100021362305</v>
+        <v>35.2599983215332</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>125.379997253418</v>
+        <v>35.70999908447266</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>135.0800018310547</v>
+        <v>37.52999877929688</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>125.379997253418</v>
+        <v>35.70999908447266</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>6401332</v>
+        <v>393532</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-7.18</v>
+        <v>-4.85</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Marsons Ltd Hits Intraday Low Amid Price Pressure on 10 Sep 2026 - MarketsMojo</t>
+          <t>We Wouldn't Be Too Quick To Buy Radiant Cash Management Services Limited (NSE:RADIANTCMS) Before It Goes Ex-Dividend - simplywall.st</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Marsons Ltd Hits Intraday Low Amid Price Pressure on 10 Sep 2026 - MarketsMojo</t>
+          <t>We Wouldn't Be Too Quick To Buy Radiant Cash Management Services Limited (NSE:RADIANTCMS) Before It Goes Ex-Dividend - simplywall.st</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Marsons Ltd. Share Price rises 8.51% | MARSONS analysis - Univest</t>
+          <t>Radiant (RADIANTCMS.NS) Market: Ends Higher by 1.40% at ₹34.66 for the Current Session; Levels: Support at ₹32.93 and Resistance at ₹36.39 Frame the Range in the Current Update - High Beta Stocks - siam.in</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Marsons (MARSONS.NS) Latest Quarter: The Report Supplies Updated Headline Figures in the Available Record; Post-Report: Shares Move Higher 6.61% in the Latest Reading - Earnings Revision Report - siam.in</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>Marsons Q1 Results FY27: PAT Rs 5 Cr, Revenue Rs 49 crore - Univest</t>
-        </is>
-      </c>
+          <t>ONEGLOBAL Stock Price and Chart — NSE:ONEGLOBAL - TradingView</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 20:07:15 IST</t>
+          <t>2026-09-11 12:54:16 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2691,68 +2667,68 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>DHATRE.NS</t>
+          <t>JINDWORLD.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Dhatre Udyog Limited</t>
+          <t>Jindal Worldwide Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>4.28000020980835</v>
+        <v>54.70000076293945</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>4.699999809265137</v>
+        <v>55.5</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>3.799999952316284</v>
+        <v>52.75</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>4.139999866485596</v>
+        <v>53.11000061035156</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>4.460000038146973</v>
+        <v>55.63999938964844</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>4.139999866485596</v>
+        <v>53.11000061035156</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>101237</v>
+        <v>8481757</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-7.17</v>
+        <v>-4.55</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Dhatre Udyog corrects 31st AGM time to 11 am on Sept 26 - scanx.trade</t>
+          <t>Jindal Worldwide (JINDWORLD.NS) Edges Higher at ₹38.31; Key Support and Resistance in Focus - Dividend Growth Stocks - siam.in</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Dhatre Udyog corrects 31st AGM time to 11 am on Sept 26 - scanx.trade</t>
+          <t>Most Active Equities on September 4, 2026 at 4:00 PM - HDFC Sky</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>DHATRE Stock Price and Chart — NSE:DHATRE - TradingView</t>
+          <t>Jindal (JINDWORLD.NS) Quarterly Results: The Company Publishes Its Latest Results; Session Move: The Stock Records a 1.05% Increase in Latest Trading - Guidance Revision Trend - siam.in</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Dhatre Udyog Ltd. (DHATRE) Profile, Company FAQs &amp; Facts, Industry, Sector, Employee Strength - Stocktwits</t>
+          <t>Jindal Worldwide (NSE: JINDWORLD) New High Analysis - Kalkine India</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>Dhatre Udyog Q1 FY27 Results: Revenue and PAT Highlights - Univest</t>
+          <t>Jindal Worldwide stock hits upper circuit - What's behind the share price jump? - Livemint</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 20:07:15 IST</t>
+          <t>2026-09-11 12:54:16 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2760,68 +2736,64 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>ARVEE.NS</t>
+          <t>AVROIND.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Arvee Laboratories (India) Limited</t>
+          <t>AVRO INDIA LIMITED</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>210.2899932861328</v>
+        <v>8.399999618530273</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>210.2899932861328</v>
+        <v>8.430000305175781</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>194</v>
+        <v>7.900000095367432</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>195.25</v>
+        <v>7.96999979019165</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>210.2899932861328</v>
+        <v>8.340000152587891</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>195.25</v>
+        <v>7.96999979019165</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>18221</v>
+        <v>593350</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-7.15</v>
+        <v>-4.44</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Arvee Laboratories India Share: Bull Case vs Bear Case for 2026 - Univest</t>
+          <t>Avro India Ltd. Share Price Today: Price Rise Breakdown - Univest</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Arvee Laboratories India Share: Bull Case vs Bear Case for 2026 - Univest</t>
+          <t>Avro India sets Sep 23 record date for 30th AGM - scanx.trade</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Arvee Laboratories (India) Share Price rises 11.69%: - Univest</t>
+          <t>Avro India Ltd. Share Price Today: 9.6% Gain, Key Metrics - Univest</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Arvee (ARVEE.NS) Outlook: Ends Lower by 1.98% at ₹165.00; Technical View: ₹156.75 and ₹173.25 Define the Nearby Reference Levels in Latest Trading - OBV Divergence - siam.in</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>Arvee Lab Standalone June 2026 Net Sales at Rs 17.23 crore, up 130.28% Y-o-Y - Moneycontrol.com</t>
-        </is>
-      </c>
+          <t>Avro India sets Sep 23 record date for 30th AGM - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 20:07:15 IST</t>
+          <t>2026-09-11 12:54:16 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2829,68 +2801,68 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>ALKALI.NS</t>
+          <t>RML.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Alkali Metals Limited</t>
+          <t>Rane (Madras) Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>83.75</v>
+        <v>1415.800048828125</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>84</v>
+        <v>1415.900024414062</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>78.11000061035156</v>
+        <v>1340.099975585938</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>79.19000244140625</v>
+        <v>1346.599975585938</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>85.20999908447266</v>
+        <v>1408.900024414062</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>79.19000244140625</v>
+        <v>1346.599975585938</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>36476</v>
+        <v>46259</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-7.06</v>
+        <v>-4.42</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Momentum Stocks: Alkali Metals, Deepak Builders jump up to 15% on sheer momentum - Moneycontrol.com</t>
+          <t>RML puts on strong Nasdaq debut - The Australian</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Tuticorin Alkali unveils new brand identity to signal sustainable growth - scanx.trade</t>
+          <t>RML puts on strong Nasdaq debut - The Australian</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>The Alkali Metals Bull Case - Univest</t>
+          <t>symbol__ Stock Quote Price and Forecast - CNN</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Tuticorin Alkali Chemicals schedules 53rd AGM for September 25, 2026 - scanx.trade</t>
+          <t>RML - Finviz</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>Lords Chloro Alkali Commissions 14.5 MW Solar Plant; Shares Rise 1.33% - HDFC Sky</t>
+          <t>Resolution Minerals Ltd (ASX:RML) Nasdaq Trading to Commence Today - ABN Newswire</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 20:07:15 IST</t>
+          <t>2026-09-11 12:54:16 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2898,64 +2870,68 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>UTKARSHBNK.NS</t>
+          <t>ABREL.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Utkarsh Small Finance Bank Limited</t>
+          <t>Aditya Birla Real Estate Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>15.75</v>
+        <v>1315.099975585938</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>15.89999961853027</v>
+        <v>1315.199951171875</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>14.01000022888184</v>
+        <v>1276</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>14.80000019073486</v>
+        <v>1284.199951171875</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>15.89999961853027</v>
+        <v>1337.400024414062</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>14.80000019073486</v>
+        <v>1284.199951171875</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>53894190</v>
+        <v>175970</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-6.92</v>
+        <v>-3.98</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Utkarsh SFB Daily Chart and Financial Analysis - Kalkine India</t>
+          <t>Rainbows and Unicorns: Aditya Birla Real Estate Limited (NSE:ABREL) Analysts Just Became A Lot More Optimistic - simplywall.st</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Utkarsh SFB Daily Chart and Financial Analysis - Kalkine India</t>
+          <t>NIFTY Realty soars 3%: Prestige Estates, Anant Raj, ABREL among realty stocks in focus on Sept 3 - Upstox</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Utkarsh Small Finance Bank Share Price Drops to Rs 14.43 - Univest</t>
+          <t>NIFTY Realty soars 3%: Prestige Estates, Anant Raj, ABREL among realty stocks in focus on Sept 3 - Upstox</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Utkarsh Small Finance Bank Ltd. Lower Circuit: Price and Key Data - Univest</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr"/>
+          <t>Aditya Birla Real Estate Share Price Update with Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>Q1 results: ABREL, Godrej, JSW Cement, FirstCry, and 693 more on Aug 13 - Business Standard</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 20:07:15 IST</t>
+          <t>2026-09-11 12:54:16 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2963,56 +2939,68 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>ARENTERP.NS</t>
+          <t>GATECH.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Rajdarshan Industries Limited</t>
+          <t>GACM Technologies Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>34.9900016784668</v>
+        <v>0.7300000190734863</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>34.9900016784668</v>
+        <v>0.7300000190734863</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>32.13000106811523</v>
+        <v>0.7300000190734863</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>32.59999847412109</v>
+        <v>0.7300000190734863</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>34.9900016784668</v>
+        <v>0.7599999904632568</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>32.59999847412109</v>
+        <v>0.7300000190734863</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>5299</v>
+        <v>3477277</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-6.83</v>
+        <v>-3.95</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Pennant Group (PNTG) Climbs 1.76% to $39.32, Holding Ground Above Key Support - Dynamic Hedging - vinanet.vn</t>
+          <t>₹0.75 MultiBagger Penny Stock, +56% in 1 Month — Why Institutions Are Paying 25% Premium for GACM TECHNOLOGIES Shares? - theprint.in</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Pennant Group (PNTG) Climbs 1.76% to $39.32, Holding Ground Above Key Support - Dynamic Hedging - vinanet.vn</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr"/>
-      <c r="P16" s="2" t="inlineStr"/>
-      <c r="Q16" s="2" t="inlineStr"/>
+          <t>GACM Technologies Slips 4.6% to ₹0.83; Key Support at ₹0.79 in Focus - MA Crossover - siam.in</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>GACM Technologies: FII holding jumps to 29%; penny stock in focus - Business Today</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>GACM Technologies Hits Fresh 52-Week High as GATECH Surges 110% in One Month; 31% FII Holding and 250 Million AI Mandate Add to Investor Focus - indiagazette.com</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>GACM Technologies Slips 4.6% to ₹0.83; Key Support at ₹0.79 in Focus - MA Crossover - siam.in</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 20:07:15 IST</t>
+          <t>2026-09-11 12:54:16 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -3020,60 +3008,68 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>RADIANTCMS.NS</t>
+          <t>VISHWARAJ.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Radiant Cash Management Services Limited</t>
+          <t>Vishwaraj Sugar Industries Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>38.20000076293945</v>
+        <v>5.519999980926514</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>38.20000076293945</v>
+        <v>5.590000152587891</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>36.40000152587891</v>
+        <v>5.329999923706055</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>37.52999877929688</v>
+        <v>5.400000095367432</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>40.25</v>
+        <v>5.619999885559082</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>37.52999877929688</v>
+        <v>5.400000095367432</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>577436</v>
+        <v>702177</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-6.76</v>
+        <v>-3.91</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>We Wouldn't Be Too Quick To Buy Radiant Cash Management Services Limited (NSE:RADIANTCMS) Before It Goes Ex-Dividend - simplywall.st</t>
+          <t>VISHWARAJ Share Price rise: price action and market cap - Univest</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>We Wouldn't Be Too Quick To Buy Radiant Cash Management Services Limited (NSE:RADIANTCMS) Before It Goes Ex-Dividend - simplywall.st</t>
+          <t>Vishwaraj Sugar Industries Publishes Notices for 31st AGM - TipRanks</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ONEGLOBAL Stock Price and Chart — NSE:ONEGLOBAL - TradingView</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr"/>
-      <c r="Q17" s="2" t="inlineStr"/>
+          <t>Vishwaraj Sugar schedules 31st AGM for September 28, 2026 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>Vishwaraj Sugar Industries reports standalone net loss of Rs 25.84 crore in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>Vishwaraj Sugar Q1 FY27 Results: Revenue Falls 20% to Rs 107 Crore, Net Loss Deepens to Rs 25 Crore - Univest</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 20:07:15 IST</t>
+          <t>2026-09-11 12:54:16 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -3081,64 +3077,68 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>KANCOTEA.NS</t>
+          <t>STALLION.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Kanco Tea &amp; Industries Limited</t>
+          <t>Stallion India Fluorochemicals Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>55.88999938964844</v>
+        <v>229.6999969482422</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>55.93999862670898</v>
+        <v>229.6999969482422</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>52.29000091552734</v>
+        <v>223</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>52.29000091552734</v>
+        <v>225.1000061035156</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>55.95000076293945</v>
+        <v>234.2599945068359</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>52.29000091552734</v>
+        <v>225.1000061035156</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>860</v>
+        <v>278348</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-6.54</v>
+        <v>-3.91</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>KANCOTEA Stock Price and Chart — NSE:KANCOTEA - TradingView</t>
+          <t>Stallion India Fluorochemicals' Rajasthan Plants to Benefit from RIPS 2024 Subsidies - scanx.trade</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Kanco Tea &amp; Industries Ltd (KANCOTEA) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
+          <t>Megan Thee Stallion Shares What She’s Learned About Love and Life Since Klay Thompson Breakup - The Root</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Kanco Tea &amp; Industries Ltd (KANCOTEA) Fundamental and Financial Data - Stocktwits</t>
+          <t>Stallion India Fluorochemicals Ltd Locks at Upper Circuit With 5% Gain — Buyers Queue, Sellers Absent - MarketsMojo</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Kanco Tea &amp; Industries Ltd (KANCOTEA) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr"/>
+          <t>Stallion (STALLION.NS) Results Check: The Latest Financial Metrics Are Now Available in the Latest Reading; Stock Move: The Stock Records a 1.36% Decrease in Latest Trading - EBITDA Margin Trends - siam.in</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>Retail investors bet big on these 12 smallcap stocks that rallied up to 150%; 3 turned multibaggers - The Economic Times</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 20:07:15 IST</t>
+          <t>2026-09-11 12:54:16 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -3146,56 +3146,68 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>SBGLP.NS</t>
+          <t>RATNAVEER.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Suratwwala Business Group Limited</t>
+          <t>Ratnaveer Precision Engineering Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>24.04999923706055</v>
+        <v>310</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>24.28000068664551</v>
+        <v>310.3999938964844</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>19.20000076293945</v>
+        <v>295.6499938964844</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>22.44000053405762</v>
+        <v>299</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>23.98999977111816</v>
+        <v>310.6000061035156</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>22.44000053405762</v>
+        <v>299</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>485619</v>
+        <v>1600570</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-6.46</v>
+        <v>-3.73</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Suratwwala Business Group Slips 1.91% to ₹24.16: Stock Tests Key Support Zone - Equal Weight ETF - siam.in</t>
+          <t>Ratnaveer Precision Engineering Approves Allotment of Equity Shares via Rights Issue - EquityBulls</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Suratwwala Business Group Slips 1.91% to ₹24.16: Stock Tests Key Support Zone - Equal Weight ETF - siam.in</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr"/>
-      <c r="P19" s="2" t="inlineStr"/>
-      <c r="Q19" s="2" t="inlineStr"/>
+          <t>Ratnaveer Precision Engineering Approves Allotment of Equity Shares via Rights Issue - EquityBulls</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>Press Release Distribution India - Business Wire India</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>Ratnaveer Precision approves ₹329.99 crore rights issue allotment - scanx.trade</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>Ratnaveer Precision Engineering Limited Rights 2026-09.09.26 for Shares Cash Flow – NSE:RATNA_RE - TradingView</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 20:07:15 IST</t>
+          <t>2026-09-11 12:54:16 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -3203,56 +3215,56 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>RUBYMILLS.NS</t>
+          <t>GSFC.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>The Ruby Mills Limited</t>
+          <t>Gujarat State Fertilizers &amp; Chemicals Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>485</v>
+        <v>154.9100036621094</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>485</v>
+        <v>154.9100036621094</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>441.2000122070312</v>
+        <v>152.8500061035156</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>445.8999938964844</v>
+        <v>154.5099945068359</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>474.8500061035156</v>
+        <v>160.3800048828125</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>445.8999938964844</v>
+        <v>154.5099945068359</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>31491</v>
+        <v>932846</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-6.1</v>
+        <v>-3.66</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>The Ruby Mills Share Price Rises 11.94% on Price Action - Univest</t>
+          <t>GSFC to transfer unclaimed dividend to IEPF by Aug 31 - scanx.trade</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>The Ruby Mills Share Price Rises 11.94% on Price Action - Univest</t>
+          <t>GSFC Revises Dividend Record Date to 12 September 2026 - TipRanks</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Ad-hoc Addition Towards Undervaluation of Closing Stock After Sec.145 Rejection Unsustainable under Income Tax Act: ITAT [Read Order] - Taxscan</t>
+          <t>GSFC Q1 FY27 Results: Revenue Rs 3,583 Cr, PAT Rs 155 Cr and Key Highlights - Univest</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Ruby Mills Q1 EBITDA jumps 134% to ₹255M; profit dips 2% - scanx.trade</t>
+          <t>GSFC Revises Dividend Record Date to 12 September 2026 - TipRanks</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr"/>
@@ -3260,7 +3272,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 20:07:15 IST</t>
+          <t>2026-09-11 12:54:16 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -3268,61 +3280,61 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>ASTEC.NS</t>
+          <t>THOMASCOTT.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Astec LifeSciences Limited</t>
+          <t>Thomas Scott (India) Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>751</v>
+        <v>241</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>751</v>
+        <v>244.1999969482422</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>693.4000244140625</v>
+        <v>233.8000030517578</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>715.7999877929688</v>
+        <v>235.1000061035156</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>761</v>
+        <v>243.8999938964844</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>715.7999877929688</v>
+        <v>235.1000061035156</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>523902</v>
+        <v>51557</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-5.94</v>
+        <v>-3.61</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Astec Lifesciences share price skyrockets 17% despite weak sentiments on D-Street. Do you own? - Livemint</t>
+          <t>Thomas Scott (India) Ltd. (THOMASCOTT) Share Price Falls 8.36% Today; Textile Micro Cap Among Top Decliners - Univest</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Astec Lifesciences share price skyrockets 17% despite weak sentiments on D-Street. Do you own? - TradingView</t>
+          <t>Thomas Scott அதிரடி லாபம்: ப்ராஃபிட் **51%** உயர்வு, **₹300 கோடி** பரிவர்த்தனைகளுக்கு அனுமதி! - Whalesbook</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Astec Lifesciences share price skyrockets 17% despite weak sentiments on D-Street. Do you own? - TradingView</t>
+          <t>KDGREEN Stock Price and Chart — NSE:KDGREEN - TradingView</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Astec Lifesciences Share Price rises 9.49% on price action - Univest</t>
+          <t>Bang Overseas dispatches 34th AGM notice; e-voting starts Sept 25 - scanx.trade</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>Astec (ASTE) Price: Advances 0.14% to $41.77; Range Check: the Near-Term Reference Band Stretches From $39.68 to $43.86 - Social Sentiment - siam.in</t>
+          <t>Thomas Scott அதிரடி லாபம்: ப்ராஃபிட் **51%** உயர்வு, **₹300 கோடி** பரிவர்த்தனைகளுக்கு அனுமதி! - Whalesbook</t>
         </is>
       </c>
     </row>

--- a/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
+++ b/NEWS_Daily_Report/output/latest/NEWS_Daily_Report.xlsx
@@ -439,7 +439,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -448,11 +448,11 @@
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="60" customWidth="1" min="13" max="13"/>
-    <col width="60" customWidth="1" min="14" max="14"/>
-    <col width="60" customWidth="1" min="15" max="15"/>
-    <col width="60" customWidth="1" min="16" max="16"/>
-    <col width="60" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 12:54:16 IST</t>
+          <t>2026-09-11 20:12:10 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -553,64 +553,48 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>NIBL.NS</t>
+          <t>LADDERUP.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>NRB Industrial Bearings Limited</t>
+          <t>Ladderup Finance Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>36.68999862670898</v>
+        <v>74.30999755859375</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>29.96999931335449</v>
+        <v>73</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>36</v>
+        <v>74.30999755859375</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>30.57999992370605</v>
+        <v>61.93000030517578</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>36</v>
+        <v>74.30999755859375</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>207036</v>
+        <v>59231</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>17.72</v>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>NRB (NIBL.NS) Session Brief: Posts a 3.94% Loss to ₹31.43 at the Close; Reference Levels - siam.in</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>NRB Industrial Bearings accepts VP Manufacturing resignation - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>NRB Industrial Bearings accepts VP Manufacturing resignation - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>NSE returns NRB Industrial Bearings promoter reclassification application - scanx.trade</t>
-        </is>
-      </c>
+        <v>19.99</v>
+      </c>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr"/>
       <c r="Q2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 12:54:16 IST</t>
+          <t>2026-09-11 20:12:10 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -618,68 +602,48 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>RAYMOND.NS</t>
+          <t>AWFIS.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Raymond Limited</t>
+          <t>Awfis Space Solutions Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>853.8499755859375</v>
+        <v>248.5</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1024.5</v>
+        <v>299.4500122070312</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>835.0499877929688</v>
+        <v>244.1000061035156</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>986.9500122070312</v>
+        <v>293.2000122070312</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>853.8499755859375</v>
+        <v>249.6000061035156</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>986.9500122070312</v>
+        <v>293.2000122070312</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>13306913</v>
+        <v>23943415</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>15.59</v>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>Raymond surges 20% on huge volume; here's why stock rose 66% in 11 days - Business Standard</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>Raymond shares rally over 57% in two weeks; what's fuelling the surge? - Business Today</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>Raymond shares rally over 57% in two weeks; what's fuelling the surge? - Business Today</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>Stock to buy today: Raymond (₹853.50) - BusinessLine</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>Ceribell CTO Raymond Woo sells $118,900 of company stock - Investing.com India</t>
-        </is>
-      </c>
+        <v>17.47</v>
+      </c>
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr"/>
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 12:54:16 IST</t>
+          <t>2026-09-11 20:12:10 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -687,68 +651,48 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>UGARSUGAR.NS</t>
+          <t>VGL.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>The Ugar Sugar Works Limited</t>
+          <t>VARVEE GLOBAL LIMITED</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>49.9900016784668</v>
+        <v>57.95999908447266</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>57.9900016784668</v>
+        <v>69.33000183105469</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>48.4900016784668</v>
+        <v>54.61999893188477</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>56.31999969482422</v>
+        <v>66.81999969482422</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>49.91999816894531</v>
+        <v>57.77999877929688</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>56.31999969482422</v>
+        <v>66.81999969482422</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>4668049</v>
+        <v>2056788</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>12.82</v>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>UGARSUGAR Share Price Rise: Fundamentals and Sector View - Univest</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>Ugar Sugar Works (NSE: UGARSUGAR) Analysis - Kalkine India</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>Ugar (UGARSUGAR.NS) Earnings Update: The Report Provides a New Financial Snapshot in the Reported Period; Trading Response: Shares Finish 4.05% Down in the Latest Reading - Financial Data - siam.in</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>Ugar (UGARSUGAR.NS) Results Versus Estimates: The Company Releases Its Current Earnings Data in the Available Record; Price Move: The Stock Ends Down 0.14% - Guidance Downgrade Alert - siam.in</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>Ugar Sugar Works (NSE: UGARSUGAR) Analysis - Kalkine India</t>
-        </is>
-      </c>
+        <v>15.65</v>
+      </c>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 12:54:16 IST</t>
+          <t>2026-09-11 20:12:10 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -756,68 +700,48 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>PINELABS.NS</t>
+          <t>AMDIND.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Pine Labs Limited</t>
+          <t>AMD Industries Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>171</v>
+        <v>56.31999969482422</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>192.8999938964844</v>
+        <v>65.19999694824219</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>170.9600067138672</v>
+        <v>55.5099983215332</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>192.8399963378906</v>
+        <v>64.02999877929688</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>173.1699981689453</v>
+        <v>56.04000091552734</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>192.8399963378906</v>
+        <v>64.02999877929688</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>143835794</v>
+        <v>483363</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>11.36</v>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>Pine (PINELABS.NS) Chart: Loses 1.77% to Close at ₹156.91 for the Current Session; Market Levels: ₹149.06 and ₹164.76 Define the Nearby Reference Levels in Latest Trading - Sign of Strength - siam.in</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>PINE LABS LIMITED (PINELABS) Share Price Rises 5.43% Today - Univest</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>Pine (PINELABS.NS) Results at a Glance: The Company Publishes Its Latest Results for the Current Session - siam.in</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>PINE LABS LIMITED (PINELABS) Share Price Rises 5.43% Today - Univest</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>Chandan Pinelabs.mp4 - What Our Speaker Says - The Economic Times</t>
-        </is>
-      </c>
+        <v>14.26</v>
+      </c>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 12:54:16 IST</t>
+          <t>2026-09-11 20:12:10 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -825,68 +749,48 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>ORIENTTECH.NS</t>
+          <t>AHCL.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Orient Technologies Limited</t>
+          <t>Anlon Healthcare Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>237.1799926757812</v>
+        <v>17.72999954223633</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>274.5</v>
+        <v>20</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>233.6999969482422</v>
+        <v>17.54000091552734</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>258.8399963378906</v>
+        <v>19.56999969482422</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>235.3600006103516</v>
+        <v>17.54000091552734</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>258.8399963378906</v>
+        <v>19.56999969482422</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>7339204</v>
+        <v>150744012</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>ORIENT TECHNOLOGIES LTD Share Price - Live NSE: ORIENTTECH Stock Price &amp; Chart - Upstox</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>Orient Technologies Share Price Today: market cap, valuation - Univest</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>Orient (ORIENTTECH.NS) Quarterly Results: The Latest Report Adds New Financial Reference Points in Latest Trading; Market Reaction: Shares Move Lower 0.35% in Latest Trading - Next Quarter Guidance - siam.in</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>Orient Technologies Share Price Today: market cap, valuation - Univest</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>Orient (ORIENTTECH.NS) Today: Climbs 0.27% to ₹244.30 in the Latest Session; Level Watch: Support at ₹232.09 and Resistance at ₹256.52 Frame the Range in the Current Update - Delta Hedging - siam.in</t>
-        </is>
-      </c>
+        <v>11.57</v>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 12:54:16 IST</t>
+          <t>2026-09-11 20:12:10 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -894,60 +798,48 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>QUADFUTURE.NS</t>
+          <t>TRACXN.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Quadrant Future Tek Limited</t>
+          <t>Tracxn Technologies Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>431</v>
+        <v>28.59000015258789</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>511.7999877929688</v>
+        <v>32.38999938964844</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>428.2000122070312</v>
+        <v>28.43000030517578</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>478.1000061035156</v>
+        <v>31.89999961853027</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>435.7999877929688</v>
+        <v>28.61000061035156</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>478.1000061035156</v>
+        <v>31.89999961853027</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>8566368</v>
+        <v>1039487</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>9.710000000000001</v>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>Quadrant Future Tek Holds Firm Near ₹362 Amid Positive Momentum - PCR Moving Average - siam.in</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>QUADRANT FUTURE TEK LTD Share Price, Valuation, Sector View - Univest</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>QUADRANT FUTURE TEK LTD Share Price, Valuation, Sector View - Univest</t>
-        </is>
-      </c>
+        <v>11.5</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr"/>
       <c r="P7" s="2" t="inlineStr"/>
       <c r="Q7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 12:54:16 IST</t>
+          <t>2026-09-11 20:12:10 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -955,68 +847,48 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>AWFIS.NS</t>
+          <t>SMSPHARMA.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Awfis Space Solutions Limited</t>
+          <t>SMS Pharmaceuticals Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>248.5</v>
+        <v>417.8500061035156</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>285</v>
+        <v>469</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>244.1000061035156</v>
+        <v>414.5499877929688</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>273.6000061035156</v>
+        <v>463.4500122070312</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>249.6000061035156</v>
+        <v>417.4500122070312</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>273.6000061035156</v>
+        <v>463.4500122070312</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>10681874</v>
+        <v>10400042</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>9.619999999999999</v>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>Awfis Space Solutions Share Price: Buy or Sell - Univest</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>Awfis Space Solutions Share Price: Buy or Sell - Univest</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>Awfis Closes GST Litigation; Pays Interest - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>₹524: That's What Analysts Think Awfis Space Solutions Limited (NSE:AWFIS) Is Worth After Its Latest Results - simplywall.st</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>Awfis Space Solutions Declines 1.54% to ₹268.35, Holds Above Key Support at ₹254.93 - News Sentiment - siam.in</t>
-        </is>
-      </c>
+        <v>11.02</v>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 12:54:16 IST</t>
+          <t>2026-09-11 20:12:10 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1024,68 +896,48 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>DAVANGERE.NS</t>
+          <t>RACLGEAR.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Davangere Sugar Company Limited</t>
+          <t>RACL Geartech Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1.950000047683716</v>
+        <v>1586</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>2.099999904632568</v>
+        <v>1856</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>1.899999976158142</v>
+        <v>1551</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>2.089999914169312</v>
+        <v>1756.699951171875</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1.909999966621399</v>
+        <v>1588.199951171875</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2.089999914169312</v>
+        <v>1756.699951171875</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>31096409</v>
+        <v>1142822</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>9.42</v>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>Sugar stock under ₹10 jumps 6% despite sideways trend in Indian stock market | Here's why - Livemint</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>Davangere Sugar Company Ltd Locks at Upper Circuit With 9.95% Gain — Buyers Queue, Sellers Absent - MarketsMojo</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>Davangere Sugar Company Ltd Locks at Upper Circuit With 9.95% Gain — Buyers Queue, Sellers Absent - MarketsMojo</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>Davangere Sugar Company Share: Bull Case vs Bear Case for 2026 - Univest</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>Trending Stocks Today, September 9, 2026: PC Jeweller, Vodafone Idea, IFCI, Davangere Sugar In Focus - HDFC Sky</t>
-        </is>
-      </c>
+        <v>10.61</v>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 12:54:16 IST</t>
+          <t>2026-09-11 20:12:10 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1093,48 +945,40 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>PWL.NS</t>
+          <t>HLEGLAS.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Physicswallah Limited</t>
+          <t>HLE Glascoat Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>125.5</v>
+        <v>367.8500061035156</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>137.1199951171875</v>
+        <v>404.3500061035156</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>125.370002746582</v>
+        <v>363</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>135.8200073242188</v>
+        <v>404.3500061035156</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>126.7300033569336</v>
+        <v>367.6000061035156</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>135.8200073242188</v>
+        <v>404.3500061035156</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>25825059</v>
+        <v>870030</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>7.17</v>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>Earnings Update: Physicswallah Limited (NSE:PWL) Just Reported Its First-Quarter Results And Analysts Are Updating Their Forecasts - simplywall.st</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>Earnings Update: Physicswallah Limited (NSE:PWL) Just Reported Its First-Quarter Results And Analysts Are Updating Their Forecasts - simplywall.st</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr"/>
       <c r="P10" s="2" t="inlineStr"/>
       <c r="Q10" s="2" t="inlineStr"/>
@@ -1142,7 +986,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 12:54:16 IST</t>
+          <t>2026-09-11 20:12:10 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1150,68 +994,48 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>SHANKESH.NS</t>
+          <t>ANMOL.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Shankesh Jewellers Limited</t>
+          <t>Anmol India Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>104.4000015258789</v>
+        <v>15</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>115.9000015258789</v>
+        <v>16.8700008392334</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>101.5100021362305</v>
+        <v>15</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>103.8199996948242</v>
+        <v>16.8700008392334</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>98.41000366210938</v>
+        <v>15.34000015258789</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>103.8199996948242</v>
+        <v>16.8700008392334</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>45170362</v>
+        <v>1521669</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>Newly-listed stock Shankesh Jewellers surges 18% to hit a record high- What is fuelling the rally? - Livemint</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>Neogen Chemicals Slides, Shankesh Jewellers Jumps 12% on Earnings - Whalesbook</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>Shankesh Jewellers bucks market sell-off to zoom 18% as Q1 PAT doubles - Business Standard</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>Shankesh Jewellers Share Price Jumps 9% As Q1 Net Profit Doubles - NDTV Profit</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>Buzzing Stocks: Neogen Chemicals shares fall 4% on QIP launch; Shankesh Jewellers surges 12% after Q1... - Moneycontrol.com</t>
-        </is>
-      </c>
+        <v>9.970000000000001</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr"/>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 12:54:16 IST</t>
+          <t>2026-09-11 20:12:10 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1219,48 +1043,40 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>KWIL.NS</t>
+          <t>QUADFUTURE.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Kwality Wall's (India) Limited</t>
+          <t>Quadrant Future Tek Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>41.09999847412109</v>
+        <v>431</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>43.90000152587891</v>
+        <v>511.7999877929688</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>40.70000076293945</v>
+        <v>428.2000122070312</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>43.72000122070312</v>
+        <v>478.5</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>41.52999877929688</v>
+        <v>435.7999877929688</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>43.72000122070312</v>
+        <v>478.5</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>28782901</v>
+        <v>10360670</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>Kwality (KWIL.NS) Results Review: The Report Supplies Updated Headline Figures in Latest Trading; Share Response: The Stock Ends Down 2.96% in the Available Record - Revenue Per Share - siam.in</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>Kwality (KWIL.NS) Results Review: The Report Supplies Updated Headline Figures in Latest Trading; Share Response: The Stock Ends Down 2.96% in the Available Record - Revenue Per Share - siam.in</t>
-        </is>
-      </c>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr"/>
       <c r="P12" s="2" t="inlineStr"/>
       <c r="Q12" s="2" t="inlineStr"/>
@@ -1268,7 +1084,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 12:54:16 IST</t>
+          <t>2026-09-11 20:12:10 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1276,68 +1092,48 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>SAKHTISUG.NS</t>
+          <t>UGARSUGAR.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Sakthi Sugars Limited</t>
+          <t>The Ugar Sugar Works Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>19.19000053405762</v>
+        <v>49.9900016784668</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>20.39999961853027</v>
+        <v>58.9900016784668</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>19.04999923706055</v>
+        <v>48.4900016784668</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>20.17000007629395</v>
+        <v>54.29999923706055</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>19.19000053405762</v>
+        <v>49.91999816894531</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>20.17000007629395</v>
+        <v>54.29999923706055</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>137952</v>
+        <v>11274239</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>5.11</v>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>Sakthi Sugars Ltd. Share Price Rises 10.69%: Full Analysis - Univest</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>Sakthi Sugars (NSE:SAKHTISUG): Cane, Ethanol and Power - Kalkine India</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>Sakthi Sugars Ltd. Share Price Up 10.82%: Stock Analysis - Univest</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>Sakthi Sugars Share Price news with sector and peer view - Univest</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>Sakthi Sugars (NSE:SAKHTISUG): Cane, Ethanol and Power - Kalkine India</t>
-        </is>
-      </c>
+        <v>8.77</v>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr"/>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 12:54:16 IST</t>
+          <t>2026-09-11 20:12:10 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1345,68 +1141,48 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>MILKYMIST.NS</t>
+          <t>ELANTAS.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Milky Mist Dairy Food Limited</t>
+          <t>Elantas Beck India Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>279</v>
+        <v>13397</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>292.7699890136719</v>
+        <v>14769</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>276.8299865722656</v>
+        <v>13162</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>292.7699890136719</v>
+        <v>14513</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>278.8299865722656</v>
+        <v>13397</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>292.7699890136719</v>
+        <v>14513</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>8589450</v>
+        <v>23980</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>Milky Mist Dairy Food Limited Share Price - Upstox</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>MILKY MIST DAIRY FOOD L 52 Week High Streak and Valuation - Univest</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>Diluted shares outstanding of Milky Mist Dairy Food Ltd. – NSE:MILKYMIST - TradingView</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>MILKYMIST Share Price Today - MILKY MIST DAIRY FOOD L Stock Price Live NSE/BSE - Univest</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>Share Price Today - Milky Mist Dairy Food Ltd. Stock Price Live NSE/BSE - HDFC Sky</t>
-        </is>
-      </c>
+        <v>8.33</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 12:54:16 IST</t>
+          <t>2026-09-11 20:12:10 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1414,48 +1190,40 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>STLNETWORK.NS</t>
+          <t>MOBIKWIK.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>STL Networks Limited</t>
+          <t>One Mobikwik Systems Limited</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>36</v>
+        <v>194.4199981689453</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>36.59999847412109</v>
+        <v>220.2200012207031</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>35.56999969482422</v>
+        <v>193.2100067138672</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>36.59999847412109</v>
+        <v>209.6999969482422</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>34.86000061035156</v>
+        <v>194.6799926757812</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>36.59999847412109</v>
+        <v>209.6999969482422</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>5409543</v>
+        <v>18103148</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>STLNETWORK Stock Price and Chart — NSE:STLNETWORK - TradingView</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>STLNETWORK Stock Price and Chart — NSE:STLNETWORK - TradingView</t>
-        </is>
-      </c>
+        <v>7.72</v>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr"/>
       <c r="P15" s="2" t="inlineStr"/>
       <c r="Q15" s="2" t="inlineStr"/>
@@ -1463,7 +1231,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 12:54:16 IST</t>
+          <t>2026-09-11 20:12:10 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1471,64 +1239,48 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>TRACXN.NS</t>
+          <t>BBOX.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Tracxn Technologies Limited</t>
+          <t>Black Box Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>28.59000015258789</v>
+        <v>741</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>30.29999923706055</v>
+        <v>808.4000244140625</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>28.43000030517578</v>
+        <v>740</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>30.01000022888184</v>
+        <v>800.7999877929688</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>28.61000061035156</v>
+        <v>744.8499755859375</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>30.01000022888184</v>
+        <v>800.7999877929688</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>164614</v>
+        <v>1663663</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>Tracxn Technologies (TRACXN.NS) Slips 1.16% to ₹29.71 — Key Support at ₹28.22 Comes into Focus - Breakout Stock Alerts - siam.in</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>Tracxn Technologies (TRACXN.NS) Slips 1.16% to ₹29.71 — Key Support at ₹28.22 Comes into Focus - Breakout Stock Alerts - siam.in</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>Tracxn (TRACXN.NS) Watch: Rises 0.64% to ₹29.76 for the Current Session; Technical Setup: Traders Can Monitor the ₹28.27-₹31.25 Range in the Available Record - Growth ETF - siam.in</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>Tracxn (TRACXN.NS) Snapshot: Climbs 1.49% to ₹30.01 at the Close; Range View: Price Remains Between ₹28.51 Support and ₹31.51 Resistance in the Current Update - Bull Flag - siam.in</t>
-        </is>
-      </c>
+        <v>7.51</v>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr"/>
       <c r="Q16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 12:54:16 IST</t>
+          <t>2026-09-11 20:12:10 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1536,64 +1288,48 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>TOYAMSL.NS</t>
+          <t>PWL.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Toyam Sports Limited</t>
+          <t>Physicswallah Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.6399999856948853</v>
+        <v>125.5</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0.6600000262260437</v>
+        <v>137.1199951171875</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.6299999952316284</v>
+        <v>125.370002746582</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>0.6600000262260437</v>
+        <v>136.1000061035156</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0.6299999952316284</v>
+        <v>126.7300033569336</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.6600000262260437</v>
+        <v>136.1000061035156</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>1594795</v>
+        <v>41158432</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>Toyam Sports Reports Q3 FY27 Results with Qualified Audit Opinion - scanx.trade</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>Can Toyam Sports (BSE: TOYAMSL) Surprise the Market in 2026? The Numbers and Catalysts to Watch - Kalkine India</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>Can Toyam Sports (BSE: TOYAMSL) Surprise the Market in 2026? The Numbers and Catalysts to Watch - Kalkine India</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>Toyam Sports Ltd. (TOYAMSL) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
-        </is>
-      </c>
+        <v>7.39</v>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr"/>
+      <c r="P17" s="2" t="inlineStr"/>
       <c r="Q17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 12:54:16 IST</t>
+          <t>2026-09-11 20:12:10 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -1601,68 +1337,48 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>DISHTV.NS</t>
+          <t>BLACKBUCK.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Dish TV India Limited</t>
+          <t>BLACKBUCK LIMITED</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>2.380000114440918</v>
+        <v>575</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>2.5</v>
+        <v>634.4000244140625</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>2.329999923706055</v>
+        <v>575</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>2.5</v>
+        <v>628.1500244140625</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>2.390000104904175</v>
+        <v>585.9000244140625</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>2.5</v>
+        <v>628.1500244140625</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>1186572</v>
+        <v>4432007</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>Dish TV India Limited Dispatches Postal Ballot Notice for Independent Directors - scanx.trade</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>Dish TV schedules 38th AGM for September 29, 2026 via video conferencing - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>Dish (DISHTV.NS) Q2 2026 Results: The Report Provides a New Financial Snapshot for the Current Session; Investor Response: Shares Fall 0.72% in the Latest Session - Energy Earnings Report - siam.in</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>Dish (DISHTV.NS) Move: Advances 0.36% to ₹2.80 in Latest Trading; Support at ₹2.66 and Resistance at ₹2.94 Frame the Range for the Current Session - Continuation Pattern Picks - siam.in</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>Dish TV India Limited Announces Resignation of Abhishek Gupta from Corporate Head ? Information Technology, Effective August 31, 2026 - marketscreener.com</t>
-        </is>
-      </c>
+        <v>7.21</v>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 12:54:16 IST</t>
+          <t>2026-09-11 20:12:10 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -1670,60 +1386,48 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>INDUSTOWER.NS</t>
+          <t>KIRLOSIND.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Indus Towers Limited</t>
+          <t>Kirloskar Industries Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>372</v>
+        <v>3575</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>389.7999877929688</v>
+        <v>4055</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>372</v>
+        <v>3562.300048828125</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>389.1000061035156</v>
+        <v>3828.300048828125</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>372</v>
+        <v>3576.800048828125</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>389.1000061035156</v>
+        <v>3828.300048828125</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>13465319</v>
+        <v>639315</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>INDUSTOWER Outlook for the Week - Equitypandit</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>INDUSTOWER Outlook for the Week - Equitypandit</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>Indus (INDUSTOWER.NS) Financial Results: The Company Reports Its Latest Available Figures in the Current Update; Investor Response: Shares Fall 0.70% at the Close - Dividend Increase Stocks - siam.in</t>
-        </is>
-      </c>
+        <v>7.03</v>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr"/>
       <c r="P19" s="2" t="inlineStr"/>
       <c r="Q19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 12:54:16 IST</t>
+          <t>2026-09-11 20:12:10 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1731,64 +1435,48 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>EMPOWER.NS</t>
+          <t>TEXMOPIPES.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Empower India Limited</t>
+          <t>Texmo Pipes and Products Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>2.230000019073486</v>
+        <v>56.25</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>2.289999961853027</v>
+        <v>62.9900016784668</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>2.230000019073486</v>
+        <v>55.5</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>2.289999961853027</v>
+        <v>60.08000183105469</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>2.190000057220459</v>
+        <v>56.43999862670898</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>2.289999961853027</v>
+        <v>60.08000183105469</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>16023696</v>
+        <v>1131516</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>AI penny stock under ₹10 hits 5% upper circuit as IndiaAI Mission boosts infrastructure demand - Livemint</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>AI penny stock under ₹10 hits 5% upper circuit as IndiaAI Mission boosts infrastructure demand - Livemint</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>NET Power Closes Acquisition of 123 MW Power Generation Rights From EMPower; Shares Rise - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>A West Texas project plans 10 gas engines totaling 123 megawatts - Stock Titan</t>
-        </is>
-      </c>
+        <v>6.45</v>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr"/>
       <c r="Q20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 12:54:16 IST</t>
+          <t>2026-09-11 20:12:10 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1796,63 +1484,43 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>BALPHARMA.NS</t>
+          <t>RRECL.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Bal Pharma Limited</t>
+          <t>RDB Real Estate Constructions Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>105.5999984741211</v>
+        <v>126</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>114.9499969482422</v>
+        <v>138.6000061035156</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>104.129997253418</v>
+        <v>125.5800018310547</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>111</v>
+        <v>133.8000030517578</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>106.2099990844727</v>
+        <v>126</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>111</v>
+        <v>133.8000030517578</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>245004</v>
+        <v>883</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>4.51</v>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>Bal Pharma Gains 2.9% to ₹95.38; Resistance at ₹100.15 in Focus - Volatility Term Structure - siam.in</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>Bal Pharma 19.99% Surge: Key Chart Levels - Kalkine India</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>Bal Pharma 19.99% Surge: Key Chart Levels - Kalkine India</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>Bal Pharma Ltd. Upper Circuit Today: Price, Data and Peers - Univest</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>Bal Pharma Limited announced that it has received INR 21 million in funding - marketscreener.com</t>
-        </is>
-      </c>
+        <v>6.19</v>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr"/>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1878,13 +1546,13 @@
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="60" customWidth="1" min="13" max="13"/>
-    <col width="60" customWidth="1" min="14" max="14"/>
-    <col width="60" customWidth="1" min="15" max="15"/>
-    <col width="60" customWidth="1" min="16" max="16"/>
-    <col width="60" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1977,7 +1645,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 12:54:16 IST</t>
+          <t>2026-09-11 20:12:10 IST</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -1985,68 +1653,48 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>SUNSHINE.NS</t>
+          <t>SRGHFL.NS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Sunshine Pictures Limited</t>
+          <t>SRG Housing Finance Limited</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>512.4000244140625</v>
+        <v>156</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>524.9500122070312</v>
+        <v>156</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>407.7999877929688</v>
+        <v>156</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>407.7999877929688</v>
+        <v>156</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>509.7000122070312</v>
+        <v>195</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>407.7999877929688</v>
+        <v>156</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>3886396</v>
+        <v>11736</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>-19.99</v>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>SUNSHINE Share Price Today - SUNSHINE PICTURES LIMITED Stock Price Live NSE/BSE - Univest</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>Sunshine Capital corrects CFO name in board meeting disclosure - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>Sunshine Capital corrects CFO name in board meeting disclosure - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>Sunshine Pictures IPO Listing: Shares List at 9.97% Premium on NSE, Fall Short of Grey-Market Hopes - India Infoline</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>Sunshine Pictures shares list at 10% premium over IPO price - The Economic Times</t>
-        </is>
-      </c>
+        <v>-20</v>
+      </c>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 12:54:16 IST</t>
+          <t>2026-09-11 20:12:10 IST</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -2054,64 +1702,48 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COCHINSHIP.NS</t>
+          <t>SREEL.NS</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Cochin Shipyard Limited</t>
+          <t>Sreeleathers Limited</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1510</v>
+        <v>365</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>1510</v>
+        <v>365.7999877929688</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>1386</v>
+        <v>333.2699890136719</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>1390</v>
+        <v>333.2699890136719</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1520.400024414062</v>
+        <v>370.2999877929688</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1390</v>
+        <v>333.2699890136719</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>4247868</v>
+        <v>129115</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>-8.58</v>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>Cochin Shipyard Share Price Today, August 24, 2026: COCHINSHIP Closes at ₹1,514 on NSE - The Eastern Herald</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>Cochin Shipyard Ltd. Share Price News After Higher Closes - Univest</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>Cochin Shipyard Ltd. Share Price News After Higher Closes - Univest</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>Cochin Shipyard Ltd receives Notice from stock exchange for non-compliance - PSU Connect</t>
-        </is>
-      </c>
+        <v>-10</v>
+      </c>
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr"/>
+      <c r="P3" s="2" t="inlineStr"/>
       <c r="Q3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 12:54:16 IST</t>
+          <t>2026-09-11 20:12:10 IST</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -2119,68 +1751,48 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>KOTIC.NS</t>
+          <t>MEDICAPQ.NS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Kothari Industrial Corporation Limited</t>
+          <t>Medi Caps Limited</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>148.7599945068359</v>
+        <v>34.59000015258789</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>148.7599945068359</v>
+        <v>36.20000076293945</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>137.3000030517578</v>
+        <v>31.70000076293945</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>139.0899963378906</v>
+        <v>31.70000076293945</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>151.2100067138672</v>
+        <v>35.22000122070312</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>139.0899963378906</v>
+        <v>31.70000076293945</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>67618</v>
+        <v>64727</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>-8.02</v>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>Kothari Industrial share price zooms 11%! Stock down 74% in one year | What’s fuelling the rally? - Livemint</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>Kothari Industrial Share Price Today: Fundamental Check - Univest</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>Kothari Industrial Corporation (KOTIC.NS) Slips 1.23% to ₹134.79; Support at ₹128.05 in Focus - Bullish Sentiment - siam.in</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>Kothari Industrial Declines 2.23%: KOTIC.NS Navigates Key Support Zone - Volume Dry Up - siam.in</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>Kothari Industrial Corporation Share Price rises 10.14% - Univest</t>
-        </is>
-      </c>
+        <v>-9.99</v>
+      </c>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 12:54:16 IST</t>
+          <t>2026-09-11 20:12:10 IST</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -2188,68 +1800,48 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>KAVDEFENCE.NS</t>
+          <t>CSLFINANCE.NS</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Kavveri Defence &amp; Wireless Technologies Limited</t>
+          <t>CSL Finance Limited</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>72.41000366210938</v>
+        <v>234.5399932861328</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>73.80000305175781</v>
+        <v>234.5399932861328</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>68.19999694824219</v>
+        <v>217.1199951171875</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>69.56999969482422</v>
+        <v>220.9799957275391</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>74.76999664306641</v>
+        <v>241.0399932861328</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>69.56999969482422</v>
+        <v>220.9799957275391</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>999558</v>
+        <v>149274</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>-6.95</v>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>Kavveri Defence &amp; Wireless Technologies (KAVDEFENCE.NS): Defence Stock Moves Up 1.52% as Rangebound Trading Continues - Intraday Trade Ideas - siam.in</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>Kavveri Defence Board Clears Amalgamation of Samoro Telecoms Unit - TipRanks</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>KAVDEFENCE Share Price Rise: Price Action and Valuation - Univest</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>Kavveri Defence Board Clears Amalgamation of Samoro Telecoms Unit - TipRanks</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>Kavveri Defence &amp; Wireless Technologies Clears Amalgamation with Samoro Telecoms - TipRanks</t>
-        </is>
-      </c>
+        <v>-8.32</v>
+      </c>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 12:54:16 IST</t>
+          <t>2026-09-11 20:12:10 IST</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -2257,68 +1849,48 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>HEIDELBERG.NS</t>
+          <t>THAKDEV.NS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>HeidelbergCement India Limited</t>
+          <t>Thakkers Developers Limited</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>150.9499969482422</v>
+        <v>130.6499938964844</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>150.9499969482422</v>
+        <v>139.8000030517578</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>147.8000030517578</v>
+        <v>125.3499984741211</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>149.6199951171875</v>
+        <v>128.1499938964844</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>158.7899932861328</v>
+        <v>138.9900054931641</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>149.6199951171875</v>
+        <v>128.1499938964844</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>231222</v>
+        <v>660</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>-5.77</v>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>Heidelberg Materials stock heads into the open after a steady Xetra close - AD HOC NEWS</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>Heidelberg Materials stock heads into the open after a steady Xetra close - AD HOC NEWS</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>Heidelberg Cement India Ltd. Stock News - Value Research</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>Heidelberg Materials Tokenized Stock (xStock) price today, HEI.DEx to USD live price, marketcap and chart - CoinMarketCap</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>BlackRock lifts Heidelberg Materials voting stake to 5.22% as shares holding rises - Bitget</t>
-        </is>
-      </c>
+        <v>-7.8</v>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 12:54:16 IST</t>
+          <t>2026-09-11 20:12:10 IST</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -2326,68 +1898,48 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>GUJENERGY.NS</t>
+          <t>SSDL.NS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>GUJARAT ENERGY LIMITED</t>
+          <t>Saraswati Saree Depot Limited</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>247.9400024414062</v>
+        <v>71</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>249.2100067138672</v>
+        <v>72.69999694824219</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>240.3600006103516</v>
+        <v>61.36999893188477</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>240.9400024414062</v>
+        <v>62.59000015258789</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>254.8000030517578</v>
+        <v>67.83999633789062</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>240.9400024414062</v>
+        <v>62.59000015258789</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>1143830</v>
+        <v>557556</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-5.44</v>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>Gujarat Energy (NSE:GUJENERGY) Could Be A Buy For Its Upcoming Dividend - simplywall.st</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>Gujarat Energy Limited Appoints Dhirubhai Shah &amp; Co. LLP as Statutory Auditors - PSU Connect</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>Gujarat Gas Share Price Up 2.36%: Price, Valuation View - Univest</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>Gujarat Energy Limited announces Annual dividend, payable on October 28, 2026 - marketscreener.com</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>Gujarat Energy schedules 14th AGM for September 29, 2026 - scanx.trade</t>
-        </is>
-      </c>
+        <v>-7.74</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr"/>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 12:54:16 IST</t>
+          <t>2026-09-11 20:12:10 IST</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -2395,68 +1947,48 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>HEG.NS</t>
+          <t>ARVEE.NS</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>HEG Limited</t>
+          <t>Arvee Laboratories (India) Limited</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>238.1000061035156</v>
+        <v>195</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>243</v>
+        <v>195</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>237.1999969482422</v>
+        <v>176.5</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>237.1999969482422</v>
+        <v>180.6900024414062</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>249.6499938964844</v>
+        <v>195.25</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>237.1999969482422</v>
+        <v>180.6900024414062</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>857020</v>
+        <v>7308</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-4.99</v>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>Here’s why you should ignore the 65% plunge in HEG share price today post demerger - Moneycontrol.com</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>HEG Advanced Materials Debuts At Rs 260 As Demerger Creates Separate Graphite Play - BW Businessworld</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>Why are HEG Ltd shares showing a fall of 63% in Monday's trade? - Business Standard</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>Did HEG shares really crash 64% in one day? Here’s how the demerger math works - The Economic Times</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>HEG share price falls over 64% to ₹260: Don’t panic! Here’s what actually happened - Livemint</t>
-        </is>
-      </c>
+        <v>-7.46</v>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 12:54:16 IST</t>
+          <t>2026-09-11 20:12:10 IST</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -2464,68 +1996,48 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>SUPTANERY.NS</t>
+          <t>AARON.NS</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Super Tannery Limited</t>
+          <t>Aaron Industries Limited</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>10.27999973297119</v>
+        <v>137</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>10.27999973297119</v>
+        <v>137</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>10.27999973297119</v>
+        <v>121.1600036621094</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>10.27999973297119</v>
+        <v>126.9400024414062</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>10.81999969482422</v>
+        <v>136.9499969482422</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>10.27999973297119</v>
+        <v>126.9400024414062</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>10890</v>
+        <v>34703</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-4.99</v>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>Super Tannery Ltd. (SUPTANERY) Profile, Company FAQs &amp; Facts, Industry, Sector, Employee Strength - Stocktwits</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>Super Tannery Ltd. (SUPTANERY) Profile, Company FAQs &amp; Facts, Industry, Sector, Employee Strength - Stocktwits</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>Super Tannery Ltd. (SUPTANERY) Share Price Today, Quote, Latest Discussions, Interactive Chart and News - Stocktwits</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>Super Tannery Ltd. (SUPTANERY) Fundamental and Financial Data - Stocktwits</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>Super Tannery Ltd. (SUPTANERY) sentiment score, message volume, participation score and buzz level - Stocktwits</t>
-        </is>
-      </c>
+        <v>-7.31</v>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 12:54:16 IST</t>
+          <t>2026-09-11 20:12:10 IST</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -2533,68 +2045,48 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>AKI.NS</t>
+          <t>KAVDEFENCE.NS</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>AKI India Limited</t>
+          <t>Kavveri Defence &amp; Wireless Technologies Limited</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>6.150000095367432</v>
+        <v>72.41000366210938</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>6.150000095367432</v>
+        <v>73.80000305175781</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>6.139999866485596</v>
+        <v>68.19999694824219</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>6.139999866485596</v>
+        <v>69.33000183105469</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>6.460000038146973</v>
+        <v>74.76999664306641</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>6.139999866485596</v>
+        <v>69.33000183105469</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>84658</v>
+        <v>1319873</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>-4.95</v>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>AKI India Share: Bull Case vs Bear Case for 2026 - Univest</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>AKI India Share: Bull Case vs Bear Case for 2026 - Univest</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>Penny stock under 10 rupees: Upper circuit - Leather share jumps 74% in 4 sessions | Back-to-back surge for third day - TradingView</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>AKI India Limited (AKI.NS) Jumps 10.12% to ₹4.57: Key Levels to Watch - On Balance Volume - siam.in</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>Penny stock under 10 rupees: Upper circuit — Leather share jumps 74% in 4 sessions | Back-to-back surge for third day - Livemint</t>
-        </is>
-      </c>
+        <v>-7.28</v>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 12:54:16 IST</t>
+          <t>2026-09-11 20:12:10 IST</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -2602,64 +2094,48 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>RADIANTCMS.NS</t>
+          <t>KENNAMET.NS</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Radiant Cash Management Services Limited</t>
+          <t>Kennametal India Limited</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>37.20999908447266</v>
+        <v>5000</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>37.68999862670898</v>
+        <v>5000</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>35.2599983215332</v>
+        <v>4660</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>35.70999908447266</v>
+        <v>4682.39990234375</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>37.52999877929688</v>
+        <v>5027.89990234375</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>35.70999908447266</v>
+        <v>4682.39990234375</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>393532</v>
+        <v>70321</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>-4.85</v>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>We Wouldn't Be Too Quick To Buy Radiant Cash Management Services Limited (NSE:RADIANTCMS) Before It Goes Ex-Dividend - simplywall.st</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>We Wouldn't Be Too Quick To Buy Radiant Cash Management Services Limited (NSE:RADIANTCMS) Before It Goes Ex-Dividend - simplywall.st</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>Radiant (RADIANTCMS.NS) Market: Ends Higher by 1.40% at ₹34.66 for the Current Session; Levels: Support at ₹32.93 and Resistance at ₹36.39 Frame the Range in the Current Update - High Beta Stocks - siam.in</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>ONEGLOBAL Stock Price and Chart — NSE:ONEGLOBAL - TradingView</t>
-        </is>
-      </c>
+        <v>-6.87</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr"/>
+      <c r="P11" s="2" t="inlineStr"/>
       <c r="Q11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 12:54:16 IST</t>
+          <t>2026-09-11 20:12:10 IST</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -2667,68 +2143,48 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>JINDWORLD.NS</t>
+          <t>SUVIDHAA.NS</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Jindal Worldwide Limited</t>
+          <t>Suvidhaa Infoserve Limited</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>54.70000076293945</v>
+        <v>2.470000028610229</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>55.5</v>
+        <v>2.470000028610229</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>52.75</v>
+        <v>2.190000057220459</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>53.11000061035156</v>
+        <v>2.25</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>55.63999938964844</v>
+        <v>2.410000085830688</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>53.11000061035156</v>
+        <v>2.25</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>8481757</v>
+        <v>184883</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>-4.55</v>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>Jindal Worldwide (JINDWORLD.NS) Edges Higher at ₹38.31; Key Support and Resistance in Focus - Dividend Growth Stocks - siam.in</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>Most Active Equities on September 4, 2026 at 4:00 PM - HDFC Sky</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>Jindal (JINDWORLD.NS) Quarterly Results: The Company Publishes Its Latest Results; Session Move: The Stock Records a 1.05% Increase in Latest Trading - Guidance Revision Trend - siam.in</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>Jindal Worldwide (NSE: JINDWORLD) New High Analysis - Kalkine India</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>Jindal Worldwide stock hits upper circuit - What's behind the share price jump? - Livemint</t>
-        </is>
-      </c>
+        <v>-6.64</v>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 12:54:16 IST</t>
+          <t>2026-09-11 20:12:10 IST</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -2736,64 +2192,48 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>AVROIND.NS</t>
+          <t>GODREJPROP.NS</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>AVRO INDIA LIMITED</t>
+          <t>Godrej Properties Limited</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>8.399999618530273</v>
+        <v>1855</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>8.430000305175781</v>
+        <v>1855</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>7.900000095367432</v>
+        <v>1719</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>7.96999979019165</v>
+        <v>1748</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>8.340000152587891</v>
+        <v>1872</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>7.96999979019165</v>
+        <v>1748</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>593350</v>
+        <v>2683753</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-4.44</v>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>Avro India Ltd. Share Price Today: Price Rise Breakdown - Univest</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>Avro India sets Sep 23 record date for 30th AGM - scanx.trade</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>Avro India Ltd. Share Price Today: 9.6% Gain, Key Metrics - Univest</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>Avro India sets Sep 23 record date for 30th AGM - scanx.trade</t>
-        </is>
-      </c>
+        <v>-6.62</v>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr"/>
+      <c r="P13" s="2" t="inlineStr"/>
       <c r="Q13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 12:54:16 IST</t>
+          <t>2026-09-11 20:12:10 IST</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -2801,68 +2241,48 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>RML.NS</t>
+          <t>PODDARMENT.NS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Rane (Madras) Limited</t>
+          <t>Poddar Pigments Limited</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1415.800048828125</v>
+        <v>295.1000061035156</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1415.900024414062</v>
+        <v>298.9500122070312</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>1340.099975585938</v>
+        <v>275.0499877929688</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>1346.599975585938</v>
+        <v>279.8500061035156</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1408.900024414062</v>
+        <v>299.3999938964844</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1346.599975585938</v>
+        <v>279.8500061035156</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>46259</v>
+        <v>12804</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-4.42</v>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>RML puts on strong Nasdaq debut - The Australian</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>RML puts on strong Nasdaq debut - The Australian</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>symbol__ Stock Quote Price and Forecast - CNN</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>RML - Finviz</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>Resolution Minerals Ltd (ASX:RML) Nasdaq Trading to Commence Today - ABN Newswire</t>
-        </is>
-      </c>
+        <v>-6.53</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 12:54:16 IST</t>
+          <t>2026-09-11 20:12:10 IST</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2870,68 +2290,48 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>ABREL.NS</t>
+          <t>AVROIND.NS</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Aditya Birla Real Estate Limited</t>
+          <t>AVRO INDIA LIMITED</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1315.099975585938</v>
+        <v>8.399999618530273</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>1315.199951171875</v>
+        <v>8.430000305175781</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>1276</v>
+        <v>7.71999979019165</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>1284.199951171875</v>
+        <v>7.809999942779541</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1337.400024414062</v>
+        <v>8.340000152587891</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1284.199951171875</v>
+        <v>7.809999942779541</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>175970</v>
+        <v>890191</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-3.98</v>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>Rainbows and Unicorns: Aditya Birla Real Estate Limited (NSE:ABREL) Analysts Just Became A Lot More Optimistic - simplywall.st</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>NIFTY Realty soars 3%: Prestige Estates, Anant Raj, ABREL among realty stocks in focus on Sept 3 - Upstox</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>NIFTY Realty soars 3%: Prestige Estates, Anant Raj, ABREL among realty stocks in focus on Sept 3 - Upstox</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>Aditya Birla Real Estate Share Price Update with Valuation - Univest</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>Q1 results: ABREL, Godrej, JSW Cement, FirstCry, and 693 more on Aug 13 - Business Standard</t>
-        </is>
-      </c>
+        <v>-6.35</v>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr"/>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 12:54:16 IST</t>
+          <t>2026-09-11 20:12:10 IST</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -2939,68 +2339,48 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>GATECH.NS</t>
+          <t>CREATIVEYE.NS</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>GACM Technologies Limited</t>
+          <t>Creative Eye Limited</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.7300000190734863</v>
+        <v>5.989999771118164</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>0.7300000190734863</v>
+        <v>5.989999771118164</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.7300000190734863</v>
+        <v>5.260000228881836</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>0.7300000190734863</v>
+        <v>5.71999979019165</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0.7599999904632568</v>
+        <v>6.070000171661377</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.7300000190734863</v>
+        <v>5.71999979019165</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>3477277</v>
+        <v>81217</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-3.95</v>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>₹0.75 MultiBagger Penny Stock, +56% in 1 Month — Why Institutions Are Paying 25% Premium for GACM TECHNOLOGIES Shares? - theprint.in</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>GACM Technologies Slips 4.6% to ₹0.83; Key Support at ₹0.79 in Focus - MA Crossover - siam.in</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>GACM Technologies: FII holding jumps to 29%; penny stock in focus - Business Today</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>GACM Technologies Hits Fresh 52-Week High as GATECH Surges 110% in One Month; 31% FII Holding and 250 Million AI Mandate Add to Investor Focus - indiagazette.com</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>GACM Technologies Slips 4.6% to ₹0.83; Key Support at ₹0.79 in Focus - MA Crossover - siam.in</t>
-        </is>
-      </c>
+        <v>-5.77</v>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 12:54:16 IST</t>
+          <t>2026-09-11 20:12:10 IST</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -3008,68 +2388,48 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>VISHWARAJ.NS</t>
+          <t>HEIDELBERG.NS</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Vishwaraj Sugar Industries Limited</t>
+          <t>HeidelbergCement India Limited</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>5.519999980926514</v>
+        <v>150.9499969482422</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>5.590000152587891</v>
+        <v>150.9499969482422</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>5.329999923706055</v>
+        <v>147.8000030517578</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>5.400000095367432</v>
+        <v>149.8000030517578</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>5.619999885559082</v>
+        <v>158.7899932861328</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>5.400000095367432</v>
+        <v>149.8000030517578</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>702177</v>
+        <v>313598</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-3.91</v>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>VISHWARAJ Share Price rise: price action and market cap - Univest</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>Vishwaraj Sugar Industries Publishes Notices for 31st AGM - TipRanks</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>Vishwaraj Sugar schedules 31st AGM for September 28, 2026 - scanx.trade</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>Vishwaraj Sugar Industries reports standalone net loss of Rs 25.84 crore in the June 2026 quarter - Business Standard</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>Vishwaraj Sugar Q1 FY27 Results: Revenue Falls 20% to Rs 107 Crore, Net Loss Deepens to Rs 25 Crore - Univest</t>
-        </is>
-      </c>
+        <v>-5.66</v>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr"/>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 12:54:16 IST</t>
+          <t>2026-09-11 20:12:10 IST</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -3077,68 +2437,48 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>STALLION.NS</t>
+          <t>REGENCERAM.NS</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Stallion India Fluorochemicals Limited</t>
+          <t>Regency Ceramics Limited</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>229.6999969482422</v>
+        <v>34.65999984741211</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>229.6999969482422</v>
+        <v>37.5</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>223</v>
+        <v>33.20000076293945</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>225.1000061035156</v>
+        <v>34.09999847412109</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>234.2599945068359</v>
+        <v>36.04999923706055</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>225.1000061035156</v>
+        <v>34.09999847412109</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>278348</v>
+        <v>4604</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-3.91</v>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>Stallion India Fluorochemicals' Rajasthan Plants to Benefit from RIPS 2024 Subsidies - scanx.trade</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>Megan Thee Stallion Shares What She’s Learned About Love and Life Since Klay Thompson Breakup - The Root</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>Stallion India Fluorochemicals Ltd Locks at Upper Circuit With 5% Gain — Buyers Queue, Sellers Absent - MarketsMojo</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>Stallion (STALLION.NS) Results Check: The Latest Financial Metrics Are Now Available in the Latest Reading; Stock Move: The Stock Records a 1.36% Decrease in Latest Trading - EBITDA Margin Trends - siam.in</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>Retail investors bet big on these 12 smallcap stocks that rallied up to 150%; 3 turned multibaggers - The Economic Times</t>
-        </is>
-      </c>
+        <v>-5.41</v>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 12:54:16 IST</t>
+          <t>2026-09-11 20:12:10 IST</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -3146,68 +2486,48 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>RATNAVEER.NS</t>
+          <t>SKIPPER.NS</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Ratnaveer Precision Engineering Limited</t>
+          <t>Skipper Limited</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>310</v>
+        <v>581</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>310.3999938964844</v>
+        <v>581</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>295.6499938964844</v>
+        <v>541.3499755859375</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>299</v>
+        <v>551.5499877929688</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>310.6000061035156</v>
+        <v>583</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>299</v>
+        <v>551.5499877929688</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>1600570</v>
+        <v>2162749</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-3.73</v>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>Ratnaveer Precision Engineering Approves Allotment of Equity Shares via Rights Issue - EquityBulls</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>Ratnaveer Precision Engineering Approves Allotment of Equity Shares via Rights Issue - EquityBulls</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>Press Release Distribution India - Business Wire India</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>Ratnaveer Precision approves ₹329.99 crore rights issue allotment - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>Ratnaveer Precision Engineering Limited Rights 2026-09.09.26 for Shares Cash Flow – NSE:RATNA_RE - TradingView</t>
-        </is>
-      </c>
+        <v>-5.39</v>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr"/>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 12:54:16 IST</t>
+          <t>2026-09-11 20:12:10 IST</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -3215,64 +2535,48 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>GSFC.NS</t>
+          <t>SECMARK.NS</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Gujarat State Fertilizers &amp; Chemicals Limited</t>
+          <t>SecMark Consultancy Limited</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>154.9100036621094</v>
+        <v>148</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>154.9100036621094</v>
+        <v>148</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>152.8500061035156</v>
+        <v>138</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>154.5099945068359</v>
+        <v>141.3099975585938</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>160.3800048828125</v>
+        <v>149.1600036621094</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>154.5099945068359</v>
+        <v>141.3099975585938</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>932846</v>
+        <v>2320</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>-3.66</v>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>GSFC to transfer unclaimed dividend to IEPF by Aug 31 - scanx.trade</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>GSFC Revises Dividend Record Date to 12 September 2026 - TipRanks</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>GSFC Q1 FY27 Results: Revenue Rs 3,583 Cr, PAT Rs 155 Cr and Key Highlights - Univest</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>GSFC Revises Dividend Record Date to 12 September 2026 - TipRanks</t>
-        </is>
-      </c>
+        <v>-5.26</v>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr"/>
       <c r="Q20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11 12:54:16 IST</t>
+          <t>2026-09-11 20:12:10 IST</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -3280,63 +2584,43 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>THOMASCOTT.NS</t>
+          <t>INDOTHAI.NS</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Thomas Scott (India) Limited</t>
+          <t>Indo Thai Securities Limited</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>241</v>
+        <v>43.40000152587891</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>244.1999969482422</v>
+        <v>45.4900016784668</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>233.8000030517578</v>
+        <v>41.16999816894531</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>235.1000061035156</v>
+        <v>41.16999816894531</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>243.8999938964844</v>
+        <v>43.43000030517578</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>235.1000061035156</v>
+        <v>41.16999816894531</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>51557</v>
+        <v>20199028</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>-3.61</v>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>Thomas Scott (India) Ltd. (THOMASCOTT) Share Price Falls 8.36% Today; Textile Micro Cap Among Top Decliners - Univest</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>Thomas Scott அதிரடி லாபம்: ப்ராஃபிட் **51%** உயர்வு, **₹300 கோடி** பரிவர்த்தனைகளுக்கு அனுமதி! - Whalesbook</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>KDGREEN Stock Price and Chart — NSE:KDGREEN - TradingView</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>Bang Overseas dispatches 34th AGM notice; e-voting starts Sept 25 - scanx.trade</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>Thomas Scott அதிரடி லாபம்: ப்ராஃபிட் **51%** உயர்வு, **₹300 கோடி** பரிவர்த்தனைகளுக்கு அனுமதி! - Whalesbook</t>
-        </is>
-      </c>
+        <v>-5.2</v>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr"/>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
